--- a/AI_Factory_Model.xlsx
+++ b/AI_Factory_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="385">
   <si>
     <t xml:space="preserve">AI Factory Dashboard — 32x Vera Rubin NVL72, Abu Dhabi, UAE</t>
   </si>
@@ -335,6 +335,30 @@
     <t xml:space="preserve">S45 direct-to-chip loop</t>
   </si>
   <si>
+    <t xml:space="preserve">Liquid_Return_Temp_FWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility water return — sets the loop delta-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolant_Specific_Heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kJ/kg·K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: PG25 water/glycol at ~50°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolant_Density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: PG25 mixture density</t>
+  </si>
+  <si>
     <t xml:space="preserve">Target_Annualized_PUE</t>
   </si>
   <si>
@@ -680,7 +704,7 @@
     <t xml:space="preserve">S45 Loop Return Temperature</t>
   </si>
   <si>
-    <t xml:space="preserve">Facility Water Return (FWR) — assumption</t>
+    <t xml:space="preserve">Facility Water Return (FWR)</t>
   </si>
   <si>
     <t xml:space="preserve">S45 Loop Delta T</t>
@@ -689,19 +713,19 @@
     <t xml:space="preserve">Hydraulic temperature split</t>
   </si>
   <si>
-    <t xml:space="preserve">S45 Liquid Flow Rate per Rack</t>
+    <t xml:space="preserve">S45 Liquid Flow Rate per VR Rack</t>
   </si>
   <si>
     <t xml:space="preserve">LPM</t>
   </si>
   <si>
-    <t xml:space="preserve">PG25 water/glycol mixture — vendor spec</t>
+    <t xml:space="preserve">Physics: Q/(rho*Cp*dT)*60 — flow required to absorb one VR rack</t>
   </si>
   <si>
     <t xml:space="preserve">Total S45 Cluster Flow Rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Flow per rack x liquid-cooled rack count</t>
+    <t xml:space="preserve">Physics: liquid-cooled load/(rho*Cp*dT)*60</t>
   </si>
   <si>
     <t xml:space="preserve">Peak Ambient Dry-Bulb (N=20yr)</t>
@@ -1164,7 +1188,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
@@ -1176,9 +1200,10 @@
     <numFmt numFmtId="172" formatCode="\$#,##0.000"/>
     <numFmt numFmtId="173" formatCode="@"/>
     <numFmt numFmtId="174" formatCode="#,##0.0"/>
-    <numFmt numFmtId="175" formatCode="0.00%"/>
-    <numFmt numFmtId="176" formatCode="\$#,##0.0000"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="0.00"/>
+    <numFmt numFmtId="176" formatCode="0.00%"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.0000"/>
+    <numFmt numFmtId="178" formatCode="0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1361,7 +1386,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1474,6 +1499,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="172" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1518,7 +1547,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1574,7 +1603,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2231,7 +2260,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2613,10 +2642,12 @@
       <c r="B25" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D25" s="6"/>
+      <c r="C25" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="E25" s="6" t="s">
         <v>103</v>
       </c>
@@ -2628,14 +2659,14 @@
       <c r="B26" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="26" t="n">
-        <v>0.85</v>
+      <c r="C26" s="27" t="n">
+        <v>3.85</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2643,16 +2674,16 @@
         <v>70</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="27" t="n">
-        <v>0.995</v>
+        <v>1.03</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>7</v>
+        <v>108</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2660,16 +2691,14 @@
         <v>70</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>109</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2677,30 +2706,30 @@
         <v>70</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" s="26" t="n">
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C30" s="28" t="n">
-        <v>0.06</v>
+        <v>0.995</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -2708,13 +2737,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="26" t="n">
-        <v>0.02</v>
+      <c r="C31" s="24" t="n">
+        <v>1800</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>117</v>
@@ -2725,16 +2754,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="29" t="n">
-        <v>139500000</v>
+      <c r="C32" s="26" t="n">
+        <v>0.3</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -2742,203 +2771,203 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="26" t="n">
-        <v>0.1</v>
+        <v>122</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>0.06</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C34" s="26" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="26" t="n">
-        <v>0.065</v>
+        <v>127</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>139500000</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>5</v>
+        <v>129</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>0.1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>5</v>
+        <v>131</v>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>0.8</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <v>5</v>
+        <v>133</v>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>0.065</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" s="26" t="n">
-        <v>0.09</v>
+        <v>135</v>
+      </c>
+      <c r="C39" s="24" t="n">
+        <v>5</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="26" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E40" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="26" t="n">
-        <v>0.15</v>
+        <v>140</v>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>5</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="29" t="n">
-        <v>10877000</v>
+        <v>142</v>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>0.09</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" s="26" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="29" t="n">
-        <v>58800000</v>
+      <c r="C44" s="26" t="n">
+        <v>0.15</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>147</v>
@@ -2946,102 +2975,153 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C45" s="29" t="n">
-        <v>25200000</v>
+      <c r="C45" s="30" t="n">
+        <v>10877000</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C46" s="26" t="n">
-        <v>0.9</v>
+        <v>0.03</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C47" s="26" t="n">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>58800000</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="26" t="n">
-        <v>0.15</v>
+        <v>156</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>25200000</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C49" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>160</v>
+      <c r="D52" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3072,32 +3152,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3105,277 +3185,277 @@
         <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="30" t="n">
+        <v>177</v>
+      </c>
+      <c r="C5" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="32" t="n">
         <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="C6" s="31" t="n">
         <v>0.28</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="32" t="n">
         <v>49.5</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="32" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="C7" s="31" t="n">
         <v>0.28</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="32" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="30" t="n">
+        <v>184</v>
+      </c>
+      <c r="C8" s="31" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <v>36.5</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="32" t="n">
         <v>29.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="30" t="n">
+        <v>184</v>
+      </c>
+      <c r="C9" s="31" t="n">
         <v>0.28</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="32" t="n">
         <v>39.5</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="32" t="n">
         <v>30</v>
       </c>
       <c r="F9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="30" t="n">
+        <v>188</v>
+      </c>
+      <c r="C10" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="32" t="n">
         <v>48.5</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="32" t="n">
         <v>26.5</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="C11" s="31" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="32" t="n">
         <v>43.5</v>
       </c>
-      <c r="E11" s="31" t="n">
+      <c r="E11" s="32" t="n">
         <v>27.5</v>
       </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="30" t="n">
+        <v>192</v>
+      </c>
+      <c r="C12" s="31" t="n">
         <v>0.19</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="32" t="n">
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="30" t="n">
+        <v>195</v>
+      </c>
+      <c r="C13" s="31" t="n">
         <v>0.16</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="32" t="n">
         <v>38.5</v>
       </c>
-      <c r="E13" s="31" t="n">
+      <c r="E13" s="32" t="n">
         <v>27</v>
       </c>
       <c r="F13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="30" t="n">
+        <v>195</v>
+      </c>
+      <c r="C14" s="31" t="n">
         <v>0.16</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="32" t="n">
         <v>37.5</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="32" t="n">
         <v>23</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C15" s="30" t="n">
+        <v>195</v>
+      </c>
+      <c r="C15" s="31" t="n">
         <v>0.16</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="32" t="n">
         <v>22</v>
       </c>
       <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" s="30" t="n">
+        <v>195</v>
+      </c>
+      <c r="C16" s="31" t="n">
         <v>0.16</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="32" t="n">
         <v>28.5</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="32" t="n">
         <v>19.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="30" t="n">
+        <v>201</v>
+      </c>
+      <c r="C17" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="32" t="n">
         <v>21</v>
       </c>
       <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="C18" s="31" t="n">
         <v>0.21</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="32" t="n">
         <v>37.5</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="32" t="n">
         <v>27.5</v>
       </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="C19" s="31" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="32" t="n">
         <v>24.5</v>
       </c>
       <c r="F19" s="6"/>
@@ -3407,17 +3487,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -3426,104 +3506,104 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="32" t="n">
+        <v>207</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$13</f>
         <v>7264</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="32" t="n">
+        <v>210</v>
+      </c>
+      <c r="B6" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$15*'Control Panel &amp; Inputs'!$C$16</f>
         <v>600</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B7" s="32" t="n">
+        <v>212</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$19</f>
         <v>400</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="32" t="n">
+        <v>214</v>
+      </c>
+      <c r="B8" s="33" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>8264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="32" t="n">
+        <v>216</v>
+      </c>
+      <c r="B9" s="33" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",B7,0)</f>
         <v>7264</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B10" s="32" t="n">
+        <v>218</v>
+      </c>
+      <c r="B10" s="33" t="n">
         <f aca="false">B8-B9</f>
         <v>1000</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="33" t="n">
+        <v>220</v>
+      </c>
+      <c r="B11" s="34" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",'Control Panel &amp; Inputs'!$C$12,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",'Control Panel &amp; Inputs'!$C$15,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",'Control Panel &amp; Inputs'!$C$18,0)</f>
         <v>32</v>
       </c>
@@ -3531,14 +3611,14 @@
         <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" s="32" t="n">
+        <v>222</v>
+      </c>
+      <c r="B12" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$24</f>
         <v>45</v>
       </c>
@@ -3546,28 +3626,29 @@
         <v>60</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>224</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$25</f>
         <v>55</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B14" s="32" t="n">
+        <v>226</v>
+      </c>
+      <c r="B14" s="33" t="n">
         <f aca="false">B13-B12</f>
         <v>10</v>
       </c>
@@ -3575,43 +3656,44 @@
         <v>60</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <v>195</v>
+        <v>228</v>
+      </c>
+      <c r="B15" s="33" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
+        <v>343.462362879839</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B16" s="32" t="n">
-        <f aca="false">B15*B11</f>
-        <v>6240</v>
+        <v>231</v>
+      </c>
+      <c r="B16" s="33" t="n">
+        <f aca="false">B9/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
+        <v>10990.7956121548</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="32" t="n">
+        <v>233</v>
+      </c>
+      <c r="B17" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
         <v>50</v>
       </c>
@@ -3619,14 +3701,14 @@
         <v>60</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="32" t="n">
+        <v>235</v>
+      </c>
+      <c r="B18" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
         <v>30</v>
       </c>
@@ -3634,100 +3716,100 @@
         <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="32" t="n">
+        <v>237</v>
+      </c>
+      <c r="B19" s="33" t="n">
         <f aca="false">B13-B17</f>
         <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B20" s="32" t="n">
+        <v>240</v>
+      </c>
+      <c r="B20" s="33" t="n">
         <f aca="false">B9*'Control Panel &amp; Inputs'!$C$22</f>
         <v>363.2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="32" t="n">
+        <v>242</v>
+      </c>
+      <c r="B21" s="33" t="n">
         <f aca="false">B10*'Control Panel &amp; Inputs'!$C$23</f>
         <v>280</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B22" s="32" t="n">
+        <v>244</v>
+      </c>
+      <c r="B22" s="33" t="n">
         <f aca="false">B20+B21</f>
         <v>643.2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B23" s="34" t="n">
+        <v>246</v>
+      </c>
+      <c r="B23" s="35" t="n">
         <f aca="false">B22/B8</f>
         <v>0.0778315585672798</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B24" s="34" t="n">
+        <v>248</v>
+      </c>
+      <c r="B24" s="35" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
         <v>0.26</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B25" s="35" t="n">
+        <v>250</v>
+      </c>
+      <c r="B25" s="36" t="n">
         <f aca="false">(B24-B23)/B24</f>
         <v>0.700647851664309</v>
       </c>
@@ -3735,42 +3817,42 @@
         <v>7</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B26" s="32" t="n">
-        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$26*'Control Panel &amp; Inputs'!$C$27</f>
+        <v>252</v>
+      </c>
+      <c r="B26" s="33" t="n">
+        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30</f>
         <v>6989.278</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B27" s="34" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$25</f>
+        <v>254</v>
+      </c>
+      <c r="B27" s="35" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$28</f>
         <v>1.08</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="33" t="n">
+      <c r="B28" s="34" t="n">
         <f aca="false">B26*8760*B27/1000</f>
         <v>66124.1613024</v>
       </c>
@@ -3778,14 +3860,14 @@
         <v>25</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="33" t="n">
+      <c r="B29" s="34" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$11</f>
         <v>9918.62419536</v>
       </c>
@@ -3793,14 +3875,14 @@
         <v>29</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="33" t="n">
+      <c r="B30" s="34" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$10</f>
         <v>25788.422907936</v>
       </c>
@@ -3808,7 +3890,7 @@
         <v>27</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3836,842 +3918,842 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$46</f>
+      <c r="C5" s="38" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$49</f>
         <v>0.9</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="38" t="n">
+      <c r="A6" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$44*POWER(1+'Control Panel &amp; Inputs'!$C$47,0)*C5</f>
+      <c r="C6" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,0)*C5</f>
         <v>52920000</v>
       </c>
-      <c r="D6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$44*POWER(1+'Control Panel &amp; Inputs'!$C$47,1)*D5</f>
+      <c r="D6" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,1)*D5</f>
         <v>58800000</v>
       </c>
-      <c r="E6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$44*POWER(1+'Control Panel &amp; Inputs'!$C$47,2)*E5</f>
+      <c r="E6" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,2)*E5</f>
         <v>58800000</v>
       </c>
-      <c r="F6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$44*POWER(1+'Control Panel &amp; Inputs'!$C$47,3)*F5</f>
+      <c r="F6" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,3)*F5</f>
         <v>58800000</v>
       </c>
-      <c r="G6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$44*POWER(1+'Control Panel &amp; Inputs'!$C$47,4)*G5</f>
+      <c r="G6" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,4)*G5</f>
         <v>58800000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="B7" s="38" t="n">
+      <c r="A7" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER((1+'Control Panel &amp; Inputs'!$C$49)*(1-'Control Panel &amp; Inputs'!$C$48),0)*C5</f>
+      <c r="C7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),0)*C5</f>
         <v>22680000</v>
       </c>
-      <c r="D7" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER((1+'Control Panel &amp; Inputs'!$C$49)*(1-'Control Panel &amp; Inputs'!$C$48),1)*D5</f>
+      <c r="D7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),1)*D5</f>
         <v>26775000</v>
       </c>
-      <c r="E7" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER((1+'Control Panel &amp; Inputs'!$C$49)*(1-'Control Panel &amp; Inputs'!$C$48),2)*E5</f>
+      <c r="E7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),2)*E5</f>
         <v>28448437.5</v>
       </c>
-      <c r="F7" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER((1+'Control Panel &amp; Inputs'!$C$49)*(1-'Control Panel &amp; Inputs'!$C$48),3)*F5</f>
+      <c r="F7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),3)*F5</f>
         <v>30226464.84375</v>
       </c>
-      <c r="G7" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER((1+'Control Panel &amp; Inputs'!$C$49)*(1-'Control Panel &amp; Inputs'!$C$48),4)*G5</f>
+      <c r="G7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),4)*G5</f>
         <v>32115618.8964844</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="38" t="n">
+      <c r="A8" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="39" t="n">
         <f aca="false">C6+C7</f>
         <v>75600000</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="39" t="n">
         <f aca="false">D6+D7</f>
         <v>85575000</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="39" t="n">
         <f aca="false">E6+E7</f>
         <v>87248437.5</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="39" t="n">
         <f aca="false">F6+F7</f>
         <v>89026464.84375</v>
       </c>
-      <c r="G8" s="38" t="n">
+      <c r="G8" s="39" t="n">
         <f aca="false">G6+G7</f>
         <v>90915618.8964844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="B9" s="39" t="n">
+      <c r="A9" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="C9" s="40" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="D9" s="40" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>0.0612</v>
       </c>
-      <c r="E9" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="E9" s="40" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>0.062424</v>
       </c>
-      <c r="F9" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="F9" s="40" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>0.06367248</v>
       </c>
-      <c r="G9" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="G9" s="40" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>0.0649459296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="B10" s="40" t="n">
+      <c r="A10" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="41" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="41" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="41" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="41" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="G10" s="40" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="38" t="n">
+      <c r="A11" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="38" t="n">
+      <c r="C11" s="39" t="n">
         <f aca="false">C10*C9</f>
         <v>3967449.678144</v>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="39" t="n">
         <f aca="false">D10*D9</f>
         <v>4046798.67170688</v>
       </c>
-      <c r="E11" s="38" t="n">
+      <c r="E11" s="39" t="n">
         <f aca="false">E10*E9</f>
         <v>4127734.64514102</v>
       </c>
-      <c r="F11" s="38" t="n">
+      <c r="F11" s="39" t="n">
         <f aca="false">F10*F9</f>
         <v>4210289.33804384</v>
       </c>
-      <c r="G11" s="38" t="n">
+      <c r="G11" s="39" t="n">
         <f aca="false">G10*G9</f>
         <v>4294495.12480471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="38" t="n">
+      <c r="A12" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="B12" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$42*POWER(1+'Control Panel &amp; Inputs'!$C$43,0)</f>
+      <c r="C12" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>10877000</v>
       </c>
-      <c r="D12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$42*POWER(1+'Control Panel &amp; Inputs'!$C$43,1)</f>
+      <c r="D12" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,1)</f>
         <v>11203310</v>
       </c>
-      <c r="E12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$42*POWER(1+'Control Panel &amp; Inputs'!$C$43,2)</f>
+      <c r="E12" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,2)</f>
         <v>11539409.3</v>
       </c>
-      <c r="F12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$42*POWER(1+'Control Panel &amp; Inputs'!$C$43,3)</f>
+      <c r="F12" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,3)</f>
         <v>11885591.579</v>
       </c>
-      <c r="G12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$42*POWER(1+'Control Panel &amp; Inputs'!$C$43,4)</f>
+      <c r="G12" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,4)</f>
         <v>12242159.32637</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="38" t="n">
+      <c r="A13" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C13" s="39" t="n">
         <f aca="false">C11+C12</f>
         <v>14844449.678144</v>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="39" t="n">
         <f aca="false">D11+D12</f>
         <v>15250108.6717069</v>
       </c>
-      <c r="E13" s="38" t="n">
+      <c r="E13" s="39" t="n">
         <f aca="false">E11+E12</f>
         <v>15667143.945141</v>
       </c>
-      <c r="F13" s="38" t="n">
+      <c r="F13" s="39" t="n">
         <f aca="false">F11+F12</f>
         <v>16095880.9170438</v>
       </c>
-      <c r="G13" s="38" t="n">
+      <c r="G13" s="39" t="n">
         <f aca="false">G11+G12</f>
         <v>16536654.4511747</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="38" t="n">
+      <c r="A14" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C14" s="39" t="n">
         <f aca="false">C8-C13</f>
         <v>60755550.321856</v>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="39" t="n">
         <f aca="false">D8-D13</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="E14" s="38" t="n">
+      <c r="E14" s="39" t="n">
         <f aca="false">E8-E13</f>
         <v>71581293.554859</v>
       </c>
-      <c r="F14" s="38" t="n">
+      <c r="F14" s="39" t="n">
         <f aca="false">F8-F13</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="G14" s="38" t="n">
+      <c r="G14" s="39" t="n">
         <f aca="false">G8-G13</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="B15" s="37" t="n">
+      <c r="A15" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="B15" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="38" t="n">
         <f aca="false">C14/C8</f>
         <v>0.803644845527196</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="38" t="n">
         <f aca="false">D14/D8</f>
         <v>0.821792478273948</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="38" t="n">
         <f aca="false">E14/E8</f>
         <v>0.820430664501688</v>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="38" t="n">
         <f aca="false">F14/F8</f>
         <v>0.819201167368673</v>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G15" s="38" t="n">
         <f aca="false">G14/G8</f>
         <v>0.818109862178872</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="B16" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32</f>
+      <c r="A16" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B16" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35</f>
         <v>139500000</v>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="38" t="n">
+      <c r="D16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="38" t="n">
+      <c r="E16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="38" t="n">
+      <c r="F16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="38" t="n">
+      <c r="G16" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="B17" s="38" t="n">
-        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$34</f>
+      <c r="A17" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" s="39" t="n">
+        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$37</f>
         <v>111600000</v>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="38" t="n">
+      <c r="F17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="38" t="n">
+      <c r="G17" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B18" s="38" t="n">
+      <c r="A18" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="B18" s="39" t="n">
         <f aca="false">B16-B17</f>
         <v>27900000</v>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="38" t="n">
+      <c r="E18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="38" t="n">
+      <c r="F18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="38" t="n">
+      <c r="G18" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="38" t="n">
+      <c r="A19" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="39" t="n">
         <f aca="false">B17</f>
         <v>111600000</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="39" t="n">
         <f aca="false">C23</f>
         <v>91999185.6041205</v>
       </c>
-      <c r="E19" s="38" t="n">
+      <c r="E19" s="39" t="n">
         <f aca="false">D23</f>
         <v>71124318.2725088</v>
       </c>
-      <c r="F19" s="38" t="n">
+      <c r="F19" s="39" t="n">
         <f aca="false">E23</f>
         <v>48892584.5643424</v>
       </c>
-      <c r="G19" s="38" t="n">
+      <c r="G19" s="39" t="n">
         <f aca="false">F23</f>
         <v>25215788.1651451</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="B20" s="38" t="n">
+      <c r="A20" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="38" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,B17),0)</f>
+      <c r="C20" s="39" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="D20" s="38" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,B17),0)</f>
+      <c r="D20" s="39" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="E20" s="38" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,B17),0)</f>
+      <c r="E20" s="39" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="F20" s="38" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,B17),0)</f>
+      <c r="F20" s="39" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="G20" s="38" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,B17),0)</f>
+      <c r="G20" s="39" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>26854814.3958795</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="B21" s="38" t="n">
+      <c r="A21" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="38" t="n">
-        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="C21" s="39" t="n">
+        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>7254000</v>
       </c>
-      <c r="D21" s="38" t="n">
-        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="D21" s="39" t="n">
+        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>5979947.06426783</v>
       </c>
-      <c r="E21" s="38" t="n">
-        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="E21" s="39" t="n">
+        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>4623080.68771307</v>
       </c>
-      <c r="F21" s="38" t="n">
-        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="F21" s="39" t="n">
+        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>3178017.99668225</v>
       </c>
-      <c r="G21" s="38" t="n">
-        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="G21" s="39" t="n">
+        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>1639026.23073443</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="B22" s="38" t="n">
+      <c r="A22" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C22" s="39" t="n">
         <f aca="false">C20-C21</f>
         <v>19600814.3958795</v>
       </c>
-      <c r="D22" s="38" t="n">
+      <c r="D22" s="39" t="n">
         <f aca="false">D20-D21</f>
         <v>20874867.3316117</v>
       </c>
-      <c r="E22" s="38" t="n">
+      <c r="E22" s="39" t="n">
         <f aca="false">E20-E21</f>
         <v>22231733.7081664</v>
       </c>
-      <c r="F22" s="38" t="n">
+      <c r="F22" s="39" t="n">
         <f aca="false">F20-F21</f>
         <v>23676796.3991973</v>
       </c>
-      <c r="G22" s="38" t="n">
+      <c r="G22" s="39" t="n">
         <f aca="false">G20-G21</f>
         <v>25215788.1651451</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="B23" s="38" t="n">
+      <c r="A23" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C23" s="39" t="n">
         <f aca="false">C19-C22</f>
         <v>91999185.6041205</v>
       </c>
-      <c r="D23" s="38" t="n">
+      <c r="D23" s="39" t="n">
         <f aca="false">D19-D22</f>
         <v>71124318.2725088</v>
       </c>
-      <c r="E23" s="38" t="n">
+      <c r="E23" s="39" t="n">
         <f aca="false">E19-E22</f>
         <v>48892584.5643424</v>
       </c>
-      <c r="F23" s="38" t="n">
+      <c r="F23" s="39" t="n">
         <f aca="false">F19-F22</f>
         <v>25215788.1651451</v>
       </c>
-      <c r="G23" s="38" t="n">
+      <c r="G23" s="39" t="n">
         <f aca="false">G19-G22</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="B24" s="38" t="n">
+      <c r="A24" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="B24" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="38" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$38,B16/'Control Panel &amp; Inputs'!$C$38,0)</f>
+      <c r="C24" s="39" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>27900000</v>
       </c>
-      <c r="D24" s="38" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$38,B16/'Control Panel &amp; Inputs'!$C$38,0)</f>
+      <c r="D24" s="39" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>27900000</v>
       </c>
-      <c r="E24" s="38" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$38,B16/'Control Panel &amp; Inputs'!$C$38,0)</f>
+      <c r="E24" s="39" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>27900000</v>
       </c>
-      <c r="F24" s="38" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$38,B16/'Control Panel &amp; Inputs'!$C$38,0)</f>
+      <c r="F24" s="39" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>27900000</v>
       </c>
-      <c r="G24" s="38" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$38,B16/'Control Panel &amp; Inputs'!$C$38,0)</f>
+      <c r="G24" s="39" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>27900000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B25" s="38" t="n">
+      <c r="A25" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="38" t="n">
-        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$40*C14)</f>
+      <c r="C25" s="39" t="n">
+        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$43*C14)</f>
         <v>7254000</v>
       </c>
-      <c r="D25" s="38" t="n">
-        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$40*D14)</f>
+      <c r="D25" s="39" t="n">
+        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$43*D14)</f>
         <v>5979947.06426783</v>
       </c>
-      <c r="E25" s="38" t="n">
-        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$40*E14)</f>
+      <c r="E25" s="39" t="n">
+        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$43*E14)</f>
         <v>4623080.68771307</v>
       </c>
-      <c r="F25" s="38" t="n">
-        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$40*F14)</f>
+      <c r="F25" s="39" t="n">
+        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$43*F14)</f>
         <v>3178017.99668225</v>
       </c>
-      <c r="G25" s="38" t="n">
-        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$40*G14)</f>
+      <c r="G25" s="39" t="n">
+        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$43*G14)</f>
         <v>1639026.23073443</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="B26" s="38" t="n">
+      <c r="A26" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B26" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="38" t="n">
+      <c r="C26" s="39" t="n">
         <f aca="false">C14-C24-C25</f>
         <v>25601550.321856</v>
       </c>
-      <c r="D26" s="38" t="n">
+      <c r="D26" s="39" t="n">
         <f aca="false">D14-D24-D25</f>
         <v>36444944.2640253</v>
       </c>
-      <c r="E26" s="38" t="n">
+      <c r="E26" s="39" t="n">
         <f aca="false">E14-E24-E25</f>
         <v>39058212.8671459</v>
       </c>
-      <c r="F26" s="38" t="n">
+      <c r="F26" s="39" t="n">
         <f aca="false">F14-F24-F25</f>
         <v>41852565.9300239</v>
       </c>
-      <c r="G26" s="38" t="n">
+      <c r="G26" s="39" t="n">
         <f aca="false">G14-G24-G25</f>
         <v>44839938.2145752</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="B27" s="38" t="n">
+      <c r="A27" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="B27" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="38" t="n">
-        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="C27" s="39" t="n">
+        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>2304139.52896704</v>
       </c>
-      <c r="D27" s="38" t="n">
-        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="D27" s="39" t="n">
+        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>3280044.98376228</v>
       </c>
-      <c r="E27" s="38" t="n">
-        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="E27" s="39" t="n">
+        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>3515239.15804313</v>
       </c>
-      <c r="F27" s="38" t="n">
-        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="F27" s="39" t="n">
+        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>3766730.93370215</v>
       </c>
-      <c r="G27" s="38" t="n">
-        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="G27" s="39" t="n">
+        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>4035594.43931177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="B28" s="38" t="n">
+      <c r="A28" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="38" t="n">
+      <c r="D28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="38" t="n">
+      <c r="E28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="38" t="n">
+      <c r="F28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="G28" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>13950000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="B29" s="42" t="n">
+      <c r="A29" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="B29" s="43" t="n">
         <f aca="false">-B18</f>
         <v>-27900000</v>
       </c>
-      <c r="C29" s="42" t="n">
+      <c r="C29" s="43" t="n">
         <f aca="false">C14-C20-C27+C28</f>
         <v>31596596.3970094</v>
       </c>
-      <c r="D29" s="42" t="n">
+      <c r="D29" s="43" t="n">
         <f aca="false">D14-D20-D27+D28</f>
         <v>40190031.9486513</v>
       </c>
-      <c r="E29" s="42" t="n">
+      <c r="E29" s="43" t="n">
         <f aca="false">E14-E20-E27+E28</f>
         <v>41211240.0009363</v>
       </c>
-      <c r="F29" s="42" t="n">
+      <c r="F29" s="43" t="n">
         <f aca="false">F14-F20-F27+F28</f>
         <v>42309038.5971245</v>
       </c>
-      <c r="G29" s="42" t="n">
+      <c r="G29" s="43" t="n">
         <f aca="false">G14-G20-G27+G28</f>
         <v>57438555.6101184</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="B30" s="38" t="n">
+      <c r="A30" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="39" t="n">
         <f aca="false">B29</f>
         <v>-27900000</v>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C30" s="39" t="n">
         <f aca="false">B30+C29</f>
         <v>3696596.39700945</v>
       </c>
-      <c r="D30" s="38" t="n">
+      <c r="D30" s="39" t="n">
         <f aca="false">C30+D29</f>
         <v>43886628.3456608</v>
       </c>
-      <c r="E30" s="38" t="n">
+      <c r="E30" s="39" t="n">
         <f aca="false">D30+E29</f>
         <v>85097868.3465971</v>
       </c>
-      <c r="F30" s="38" t="n">
+      <c r="F30" s="39" t="n">
         <f aca="false">E30+F29</f>
         <v>127406906.943722</v>
       </c>
-      <c r="G30" s="38" t="n">
+      <c r="G30" s="39" t="n">
         <f aca="false">F30+G29</f>
         <v>184845462.55384</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="B31" s="43" t="n">
+      <c r="A31" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="43" t="n">
+      <c r="C31" s="44" t="n">
         <f aca="false">IF(C20=0,"",C14/C20)</f>
         <v>2.26237088911618</v>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="44" t="n">
         <f aca="false">IF(D20=0,"",D14/D20)</f>
         <v>2.61870703299604</v>
       </c>
-      <c r="E31" s="43" t="n">
+      <c r="E31" s="44" t="n">
         <f aca="false">IF(E20=0,"",E14/E20)</f>
         <v>2.6654920231302</v>
       </c>
-      <c r="F31" s="43" t="n">
+      <c r="F31" s="44" t="n">
         <f aca="false">IF(F20=0,"",F14/F20)</f>
         <v>2.71573591429834</v>
       </c>
-      <c r="G31" s="43" t="n">
+      <c r="G31" s="44" t="n">
         <f aca="false">IF(G20=0,"",G14/G20)</f>
         <v>2.76966965210983</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="B32" s="38" t="n">
+      <c r="A32" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="B32" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="38" t="n">
-        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="C32" s="39" t="n">
+        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>2956999.52896704</v>
       </c>
-      <c r="D32" s="38" t="n">
-        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="D32" s="39" t="n">
+        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>3818240.21954638</v>
       </c>
-      <c r="E32" s="38" t="n">
-        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="E32" s="39" t="n">
+        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>3931316.41993731</v>
       </c>
-      <c r="F32" s="38" t="n">
-        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="F32" s="39" t="n">
+        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>4052752.55340355</v>
       </c>
-      <c r="G32" s="38" t="n">
-        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="G32" s="39" t="n">
+        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>4183106.80007787</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="B33" s="38" t="n">
+      <c r="A33" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="39" t="n">
         <f aca="false">-B16</f>
         <v>-139500000</v>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C33" s="39" t="n">
         <f aca="false">C14-C32+C28</f>
         <v>57798550.792889</v>
       </c>
-      <c r="D33" s="38" t="n">
+      <c r="D33" s="39" t="n">
         <f aca="false">D14-D32+D28</f>
         <v>66506651.1087467</v>
       </c>
-      <c r="E33" s="38" t="n">
+      <c r="E33" s="39" t="n">
         <f aca="false">E14-E32+E28</f>
         <v>67649977.1349217</v>
       </c>
-      <c r="F33" s="38" t="n">
+      <c r="F33" s="39" t="n">
         <f aca="false">F14-F32+F28</f>
         <v>68877831.3733026</v>
       </c>
-      <c r="G33" s="38" t="n">
+      <c r="G33" s="39" t="n">
         <f aca="false">G14-G32+G28</f>
         <v>84145857.6452318</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="44" t="s">
-        <v>289</v>
+      <c r="A35" s="45" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="45" t="n">
+      <c r="B36" s="46" t="n">
         <f aca="false">IRR(B29:G29)</f>
         <v>1.26506825092475</v>
       </c>
@@ -4680,7 +4762,7 @@
       <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="45" t="n">
+      <c r="B37" s="46" t="n">
         <f aca="false">IRR(B33:G33)</f>
         <v>0.37548919844065</v>
       </c>
@@ -4689,16 +4771,16 @@
       <c r="A38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="46" t="n">
-        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$41,C29:G29)</f>
+      <c r="B38" s="47" t="n">
+        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$44,C29:G29)</f>
         <v>109809242.3148</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B39" s="47" t="n">
+        <v>298</v>
+      </c>
+      <c r="B39" s="48" t="n">
         <f aca="false">SUM(C29:G29)/-B29</f>
         <v>7.62528539619498</v>
       </c>
@@ -4707,7 +4789,7 @@
       <c r="A40" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="48" t="n">
+      <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(COUNTIF(B30:G30,"&lt;0")-1+ABS(INDEX(B30:G30,COUNTIF(B30:G30,"&lt;0")))/INDEX(B29:G29,COUNTIF(B30:G30,"&lt;0")+1),"&gt;5 yrs")</f>
         <v>0.8830065001128</v>
       </c>
@@ -4716,16 +4798,16 @@
       <c r="A41" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="47" t="n">
+      <c r="B41" s="48" t="n">
         <f aca="false">MIN(C31:G31)</f>
         <v>2.26237088911618</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B42" s="47" t="n">
+        <v>299</v>
+      </c>
+      <c r="B42" s="48" t="n">
         <f aca="false">AVERAGE(C31:G31)</f>
         <v>2.60639510233012</v>
       </c>
@@ -4757,12 +4839,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4776,14 +4858,14 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="34" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$21</f>
         <v>2304</v>
       </c>
@@ -4791,44 +4873,44 @@
         <v>31</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B6" s="33" t="n">
-        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$27</f>
+        <v>304</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$30</f>
         <v>20082124.8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="33" t="n">
-        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$26</f>
+        <v>307</v>
+      </c>
+      <c r="B7" s="34" t="n">
+        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$29</f>
         <v>17069806.08</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="50" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/B7</f>
         <v>5.01323797112521</v>
       </c>
@@ -4836,14 +4918,14 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="49" t="n">
+        <v>310</v>
+      </c>
+      <c r="B9" s="50" t="n">
         <f aca="false">'Pro Forma Financials'!D$13/B7</f>
         <v>0.893396714657164</v>
       </c>
@@ -4851,14 +4933,14 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="49" t="n">
+        <v>312</v>
+      </c>
+      <c r="B10" s="50" t="n">
         <f aca="false">B8-B9</f>
         <v>4.11984125646805</v>
       </c>
@@ -4866,74 +4948,74 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="50" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32/B5</f>
+      <c r="B11" s="51" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35/B5</f>
         <v>60546.875</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B12" s="50" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>315</v>
+      </c>
+      <c r="B12" s="51" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>16880445.3049371</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="50" t="n">
+        <v>318</v>
+      </c>
+      <c r="B13" s="51" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>10355154.8886738</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B14" s="32" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$28*3600*8760*'Control Panel &amp; Inputs'!$C$26*'Control Panel &amp; Inputs'!$C$27/1000000000000</f>
+        <v>321</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*3600*8760*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30/1000000000000</f>
         <v>33.18370301952</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B15" s="49" t="n">
+        <v>324</v>
+      </c>
+      <c r="B15" s="50" t="n">
         <f aca="false">'Pro Forma Financials'!D$7/(B14*1000000)</f>
         <v>0.806871975205717</v>
       </c>
@@ -4941,29 +5023,29 @@
         <v>38</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="49" t="n">
-        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$29/(B14*1000000)</f>
+      <c r="B16" s="50" t="n">
+        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$32/(B14*1000000)</f>
         <v>0.137869863373019</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="36" t="n">
         <f aca="false">'Pro Forma Financials'!D$11/'Pro Forma Financials'!D$8</f>
         <v>0.0472894966018917</v>
       </c>
@@ -4971,14 +5053,14 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B18" s="51" t="n">
+        <v>328</v>
+      </c>
+      <c r="B18" s="52" t="n">
         <f aca="false">('Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12)/'Pro Forma Financials'!D$10</f>
         <v>1.12472791389946</v>
       </c>
@@ -4986,29 +5068,29 @@
         <v>41</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B19" s="50" t="n">
+        <v>330</v>
+      </c>
+      <c r="B19" s="51" t="n">
         <f aca="false">'Pro Forma Financials'!D$20+'Pro Forma Financials'!D$13</f>
         <v>42104923.0675864</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="35" t="n">
+        <v>332</v>
+      </c>
+      <c r="B20" s="36" t="n">
         <f aca="false">1-B19/'Pro Forma Financials'!D$8</f>
         <v>0.507976359128409</v>
       </c>
@@ -5016,7 +5098,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5044,1376 +5126,1376 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B5" s="52" t="n">
+        <v>350</v>
+      </c>
+      <c r="B5" s="53" t="n">
         <v>0.04</v>
       </c>
-      <c r="C5" s="53" t="n">
+      <c r="C5" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C5</f>
+      <c r="D5" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C5</f>
         <v>69750000</v>
       </c>
-      <c r="E5" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D5</f>
+      <c r="E5" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D5</f>
         <v>69750000</v>
       </c>
-      <c r="F5" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D5)</f>
+      <c r="F5" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D5)</f>
         <v>16784258.9974247</v>
       </c>
-      <c r="G5" s="54" t="n">
+      <c r="G5" s="55" t="n">
         <f aca="false">-$E5</f>
         <v>-69750000</v>
       </c>
-      <c r="H5" s="54" t="n">
-        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D5),0),'Control Panel &amp; Inputs'!$C$40*B23))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H5" s="55" t="n">
+        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*B23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>42625789.0311679</v>
       </c>
-      <c r="I5" s="54" t="n">
-        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D5),0),'Control Panel &amp; Inputs'!$C$40*C23))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I5" s="55" t="n">
+        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*C23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>51286293.0641049</v>
       </c>
-      <c r="J5" s="54" t="n">
-        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D5),0),'Control Panel &amp; Inputs'!$C$40*D23))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J5" s="55" t="n">
+        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*D23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>52377845.935207</v>
       </c>
-      <c r="K5" s="54" t="n">
-        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D5),0),'Control Panel &amp; Inputs'!$C$40*E23))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K5" s="55" t="n">
+        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*E23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>53549456.9873979</v>
       </c>
-      <c r="L5" s="54" t="n">
-        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D5),0),'Control Panel &amp; Inputs'!$C$40*F23))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L5" s="55" t="n">
+        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*F23))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>68756457.3944767</v>
       </c>
-      <c r="M5" s="55" t="n">
+      <c r="M5" s="56" t="n">
         <f aca="false">IRR(G5:L5)</f>
         <v>0.643978746381705</v>
       </c>
-      <c r="N5" s="56" t="n">
+      <c r="N5" s="57" t="n">
         <f aca="false">AVERAGE(B23:F23)/$F5</f>
         <v>4.25224061963126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" s="52" t="n">
+        <v>351</v>
+      </c>
+      <c r="B6" s="53" t="n">
         <v>0.04</v>
       </c>
-      <c r="C6" s="53" t="n">
+      <c r="C6" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C6</f>
+      <c r="D6" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C6</f>
         <v>83700000</v>
       </c>
-      <c r="E6" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D6</f>
+      <c r="E6" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D6</f>
         <v>55800000</v>
       </c>
-      <c r="F6" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D6)</f>
+      <c r="F6" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D6)</f>
         <v>20141110.7969096</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="55" t="n">
         <f aca="false">-$E6</f>
         <v>-55800000</v>
       </c>
-      <c r="H6" s="54" t="n">
-        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D6),0),'Control Panel &amp; Inputs'!$C$40*B24))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H6" s="55" t="n">
+        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*B24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>39350544.731683</v>
       </c>
-      <c r="I6" s="54" t="n">
-        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D6),0),'Control Panel &amp; Inputs'!$C$40*C24))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I6" s="55" t="n">
+        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*C24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>47996715.6690929</v>
       </c>
-      <c r="J6" s="54" t="n">
-        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D6),0),'Control Panel &amp; Inputs'!$C$40*D24))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J6" s="55" t="n">
+        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*D24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>49073003.7934588</v>
       </c>
-      <c r="K6" s="54" t="n">
-        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D6),0),'Control Panel &amp; Inputs'!$C$40*E24))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K6" s="55" t="n">
+        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*E24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>50228357.8903757</v>
       </c>
-      <c r="L6" s="54" t="n">
-        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D6),0),'Control Panel &amp; Inputs'!$C$40*F24))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L6" s="55" t="n">
+        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*F24))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>65418044.6400875</v>
       </c>
-      <c r="M6" s="55" t="n">
+      <c r="M6" s="56" t="n">
         <f aca="false">IRR(G6:L6)</f>
         <v>0.762382519931947</v>
       </c>
-      <c r="N6" s="56" t="n">
+      <c r="N6" s="57" t="n">
         <f aca="false">AVERAGE(B24:F24)/$F6</f>
         <v>3.54353384969272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="B7" s="52" t="n">
+        <v>352</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>0.04</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C7</f>
+      <c r="D7" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C7</f>
         <v>97650000</v>
       </c>
-      <c r="E7" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D7</f>
+      <c r="E7" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D7</f>
         <v>41850000</v>
       </c>
-      <c r="F7" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D7)</f>
+      <c r="F7" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D7)</f>
         <v>23497962.5963946</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="55" t="n">
         <f aca="false">-$E7</f>
         <v>-41850000</v>
       </c>
-      <c r="H7" s="54" t="n">
-        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D7),0),'Control Panel &amp; Inputs'!$C$40*B25))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H7" s="55" t="n">
+        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*B25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>36075300.4321981</v>
       </c>
-      <c r="I7" s="54" t="n">
-        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D7),0),'Control Panel &amp; Inputs'!$C$40*C25))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I7" s="55" t="n">
+        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*C25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>44707138.274081</v>
       </c>
-      <c r="J7" s="54" t="n">
-        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D7),0),'Control Panel &amp; Inputs'!$C$40*D25))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J7" s="55" t="n">
+        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*D25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>45768161.6517106</v>
       </c>
-      <c r="K7" s="54" t="n">
-        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D7),0),'Control Panel &amp; Inputs'!$C$40*E25))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K7" s="55" t="n">
+        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*E25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>46907258.7933534</v>
       </c>
-      <c r="L7" s="54" t="n">
-        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D7),0),'Control Panel &amp; Inputs'!$C$40*F25))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L7" s="55" t="n">
+        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*F25))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>62079631.8856983</v>
       </c>
-      <c r="M7" s="55" t="n">
+      <c r="M7" s="56" t="n">
         <f aca="false">IRR(G7:L7)</f>
         <v>0.950597457234898</v>
       </c>
-      <c r="N7" s="56" t="n">
+      <c r="N7" s="57" t="n">
         <f aca="false">AVERAGE(B25:F25)/$F7</f>
         <v>3.03731472830805</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="B8" s="52" t="n">
+        <v>353</v>
+      </c>
+      <c r="B8" s="53" t="n">
         <v>0.04</v>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="D8" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C8</f>
+      <c r="D8" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C8</f>
         <v>111600000</v>
       </c>
-      <c r="E8" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D8</f>
+      <c r="E8" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D8</f>
         <v>27900000</v>
       </c>
-      <c r="F8" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D8)</f>
+      <c r="F8" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D8)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="55" t="n">
         <f aca="false">-$E8</f>
         <v>-27900000</v>
       </c>
-      <c r="H8" s="54" t="n">
-        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D8),0),'Control Panel &amp; Inputs'!$C$40*B26))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H8" s="55" t="n">
+        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*B26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>32800056.1327131</v>
       </c>
-      <c r="I8" s="54" t="n">
-        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D8),0),'Control Panel &amp; Inputs'!$C$40*C26))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I8" s="55" t="n">
+        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*C26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>41417560.8790691</v>
       </c>
-      <c r="J8" s="54" t="n">
-        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D8),0),'Control Panel &amp; Inputs'!$C$40*D26))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J8" s="55" t="n">
+        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*D26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>42463319.5099624</v>
       </c>
-      <c r="K8" s="54" t="n">
-        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D8),0),'Control Panel &amp; Inputs'!$C$40*E26))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K8" s="55" t="n">
+        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*E26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>43586159.6963311</v>
       </c>
-      <c r="L8" s="54" t="n">
-        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D8),0),'Control Panel &amp; Inputs'!$C$40*F26))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L8" s="55" t="n">
+        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*F26))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>58741219.1313091</v>
       </c>
-      <c r="M8" s="55" t="n">
+      <c r="M8" s="56" t="n">
         <f aca="false">IRR(G8:L8)</f>
         <v>1.30679835036219</v>
       </c>
-      <c r="N8" s="56" t="n">
+      <c r="N8" s="57" t="n">
         <f aca="false">AVERAGE(B26:F26)/$F8</f>
         <v>2.65765038726954</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="B9" s="52" t="n">
+        <v>354</v>
+      </c>
+      <c r="B9" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="C9" s="53" t="n">
+      <c r="C9" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C9</f>
+      <c r="D9" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C9</f>
         <v>69750000</v>
       </c>
-      <c r="E9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D9</f>
+      <c r="E9" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D9</f>
         <v>69750000</v>
       </c>
-      <c r="F9" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D9)</f>
+      <c r="F9" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D9)</f>
         <v>16784258.9974247</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="55" t="n">
         <f aca="false">-$E9</f>
         <v>-69750000</v>
       </c>
-      <c r="H9" s="54" t="n">
-        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D9),0),'Control Panel &amp; Inputs'!$C$40*B27))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H9" s="55" t="n">
+        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*B27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>41422329.2954643</v>
       </c>
-      <c r="I9" s="54" t="n">
-        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D9),0),'Control Panel &amp; Inputs'!$C$40*C27))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I9" s="55" t="n">
+        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*C27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>50058764.1336871</v>
       </c>
-      <c r="J9" s="54" t="n">
-        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D9),0),'Control Panel &amp; Inputs'!$C$40*D27))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J9" s="55" t="n">
+        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*D27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>51125766.4261808</v>
       </c>
-      <c r="K9" s="54" t="n">
-        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D9),0),'Control Panel &amp; Inputs'!$C$40*E27))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K9" s="55" t="n">
+        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*E27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>52272335.8881913</v>
       </c>
-      <c r="L9" s="54" t="n">
-        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D9),0),'Control Panel &amp; Inputs'!$C$40*F27))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L9" s="55" t="n">
+        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*F27))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>67453793.8732859</v>
       </c>
-      <c r="M9" s="55" t="n">
+      <c r="M9" s="56" t="n">
         <f aca="false">IRR(G9:L9)</f>
         <v>0.625634391500291</v>
       </c>
-      <c r="N9" s="56" t="n">
+      <c r="N9" s="57" t="n">
         <f aca="false">AVERAGE(B27:F27)/$F9</f>
         <v>4.17023216372819</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="52" t="n">
+        <v>355</v>
+      </c>
+      <c r="B10" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="C10" s="53" t="n">
+      <c r="C10" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C10</f>
+      <c r="D10" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C10</f>
         <v>83700000</v>
       </c>
-      <c r="E10" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D10</f>
+      <c r="E10" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D10</f>
         <v>55800000</v>
       </c>
-      <c r="F10" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D10)</f>
+      <c r="F10" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D10)</f>
         <v>20141110.7969096</v>
       </c>
-      <c r="G10" s="54" t="n">
+      <c r="G10" s="55" t="n">
         <f aca="false">-$E10</f>
         <v>-55800000</v>
       </c>
-      <c r="H10" s="54" t="n">
-        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D10),0),'Control Panel &amp; Inputs'!$C$40*B28))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H10" s="55" t="n">
+        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*B28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>38147084.9959793</v>
       </c>
-      <c r="I10" s="54" t="n">
-        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D10),0),'Control Panel &amp; Inputs'!$C$40*C28))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I10" s="55" t="n">
+        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*C28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>46769186.7386752</v>
       </c>
-      <c r="J10" s="54" t="n">
-        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D10),0),'Control Panel &amp; Inputs'!$C$40*D28))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J10" s="55" t="n">
+        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*D28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>47820924.2844327</v>
       </c>
-      <c r="K10" s="54" t="n">
-        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D10),0),'Control Panel &amp; Inputs'!$C$40*E28))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K10" s="55" t="n">
+        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*E28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>48951236.791169</v>
       </c>
-      <c r="L10" s="54" t="n">
-        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D10),0),'Control Panel &amp; Inputs'!$C$40*F28))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L10" s="55" t="n">
+        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*F28))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>64115381.1188967</v>
       </c>
-      <c r="M10" s="55" t="n">
+      <c r="M10" s="56" t="n">
         <f aca="false">IRR(G10:L10)</f>
         <v>0.740129255041265</v>
       </c>
-      <c r="N10" s="56" t="n">
+      <c r="N10" s="57" t="n">
         <f aca="false">AVERAGE(B28:F28)/$F10</f>
         <v>3.47519346977349</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="52" t="n">
+        <v>356</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="C11" s="53" t="n">
+      <c r="C11" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="D11" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C11</f>
+      <c r="D11" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C11</f>
         <v>97650000</v>
       </c>
-      <c r="E11" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D11</f>
+      <c r="E11" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D11</f>
         <v>41850000</v>
       </c>
-      <c r="F11" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D11)</f>
+      <c r="F11" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D11)</f>
         <v>23497962.5963946</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="55" t="n">
         <f aca="false">-$E11</f>
         <v>-41850000</v>
       </c>
-      <c r="H11" s="54" t="n">
-        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D11),0),'Control Panel &amp; Inputs'!$C$40*B29))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H11" s="55" t="n">
+        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*B29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>34871840.6964944</v>
       </c>
-      <c r="I11" s="54" t="n">
-        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D11),0),'Control Panel &amp; Inputs'!$C$40*C29))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I11" s="55" t="n">
+        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*C29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>43479609.3436633</v>
       </c>
-      <c r="J11" s="54" t="n">
-        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D11),0),'Control Panel &amp; Inputs'!$C$40*D29))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J11" s="55" t="n">
+        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*D29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>44516082.1426845</v>
       </c>
-      <c r="K11" s="54" t="n">
-        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D11),0),'Control Panel &amp; Inputs'!$C$40*E29))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K11" s="55" t="n">
+        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*E29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>45630137.6941468</v>
       </c>
-      <c r="L11" s="54" t="n">
-        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D11),0),'Control Panel &amp; Inputs'!$C$40*F29))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L11" s="55" t="n">
+        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*F29))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>60776968.3645076</v>
       </c>
-      <c r="M11" s="55" t="n">
+      <c r="M11" s="56" t="n">
         <f aca="false">IRR(G11:L11)</f>
         <v>0.921875356077546</v>
       </c>
-      <c r="N11" s="56" t="n">
+      <c r="N11" s="57" t="n">
         <f aca="false">AVERAGE(B29:F29)/$F11</f>
         <v>2.97873725980585</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B12" s="52" t="n">
+        <v>357</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="C12" s="53" t="n">
+      <c r="C12" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="D12" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C12</f>
+      <c r="D12" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C12</f>
         <v>111600000</v>
       </c>
-      <c r="E12" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D12</f>
+      <c r="E12" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D12</f>
         <v>27900000</v>
       </c>
-      <c r="F12" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D12)</f>
+      <c r="F12" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D12)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="55" t="n">
         <f aca="false">-$E12</f>
         <v>-27900000</v>
       </c>
-      <c r="H12" s="54" t="n">
-        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D12),0),'Control Panel &amp; Inputs'!$C$40*B30))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H12" s="55" t="n">
+        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*B30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>31596596.3970094</v>
       </c>
-      <c r="I12" s="54" t="n">
-        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D12),0),'Control Panel &amp; Inputs'!$C$40*C30))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I12" s="55" t="n">
+        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*C30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>40190031.9486513</v>
       </c>
-      <c r="J12" s="54" t="n">
-        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D12),0),'Control Panel &amp; Inputs'!$C$40*D30))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J12" s="55" t="n">
+        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*D30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>41211240.0009363</v>
       </c>
-      <c r="K12" s="54" t="n">
-        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D12),0),'Control Panel &amp; Inputs'!$C$40*E30))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K12" s="55" t="n">
+        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*E30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>42309038.5971245</v>
       </c>
-      <c r="L12" s="54" t="n">
-        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D12),0),'Control Panel &amp; Inputs'!$C$40*F30))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L12" s="55" t="n">
+        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*F30))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>57438555.6101184</v>
       </c>
-      <c r="M12" s="55" t="n">
+      <c r="M12" s="56" t="n">
         <f aca="false">IRR(G12:L12)</f>
         <v>1.26506825092475</v>
       </c>
-      <c r="N12" s="56" t="n">
+      <c r="N12" s="57" t="n">
         <f aca="false">AVERAGE(B30:F30)/$F12</f>
         <v>2.60639510233012</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B13" s="52" t="n">
+        <v>358</v>
+      </c>
+      <c r="B13" s="53" t="n">
         <v>0.08</v>
       </c>
-      <c r="C13" s="53" t="n">
+      <c r="C13" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C13</f>
+      <c r="D13" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C13</f>
         <v>69750000</v>
       </c>
-      <c r="E13" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D13</f>
+      <c r="E13" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D13</f>
         <v>69750000</v>
       </c>
-      <c r="F13" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D13)</f>
+      <c r="F13" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D13)</f>
         <v>16784258.9974247</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G13" s="55" t="n">
         <f aca="false">-$E13</f>
         <v>-69750000</v>
       </c>
-      <c r="H13" s="54" t="n">
-        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D13),0),'Control Panel &amp; Inputs'!$C$40*B31))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H13" s="55" t="n">
+        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*B31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>40218869.5597606</v>
       </c>
-      <c r="I13" s="54" t="n">
-        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D13),0),'Control Panel &amp; Inputs'!$C$40*C31))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I13" s="55" t="n">
+        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*C31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>48831235.2032694</v>
       </c>
-      <c r="J13" s="54" t="n">
-        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D13),0),'Control Panel &amp; Inputs'!$C$40*D31))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J13" s="55" t="n">
+        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*D31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>49873686.9171547</v>
       </c>
-      <c r="K13" s="54" t="n">
-        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D13),0),'Control Panel &amp; Inputs'!$C$40*E31))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K13" s="55" t="n">
+        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*E31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>50995214.7889847</v>
       </c>
-      <c r="L13" s="54" t="n">
-        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D13),0),'Control Panel &amp; Inputs'!$C$40*F31))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L13" s="55" t="n">
+        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*F31))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>66151130.3520951</v>
       </c>
-      <c r="M13" s="55" t="n">
+      <c r="M13" s="56" t="n">
         <f aca="false">IRR(G13:L13)</f>
         <v>0.607230227403353</v>
       </c>
-      <c r="N13" s="56" t="n">
+      <c r="N13" s="57" t="n">
         <f aca="false">AVERAGE(B31:F31)/$F13</f>
         <v>4.08822370782512</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B14" s="52" t="n">
+        <v>359</v>
+      </c>
+      <c r="B14" s="53" t="n">
         <v>0.08</v>
       </c>
-      <c r="C14" s="53" t="n">
+      <c r="C14" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="D14" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C14</f>
+      <c r="D14" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C14</f>
         <v>83700000</v>
       </c>
-      <c r="E14" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D14</f>
+      <c r="E14" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D14</f>
         <v>55800000</v>
       </c>
-      <c r="F14" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D14)</f>
+      <c r="F14" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D14)</f>
         <v>20141110.7969096</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="55" t="n">
         <f aca="false">-$E14</f>
         <v>-55800000</v>
       </c>
-      <c r="H14" s="54" t="n">
-        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D14),0),'Control Panel &amp; Inputs'!$C$40*B32))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H14" s="55" t="n">
+        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*B32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>36943625.2602756</v>
       </c>
-      <c r="I14" s="54" t="n">
-        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D14),0),'Control Panel &amp; Inputs'!$C$40*C32))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I14" s="55" t="n">
+        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*C32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>45541657.8082574</v>
       </c>
-      <c r="J14" s="54" t="n">
-        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D14),0),'Control Panel &amp; Inputs'!$C$40*D32))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J14" s="55" t="n">
+        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*D32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>46568844.7754066</v>
       </c>
-      <c r="K14" s="54" t="n">
-        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D14),0),'Control Panel &amp; Inputs'!$C$40*E32))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K14" s="55" t="n">
+        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*E32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>47674115.6919624</v>
       </c>
-      <c r="L14" s="54" t="n">
-        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D14),0),'Control Panel &amp; Inputs'!$C$40*F32))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L14" s="55" t="n">
+        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*F32))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>62812717.597706</v>
       </c>
-      <c r="M14" s="55" t="n">
+      <c r="M14" s="56" t="n">
         <f aca="false">IRR(G14:L14)</f>
         <v>0.717819474593702</v>
       </c>
-      <c r="N14" s="56" t="n">
+      <c r="N14" s="57" t="n">
         <f aca="false">AVERAGE(B32:F32)/$F14</f>
         <v>3.40685308985427</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B15" s="52" t="n">
+        <v>360</v>
+      </c>
+      <c r="B15" s="53" t="n">
         <v>0.08</v>
       </c>
-      <c r="C15" s="53" t="n">
+      <c r="C15" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C15</f>
+      <c r="D15" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C15</f>
         <v>97650000</v>
       </c>
-      <c r="E15" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D15</f>
+      <c r="E15" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D15</f>
         <v>41850000</v>
       </c>
-      <c r="F15" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D15)</f>
+      <c r="F15" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D15)</f>
         <v>23497962.5963946</v>
       </c>
-      <c r="G15" s="54" t="n">
+      <c r="G15" s="55" t="n">
         <f aca="false">-$E15</f>
         <v>-41850000</v>
       </c>
-      <c r="H15" s="54" t="n">
-        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D15),0),'Control Panel &amp; Inputs'!$C$40*B33))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H15" s="55" t="n">
+        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*B33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>33668380.9607907</v>
       </c>
-      <c r="I15" s="54" t="n">
-        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D15),0),'Control Panel &amp; Inputs'!$C$40*C33))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I15" s="55" t="n">
+        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*C33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>42252080.4132455</v>
       </c>
-      <c r="J15" s="54" t="n">
-        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D15),0),'Control Panel &amp; Inputs'!$C$40*D33))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J15" s="55" t="n">
+        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*D33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>43264002.6336584</v>
       </c>
-      <c r="K15" s="54" t="n">
-        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D15),0),'Control Panel &amp; Inputs'!$C$40*E33))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K15" s="55" t="n">
+        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*E33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>44353016.5949401</v>
       </c>
-      <c r="L15" s="54" t="n">
-        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D15),0),'Control Panel &amp; Inputs'!$C$40*F33))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L15" s="55" t="n">
+        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*F33))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>59474304.8433168</v>
       </c>
-      <c r="M15" s="55" t="n">
+      <c r="M15" s="56" t="n">
         <f aca="false">IRR(G15:L15)</f>
         <v>0.893112538570458</v>
       </c>
-      <c r="N15" s="56" t="n">
+      <c r="N15" s="57" t="n">
         <f aca="false">AVERAGE(B33:F33)/$F15</f>
         <v>2.92015979130366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B16" s="52" t="n">
+        <v>361</v>
+      </c>
+      <c r="B16" s="53" t="n">
         <v>0.08</v>
       </c>
-      <c r="C16" s="53" t="n">
+      <c r="C16" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="D16" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C16</f>
+      <c r="D16" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C16</f>
         <v>111600000</v>
       </c>
-      <c r="E16" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D16</f>
+      <c r="E16" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D16</f>
         <v>27900000</v>
       </c>
-      <c r="F16" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D16)</f>
+      <c r="F16" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D16)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="G16" s="54" t="n">
+      <c r="G16" s="55" t="n">
         <f aca="false">-$E16</f>
         <v>-27900000</v>
       </c>
-      <c r="H16" s="54" t="n">
-        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D16),0),'Control Panel &amp; Inputs'!$C$40*B34))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H16" s="55" t="n">
+        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*B34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>30393136.6613058</v>
       </c>
-      <c r="I16" s="54" t="n">
-        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D16),0),'Control Panel &amp; Inputs'!$C$40*C34))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I16" s="55" t="n">
+        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*C34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>38962503.0182336</v>
       </c>
-      <c r="J16" s="54" t="n">
-        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D16),0),'Control Panel &amp; Inputs'!$C$40*D34))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J16" s="55" t="n">
+        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*D34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>39959160.4919102</v>
       </c>
-      <c r="K16" s="54" t="n">
-        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D16),0),'Control Panel &amp; Inputs'!$C$40*E34))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K16" s="55" t="n">
+        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*E34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>41031917.4979179</v>
       </c>
-      <c r="L16" s="54" t="n">
-        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D16),0),'Control Panel &amp; Inputs'!$C$40*F34))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L16" s="55" t="n">
+        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*F34))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>56135892.0889276</v>
       </c>
-      <c r="M16" s="55" t="n">
+      <c r="M16" s="56" t="n">
         <f aca="false">IRR(G16:L16)</f>
         <v>1.22335056745985</v>
       </c>
-      <c r="N16" s="56" t="n">
+      <c r="N16" s="57" t="n">
         <f aca="false">AVERAGE(B34:F34)/$F16</f>
         <v>2.5551398173907</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="B17" s="52" t="n">
+        <v>362</v>
+      </c>
+      <c r="B17" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="C17" s="53" t="n">
+      <c r="C17" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C17</f>
+      <c r="D17" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C17</f>
         <v>69750000</v>
       </c>
-      <c r="E17" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D17</f>
+      <c r="E17" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D17</f>
         <v>69750000</v>
       </c>
-      <c r="F17" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D17)</f>
+      <c r="F17" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D17)</f>
         <v>16784258.9974247</v>
       </c>
-      <c r="G17" s="54" t="n">
+      <c r="G17" s="55" t="n">
         <f aca="false">-$E17</f>
         <v>-69750000</v>
       </c>
-      <c r="H17" s="54" t="n">
-        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D17),0),'Control Panel &amp; Inputs'!$C$40*B35))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H17" s="55" t="n">
+        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*B35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>39015409.8240569</v>
       </c>
-      <c r="I17" s="54" t="n">
-        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D17),0),'Control Panel &amp; Inputs'!$C$40*C35))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I17" s="55" t="n">
+        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*C35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>47603706.2728516</v>
       </c>
-      <c r="J17" s="54" t="n">
-        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D17),0),'Control Panel &amp; Inputs'!$C$40*D35))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J17" s="55" t="n">
+        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*D35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>48621607.4081286</v>
       </c>
-      <c r="K17" s="54" t="n">
-        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D17),0),'Control Panel &amp; Inputs'!$C$40*E35))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K17" s="55" t="n">
+        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*E35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>49718093.689778</v>
       </c>
-      <c r="L17" s="54" t="n">
-        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D17),0),'Control Panel &amp; Inputs'!$C$40*F35))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L17" s="55" t="n">
+        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*F35))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>64848466.8309044</v>
       </c>
-      <c r="M17" s="55" t="n">
+      <c r="M17" s="56" t="n">
         <f aca="false">IRR(G17:L17)</f>
         <v>0.588762837234268</v>
       </c>
-      <c r="N17" s="56" t="n">
+      <c r="N17" s="57" t="n">
         <f aca="false">AVERAGE(B35:F35)/$F17</f>
         <v>4.00621525192205</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B18" s="52" t="n">
+        <v>363</v>
+      </c>
+      <c r="B18" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" s="53" t="n">
+      <c r="C18" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="D18" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C18</f>
+      <c r="D18" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C18</f>
         <v>83700000</v>
       </c>
-      <c r="E18" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D18</f>
+      <c r="E18" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D18</f>
         <v>55800000</v>
       </c>
-      <c r="F18" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D18)</f>
+      <c r="F18" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D18)</f>
         <v>20141110.7969096</v>
       </c>
-      <c r="G18" s="54" t="n">
+      <c r="G18" s="55" t="n">
         <f aca="false">-$E18</f>
         <v>-55800000</v>
       </c>
-      <c r="H18" s="54" t="n">
-        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D18),0),'Control Panel &amp; Inputs'!$C$40*B36))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H18" s="55" t="n">
+        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*B36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>35740165.524572</v>
       </c>
-      <c r="I18" s="54" t="n">
-        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D18),0),'Control Panel &amp; Inputs'!$C$40*C36))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I18" s="55" t="n">
+        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*C36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>44314128.8778397</v>
       </c>
-      <c r="J18" s="54" t="n">
-        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D18),0),'Control Panel &amp; Inputs'!$C$40*D36))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J18" s="55" t="n">
+        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*D36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>45316765.2663805</v>
       </c>
-      <c r="K18" s="54" t="n">
-        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D18),0),'Control Panel &amp; Inputs'!$C$40*E36))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K18" s="55" t="n">
+        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*E36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>46396994.5927558</v>
       </c>
-      <c r="L18" s="54" t="n">
-        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D18),0),'Control Panel &amp; Inputs'!$C$40*F36))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L18" s="55" t="n">
+        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*F36))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>61510054.0765152</v>
       </c>
-      <c r="M18" s="55" t="n">
+      <c r="M18" s="56" t="n">
         <f aca="false">IRR(G18:L18)</f>
         <v>0.695449303949312</v>
       </c>
-      <c r="N18" s="56" t="n">
+      <c r="N18" s="57" t="n">
         <f aca="false">AVERAGE(B36:F36)/$F18</f>
         <v>3.33851270993504</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="B19" s="52" t="n">
+        <v>364</v>
+      </c>
+      <c r="B19" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="D19" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C19</f>
+      <c r="D19" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C19</f>
         <v>97650000</v>
       </c>
-      <c r="E19" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D19</f>
+      <c r="E19" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D19</f>
         <v>41850000</v>
       </c>
-      <c r="F19" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D19)</f>
+      <c r="F19" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D19)</f>
         <v>23497962.5963946</v>
       </c>
-      <c r="G19" s="54" t="n">
+      <c r="G19" s="55" t="n">
         <f aca="false">-$E19</f>
         <v>-41850000</v>
       </c>
-      <c r="H19" s="54" t="n">
-        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D19),0),'Control Panel &amp; Inputs'!$C$40*B37))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H19" s="55" t="n">
+        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*B37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>32464921.225087</v>
       </c>
-      <c r="I19" s="54" t="n">
-        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D19),0),'Control Panel &amp; Inputs'!$C$40*C37))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I19" s="55" t="n">
+        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*C37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>41024551.4828278</v>
       </c>
-      <c r="J19" s="54" t="n">
-        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D19),0),'Control Panel &amp; Inputs'!$C$40*D37))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J19" s="55" t="n">
+        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*D37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>42011923.1246323</v>
       </c>
-      <c r="K19" s="54" t="n">
-        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D19),0),'Control Panel &amp; Inputs'!$C$40*E37))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K19" s="55" t="n">
+        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*E37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>43075895.4957335</v>
       </c>
-      <c r="L19" s="54" t="n">
-        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D19),0),'Control Panel &amp; Inputs'!$C$40*F37))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L19" s="55" t="n">
+        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*F37))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>58171641.322126</v>
       </c>
-      <c r="M19" s="55" t="n">
+      <c r="M19" s="56" t="n">
         <f aca="false">IRR(G19:L19)</f>
         <v>0.864305027747797</v>
       </c>
-      <c r="N19" s="56" t="n">
+      <c r="N19" s="57" t="n">
         <f aca="false">AVERAGE(B37:F37)/$F19</f>
         <v>2.86158232280146</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B20" s="52" t="n">
+        <v>365</v>
+      </c>
+      <c r="B20" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="D20" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32*$C20</f>
+      <c r="D20" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C20</f>
         <v>111600000</v>
       </c>
-      <c r="E20" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$32-$D20</f>
+      <c r="E20" s="55" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D20</f>
         <v>27900000</v>
       </c>
-      <c r="F20" s="54" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$35,'Control Panel &amp; Inputs'!$C$36,$D20)</f>
+      <c r="F20" s="55" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D20)</f>
         <v>26854814.3958795</v>
       </c>
-      <c r="G20" s="54" t="n">
+      <c r="G20" s="55" t="n">
         <f aca="false">-$E20</f>
         <v>-27900000</v>
       </c>
-      <c r="H20" s="54" t="n">
-        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$36,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,1,'Control Panel &amp; Inputs'!$C$36,$D20),0),'Control Panel &amp; Inputs'!$C$40*B38))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="H20" s="55" t="n">
+        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*B38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>29189676.9256021</v>
       </c>
-      <c r="I20" s="54" t="n">
-        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$36,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,2,'Control Panel &amp; Inputs'!$C$36,$D20),0),'Control Panel &amp; Inputs'!$C$40*C38))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="I20" s="55" t="n">
+        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*C38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>37734974.0878158</v>
       </c>
-      <c r="J20" s="54" t="n">
-        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$36,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,3,'Control Panel &amp; Inputs'!$C$36,$D20),0),'Control Panel &amp; Inputs'!$C$40*D38))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="J20" s="55" t="n">
+        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*D38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>38707080.9828841</v>
       </c>
-      <c r="K20" s="54" t="n">
-        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$36,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,4,'Control Panel &amp; Inputs'!$C$36,$D20),0),'Control Panel &amp; Inputs'!$C$40*E38))*'Control Panel &amp; Inputs'!$C$39</f>
+      <c r="K20" s="55" t="n">
+        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*E38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>39754796.3987112</v>
       </c>
-      <c r="L20" s="54" t="n">
-        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$36,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$32/'Control Panel &amp; Inputs'!$C$38,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$36,-IPMT('Control Panel &amp; Inputs'!$C$35,5,'Control Panel &amp; Inputs'!$C$36,$D20),0),'Control Panel &amp; Inputs'!$C$40*F38))*'Control Panel &amp; Inputs'!$C$39+'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$33</f>
+      <c r="L20" s="55" t="n">
+        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*F38))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>54833228.5677368</v>
       </c>
-      <c r="M20" s="55" t="n">
+      <c r="M20" s="56" t="n">
         <f aca="false">IRR(G20:L20)</f>
         <v>1.18164323060214</v>
       </c>
-      <c r="N20" s="56" t="n">
+      <c r="N20" s="57" t="n">
         <f aca="false">AVERAGE(B38:F38)/$F20</f>
         <v>2.50388453245128</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="s">
-        <v>358</v>
+      <c r="A21" s="45" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="57" t="str">
+      <c r="A23" s="58" t="str">
         <f aca="false">A5</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B23" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B23" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C23" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C23" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D23" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D23" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E23" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E23" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F23" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F23" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="57" t="str">
+      <c r="A24" s="58" t="str">
         <f aca="false">A6</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B24" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B24" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C24" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C24" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D24" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D24" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E24" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E24" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F24" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F24" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="str">
+      <c r="A25" s="58" t="str">
         <f aca="false">A7</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B25" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B25" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C25" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C25" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D25" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D25" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E25" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E25" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F25" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F25" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="57" t="str">
+      <c r="A26" s="58" t="str">
         <f aca="false">A8</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B26" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B26" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C26" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C26" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D26" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D26" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E26" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E26" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F26" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F26" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="57" t="str">
+      <c r="A27" s="58" t="str">
         <f aca="false">A9</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B27" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B27" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C27" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C27" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D27" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D27" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E27" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E27" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F27" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F27" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="57" t="str">
+      <c r="A28" s="58" t="str">
         <f aca="false">A10</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B28" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B28" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C28" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C28" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D28" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D28" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E28" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E28" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F28" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F28" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="57" t="str">
+      <c r="A29" s="58" t="str">
         <f aca="false">A11</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B29" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B29" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C29" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C29" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D29" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D29" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E29" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E29" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F29" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F29" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="57" t="str">
+      <c r="A30" s="58" t="str">
         <f aca="false">A12</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B30" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B30" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C30" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C30" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D30" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D30" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E30" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E30" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F30" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F30" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="57" t="str">
+      <c r="A31" s="58" t="str">
         <f aca="false">A13</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B31" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B31" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C31" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C31" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D31" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D31" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E31" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E31" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F31" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F31" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57" t="str">
+      <c r="A32" s="58" t="str">
         <f aca="false">A14</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B32" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B32" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C32" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C32" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D32" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D32" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E32" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E32" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F32" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F32" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="57" t="str">
+      <c r="A33" s="58" t="str">
         <f aca="false">A15</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B33" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B33" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C33" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C33" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D33" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D33" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E33" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E33" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F33" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F33" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="57" t="str">
+      <c r="A34" s="58" t="str">
         <f aca="false">A16</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B34" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B34" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C34" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C34" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D34" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D34" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E34" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E34" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F34" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F34" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="57" t="str">
+      <c r="A35" s="58" t="str">
         <f aca="false">A17</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B35" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B35" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C35" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C35" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D35" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D35" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E35" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E35" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F35" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F35" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="57" t="str">
+      <c r="A36" s="58" t="str">
         <f aca="false">A18</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B36" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B36" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C36" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C36" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D36" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D36" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E36" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E36" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F36" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F36" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="57" t="str">
+      <c r="A37" s="58" t="str">
         <f aca="false">A19</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B37" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B37" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C37" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C37" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D37" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D37" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E37" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E37" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F37" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F37" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="57" t="str">
+      <c r="A38" s="58" t="str">
         <f aca="false">A20</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B38" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$31,0)</f>
+      <c r="B38" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C38" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$31,1)</f>
+      <c r="C38" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D38" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$31,2)</f>
+      <c r="D38" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E38" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$31,3)</f>
+      <c r="E38" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F38" s="54" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$31,4)</f>
+      <c r="F38" s="55" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
@@ -6442,222 +6524,222 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
-        <v>366</v>
+      <c r="A4" s="45" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="B6" s="58" t="n">
+        <v>380</v>
+      </c>
+      <c r="B6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M5</f>
         <v>0.643978746381705</v>
       </c>
-      <c r="C6" s="58" t="n">
+      <c r="C6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M6</f>
         <v>0.762382519931947</v>
       </c>
-      <c r="D6" s="58" t="n">
+      <c r="D6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M7</f>
         <v>0.950597457234898</v>
       </c>
-      <c r="E6" s="58" t="n">
+      <c r="E6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M8</f>
         <v>1.30679835036219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="B7" s="58" t="n">
+        <v>381</v>
+      </c>
+      <c r="B7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M9</f>
         <v>0.625634391500291</v>
       </c>
-      <c r="C7" s="58" t="n">
+      <c r="C7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M10</f>
         <v>0.740129255041265</v>
       </c>
-      <c r="D7" s="58" t="n">
+      <c r="D7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M11</f>
         <v>0.921875356077546</v>
       </c>
-      <c r="E7" s="58" t="n">
+      <c r="E7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M12</f>
         <v>1.26506825092475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B8" s="58" t="n">
+        <v>382</v>
+      </c>
+      <c r="B8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M13</f>
         <v>0.607230227403353</v>
       </c>
-      <c r="C8" s="58" t="n">
+      <c r="C8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M14</f>
         <v>0.717819474593702</v>
       </c>
-      <c r="D8" s="58" t="n">
+      <c r="D8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M15</f>
         <v>0.893112538570458</v>
       </c>
-      <c r="E8" s="58" t="n">
+      <c r="E8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M16</f>
         <v>1.22335056745985</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="B9" s="58" t="n">
+        <v>383</v>
+      </c>
+      <c r="B9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M17</f>
         <v>0.588762837234268</v>
       </c>
-      <c r="C9" s="58" t="n">
+      <c r="C9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M18</f>
         <v>0.695449303949312</v>
       </c>
-      <c r="D9" s="58" t="n">
+      <c r="D9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M19</f>
         <v>0.864305027747797</v>
       </c>
-      <c r="E9" s="58" t="n">
+      <c r="E9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M20</f>
         <v>1.18164323060214</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>376</v>
+      <c r="A12" s="45" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="B14" s="59" t="n">
+        <v>380</v>
+      </c>
+      <c r="B14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N5</f>
         <v>4.25224061963126</v>
       </c>
-      <c r="C14" s="59" t="n">
+      <c r="C14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N6</f>
         <v>3.54353384969272</v>
       </c>
-      <c r="D14" s="59" t="n">
+      <c r="D14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N7</f>
         <v>3.03731472830805</v>
       </c>
-      <c r="E14" s="59" t="n">
+      <c r="E14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N8</f>
         <v>2.65765038726954</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="B15" s="59" t="n">
+        <v>381</v>
+      </c>
+      <c r="B15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N9</f>
         <v>4.17023216372819</v>
       </c>
-      <c r="C15" s="59" t="n">
+      <c r="C15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N10</f>
         <v>3.47519346977349</v>
       </c>
-      <c r="D15" s="59" t="n">
+      <c r="D15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N11</f>
         <v>2.97873725980585</v>
       </c>
-      <c r="E15" s="59" t="n">
+      <c r="E15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N12</f>
         <v>2.60639510233012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B16" s="59" t="n">
+        <v>382</v>
+      </c>
+      <c r="B16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N13</f>
         <v>4.08822370782512</v>
       </c>
-      <c r="C16" s="59" t="n">
+      <c r="C16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N14</f>
         <v>3.40685308985427</v>
       </c>
-      <c r="D16" s="59" t="n">
+      <c r="D16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N15</f>
         <v>2.92015979130366</v>
       </c>
-      <c r="E16" s="59" t="n">
+      <c r="E16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N16</f>
         <v>2.5551398173907</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="B17" s="59" t="n">
+        <v>383</v>
+      </c>
+      <c r="B17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N17</f>
         <v>4.00621525192205</v>
       </c>
-      <c r="C17" s="59" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N18</f>
         <v>3.33851270993504</v>
       </c>
-      <c r="D17" s="59" t="n">
+      <c r="D17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N19</f>
         <v>2.86158232280146</v>
       </c>
-      <c r="E17" s="59" t="n">
+      <c r="E17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N20</f>
         <v>2.50388453245128</v>
       </c>

--- a/AI_Factory_Model.xlsx
+++ b/AI_Factory_Model.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Unit Economics &amp; KPIs" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Sensitivity Engine" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Sensitivity Matrices" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Phased Expansion" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="410">
   <si>
     <t xml:space="preserve">AI Factory Dashboard — 32x Vera Rubin NVL72, Abu Dhabi, UAE</t>
   </si>
@@ -413,7 +414,7 @@
     <t xml:space="preserve">CapEx_Initial</t>
   </si>
   <si>
-    <t xml:space="preserve">Total turnkey deployment</t>
+    <t xml:space="preserve">All-in benchmark midpoint: ~$91M facility (at $9.9-12.2M/MW) + 32 VR racks at ~$7.4M each (reported $6.0-8.8M). Set to ~$91M if IT is leased/vendor-financed.</t>
   </si>
   <si>
     <t xml:space="preserve">Residual_Value_Pct</t>
@@ -527,6 +528,21 @@
     <t xml:space="preserve">Token demand growth (partially offsets price decline)</t>
   </si>
   <si>
+    <t xml:space="preserve">Phased Expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansion_Blocks_Per_Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,2,4,4,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocks/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated blocks added per year (padded/truncated to the horizon); one block = this workbook's full rack architecture. Live numeric cells are on the 'Phased Expansion' sheet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legend: yellow cells with blue text are the editable inputs; all other cells in this workbook are formulas.</t>
   </si>
   <si>
@@ -1182,6 +1198,66 @@
   </si>
   <si>
     <t xml:space="preserve">Matrix 2: Average Debt Service Coverage Ratio (DSCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phased Campus Expansion — Identical Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each block replicates this workbook's rack architecture; block economics use the single-block Year-2 (steady-state) pro forma. Simplification: per-vintage token-price dynamics and per-block financing are not modeled here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocks Added (input)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus IT Capacity (MW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Revenue Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CapEx Deployed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus Net Cash Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Funding Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus KPIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Funding Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus Cash-Positive Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Campus IT Capacity (MW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Campus GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-Rate Campus EBITDA (full blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Campus CapEx</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1462,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1629,6 +1705,18 @@
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1922,7 +2010,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">'Pro Forma Financials'!B36</f>
-        <v>1.26506825092475</v>
+        <v>0.00348283951629262</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
@@ -1937,7 +2025,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Pro Forma Financials'!B37</f>
-        <v>0.37548919844065</v>
+        <v>0.0473981776304923</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>7</v>
@@ -1952,7 +2040,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">'Pro Forma Financials'!B38</f>
-        <v>109809242.3148</v>
+        <v>-29426161.8959998</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>11</v>
@@ -1967,7 +2055,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!B39</f>
-        <v>7.62528539619498</v>
+        <v>1.01548022177123</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>13</v>
@@ -1982,7 +2070,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">'Pro Forma Financials'!B40</f>
-        <v>0.8830065001128</v>
+        <v>4.97670502082603</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>15</v>
@@ -2042,7 +2130,7 @@
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">'Pro Forma Financials'!B41</f>
-        <v>2.26237088911618</v>
+        <v>0.962197375096669</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>13</v>
@@ -2147,7 +2235,7 @@
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B11</f>
-        <v>60546.875</v>
+        <v>142361.111111111</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>34</v>
@@ -2260,7 +2348,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2811,7 +2899,7 @@
         <v>127</v>
       </c>
       <c r="C35" s="30" t="n">
-        <v>139500000</v>
+        <v>328000000</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>11</v>
@@ -3109,19 +3197,36 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
         <v>166</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3152,32 +3257,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,7 +3290,7 @@
         <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C5" s="31" t="n">
         <v>0.26</v>
@@ -3197,15 +3302,15 @@
         <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>0.28</v>
@@ -3220,10 +3325,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>0.28</v>
@@ -3235,15 +3340,15 @@
         <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>0.28</v>
@@ -3255,15 +3360,15 @@
         <v>29.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C9" s="31" t="n">
         <v>0.28</v>
@@ -3278,10 +3383,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C10" s="31" t="n">
         <v>0.25</v>
@@ -3296,10 +3401,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C11" s="31" t="n">
         <v>0.21</v>
@@ -3314,10 +3419,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C12" s="31" t="n">
         <v>0.19</v>
@@ -3329,15 +3434,15 @@
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C13" s="31" t="n">
         <v>0.16</v>
@@ -3352,10 +3457,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C14" s="31" t="n">
         <v>0.16</v>
@@ -3370,10 +3475,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C15" s="31" t="n">
         <v>0.16</v>
@@ -3388,10 +3493,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C16" s="31" t="n">
         <v>0.16</v>
@@ -3403,15 +3508,15 @@
         <v>19.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C17" s="31" t="n">
         <v>0.15</v>
@@ -3426,10 +3531,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C18" s="31" t="n">
         <v>0.21</v>
@@ -3444,10 +3549,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C19" s="31" t="n">
         <v>0.21</v>
@@ -3487,17 +3592,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -3506,102 +3611,102 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B5" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$13</f>
         <v>7264</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B6" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$15*'Control Panel &amp; Inputs'!$C$16</f>
         <v>600</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B7" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$19</f>
         <v>400</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>8264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B9" s="33" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",B7,0)</f>
         <v>7264</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B10" s="33" t="n">
         <f aca="false">B8-B9</f>
         <v>1000</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",'Control Panel &amp; Inputs'!$C$12,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",'Control Panel &amp; Inputs'!$C$15,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",'Control Panel &amp; Inputs'!$C$18,0)</f>
@@ -3611,12 +3716,12 @@
         <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B12" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$24</f>
@@ -3626,12 +3731,12 @@
         <v>60</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B13" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$25</f>
@@ -3641,12 +3746,12 @@
         <v>60</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B14" s="33" t="n">
         <f aca="false">B13-B12</f>
@@ -3656,42 +3761,42 @@
         <v>60</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B15" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
         <v>343.462362879839</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B16" s="33" t="n">
         <f aca="false">B9/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
         <v>10990.7956121548</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B17" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
@@ -3701,12 +3806,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B18" s="33" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
@@ -3716,72 +3821,72 @@
         <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">B13-B17</f>
         <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B20" s="33" t="n">
         <f aca="false">B9*'Control Panel &amp; Inputs'!$C$22</f>
         <v>363.2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B21" s="33" t="n">
         <f aca="false">B10*'Control Panel &amp; Inputs'!$C$23</f>
         <v>280</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B22" s="33" t="n">
         <f aca="false">B20+B21</f>
         <v>643.2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B23" s="35" t="n">
         <f aca="false">B22/B8</f>
@@ -3789,12 +3894,12 @@
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B24" s="35" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
@@ -3802,12 +3907,12 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B25" s="36" t="n">
         <f aca="false">(B24-B23)/B24</f>
@@ -3817,27 +3922,27 @@
         <v>7</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B26" s="33" t="n">
         <f aca="false">B8*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30</f>
         <v>6989.278</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B27" s="35" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$28</f>
@@ -3845,7 +3950,7 @@
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3860,7 +3965,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3875,7 +3980,7 @@
         <v>29</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3890,7 +3995,7 @@
         <v>27</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3918,40 +4023,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B5" s="38" t="n">
         <v>0</v>
@@ -3975,7 +4080,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B6" s="39" t="n">
         <v>0</v>
@@ -4003,7 +4108,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B7" s="39" t="n">
         <v>0</v>
@@ -4031,7 +4136,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B8" s="39" t="n">
         <v>0</v>
@@ -4059,7 +4164,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B9" s="40" t="n">
         <v>0</v>
@@ -4087,7 +4192,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>0</v>
@@ -4115,7 +4220,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B11" s="39" t="n">
         <v>0</v>
@@ -4143,7 +4248,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B12" s="39" t="n">
         <v>0</v>
@@ -4171,7 +4276,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B13" s="39" t="n">
         <v>0</v>
@@ -4199,7 +4304,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B14" s="39" t="n">
         <v>0</v>
@@ -4227,7 +4332,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B15" s="38" t="n">
         <v>0</v>
@@ -4255,11 +4360,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B16" s="39" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35</f>
-        <v>139500000</v>
+        <v>328000000</v>
       </c>
       <c r="C16" s="39" t="n">
         <v>0</v>
@@ -4279,11 +4384,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">B16*'Control Panel &amp; Inputs'!$C$37</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="C17" s="39" t="n">
         <v>0</v>
@@ -4303,11 +4408,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B18" s="39" t="n">
         <f aca="false">B16-B17</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="C18" s="39" t="n">
         <v>0</v>
@@ -4327,138 +4432,138 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B19" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">B17</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="D19" s="39" t="n">
         <f aca="false">C23</f>
-        <v>91999185.6041205</v>
+        <v>216313497.33442</v>
       </c>
       <c r="E19" s="39" t="n">
         <f aca="false">D23</f>
-        <v>71124318.2725088</v>
+        <v>167231371.995576</v>
       </c>
       <c r="F19" s="39" t="n">
         <f aca="false">E23</f>
-        <v>48892584.5643424</v>
+        <v>114958908.509708</v>
       </c>
       <c r="G19" s="39" t="n">
         <f aca="false">F23</f>
-        <v>25215788.1651451</v>
+        <v>59288734.8972587</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B20" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="39" t="n">
         <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="D20" s="39" t="n">
         <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="E20" s="39" t="n">
         <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="F20" s="39" t="n">
         <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="G20" s="39" t="n">
         <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B21" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">C19*'Control Panel &amp; Inputs'!$C$38</f>
-        <v>7254000</v>
+        <v>17056000</v>
       </c>
       <c r="D21" s="39" t="n">
         <f aca="false">D19*'Control Panel &amp; Inputs'!$C$38</f>
-        <v>5979947.06426783</v>
+        <v>14060377.3267373</v>
       </c>
       <c r="E21" s="39" t="n">
         <f aca="false">E19*'Control Panel &amp; Inputs'!$C$38</f>
-        <v>4623080.68771307</v>
+        <v>10870039.1797125</v>
       </c>
       <c r="F21" s="39" t="n">
         <f aca="false">F19*'Control Panel &amp; Inputs'!$C$38</f>
-        <v>3178017.99668225</v>
+        <v>7472329.05313103</v>
       </c>
       <c r="G21" s="39" t="n">
         <f aca="false">G19*'Control Panel &amp; Inputs'!$C$38</f>
-        <v>1639026.23073443</v>
+        <v>3853767.76832181</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B22" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="39" t="n">
         <f aca="false">C20-C21</f>
-        <v>19600814.3958795</v>
+        <v>46086502.6655805</v>
       </c>
       <c r="D22" s="39" t="n">
         <f aca="false">D20-D21</f>
-        <v>20874867.3316117</v>
+        <v>49082125.3388433</v>
       </c>
       <c r="E22" s="39" t="n">
         <f aca="false">E20-E21</f>
-        <v>22231733.7081664</v>
+        <v>52272463.4858681</v>
       </c>
       <c r="F22" s="39" t="n">
         <f aca="false">F20-F21</f>
-        <v>23676796.3991973</v>
+        <v>55670173.6124495</v>
       </c>
       <c r="G22" s="39" t="n">
         <f aca="false">G20-G21</f>
-        <v>25215788.1651451</v>
+        <v>59288734.8972587</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B23" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="39" t="n">
         <f aca="false">C19-C22</f>
-        <v>91999185.6041205</v>
+        <v>216313497.33442</v>
       </c>
       <c r="D23" s="39" t="n">
         <f aca="false">D19-D22</f>
-        <v>71124318.2725088</v>
+        <v>167231371.995576</v>
       </c>
       <c r="E23" s="39" t="n">
         <f aca="false">E19-E22</f>
-        <v>48892584.5643424</v>
+        <v>114958908.509708</v>
       </c>
       <c r="F23" s="39" t="n">
         <f aca="false">F19-F22</f>
-        <v>25215788.1651451</v>
+        <v>59288734.8972587</v>
       </c>
       <c r="G23" s="39" t="n">
         <f aca="false">G19-G22</f>
@@ -4467,119 +4572,119 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B24" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="39" t="n">
         <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="D24" s="39" t="n">
         <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="E24" s="39" t="n">
         <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="F24" s="39" t="n">
         <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="G24" s="39" t="n">
         <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B25" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="39" t="n">
         <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$43*C14)</f>
-        <v>7254000</v>
+        <v>17056000</v>
       </c>
       <c r="D25" s="39" t="n">
         <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$43*D14)</f>
-        <v>5979947.06426783</v>
+        <v>14060377.3267373</v>
       </c>
       <c r="E25" s="39" t="n">
         <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$43*E14)</f>
-        <v>4623080.68771307</v>
+        <v>10870039.1797125</v>
       </c>
       <c r="F25" s="39" t="n">
         <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$43*F14)</f>
-        <v>3178017.99668225</v>
+        <v>7472329.05313103</v>
       </c>
       <c r="G25" s="39" t="n">
         <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$43*G14)</f>
-        <v>1639026.23073443</v>
+        <v>3853767.76832181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="37" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B26" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="39" t="n">
         <f aca="false">C14-C24-C25</f>
-        <v>25601550.321856</v>
+        <v>-21900449.678144</v>
       </c>
       <c r="D26" s="39" t="n">
         <f aca="false">D14-D24-D25</f>
-        <v>36444944.2640253</v>
+        <v>-9335485.99844415</v>
       </c>
       <c r="E26" s="39" t="n">
         <f aca="false">E14-E24-E25</f>
-        <v>39058212.8671459</v>
+        <v>-4888745.62485347</v>
       </c>
       <c r="F26" s="39" t="n">
         <f aca="false">F14-F24-F25</f>
-        <v>41852565.9300239</v>
+        <v>-141745.126424866</v>
       </c>
       <c r="G26" s="39" t="n">
         <f aca="false">G14-G24-G25</f>
-        <v>44839938.2145752</v>
+        <v>4925196.67698786</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B27" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="39" t="n">
         <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>2304139.52896704</v>
+        <v>0</v>
       </c>
       <c r="D27" s="39" t="n">
         <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>3280044.98376228</v>
+        <v>0</v>
       </c>
       <c r="E27" s="39" t="n">
         <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>3515239.15804313</v>
+        <v>0</v>
       </c>
       <c r="F27" s="39" t="n">
         <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>3766730.93370215</v>
+        <v>0</v>
       </c>
       <c r="G27" s="39" t="n">
         <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>4035594.43931177</v>
+        <v>443267.700928907</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="37" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B28" s="39" t="n">
         <v>0</v>
@@ -4598,155 +4703,155 @@
       </c>
       <c r="G28" s="39" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>13950000</v>
+        <v>32800000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="42" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B29" s="43" t="n">
         <f aca="false">-B18</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="C29" s="43" t="n">
         <f aca="false">C14-C20-C27+C28</f>
-        <v>31596596.3970094</v>
+        <v>-2386952.34372452</v>
       </c>
       <c r="D29" s="43" t="n">
         <f aca="false">D14-D20-D27+D28</f>
-        <v>40190031.9486513</v>
+        <v>7182388.6627126</v>
       </c>
       <c r="E29" s="43" t="n">
         <f aca="false">E14-E20-E27+E28</f>
-        <v>41211240.0009363</v>
+        <v>8438790.88927846</v>
       </c>
       <c r="F29" s="43" t="n">
         <f aca="false">F14-F20-F27+F28</f>
-        <v>42309038.5971245</v>
+        <v>9788081.26112565</v>
       </c>
       <c r="G29" s="43" t="n">
         <f aca="false">G14-G20-G27+G28</f>
-        <v>57438555.6101184</v>
+        <v>43593194.0788002</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="37" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B30" s="39" t="n">
         <f aca="false">B29</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="C30" s="39" t="n">
         <f aca="false">B30+C29</f>
-        <v>3696596.39700945</v>
+        <v>-67986952.3437245</v>
       </c>
       <c r="D30" s="39" t="n">
         <f aca="false">C30+D29</f>
-        <v>43886628.3456608</v>
+        <v>-60804563.6810119</v>
       </c>
       <c r="E30" s="39" t="n">
         <f aca="false">D30+E29</f>
-        <v>85097868.3465971</v>
+        <v>-52365772.7917335</v>
       </c>
       <c r="F30" s="39" t="n">
         <f aca="false">E30+F29</f>
-        <v>127406906.943722</v>
+        <v>-42577691.5306078</v>
       </c>
       <c r="G30" s="39" t="n">
         <f aca="false">F30+G29</f>
-        <v>184845462.55384</v>
+        <v>1015502.54819243</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="37" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B31" s="44" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="44" t="n">
         <f aca="false">IF(C20=0,"",C14/C20)</f>
-        <v>2.26237088911618</v>
+        <v>0.962197375096669</v>
       </c>
       <c r="D31" s="44" t="n">
         <f aca="false">IF(D20=0,"",D14/D20)</f>
-        <v>2.61870703299604</v>
+        <v>1.11374887531387</v>
       </c>
       <c r="E31" s="44" t="n">
         <f aca="false">IF(E20=0,"",E14/E20)</f>
-        <v>2.6654920231302</v>
+        <v>1.13364675983739</v>
       </c>
       <c r="F31" s="44" t="n">
         <f aca="false">IF(F20=0,"",F14/F20)</f>
-        <v>2.71573591429834</v>
+        <v>1.15501573184335</v>
       </c>
       <c r="G31" s="44" t="n">
         <f aca="false">IF(G20=0,"",G14/G20)</f>
-        <v>2.76966965210983</v>
+        <v>1.17795401362598</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="37" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B32" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="39" t="n">
         <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>2956999.52896704</v>
+        <v>0</v>
       </c>
       <c r="D32" s="39" t="n">
         <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>3818240.21954638</v>
+        <v>425240.21954638</v>
       </c>
       <c r="E32" s="39" t="n">
         <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>3931316.41993731</v>
+        <v>538316.419937308</v>
       </c>
       <c r="F32" s="39" t="n">
         <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>4052752.55340355</v>
+        <v>659752.553403555</v>
       </c>
       <c r="G32" s="39" t="n">
         <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>4183106.80007787</v>
+        <v>790106.80007787</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="37" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B33" s="39" t="n">
         <f aca="false">-B16</f>
-        <v>-139500000</v>
+        <v>-328000000</v>
       </c>
       <c r="C33" s="39" t="n">
         <f aca="false">C14-C32+C28</f>
-        <v>57798550.792889</v>
+        <v>60755550.321856</v>
       </c>
       <c r="D33" s="39" t="n">
         <f aca="false">D14-D32+D28</f>
-        <v>66506651.1087467</v>
+        <v>69899651.1087467</v>
       </c>
       <c r="E33" s="39" t="n">
         <f aca="false">E14-E32+E28</f>
-        <v>67649977.1349217</v>
+        <v>71042977.1349217</v>
       </c>
       <c r="F33" s="39" t="n">
         <f aca="false">F14-F32+F28</f>
-        <v>68877831.3733026</v>
+        <v>72270831.3733026</v>
       </c>
       <c r="G33" s="39" t="n">
         <f aca="false">G14-G32+G28</f>
-        <v>84145857.6452318</v>
+        <v>106388857.645232</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="45" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4755,7 +4860,7 @@
       </c>
       <c r="B36" s="46" t="n">
         <f aca="false">IRR(B29:G29)</f>
-        <v>1.26506825092475</v>
+        <v>0.00348283951629262</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4764,7 +4869,7 @@
       </c>
       <c r="B37" s="46" t="n">
         <f aca="false">IRR(B33:G33)</f>
-        <v>0.37548919844065</v>
+        <v>0.0473981776304923</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4773,16 +4878,16 @@
       </c>
       <c r="B38" s="47" t="n">
         <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$44,C29:G29)</f>
-        <v>109809242.3148</v>
+        <v>-29426161.8959998</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B39" s="48" t="n">
         <f aca="false">SUM(C29:G29)/-B29</f>
-        <v>7.62528539619498</v>
+        <v>1.01548022177123</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4791,7 +4896,7 @@
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(COUNTIF(B30:G30,"&lt;0")-1+ABS(INDEX(B30:G30,COUNTIF(B30:G30,"&lt;0")))/INDEX(B29:G29,COUNTIF(B30:G30,"&lt;0")+1),"&gt;5 yrs")</f>
-        <v>0.8830065001128</v>
+        <v>4.97670502082603</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4800,16 +4905,16 @@
       </c>
       <c r="B41" s="48" t="n">
         <f aca="false">MIN(C31:G31)</f>
-        <v>2.26237088911618</v>
+        <v>0.962197375096669</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B42" s="48" t="n">
         <f aca="false">AVERAGE(C31:G31)</f>
-        <v>2.60639510233012</v>
+        <v>1.10851255114345</v>
       </c>
     </row>
   </sheetData>
@@ -4839,12 +4944,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4858,7 +4963,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,37 +4978,37 @@
         <v>31</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B6" s="34" t="n">
         <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$30</f>
         <v>20082124.8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">B6*'Control Panel &amp; Inputs'!$C$29</f>
         <v>17069806.08</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4918,12 +5023,12 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B9" s="50" t="n">
         <f aca="false">'Pro Forma Financials'!D$13/B7</f>
@@ -4933,12 +5038,12 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B10" s="50" t="n">
         <f aca="false">B8-B9</f>
@@ -4948,7 +5053,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4957,63 +5062,63 @@
       </c>
       <c r="B11" s="51" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35/B5</f>
-        <v>60546.875</v>
+        <v>142361.111111111</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B12" s="51" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>16880445.3049371</v>
+        <v>39690222.6524685</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B13" s="51" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>10355154.8886738</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B14" s="33" t="n">
         <f aca="false">B5*'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*3600*8760*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30/1000000000000</f>
         <v>33.18370301952</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B15" s="50" t="n">
         <f aca="false">'Pro Forma Financials'!D$7/(B14*1000000)</f>
@@ -5023,7 +5128,7 @@
         <v>38</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5038,7 +5143,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5053,12 +5158,12 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B18" s="52" t="n">
         <f aca="false">('Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12)/'Pro Forma Financials'!D$10</f>
@@ -5068,37 +5173,37 @@
         <v>41</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B19" s="51" t="n">
         <f aca="false">'Pro Forma Financials'!D$20+'Pro Forma Financials'!D$13</f>
-        <v>42104923.0675864</v>
+        <v>78392611.3372874</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>149</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B20" s="36" t="n">
         <f aca="false">1-B19/'Pro Forma Financials'!D$8</f>
-        <v>0.507976359128409</v>
+        <v>0.0839309221468023</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -5126,61 +5231,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B5" s="53" t="n">
         <v>0.04</v>
@@ -5190,52 +5295,52 @@
       </c>
       <c r="D5" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C5</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="E5" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D5</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="F5" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D5)</f>
-        <v>16784258.9974247</v>
+        <v>39464064.1659878</v>
       </c>
       <c r="G5" s="55" t="n">
         <f aca="false">-$E5</f>
-        <v>-69750000</v>
+        <v>-164000000</v>
       </c>
       <c r="H5" s="55" t="n">
         <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*B23))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>42625789.0311679</v>
+        <v>22613969.3819162</v>
       </c>
       <c r="I5" s="55" t="n">
         <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*C23))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>51286293.0641049</v>
+        <v>32209760.0528743</v>
       </c>
       <c r="J5" s="55" t="n">
         <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*D23))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>52377845.935207</v>
+        <v>33442432.1818188</v>
       </c>
       <c r="K5" s="55" t="n">
         <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*E23))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>53549456.9873979</v>
+        <v>34504206.81576</v>
       </c>
       <c r="L5" s="55" t="n">
         <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*F23))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>68756457.3944767</v>
+        <v>68444231.4374028</v>
       </c>
       <c r="M5" s="56" t="n">
         <f aca="false">IRR(G5:L5)</f>
-        <v>0.643978746381705</v>
+        <v>0.0455581791812502</v>
       </c>
       <c r="N5" s="57" t="n">
         <f aca="false">AVERAGE(B23:F23)/$F5</f>
-        <v>4.25224061963126</v>
+        <v>1.80849867816635</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B6" s="53" t="n">
         <v>0.04</v>
@@ -5245,52 +5350,52 @@
       </c>
       <c r="D6" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C6</f>
-        <v>83700000</v>
+        <v>196800000</v>
       </c>
       <c r="E6" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D6</f>
-        <v>55800000</v>
+        <v>131200000</v>
       </c>
       <c r="F6" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D6)</f>
-        <v>20141110.7969096</v>
+        <v>47356876.9991854</v>
       </c>
       <c r="G6" s="55" t="n">
         <f aca="false">-$E6</f>
-        <v>-55800000</v>
+        <v>-131200000</v>
       </c>
       <c r="H6" s="55" t="n">
         <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*B24))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>39350544.731683</v>
+        <v>14721156.5487186</v>
       </c>
       <c r="I6" s="55" t="n">
         <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*C24))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>47996715.6690929</v>
+        <v>24316947.2196767</v>
       </c>
       <c r="J6" s="55" t="n">
         <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*D24))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>49073003.7934588</v>
+        <v>25600328.1040539</v>
       </c>
       <c r="K6" s="55" t="n">
         <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*E24))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>50228357.8903757</v>
+        <v>26695457.6844102</v>
       </c>
       <c r="L6" s="55" t="n">
         <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*F24))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>65418044.6400875</v>
+        <v>60594773.4915989</v>
       </c>
       <c r="M6" s="56" t="n">
         <f aca="false">IRR(G6:L6)</f>
-        <v>0.762382519931947</v>
+        <v>0.0418311991063475</v>
       </c>
       <c r="N6" s="57" t="n">
         <f aca="false">AVERAGE(B24:F24)/$F6</f>
-        <v>3.54353384969272</v>
+        <v>1.50708223180529</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B7" s="53" t="n">
         <v>0.04</v>
@@ -5300,52 +5405,52 @@
       </c>
       <c r="D7" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C7</f>
-        <v>97650000</v>
+        <v>229600000</v>
       </c>
       <c r="E7" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D7</f>
-        <v>41850000</v>
+        <v>98400000</v>
       </c>
       <c r="F7" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D7)</f>
-        <v>23497962.5963946</v>
+        <v>55249689.832383</v>
       </c>
       <c r="G7" s="55" t="n">
         <f aca="false">-$E7</f>
-        <v>-41850000</v>
+        <v>-98400000</v>
       </c>
       <c r="H7" s="55" t="n">
         <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*B25))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>36075300.4321981</v>
+        <v>6828343.71552104</v>
       </c>
       <c r="I7" s="55" t="n">
         <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*C25))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>44707138.274081</v>
+        <v>16424134.3864791</v>
       </c>
       <c r="J7" s="55" t="n">
         <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*D25))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>45768161.6517106</v>
+        <v>17707515.2708564</v>
       </c>
       <c r="K7" s="55" t="n">
         <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*E25))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>46907258.7933534</v>
+        <v>18886708.5530603</v>
       </c>
       <c r="L7" s="55" t="n">
         <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*F25))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>62079631.8856983</v>
+        <v>52745315.5457949</v>
       </c>
       <c r="M7" s="56" t="n">
         <f aca="false">IRR(G7:L7)</f>
-        <v>0.950597457234898</v>
+        <v>0.036027847120873</v>
       </c>
       <c r="N7" s="57" t="n">
         <f aca="false">AVERAGE(B25:F25)/$F7</f>
-        <v>3.03731472830805</v>
+        <v>1.29178477011882</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B8" s="53" t="n">
         <v>0.04</v>
@@ -5355,52 +5460,52 @@
       </c>
       <c r="D8" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C8</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="E8" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D8</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="F8" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D8)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="G8" s="55" t="n">
         <f aca="false">-$E8</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="H8" s="55" t="n">
         <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*B26))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>32800056.1327131</v>
+        <v>-1064469.11767652</v>
       </c>
       <c r="I8" s="55" t="n">
         <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*C26))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>41417560.8790691</v>
+        <v>8531321.55328157</v>
       </c>
       <c r="J8" s="55" t="n">
         <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*D26))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>42463319.5099624</v>
+        <v>9814702.43765881</v>
       </c>
       <c r="K8" s="55" t="n">
         <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*E26))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>43586159.6963311</v>
+        <v>11077959.4217105</v>
       </c>
       <c r="L8" s="55" t="n">
         <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*F26))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>58741219.1313091</v>
+        <v>44895857.599991</v>
       </c>
       <c r="M8" s="56" t="n">
         <f aca="false">IRR(G8:L8)</f>
-        <v>1.30679835036219</v>
+        <v>0.0261453486370609</v>
       </c>
       <c r="N8" s="57" t="n">
         <f aca="false">AVERAGE(B26:F26)/$F8</f>
-        <v>2.65765038726954</v>
+        <v>1.13031167385397</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B9" s="53" t="n">
         <v>0.06</v>
@@ -5410,52 +5515,52 @@
       </c>
       <c r="D9" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C9</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="E9" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D9</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="F9" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D9)</f>
-        <v>16784258.9974247</v>
+        <v>39464064.1659878</v>
       </c>
       <c r="G9" s="55" t="n">
         <f aca="false">-$E9</f>
-        <v>-69750000</v>
+        <v>-164000000</v>
       </c>
       <c r="H9" s="55" t="n">
         <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*B27))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>41422329.2954643</v>
+        <v>21291486.1558682</v>
       </c>
       <c r="I9" s="55" t="n">
         <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*C27))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>50058764.1336871</v>
+        <v>30860827.1623053</v>
       </c>
       <c r="J9" s="55" t="n">
         <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*D27))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>51125766.4261808</v>
+        <v>32117229.3888712</v>
       </c>
       <c r="K9" s="55" t="n">
         <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*E27))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>52272335.8881913</v>
+        <v>33227085.7165534</v>
       </c>
       <c r="L9" s="55" t="n">
         <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*F27))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>67453793.8732859</v>
+        <v>67141567.9162121</v>
       </c>
       <c r="M9" s="56" t="n">
         <f aca="false">IRR(G9:L9)</f>
-        <v>0.625634391500291</v>
+        <v>0.0346975334245463</v>
       </c>
       <c r="N9" s="57" t="n">
         <f aca="false">AVERAGE(B27:F27)/$F9</f>
-        <v>4.17023216372819</v>
+        <v>1.77362008182952</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B10" s="53" t="n">
         <v>0.06</v>
@@ -5465,52 +5570,52 @@
       </c>
       <c r="D10" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C10</f>
-        <v>83700000</v>
+        <v>196800000</v>
       </c>
       <c r="E10" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D10</f>
-        <v>55800000</v>
+        <v>131200000</v>
       </c>
       <c r="F10" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D10)</f>
-        <v>20141110.7969096</v>
+        <v>47356876.9991854</v>
       </c>
       <c r="G10" s="55" t="n">
         <f aca="false">-$E10</f>
-        <v>-55800000</v>
+        <v>-131200000</v>
       </c>
       <c r="H10" s="55" t="n">
         <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*B28))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>38147084.9959793</v>
+        <v>13398673.3226706</v>
       </c>
       <c r="I10" s="55" t="n">
         <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*C28))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>46769186.7386752</v>
+        <v>22968014.3291077</v>
       </c>
       <c r="J10" s="55" t="n">
         <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*D28))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>47820924.2844327</v>
+        <v>24224416.5556736</v>
       </c>
       <c r="K10" s="55" t="n">
         <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*E28))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>48951236.791169</v>
+        <v>25418336.5852036</v>
       </c>
       <c r="L10" s="55" t="n">
         <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*F28))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>64115381.1188967</v>
+        <v>59292109.9704081</v>
       </c>
       <c r="M10" s="56" t="n">
         <f aca="false">IRR(G10:L10)</f>
-        <v>0.740129255041265</v>
+        <v>0.0285913820637419</v>
       </c>
       <c r="N10" s="57" t="n">
         <f aca="false">AVERAGE(B28:F28)/$F10</f>
-        <v>3.47519346977349</v>
+        <v>1.47801673485793</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B11" s="53" t="n">
         <v>0.06</v>
@@ -5520,52 +5625,52 @@
       </c>
       <c r="D11" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C11</f>
-        <v>97650000</v>
+        <v>229600000</v>
       </c>
       <c r="E11" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D11</f>
-        <v>41850000</v>
+        <v>98400000</v>
       </c>
       <c r="F11" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D11)</f>
-        <v>23497962.5963946</v>
+        <v>55249689.832383</v>
       </c>
       <c r="G11" s="55" t="n">
         <f aca="false">-$E11</f>
-        <v>-41850000</v>
+        <v>-98400000</v>
       </c>
       <c r="H11" s="55" t="n">
         <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*B29))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>34871840.6964944</v>
+        <v>5505860.48947304</v>
       </c>
       <c r="I11" s="55" t="n">
         <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*C29))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>43479609.3436633</v>
+        <v>15075201.4959102</v>
       </c>
       <c r="J11" s="55" t="n">
         <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*D29))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>44516082.1426845</v>
+        <v>16331603.722476</v>
       </c>
       <c r="K11" s="55" t="n">
         <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*E29))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>45630137.6941468</v>
+        <v>17609587.4538537</v>
       </c>
       <c r="L11" s="55" t="n">
         <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*F29))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>60776968.3645076</v>
+        <v>51442652.0246042</v>
       </c>
       <c r="M11" s="56" t="n">
         <f aca="false">IRR(G11:L11)</f>
-        <v>0.921875356077546</v>
+        <v>0.0192983072718694</v>
       </c>
       <c r="N11" s="57" t="n">
         <f aca="false">AVERAGE(B29:F29)/$F11</f>
-        <v>2.97873725980585</v>
+        <v>1.26687148702109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B12" s="53" t="n">
         <v>0.06</v>
@@ -5575,52 +5680,52 @@
       </c>
       <c r="D12" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C12</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="E12" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D12</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="F12" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D12)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="G12" s="55" t="n">
         <f aca="false">-$E12</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="H12" s="55" t="n">
         <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*B30))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>31596596.3970094</v>
+        <v>-2386952.34372452</v>
       </c>
       <c r="I12" s="55" t="n">
         <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*C30))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>40190031.9486513</v>
+        <v>7182388.6627126</v>
       </c>
       <c r="J12" s="55" t="n">
         <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*D30))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>41211240.0009363</v>
+        <v>8438790.88927846</v>
       </c>
       <c r="K12" s="55" t="n">
         <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*E30))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>42309038.5971245</v>
+        <v>9788081.26112565</v>
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*F30))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>57438555.6101184</v>
+        <v>43593194.0788002</v>
       </c>
       <c r="M12" s="56" t="n">
         <f aca="false">IRR(G12:L12)</f>
-        <v>1.26506825092475</v>
+        <v>0.00348283951629246</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">AVERAGE(B30:F30)/$F12</f>
-        <v>2.60639510233012</v>
+        <v>1.10851255114345</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B13" s="53" t="n">
         <v>0.08</v>
@@ -5630,52 +5735,52 @@
       </c>
       <c r="D13" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C13</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="E13" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D13</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="F13" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D13)</f>
-        <v>16784258.9974247</v>
+        <v>39464064.1659878</v>
       </c>
       <c r="G13" s="55" t="n">
         <f aca="false">-$E13</f>
-        <v>-69750000</v>
+        <v>-164000000</v>
       </c>
       <c r="H13" s="55" t="n">
         <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*B31))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>40218869.5597606</v>
+        <v>19969002.9298202</v>
       </c>
       <c r="I13" s="55" t="n">
         <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*C31))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>48831235.2032694</v>
+        <v>29511894.2717363</v>
       </c>
       <c r="J13" s="55" t="n">
         <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*D31))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>49873686.9171547</v>
+        <v>30741317.8404908</v>
       </c>
       <c r="K13" s="55" t="n">
         <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*E31))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>50995214.7889847</v>
+        <v>31949964.6173468</v>
       </c>
       <c r="L13" s="55" t="n">
         <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*F31))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>66151130.3520951</v>
+        <v>65838904.3950213</v>
       </c>
       <c r="M13" s="56" t="n">
         <f aca="false">IRR(G13:L13)</f>
-        <v>0.607230227403353</v>
+        <v>0.0236605946278833</v>
       </c>
       <c r="N13" s="57" t="n">
         <f aca="false">AVERAGE(B31:F31)/$F13</f>
-        <v>4.08822370782512</v>
+        <v>1.7387414854927</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B14" s="53" t="n">
         <v>0.08</v>
@@ -5685,52 +5790,52 @@
       </c>
       <c r="D14" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C14</f>
-        <v>83700000</v>
+        <v>196800000</v>
       </c>
       <c r="E14" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D14</f>
-        <v>55800000</v>
+        <v>131200000</v>
       </c>
       <c r="F14" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D14)</f>
-        <v>20141110.7969096</v>
+        <v>47356876.9991854</v>
       </c>
       <c r="G14" s="55" t="n">
         <f aca="false">-$E14</f>
-        <v>-55800000</v>
+        <v>-131200000</v>
       </c>
       <c r="H14" s="55" t="n">
         <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*B32))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>36943625.2602756</v>
+        <v>12076190.0966226</v>
       </c>
       <c r="I14" s="55" t="n">
         <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*C32))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>45541657.8082574</v>
+        <v>21619081.4385388</v>
       </c>
       <c r="J14" s="55" t="n">
         <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*D32))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>46568844.7754066</v>
+        <v>22848505.0072933</v>
       </c>
       <c r="K14" s="55" t="n">
         <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*E32))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>47674115.6919624</v>
+        <v>24141215.4859969</v>
       </c>
       <c r="L14" s="55" t="n">
         <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*F32))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>62812717.597706</v>
+        <v>57989446.4492174</v>
       </c>
       <c r="M14" s="56" t="n">
         <f aca="false">IRR(G14:L14)</f>
-        <v>0.717819474593702</v>
+        <v>0.015228148095893</v>
       </c>
       <c r="N14" s="57" t="n">
         <f aca="false">AVERAGE(B32:F32)/$F14</f>
-        <v>3.40685308985427</v>
+        <v>1.44895123791058</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B15" s="53" t="n">
         <v>0.08</v>
@@ -5740,52 +5845,52 @@
       </c>
       <c r="D15" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C15</f>
-        <v>97650000</v>
+        <v>229600000</v>
       </c>
       <c r="E15" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D15</f>
-        <v>41850000</v>
+        <v>98400000</v>
       </c>
       <c r="F15" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D15)</f>
-        <v>23497962.5963946</v>
+        <v>55249689.832383</v>
       </c>
       <c r="G15" s="55" t="n">
         <f aca="false">-$E15</f>
-        <v>-41850000</v>
+        <v>-98400000</v>
       </c>
       <c r="H15" s="55" t="n">
         <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*B33))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>33668380.9607907</v>
+        <v>4183377.26342504</v>
       </c>
       <c r="I15" s="55" t="n">
         <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*C33))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>42252080.4132455</v>
+        <v>13726268.6053412</v>
       </c>
       <c r="J15" s="55" t="n">
         <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*D33))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>43264002.6336584</v>
+        <v>14955692.1740957</v>
       </c>
       <c r="K15" s="55" t="n">
         <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*E33))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>44353016.5949401</v>
+        <v>16277464.3149753</v>
       </c>
       <c r="L15" s="55" t="n">
         <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*F33))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>59474304.8433168</v>
+        <v>50139988.5034134</v>
       </c>
       <c r="M15" s="56" t="n">
         <f aca="false">IRR(G15:L15)</f>
-        <v>0.893112538570458</v>
+        <v>0.00226387121737398</v>
       </c>
       <c r="N15" s="57" t="n">
         <f aca="false">AVERAGE(B33:F33)/$F15</f>
-        <v>2.92015979130366</v>
+        <v>1.24195820392335</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B16" s="53" t="n">
         <v>0.08</v>
@@ -5795,52 +5900,52 @@
       </c>
       <c r="D16" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C16</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="E16" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D16</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="F16" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D16)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="G16" s="55" t="n">
         <f aca="false">-$E16</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="H16" s="55" t="n">
         <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*B34))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>30393136.6613058</v>
+        <v>-3709435.56977252</v>
       </c>
       <c r="I16" s="55" t="n">
         <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*C34))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>38962503.0182336</v>
+        <v>5833455.77214364</v>
       </c>
       <c r="J16" s="55" t="n">
         <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*D34))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>39959160.4919102</v>
+        <v>7062879.34089813</v>
       </c>
       <c r="K16" s="55" t="n">
         <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*E34))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>41031917.4979179</v>
+        <v>8384651.48177771</v>
       </c>
       <c r="L16" s="55" t="n">
         <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*F34))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>56135892.0889276</v>
+        <v>42290530.5576095</v>
       </c>
       <c r="M16" s="56" t="n">
         <f aca="false">IRR(G16:L16)</f>
-        <v>1.22335056745985</v>
+        <v>-0.0197751815323907</v>
       </c>
       <c r="N16" s="57" t="n">
         <f aca="false">AVERAGE(B34:F34)/$F16</f>
-        <v>2.5551398173907</v>
+        <v>1.08671342843294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B17" s="53" t="n">
         <v>0.1</v>
@@ -5850,52 +5955,52 @@
       </c>
       <c r="D17" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C17</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="E17" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D17</f>
-        <v>69750000</v>
+        <v>164000000</v>
       </c>
       <c r="F17" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D17)</f>
-        <v>16784258.9974247</v>
+        <v>39464064.1659878</v>
       </c>
       <c r="G17" s="55" t="n">
         <f aca="false">-$E17</f>
-        <v>-69750000</v>
+        <v>-164000000</v>
       </c>
       <c r="H17" s="55" t="n">
         <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*B35))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>39015409.8240569</v>
+        <v>18646519.7037722</v>
       </c>
       <c r="I17" s="55" t="n">
         <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*C35))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>47603706.2728516</v>
+        <v>28162961.3811674</v>
       </c>
       <c r="J17" s="55" t="n">
         <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*D35))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>48621607.4081286</v>
+        <v>29365406.2921105</v>
       </c>
       <c r="K17" s="55" t="n">
         <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*E35))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>49718093.689778</v>
+        <v>30659660.2020225</v>
       </c>
       <c r="L17" s="55" t="n">
         <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*F35))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>64848466.8309044</v>
+        <v>64536240.8738305</v>
       </c>
       <c r="M17" s="56" t="n">
         <f aca="false">IRR(G17:L17)</f>
-        <v>0.588762837234268</v>
+        <v>0.0125042874959422</v>
       </c>
       <c r="N17" s="57" t="n">
         <f aca="false">AVERAGE(B35:F35)/$F17</f>
-        <v>4.00621525192205</v>
+        <v>1.70386288915587</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B18" s="53" t="n">
         <v>0.1</v>
@@ -5905,52 +6010,52 @@
       </c>
       <c r="D18" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C18</f>
-        <v>83700000</v>
+        <v>196800000</v>
       </c>
       <c r="E18" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D18</f>
-        <v>55800000</v>
+        <v>131200000</v>
       </c>
       <c r="F18" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D18)</f>
-        <v>20141110.7969096</v>
+        <v>47356876.9991854</v>
       </c>
       <c r="G18" s="55" t="n">
         <f aca="false">-$E18</f>
-        <v>-55800000</v>
+        <v>-131200000</v>
       </c>
       <c r="H18" s="55" t="n">
         <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*B36))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>35740165.524572</v>
+        <v>10753706.8705746</v>
       </c>
       <c r="I18" s="55" t="n">
         <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*C36))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>44314128.8778397</v>
+        <v>20270148.5479698</v>
       </c>
       <c r="J18" s="55" t="n">
         <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*D36))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>45316765.2663805</v>
+        <v>21472593.4589129</v>
       </c>
       <c r="K18" s="55" t="n">
         <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*E36))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>46396994.5927558</v>
+        <v>22766847.3688249</v>
       </c>
       <c r="L18" s="55" t="n">
         <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*F36))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>61510054.0765152</v>
+        <v>56686782.9280266</v>
       </c>
       <c r="M18" s="56" t="n">
         <f aca="false">IRR(G18:L18)</f>
-        <v>0.695449303949312</v>
+        <v>0.00153624264902171</v>
       </c>
       <c r="N18" s="57" t="n">
         <f aca="false">AVERAGE(B36:F36)/$F18</f>
-        <v>3.33851270993504</v>
+        <v>1.41988574096323</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B19" s="53" t="n">
         <v>0.1</v>
@@ -5960,52 +6065,52 @@
       </c>
       <c r="D19" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C19</f>
-        <v>97650000</v>
+        <v>229600000</v>
       </c>
       <c r="E19" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D19</f>
-        <v>41850000</v>
+        <v>98400000</v>
       </c>
       <c r="F19" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D19)</f>
-        <v>23497962.5963946</v>
+        <v>55249689.832383</v>
       </c>
       <c r="G19" s="55" t="n">
         <f aca="false">-$E19</f>
-        <v>-41850000</v>
+        <v>-98400000</v>
       </c>
       <c r="H19" s="55" t="n">
         <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*B37))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>32464921.225087</v>
+        <v>2860894.03737704</v>
       </c>
       <c r="I19" s="55" t="n">
         <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*C37))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>41024551.4828278</v>
+        <v>12377335.7147722</v>
       </c>
       <c r="J19" s="55" t="n">
         <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*D37))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>42011923.1246323</v>
+        <v>13579780.6257153</v>
       </c>
       <c r="K19" s="55" t="n">
         <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*E37))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>43075895.4957335</v>
+        <v>14874034.5356273</v>
       </c>
       <c r="L19" s="55" t="n">
         <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*F37))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>58171641.322126</v>
+        <v>48837324.9822226</v>
       </c>
       <c r="M19" s="56" t="n">
         <f aca="false">IRR(G19:L19)</f>
-        <v>0.864305027747797</v>
+        <v>-0.0151406941408555</v>
       </c>
       <c r="N19" s="57" t="n">
         <f aca="false">AVERAGE(B37:F37)/$F19</f>
-        <v>2.86158232280146</v>
+        <v>1.21704492082562</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B20" s="53" t="n">
         <v>0.1</v>
@@ -6015,72 +6120,72 @@
       </c>
       <c r="D20" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C20</f>
-        <v>111600000</v>
+        <v>262400000</v>
       </c>
       <c r="E20" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D20</f>
-        <v>27900000</v>
+        <v>65600000</v>
       </c>
       <c r="F20" s="55" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D20)</f>
-        <v>26854814.3958795</v>
+        <v>63142502.6655805</v>
       </c>
       <c r="G20" s="55" t="n">
         <f aca="false">-$E20</f>
-        <v>-27900000</v>
+        <v>-65600000</v>
       </c>
       <c r="H20" s="55" t="n">
         <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*B38))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>29189676.9256021</v>
+        <v>-5031918.79582052</v>
       </c>
       <c r="I20" s="55" t="n">
         <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*C38))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>37734974.0878158</v>
+        <v>4484522.88157468</v>
       </c>
       <c r="J20" s="55" t="n">
         <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*D38))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>38707080.9828841</v>
+        <v>5686967.79251779</v>
       </c>
       <c r="K20" s="55" t="n">
         <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*E38))*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>39754796.3987112</v>
+        <v>6981221.70242975</v>
       </c>
       <c r="L20" s="55" t="n">
         <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*F38))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
-        <v>54833228.5677368</v>
+        <v>40987867.0364187</v>
       </c>
       <c r="M20" s="56" t="n">
         <f aca="false">IRR(G20:L20)</f>
-        <v>1.18164323060214</v>
+        <v>-0.0432695354488995</v>
       </c>
       <c r="N20" s="57" t="n">
         <f aca="false">AVERAGE(B38:F38)/$F20</f>
-        <v>2.50388453245128</v>
+        <v>1.06491430572242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6524,224 +6629,581 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M5</f>
-        <v>0.643978746381705</v>
+        <v>0.0455581791812502</v>
       </c>
       <c r="C6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M6</f>
-        <v>0.762382519931947</v>
+        <v>0.0418311991063475</v>
       </c>
       <c r="D6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M7</f>
-        <v>0.950597457234898</v>
+        <v>0.036027847120873</v>
       </c>
       <c r="E6" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M8</f>
-        <v>1.30679835036219</v>
+        <v>0.0261453486370609</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M9</f>
-        <v>0.625634391500291</v>
+        <v>0.0346975334245463</v>
       </c>
       <c r="C7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M10</f>
-        <v>0.740129255041265</v>
+        <v>0.0285913820637419</v>
       </c>
       <c r="D7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M11</f>
-        <v>0.921875356077546</v>
+        <v>0.0192983072718694</v>
       </c>
       <c r="E7" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M12</f>
-        <v>1.26506825092475</v>
+        <v>0.00348283951629246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M13</f>
-        <v>0.607230227403353</v>
+        <v>0.0236605946278833</v>
       </c>
       <c r="C8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M14</f>
-        <v>0.717819474593702</v>
+        <v>0.015228148095893</v>
       </c>
       <c r="D8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M15</f>
-        <v>0.893112538570458</v>
+        <v>0.00226387121737398</v>
       </c>
       <c r="E8" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M16</f>
-        <v>1.22335056745985</v>
+        <v>-0.0197751815323907</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M17</f>
-        <v>0.588762837234268</v>
+        <v>0.0125042874959422</v>
       </c>
       <c r="C9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M18</f>
-        <v>0.695449303949312</v>
+        <v>0.00153624264902171</v>
       </c>
       <c r="D9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M19</f>
-        <v>0.864305027747797</v>
+        <v>-0.0151406941408555</v>
       </c>
       <c r="E9" s="59" t="n">
         <f aca="false">'Sensitivity Engine'!M20</f>
-        <v>1.18164323060214</v>
+        <v>-0.0432695354488995</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N5</f>
-        <v>4.25224061963126</v>
+        <v>1.80849867816635</v>
       </c>
       <c r="C14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N6</f>
-        <v>3.54353384969272</v>
+        <v>1.50708223180529</v>
       </c>
       <c r="D14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N7</f>
-        <v>3.03731472830805</v>
+        <v>1.29178477011882</v>
       </c>
       <c r="E14" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N8</f>
-        <v>2.65765038726954</v>
+        <v>1.13031167385397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N9</f>
-        <v>4.17023216372819</v>
+        <v>1.77362008182952</v>
       </c>
       <c r="C15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N10</f>
-        <v>3.47519346977349</v>
+        <v>1.47801673485793</v>
       </c>
       <c r="D15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N11</f>
-        <v>2.97873725980585</v>
+        <v>1.26687148702109</v>
       </c>
       <c r="E15" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N12</f>
-        <v>2.60639510233012</v>
+        <v>1.10851255114345</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N13</f>
-        <v>4.08822370782512</v>
+        <v>1.7387414854927</v>
       </c>
       <c r="C16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N14</f>
-        <v>3.40685308985427</v>
+        <v>1.44895123791058</v>
       </c>
       <c r="D16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N15</f>
-        <v>2.92015979130366</v>
+        <v>1.24195820392335</v>
       </c>
       <c r="E16" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N16</f>
-        <v>2.5551398173907</v>
+        <v>1.08671342843294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N17</f>
-        <v>4.00621525192205</v>
+        <v>1.70386288915587</v>
       </c>
       <c r="C17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N18</f>
-        <v>3.33851270993504</v>
+        <v>1.41988574096323</v>
       </c>
       <c r="D17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N19</f>
-        <v>2.86158232280146</v>
+        <v>1.21704492082562</v>
       </c>
       <c r="E17" s="60" t="n">
         <f aca="false">'Sensitivity Engine'!N20</f>
-        <v>2.50388453245128</v>
+        <v>1.06491430572242</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B6" s="41" t="n">
+        <f aca="false">B5</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="41" t="n">
+        <f aca="false">B6+C5</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <f aca="false">C6+D5</f>
+        <v>8</v>
+      </c>
+      <c r="E6" s="41" t="n">
+        <f aca="false">D6+E5</f>
+        <v>12</v>
+      </c>
+      <c r="F6" s="41" t="n">
+        <f aca="false">E6+F5</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B7" s="61" t="n">
+        <f aca="false">B6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>16.528</v>
+      </c>
+      <c r="C7" s="61" t="n">
+        <f aca="false">C6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>33.056</v>
+      </c>
+      <c r="D7" s="61" t="n">
+        <f aca="false">D6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>66.112</v>
+      </c>
+      <c r="E7" s="61" t="n">
+        <f aca="false">E6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>99.168</v>
+      </c>
+      <c r="F7" s="61" t="n">
+        <f aca="false">F6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>132.224</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="41" t="n">
+        <f aca="false">B6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>4608</v>
+      </c>
+      <c r="C8" s="41" t="n">
+        <f aca="false">C6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>9216</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <f aca="false">D6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>18432</v>
+      </c>
+      <c r="E8" s="41" t="n">
+        <f aca="false">E6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>27648</v>
+      </c>
+      <c r="F8" s="41" t="n">
+        <f aca="false">F6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>36864</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B9" s="61" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$49</f>
+        <v>1.8</v>
+      </c>
+      <c r="C9" s="61" t="n">
+        <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$49</f>
+        <v>3.8</v>
+      </c>
+      <c r="D9" s="61" t="n">
+        <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$49</f>
+        <v>7.6</v>
+      </c>
+      <c r="E9" s="61" t="n">
+        <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$49</f>
+        <v>11.6</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$49</f>
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="39" t="n">
+        <f aca="false">B9*'Pro Forma Financials'!D$8</f>
+        <v>154035000</v>
+      </c>
+      <c r="C10" s="39" t="n">
+        <f aca="false">C9*'Pro Forma Financials'!D$8</f>
+        <v>325185000</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <f aca="false">D9*'Pro Forma Financials'!D$8</f>
+        <v>650370000</v>
+      </c>
+      <c r="E10" s="39" t="n">
+        <f aca="false">E9*'Pro Forma Financials'!D$8</f>
+        <v>992670000</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <f aca="false">F9*'Pro Forma Financials'!D$8</f>
+        <v>1334970000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B11" s="39" t="n">
+        <f aca="false">B9*'Pro Forma Financials'!D$14</f>
+        <v>126584804.390928</v>
+      </c>
+      <c r="C11" s="39" t="n">
+        <f aca="false">C9*'Pro Forma Financials'!D$14</f>
+        <v>267234587.047514</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <f aca="false">D9*'Pro Forma Financials'!D$14</f>
+        <v>534469174.095028</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <f aca="false">E9*'Pro Forma Financials'!D$14</f>
+        <v>815768739.4082</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <f aca="false">F9*'Pro Forma Financials'!D$14</f>
+        <v>1097068304.72137</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B12" s="39" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>656000000</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <f aca="false">C5*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>656000000</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <f aca="false">D5*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>1312000000</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <f aca="false">E5*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>1312000000</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <f aca="false">F5*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>1312000000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B13" s="39" t="n">
+        <f aca="false">B11-B12</f>
+        <v>-529415195.609072</v>
+      </c>
+      <c r="C13" s="39" t="n">
+        <f aca="false">C11-C12</f>
+        <v>-388765412.952486</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <f aca="false">D11-D12</f>
+        <v>-777530825.904972</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <f aca="false">E11-E12</f>
+        <v>-496231260.5918</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <f aca="false">F11-F12</f>
+        <v>-214931695.278627</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="39" t="n">
+        <f aca="false">B13</f>
+        <v>-529415195.609072</v>
+      </c>
+      <c r="C14" s="39" t="n">
+        <f aca="false">B14+C13</f>
+        <v>-918180608.561559</v>
+      </c>
+      <c r="D14" s="39" t="n">
+        <f aca="false">C14+D13</f>
+        <v>-1695711434.46653</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <f aca="false">D14+E13</f>
+        <v>-2191942695.05833</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <f aca="false">E14+F13</f>
+        <v>-2406874390.33696</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B17" s="47" t="n">
+        <f aca="false">MIN(B14:F14)</f>
+        <v>-2406874390.33696</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B18" s="62" t="str">
+        <f aca="false">IF(COUNTIF(B14:F14,"&lt;0")=5,"&gt;5",COUNTIF(B14:F14,"&lt;0")+1)</f>
+        <v>&gt;5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B19" s="63" t="n">
+        <f aca="false">F7</f>
+        <v>132.224</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B20" s="62" t="n">
+        <f aca="false">F8</f>
+        <v>36864</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" s="47" t="n">
+        <f aca="false">F6*'Pro Forma Financials'!D$14</f>
+        <v>1125198261.25269</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" s="47" t="n">
+        <f aca="false">SUM(B12:F12)</f>
+        <v>5248000000</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Factory_Model.xlsx
+++ b/AI_Factory_Model.xlsx
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="410">
-  <si>
-    <t xml:space="preserve">AI Factory Dashboard — 32x Vera Rubin NVL72, Abu Dhabi, UAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headline KPIs, all live-linked; edit assumptions on 'Control Panel &amp; Inputs'</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="392">
+  <si>
+    <t xml:space="preserve">All values live-linked; edit assumptions on 'Control Panel &amp; Inputs' and everything on this page recalculates</t>
   </si>
   <si>
     <t xml:space="preserve">KPI</t>
@@ -45,7 +42,10 @@
     <t xml:space="preserve">Unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Sheet</t>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RETURNS &amp; FINANCING</t>
   </si>
   <si>
     <t xml:space="preserve">Equity IRR (levered)</t>
@@ -78,6 +78,12 @@
     <t xml:space="preserve">years</t>
   </si>
   <si>
+    <t xml:space="preserve">Minimum DSCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATIONS &amp; COMPLIANCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Year 1 Gross Revenue</t>
   </si>
   <si>
@@ -87,21 +93,33 @@
     <t xml:space="preserve">Year 1 EBITDA Margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimum DSCR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peak MLC vs ASHRAE 90.4</t>
   </si>
   <si>
-    <t xml:space="preserve">(limit 0.260)</t>
+    <t xml:space="preserve">(design max below)</t>
   </si>
   <si>
     <t xml:space="preserve">Thermal Hydraulics &amp; MLC</t>
   </si>
   <si>
+    <t xml:space="preserve">ASHRAE 90.4 MLC Limit (location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(design max)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Panel &amp; Inputs</t>
+  </si>
+  <si>
     <t xml:space="preserve">MLC Compliance Margin</t>
   </si>
   <si>
+    <t xml:space="preserve">Location / ASHRAE 169 Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUSTAINABILITY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Annual Facility Energy</t>
   </si>
   <si>
@@ -120,6 +138,9 @@
     <t xml:space="preserve">m³/yr</t>
   </si>
   <si>
+    <t xml:space="preserve">UNIT ECONOMICS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total GPU Count</t>
   </si>
   <si>
@@ -156,19 +177,31 @@
     <t xml:space="preserve">$/kWh</t>
   </si>
   <si>
-    <t xml:space="preserve">Location / ASHRAE 169 Zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control Panel &amp; Inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASHRAE 90.4 MLC Limit (location)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(design max)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA Vera Rubin NVL72 AI Factory — Abu Dhabi, UAE</t>
+    <t xml:space="preserve">CAMPUS EXPANSION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Campus IT Capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phased Expansion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Campus GPUs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Campus CapEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Funding Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-Rate Campus EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD/yr</t>
   </si>
   <si>
     <t xml:space="preserve">Master Control Panel — edit only the yellow Value cells; every other sheet recalculates from them</t>
@@ -477,9 +510,6 @@
     <t xml:space="preserve">Fixed_OpEx_Annual</t>
   </si>
   <si>
-    <t xml:space="preserve">USD/yr</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staff, maintenance, insurance, connectivity (Year 1)</t>
   </si>
   <si>
@@ -528,9 +558,6 @@
     <t xml:space="preserve">Token demand growth (partially offsets price decline)</t>
   </si>
   <si>
-    <t xml:space="preserve">Phased Expansion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Expansion_Blocks_Per_Year</t>
   </si>
   <si>
@@ -1095,54 +1122,6 @@
     <t xml:space="preserve">Avg DSCR</t>
   </si>
   <si>
-    <t xml:space="preserve">$0.04/kWh @ 50% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.04/kWh @ 60% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.04/kWh @ 70% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.04/kWh @ 80% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.06/kWh @ 50% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.06/kWh @ 60% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.06/kWh @ 70% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.06/kWh @ 80% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.08/kWh @ 50% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.08/kWh @ 60% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.08/kWh @ 70% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.08/kWh @ 80% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.10/kWh @ 50% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.10/kWh @ 60% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.10/kWh @ 70% debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.10/kWh @ 80% debt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scenario EBITDA Grid (Year 1-5)</t>
   </si>
   <si>
@@ -1173,30 +1152,6 @@
     <t xml:space="preserve">Power Tariff ($/kWh)</t>
   </si>
   <si>
-    <t xml:space="preserve">50% Debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60% Debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70% Debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80% Debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.04 / kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.06 / kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.08 / kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.10 / kWh</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matrix 2: Average Debt Service Coverage Ratio (DSCR)</t>
   </si>
   <si>
@@ -1242,22 +1197,13 @@
     <t xml:space="preserve">Campus KPIs</t>
   </si>
   <si>
-    <t xml:space="preserve">Peak Funding Requirement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campus Cash-Positive Year</t>
   </si>
   <si>
     <t xml:space="preserve">Final Campus IT Capacity (MW)</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Campus GPUs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Run-Rate Campus EBITDA (full blocks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Campus CapEx</t>
   </si>
 </sst>
 </file>
@@ -1271,17 +1217,17 @@
     <numFmt numFmtId="167" formatCode="0.00\x"/>
     <numFmt numFmtId="168" formatCode="0.00&quot; yrs&quot;"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0.000"/>
-    <numFmt numFmtId="173" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="@"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0.000"/>
     <numFmt numFmtId="174" formatCode="#,##0.0"/>
     <numFmt numFmtId="175" formatCode="0.00"/>
     <numFmt numFmtId="176" formatCode="0.00%"/>
     <numFmt numFmtId="177" formatCode="\$#,##0.0000"/>
     <numFmt numFmtId="178" formatCode="0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1307,72 +1253,113 @@
     <font>
       <b val="true"/>
       <sz val="16"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Georgia"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FFC9D7EC"/>
+      <name val="Georgia"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Segoe UI"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF737373"/>
+      <name val="Segoe UI"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF008000"/>
-      <name val="Calibri"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1387,14 +1374,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFFDECEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1462,152 +1461,212 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1615,107 +1674,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1728,11 +1771,38 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDECEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1744,16 +1814,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF878787"/>
+      <rgbColor rgb="FF5B9BD5"/>
+      <rgbColor rgb="FF7030A0"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF5F7FA"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFC9D7EC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1762,10 +1832,10 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF00B0A0"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFDECEA"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1773,22 +1843,596 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFED7D31"/>
+      <rgbColor rgb="FF737373"/>
+      <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Leveraged FCFE by Year (USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1f4e78"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pro Forma Financials'!$B$4:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Year 0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year 1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Year 2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Year 3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Year 4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Year 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pro Forma Financials'!$B$29:$G$29</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>-65600000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2386952.34372452</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7182388.6627126</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8438790.88927846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9788081.26112565</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43593194.0788002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="89999472"/>
+        <c:axId val="43964534"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="89999472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="43964534"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="43964534"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="89999472"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Campus Expansion — Cumulative Funding Position (USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c55a11"/>
+            </a:solidFill>
+            <a:ln w="28080">
+              <a:solidFill>
+                <a:srgbClr val="c55a11"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Phased Expansion'!$B$4:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Year 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Year 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Year 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Year 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Phased Expansion'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-529415195.609072</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-918180608.561559</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1695711434.46653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2191942695.05833</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2406874390.33696</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="14707480"/>
+        <c:axId val="59271816"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="14707480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="59271816"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="59271816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="14707480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>81720</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>70560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="10578960" y="895320"/>
+        <a:ext cx="3815640" cy="2375640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>81720</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>70560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="10578960" y="3581280"/>
+        <a:ext cx="3815640" cy="2375640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1969,370 +2613,532 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1F4E78"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="str">
+        <f aca="false">"AI FACTORY DASHBOARD — "&amp;TEXT('Control Panel &amp; Inputs'!$C$12,"0")&amp;"x VERA RUBIN NVL72 · "&amp;UPPER('Control Panel &amp; Inputs'!$C$5)</f>
+        <v>AI FACTORY DASHBOARD — 32x VERA RUBIN NVL72 · ABU DHABI, UAE</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B6" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!B36</f>
         <v>0.00348283951629262</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B7" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!B37</f>
         <v>0.0473981776304923</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!B38</f>
         <v>-29426161.8959998</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <f aca="false">'Pro Forma Financials'!B39</f>
         <v>1.01548022177123</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <f aca="false">'Pro Forma Financials'!B40</f>
         <v>4.97670502082603</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B11" s="10" t="n">
+        <f aca="false">'Pro Forma Financials'!B41</f>
+        <v>0.962197375096669</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!C$8</f>
         <v>75600000</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="11" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!C$14</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="12" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!C$15</f>
         <v>0.803644845527196</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="13" t="n">
-        <f aca="false">'Pro Forma Financials'!B41</f>
-        <v>0.962197375096669</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="14" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="12" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$23</f>
         <v>0.0778315585672798</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="D16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="12" t="n">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
+        <v>0.26</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="7" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$25</f>
         <v>0.700647851664309</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="15" t="n">
+      <c r="D18" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="13" t="str">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$5&amp;"  (zone "&amp;'Control Panel &amp; Inputs'!$C$6&amp;")"</f>
+        <v>Abu Dhabi, UAE  (zone 1A)</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="14" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28</f>
         <v>66124.1613024</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="15" t="n">
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="14" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$30</f>
         <v>25788.422907936</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="15" t="n">
+      <c r="C22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$29</f>
         <v>9918.62419536</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="15" t="n">
+      <c r="C23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="14" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B5</f>
         <v>2304</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="11" t="n">
+      <c r="C25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="9" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B11</f>
         <v>142361.111111111</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="16" t="n">
+      <c r="C26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="15" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B8</f>
         <v>5.01323797112521</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="16" t="n">
+      <c r="C27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="15" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B16</f>
         <v>0.137869863373019</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="C28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="12" t="n">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="7" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B17</f>
         <v>0.0472894966018917</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="17" t="n">
+      <c r="D29" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="16" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B18</f>
         <v>1.12472791389946</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="18" t="str">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$5&amp;"  (zone "&amp;'Control Panel &amp; Inputs'!$C$6&amp;")"</f>
-        <v>Abu Dhabi, UAE  (zone 1A)</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="14" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
-        <v>0.26</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>43</v>
+      <c r="C30" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <f aca="false">'Phased Expansion'!B19</f>
+        <v>132.224</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="14" t="n">
+        <f aca="false">'Phased Expansion'!B20</f>
+        <v>36864</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="9" t="n">
+        <f aca="false">'Phased Expansion'!B22</f>
+        <v>5248000000</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <f aca="false">'Phased Expansion'!B17</f>
+        <v>-2406874390.33696</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <f aca="false">'Phased Expansion'!B21</f>
+        <v>1125198261.25269</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>'Control Panel &amp; Inputs'!$C$44</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>'Control Panel &amp; Inputs'!$C$7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2340,12 +3146,14 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
@@ -2358,54 +3166,63 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="str">
+        <f aca="false">"NVIDIA VERA RUBIN NVL72 AI FACTORY — "&amp;UPPER($C$5)</f>
+        <v>NVIDIA VERA RUBIN NVL72 AI FACTORY — ABU DHABI, UAE</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>52</v>
+      <c r="A5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>63</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
-        <v>54</v>
+        <v>64</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C6" s="20" t="str">
         <f aca="false">INDEX('ASHRAE Climate Library'!$B$5:$B$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
@@ -2413,823 +3230,827 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>57</v>
+      <c r="A7" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">INDEX('ASHRAE Climate Library'!$C$5:$C$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
         <v>0.26</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>58</v>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">INDEX('ASHRAE Climate Library'!$D$5:$D$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
         <v>50</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="B9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="23" t="n">
         <f aca="false">INDEX('ASHRAE Climate Library'!$E$5:$E$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
         <v>30</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>63</v>
+      <c r="D9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" s="24" t="n">
         <v>0.39</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="A11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="24" t="n">
         <v>0.15</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>69</v>
+      <c r="D11" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="24" t="n">
+        <v>82</v>
+      </c>
+      <c r="C12" s="25" t="n">
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="25" t="n">
+      <c r="A13" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>227</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>76</v>
+      <c r="D13" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="B15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>82</v>
+      <c r="D15" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="25" t="n">
+        <v>94</v>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>100</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>85</v>
+      <c r="A17" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="24" t="n">
+        <v>99</v>
+      </c>
+      <c r="C18" s="25" t="n">
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="25" t="n">
+      <c r="A19" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>91</v>
+      <c r="D19" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="A21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>94</v>
+      <c r="D21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="26" t="n">
+        <v>106</v>
+      </c>
+      <c r="C22" s="27" t="n">
         <v>0.05</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="26" t="n">
+      <c r="A23" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="27" t="n">
         <v>0.28</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>99</v>
+      <c r="D23" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="25" t="n">
+        <v>111</v>
+      </c>
+      <c r="C24" s="26" t="n">
         <v>45</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="25" t="n">
+      <c r="A25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="26" t="n">
         <v>55</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>103</v>
+      <c r="D25" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="27" t="n">
+        <v>115</v>
+      </c>
+      <c r="C26" s="28" t="n">
         <v>3.85</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="27" t="n">
+      <c r="A27" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="28" t="n">
         <v>1.03</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>109</v>
+      <c r="D27" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="23" t="n">
+        <v>121</v>
+      </c>
+      <c r="C28" s="24" t="n">
         <v>1.08</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="26" t="n">
+      <c r="A29" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="27" t="n">
         <v>0.85</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>113</v>
+      <c r="E29" s="18" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="28" t="n">
+        <v>125</v>
+      </c>
+      <c r="C30" s="29" t="n">
         <v>0.995</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="24" t="n">
+      <c r="A31" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>118</v>
+      <c r="D31" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="26" t="n">
+        <v>130</v>
+      </c>
+      <c r="C32" s="27" t="n">
         <v>0.3</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="29" t="n">
+      <c r="A33" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="30" t="n">
         <v>0.06</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>123</v>
+      <c r="D33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" s="26" t="n">
+        <v>135</v>
+      </c>
+      <c r="C34" s="27" t="n">
         <v>0.02</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="30" t="n">
+      <c r="A35" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="31" t="n">
         <v>328000000</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>128</v>
+      <c r="E35" s="18" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C36" s="26" t="n">
+        <v>140</v>
+      </c>
+      <c r="C36" s="27" t="n">
         <v>0.1</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="26" t="n">
+      <c r="A37" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>132</v>
+      <c r="E37" s="18" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="C38" s="27" t="n">
         <v>0.065</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="24" t="n">
+      <c r="A39" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>137</v>
+      <c r="D39" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="24" t="n">
+        <v>149</v>
+      </c>
+      <c r="C40" s="25" t="n">
         <v>5</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="24" t="n">
+      <c r="A41" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>141</v>
+      <c r="D41" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" s="26" t="n">
+        <v>153</v>
+      </c>
+      <c r="C42" s="27" t="n">
         <v>0.09</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C43" s="26" t="n">
+      <c r="A43" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="27" t="n">
         <v>0.3</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>145</v>
+      <c r="E43" s="18" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="26" t="n">
+        <v>157</v>
+      </c>
+      <c r="C44" s="27" t="n">
         <v>0.15</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="30" t="n">
+      <c r="A45" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="31" t="n">
         <v>10877000</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>150</v>
+      <c r="D45" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C46" s="26" t="n">
+        <v>161</v>
+      </c>
+      <c r="C46" s="27" t="n">
         <v>0.03</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C47" s="30" t="n">
+      <c r="A47" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="31" t="n">
         <v>58800000</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>155</v>
+      <c r="D47" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C48" s="30" t="n">
+        <v>166</v>
+      </c>
+      <c r="C48" s="31" t="n">
         <v>25200000</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="26" t="n">
+      <c r="A49" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" s="27" t="n">
         <v>0.9</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>159</v>
+      <c r="E49" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C50" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="C50" s="27" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C51" s="26" t="n">
+      <c r="A51" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" s="27" t="n">
         <v>0.15</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>163</v>
+      <c r="D51" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C52" s="26" t="n">
+        <v>174</v>
+      </c>
+      <c r="C52" s="27" t="n">
         <v>0.25</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>167</v>
+      <c r="A53" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>176</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>171</v>
+      <c r="A55" s="32" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>172</v>
+      <c r="A56" s="32" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>173</v>
+      <c r="A57" s="32" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3243,6 +4064,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFA6A6A6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
@@ -3255,317 +4077,331 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C5" s="31" t="n">
+      <c r="A5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="33" t="n">
         <v>0.26</v>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>183</v>
+      <c r="F5" s="18" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="31" t="n">
+        <v>194</v>
+      </c>
+      <c r="C6" s="35" t="n">
         <v>0.28</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="36" t="n">
         <v>49.5</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="36" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="31" t="n">
+      <c r="A7" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="33" t="n">
         <v>0.28</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="34" t="n">
         <v>49</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>187</v>
+      <c r="F7" s="18" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8" s="31" t="n">
+        <v>198</v>
+      </c>
+      <c r="C8" s="35" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="36" t="n">
         <v>36.5</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="36" t="n">
         <v>29.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="31" t="n">
+      <c r="A9" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="33" t="n">
         <v>0.28</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="34" t="n">
         <v>39.5</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="31" t="n">
+        <v>202</v>
+      </c>
+      <c r="C10" s="35" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="36" t="n">
         <v>48.5</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="36" t="n">
         <v>26.5</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="31" t="n">
+      <c r="A11" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="33" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="34" t="n">
         <v>43.5</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="34" t="n">
         <v>27.5</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="31" t="n">
+        <v>206</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <v>0.19</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="36" t="n">
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="31" t="n">
+      <c r="A13" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="33" t="n">
         <v>0.16</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="34" t="n">
         <v>38.5</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="34" t="n">
         <v>27</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="31" t="n">
+        <v>209</v>
+      </c>
+      <c r="C14" s="35" t="n">
         <v>0.16</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="36" t="n">
         <v>37.5</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="36" t="n">
         <v>23</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="31" t="n">
+      <c r="A15" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="33" t="n">
         <v>0.16</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="31" t="n">
+        <v>209</v>
+      </c>
+      <c r="C16" s="35" t="n">
         <v>0.16</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="36" t="n">
         <v>28.5</v>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" s="36" t="n">
         <v>19.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C17" s="31" t="n">
+      <c r="A17" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="31" t="n">
+        <v>204</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <v>0.21</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="36" t="n">
         <v>37.5</v>
       </c>
-      <c r="E18" s="32" t="n">
+      <c r="E18" s="36" t="n">
         <v>27.5</v>
       </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="31" t="n">
+      <c r="A19" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="33" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="32" t="n">
+      <c r="D19" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="E19" s="34" t="n">
         <v>24.5</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3579,426 +4415,442 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF5B9BD5"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>218</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="33" t="n">
+      <c r="A5" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="37" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$13</f>
         <v>7264</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>214</v>
+      <c r="C5" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="33" t="n">
+        <v>224</v>
+      </c>
+      <c r="B6" s="38" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$15*'Control Panel &amp; Inputs'!$C$16</f>
         <v>600</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="33" t="n">
+      <c r="A7" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="37" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$19</f>
         <v>400</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>218</v>
+      <c r="C7" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="33" t="n">
+        <v>228</v>
+      </c>
+      <c r="B8" s="38" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>8264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="33" t="n">
+      <c r="A9" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="37" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",B7,0)</f>
         <v>7264</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="18" t="s">
         <v>222</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10" s="33" t="n">
+        <v>232</v>
+      </c>
+      <c r="B10" s="38" t="n">
         <f aca="false">B8-B9</f>
         <v>1000</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B11" s="34" t="n">
+      <c r="A11" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="39" t="n">
         <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",'Control Panel &amp; Inputs'!$C$12,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",'Control Panel &amp; Inputs'!$C$15,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",'Control Panel &amp; Inputs'!$C$18,0)</f>
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>226</v>
+      <c r="C11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="33" t="n">
+        <v>236</v>
+      </c>
+      <c r="B12" s="38" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$24</f>
         <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="33" t="n">
+      <c r="A13" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="37" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$25</f>
         <v>55</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>230</v>
+      <c r="C13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="B14" s="38" t="n">
         <f aca="false">B13-B12</f>
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="33" t="n">
+      <c r="A15" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B15" s="37" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
         <v>343.462362879839</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>235</v>
+      <c r="C15" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B16" s="33" t="n">
+        <v>245</v>
+      </c>
+      <c r="B16" s="38" t="n">
         <f aca="false">B9/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
         <v>10990.7956121548</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="33" t="n">
+      <c r="A17" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="37" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
         <v>50</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>239</v>
+      <c r="C17" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="33" t="n">
+        <v>249</v>
+      </c>
+      <c r="B18" s="38" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
         <v>30</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="33" t="n">
+      <c r="A19" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="37" t="n">
         <f aca="false">B13-B17</f>
         <v>5</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>244</v>
+      <c r="C19" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" s="33" t="n">
+        <v>254</v>
+      </c>
+      <c r="B20" s="38" t="n">
         <f aca="false">B9*'Control Panel &amp; Inputs'!$C$22</f>
         <v>363.2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B21" s="33" t="n">
+      <c r="A21" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="37" t="n">
         <f aca="false">B10*'Control Panel &amp; Inputs'!$C$23</f>
         <v>280</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>248</v>
+      <c r="C21" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B22" s="33" t="n">
+        <v>258</v>
+      </c>
+      <c r="B22" s="38" t="n">
         <f aca="false">B20+B21</f>
         <v>643.2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B23" s="35" t="n">
+      <c r="A23" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" s="40" t="n">
         <f aca="false">B22/B8</f>
         <v>0.0778315585672798</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6" t="s">
-        <v>252</v>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="35" t="n">
+        <v>262</v>
+      </c>
+      <c r="B24" s="41" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
         <v>0.26</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B25" s="36" t="n">
+      <c r="A25" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" s="42" t="n">
         <f aca="false">(B24-B23)/B24</f>
         <v>0.700647851664309</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>256</v>
+      <c r="D25" s="18" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="33" t="n">
+        <v>266</v>
+      </c>
+      <c r="B26" s="38" t="n">
         <f aca="false">B8*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30</f>
         <v>6989.278</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B27" s="35" t="n">
+      <c r="A27" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B27" s="40" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$28</f>
         <v>1.08</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6" t="s">
-        <v>260</v>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" s="43" t="n">
         <f aca="false">B26*8760*B27/1000</f>
         <v>66124.1613024</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="34" t="n">
+      <c r="A29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="39" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$11</f>
         <v>9918.62419536</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>262</v>
+      <c r="C29" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" s="43" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$10</f>
         <v>25788.422907936</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4012,6 +4864,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF70AD47"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
@@ -4021,903 +4874,919 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>273</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>265</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="38" t="n">
+      <c r="A5" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="45" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$49</f>
         <v>0.9</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="38" t="n">
+      <c r="F5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="38" t="n">
+      <c r="G5" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="39" t="n">
+      <c r="A6" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="39" t="n">
+      <c r="C6" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,0)*C5</f>
         <v>52920000</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,1)*D5</f>
         <v>58800000</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,2)*E5</f>
         <v>58800000</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,3)*F5</f>
         <v>58800000</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,4)*G5</f>
         <v>58800000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="39" t="n">
+      <c r="A7" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),0)*C5</f>
         <v>22680000</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),1)*D5</f>
         <v>26775000</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),2)*E5</f>
         <v>28448437.5</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),3)*F5</f>
         <v>30226464.84375</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),4)*G5</f>
         <v>32115618.8964844</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="39" t="n">
+      <c r="A8" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="46" t="n">
         <f aca="false">C6+C7</f>
         <v>75600000</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="46" t="n">
         <f aca="false">D6+D7</f>
         <v>85575000</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="46" t="n">
         <f aca="false">E6+E7</f>
         <v>87248437.5</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="46" t="n">
         <f aca="false">F6+F7</f>
         <v>89026464.84375</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">G6+G7</f>
         <v>90915618.8964844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="40" t="n">
+      <c r="A9" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="47" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="47" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>0.0612</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="47" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>0.062424</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="47" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>0.06367248</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="47" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>0.0649459296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="41" t="n">
+      <c r="A10" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="48" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="48" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="48" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="48" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="48" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="39" t="n">
+      <c r="A11" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="46" t="n">
         <f aca="false">C10*C9</f>
         <v>3967449.678144</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="46" t="n">
         <f aca="false">D10*D9</f>
         <v>4046798.67170688</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="46" t="n">
         <f aca="false">E10*E9</f>
         <v>4127734.64514102</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="46" t="n">
         <f aca="false">F10*F9</f>
         <v>4210289.33804384</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">G10*G9</f>
         <v>4294495.12480471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="39" t="n">
+      <c r="A12" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>10877000</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,1)</f>
         <v>11203310</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,2)</f>
         <v>11539409.3</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,3)</f>
         <v>11885591.579</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,4)</f>
         <v>12242159.32637</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="39" t="n">
+      <c r="A13" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="46" t="n">
         <f aca="false">C11+C12</f>
         <v>14844449.678144</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="46" t="n">
         <f aca="false">D11+D12</f>
         <v>15250108.6717069</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="46" t="n">
         <f aca="false">E11+E12</f>
         <v>15667143.945141</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="46" t="n">
         <f aca="false">F11+F12</f>
         <v>16095880.9170438</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">G11+G12</f>
         <v>16536654.4511747</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="B14" s="39" t="n">
+      <c r="A14" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="B14" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="46" t="n">
         <f aca="false">C8-C13</f>
         <v>60755550.321856</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="46" t="n">
         <f aca="false">D8-D13</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="46" t="n">
         <f aca="false">E8-E13</f>
         <v>71581293.554859</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="46" t="n">
         <f aca="false">F8-F13</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="46" t="n">
         <f aca="false">G8-G13</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="B15" s="38" t="n">
+      <c r="A15" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="38" t="n">
+      <c r="C15" s="45" t="n">
         <f aca="false">C14/C8</f>
         <v>0.803644845527196</v>
       </c>
-      <c r="D15" s="38" t="n">
+      <c r="D15" s="45" t="n">
         <f aca="false">D14/D8</f>
         <v>0.821792478273948</v>
       </c>
-      <c r="E15" s="38" t="n">
+      <c r="E15" s="45" t="n">
         <f aca="false">E14/E8</f>
         <v>0.820430664501688</v>
       </c>
-      <c r="F15" s="38" t="n">
+      <c r="F15" s="45" t="n">
         <f aca="false">F14/F8</f>
         <v>0.819201167368673</v>
       </c>
-      <c r="G15" s="38" t="n">
+      <c r="G15" s="45" t="n">
         <f aca="false">G14/G8</f>
         <v>0.818109862178872</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="B16" s="39" t="n">
+      <c r="A16" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35</f>
         <v>328000000</v>
       </c>
-      <c r="C16" s="39" t="n">
+      <c r="C16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="B17" s="39" t="n">
+      <c r="A17" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" s="46" t="n">
         <f aca="false">B16*'Control Panel &amp; Inputs'!$C$37</f>
         <v>262400000</v>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C17" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="39" t="n">
+      <c r="G17" s="46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="B18" s="39" t="n">
+      <c r="A18" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" s="46" t="n">
         <f aca="false">B16-B17</f>
         <v>65600000</v>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C18" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="39" t="n">
+      <c r="G18" s="46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="39" t="n">
+      <c r="A19" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="B19" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="39" t="n">
+      <c r="C19" s="46" t="n">
         <f aca="false">B17</f>
         <v>262400000</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="46" t="n">
         <f aca="false">C23</f>
         <v>216313497.33442</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="46" t="n">
         <f aca="false">D23</f>
         <v>167231371.995576</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="46" t="n">
         <f aca="false">E23</f>
         <v>114958908.509708</v>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="46" t="n">
         <f aca="false">F23</f>
         <v>59288734.8972587</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" s="39" t="n">
+      <c r="A20" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="39" t="n">
+      <c r="C20" s="46" t="n">
         <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="46" t="n">
         <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E20" s="46" t="n">
         <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F20" s="46" t="n">
         <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="46" t="n">
         <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="B21" s="39" t="n">
+      <c r="A21" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="39" t="n">
+      <c r="C21" s="46" t="n">
         <f aca="false">C19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>17056000</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="46" t="n">
         <f aca="false">D19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>14060377.3267373</v>
       </c>
-      <c r="E21" s="39" t="n">
+      <c r="E21" s="46" t="n">
         <f aca="false">E19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>10870039.1797125</v>
       </c>
-      <c r="F21" s="39" t="n">
+      <c r="F21" s="46" t="n">
         <f aca="false">F19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>7472329.05313103</v>
       </c>
-      <c r="G21" s="39" t="n">
+      <c r="G21" s="46" t="n">
         <f aca="false">G19*'Control Panel &amp; Inputs'!$C$38</f>
         <v>3853767.76832181</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="B22" s="39" t="n">
+      <c r="A22" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="39" t="n">
+      <c r="C22" s="46" t="n">
         <f aca="false">C20-C21</f>
         <v>46086502.6655805</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="46" t="n">
         <f aca="false">D20-D21</f>
         <v>49082125.3388433</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="46" t="n">
         <f aca="false">E20-E21</f>
         <v>52272463.4858681</v>
       </c>
-      <c r="F22" s="39" t="n">
+      <c r="F22" s="46" t="n">
         <f aca="false">F20-F21</f>
         <v>55670173.6124495</v>
       </c>
-      <c r="G22" s="39" t="n">
+      <c r="G22" s="46" t="n">
         <f aca="false">G20-G21</f>
         <v>59288734.8972587</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="B23" s="39" t="n">
+      <c r="A23" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="46" t="n">
         <f aca="false">C19-C22</f>
         <v>216313497.33442</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="46" t="n">
         <f aca="false">D19-D22</f>
         <v>167231371.995576</v>
       </c>
-      <c r="E23" s="39" t="n">
+      <c r="E23" s="46" t="n">
         <f aca="false">E19-E22</f>
         <v>114958908.509708</v>
       </c>
-      <c r="F23" s="39" t="n">
+      <c r="F23" s="46" t="n">
         <f aca="false">F19-F22</f>
         <v>59288734.8972587</v>
       </c>
-      <c r="G23" s="39" t="n">
+      <c r="G23" s="46" t="n">
         <f aca="false">G19-G22</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="B24" s="39" t="n">
+      <c r="A24" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="46" t="n">
         <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>65600000</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="46" t="n">
         <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>65600000</v>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E24" s="46" t="n">
         <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>65600000</v>
       </c>
-      <c r="F24" s="39" t="n">
+      <c r="F24" s="46" t="n">
         <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>65600000</v>
       </c>
-      <c r="G24" s="39" t="n">
+      <c r="G24" s="46" t="n">
         <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
         <v>65600000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="B25" s="39" t="n">
+      <c r="A25" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="B25" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="46" t="n">
         <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$43*C14)</f>
         <v>17056000</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="46" t="n">
         <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$43*D14)</f>
         <v>14060377.3267373</v>
       </c>
-      <c r="E25" s="39" t="n">
+      <c r="E25" s="46" t="n">
         <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$43*E14)</f>
         <v>10870039.1797125</v>
       </c>
-      <c r="F25" s="39" t="n">
+      <c r="F25" s="46" t="n">
         <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$43*F14)</f>
         <v>7472329.05313103</v>
       </c>
-      <c r="G25" s="39" t="n">
+      <c r="G25" s="46" t="n">
         <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$43*G14)</f>
         <v>3853767.76832181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="B26" s="39" t="n">
+      <c r="A26" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="B26" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="46" t="n">
         <f aca="false">C14-C24-C25</f>
         <v>-21900449.678144</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="46" t="n">
         <f aca="false">D14-D24-D25</f>
         <v>-9335485.99844415</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="46" t="n">
         <f aca="false">E14-E24-E25</f>
         <v>-4888745.62485347</v>
       </c>
-      <c r="F26" s="39" t="n">
+      <c r="F26" s="46" t="n">
         <f aca="false">F14-F24-F25</f>
         <v>-141745.126424866</v>
       </c>
-      <c r="G26" s="39" t="n">
+      <c r="G26" s="46" t="n">
         <f aca="false">G14-G24-G25</f>
         <v>4925196.67698786</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="B27" s="39" t="n">
+      <c r="A27" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="46" t="n">
         <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>0</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D27" s="46" t="n">
         <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>0</v>
       </c>
-      <c r="E27" s="39" t="n">
+      <c r="E27" s="46" t="n">
         <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>0</v>
       </c>
-      <c r="F27" s="39" t="n">
+      <c r="F27" s="46" t="n">
         <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>0</v>
       </c>
-      <c r="G27" s="39" t="n">
+      <c r="G27" s="46" t="n">
         <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>443267.700928907</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="B28" s="39" t="n">
+      <c r="A28" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="39" t="n">
+      <c r="C28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="39" t="n">
+      <c r="E28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="39" t="n">
+      <c r="F28" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="39" t="n">
+      <c r="G28" s="46" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>32800000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="B29" s="43" t="n">
+      <c r="A29" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" s="50" t="n">
         <f aca="false">-B18</f>
         <v>-65600000</v>
       </c>
-      <c r="C29" s="43" t="n">
+      <c r="C29" s="50" t="n">
         <f aca="false">C14-C20-C27+C28</f>
         <v>-2386952.34372452</v>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="50" t="n">
         <f aca="false">D14-D20-D27+D28</f>
         <v>7182388.6627126</v>
       </c>
-      <c r="E29" s="43" t="n">
+      <c r="E29" s="50" t="n">
         <f aca="false">E14-E20-E27+E28</f>
         <v>8438790.88927846</v>
       </c>
-      <c r="F29" s="43" t="n">
+      <c r="F29" s="50" t="n">
         <f aca="false">F14-F20-F27+F28</f>
         <v>9788081.26112565</v>
       </c>
-      <c r="G29" s="43" t="n">
+      <c r="G29" s="50" t="n">
         <f aca="false">G14-G20-G27+G28</f>
         <v>43593194.0788002</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="B30" s="39" t="n">
+      <c r="A30" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="B30" s="46" t="n">
         <f aca="false">B29</f>
         <v>-65600000</v>
       </c>
-      <c r="C30" s="39" t="n">
+      <c r="C30" s="46" t="n">
         <f aca="false">B30+C29</f>
         <v>-67986952.3437245</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="46" t="n">
         <f aca="false">C30+D29</f>
         <v>-60804563.6810119</v>
       </c>
-      <c r="E30" s="39" t="n">
+      <c r="E30" s="46" t="n">
         <f aca="false">D30+E29</f>
         <v>-52365772.7917335</v>
       </c>
-      <c r="F30" s="39" t="n">
+      <c r="F30" s="46" t="n">
         <f aca="false">E30+F29</f>
         <v>-42577691.5306078</v>
       </c>
-      <c r="G30" s="39" t="n">
+      <c r="G30" s="46" t="n">
         <f aca="false">F30+G29</f>
         <v>1015502.54819243</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="s">
-        <v>299</v>
-      </c>
-      <c r="B31" s="44" t="n">
+      <c r="A31" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="B31" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="44" t="n">
+      <c r="C31" s="51" t="n">
         <f aca="false">IF(C20=0,"",C14/C20)</f>
         <v>0.962197375096669</v>
       </c>
-      <c r="D31" s="44" t="n">
+      <c r="D31" s="51" t="n">
         <f aca="false">IF(D20=0,"",D14/D20)</f>
         <v>1.11374887531387</v>
       </c>
-      <c r="E31" s="44" t="n">
+      <c r="E31" s="51" t="n">
         <f aca="false">IF(E20=0,"",E14/E20)</f>
         <v>1.13364675983739</v>
       </c>
-      <c r="F31" s="44" t="n">
+      <c r="F31" s="51" t="n">
         <f aca="false">IF(F20=0,"",F14/F20)</f>
         <v>1.15501573184335</v>
       </c>
-      <c r="G31" s="44" t="n">
+      <c r="G31" s="51" t="n">
         <f aca="false">IF(G20=0,"",G14/G20)</f>
         <v>1.17795401362598</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="B32" s="39" t="n">
+      <c r="A32" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="B32" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="39" t="n">
+      <c r="C32" s="46" t="n">
         <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>0</v>
       </c>
-      <c r="D32" s="39" t="n">
+      <c r="D32" s="46" t="n">
         <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>425240.21954638</v>
       </c>
-      <c r="E32" s="39" t="n">
+      <c r="E32" s="46" t="n">
         <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>538316.419937308</v>
       </c>
-      <c r="F32" s="39" t="n">
+      <c r="F32" s="46" t="n">
         <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>659752.553403555</v>
       </c>
-      <c r="G32" s="39" t="n">
+      <c r="G32" s="46" t="n">
         <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$42</f>
         <v>790106.80007787</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="B33" s="39" t="n">
+      <c r="A33" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="B33" s="46" t="n">
         <f aca="false">-B16</f>
         <v>-328000000</v>
       </c>
-      <c r="C33" s="39" t="n">
+      <c r="C33" s="46" t="n">
         <f aca="false">C14-C32+C28</f>
         <v>60755550.321856</v>
       </c>
-      <c r="D33" s="39" t="n">
+      <c r="D33" s="46" t="n">
         <f aca="false">D14-D32+D28</f>
         <v>69899651.1087467</v>
       </c>
-      <c r="E33" s="39" t="n">
+      <c r="E33" s="46" t="n">
         <f aca="false">E14-E32+E28</f>
         <v>71042977.1349217</v>
       </c>
-      <c r="F33" s="39" t="n">
+      <c r="F33" s="46" t="n">
         <f aca="false">F14-F32+F28</f>
         <v>72270831.3733026</v>
       </c>
-      <c r="G33" s="39" t="n">
+      <c r="G33" s="46" t="n">
         <f aca="false">G14-G32+G28</f>
         <v>106388857.645232</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="45" t="s">
-        <v>302</v>
+      <c r="A35" s="52" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="46" t="n">
+      <c r="B36" s="54" t="n">
         <f aca="false">IRR(B29:G29)</f>
         <v>0.00348283951629262</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="46" t="n">
+      <c r="B37" s="54" t="n">
         <f aca="false">IRR(B33:G33)</f>
         <v>0.0473981776304923</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="55" t="n">
         <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$44,C29:G29)</f>
         <v>-29426161.8959998</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B39" s="48" t="n">
+      <c r="A39" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="B39" s="56" t="n">
         <f aca="false">SUM(C29:G29)/-B29</f>
         <v>1.01548022177123</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="49" t="n">
+      <c r="B40" s="57" t="n">
         <f aca="false">IFERROR(COUNTIF(B30:G30,"&lt;0")-1+ABS(INDEX(B30:G30,COUNTIF(B30:G30,"&lt;0")))/INDEX(B29:G29,COUNTIF(B30:G30,"&lt;0")+1),"&gt;5 yrs")</f>
         <v>4.97670502082603</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="48" t="n">
+      <c r="A41" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="56" t="n">
         <f aca="false">MIN(C31:G31)</f>
         <v>0.962197375096669</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B42" s="48" t="n">
+      <c r="A42" s="53" t="s">
+        <v>313</v>
+      </c>
+      <c r="B42" s="56" t="n">
         <f aca="false">AVERAGE(C31:G31)</f>
         <v>1.10851255114345</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4931,271 +5800,283 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>314</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>306</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="34" t="n">
+      <c r="A5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="39" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$21</f>
         <v>2304</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>308</v>
+      <c r="C5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B6" s="34" t="n">
+        <v>318</v>
+      </c>
+      <c r="B6" s="43" t="n">
         <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$30</f>
         <v>20082124.8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="34" t="n">
+      <c r="A7" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="39" t="n">
         <f aca="false">B6*'Control Panel &amp; Inputs'!$C$29</f>
         <v>17069806.08</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>313</v>
+      <c r="C7" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="50" t="n">
+        <v>42</v>
+      </c>
+      <c r="B8" s="58" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/B7</f>
         <v>5.01323797112521</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B9" s="50" t="n">
+      <c r="A9" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B9" s="59" t="n">
         <f aca="false">'Pro Forma Financials'!D$13/B7</f>
         <v>0.893396714657164</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>316</v>
+      <c r="C9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="B10" s="50" t="n">
+        <v>326</v>
+      </c>
+      <c r="B10" s="58" t="n">
         <f aca="false">B8-B9</f>
         <v>4.11984125646805</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="51" t="n">
+      <c r="A11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="60" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35/B5</f>
         <v>142361.111111111</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>319</v>
+      <c r="C11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" s="51" t="n">
+        <v>329</v>
+      </c>
+      <c r="B12" s="61" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>39690222.6524685</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="51" t="n">
+      <c r="A13" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="B13" s="60" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>10355154.8886738</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>325</v>
+      <c r="C13" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B14" s="33" t="n">
+        <v>335</v>
+      </c>
+      <c r="B14" s="38" t="n">
         <f aca="false">B5*'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*3600*8760*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30/1000000000000</f>
         <v>33.18370301952</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B15" s="50" t="n">
+      <c r="A15" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="59" t="n">
         <f aca="false">'Pro Forma Financials'!D$7/(B14*1000000)</f>
         <v>0.806871975205717</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>330</v>
+      <c r="C15" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="50" t="n">
+        <v>44</v>
+      </c>
+      <c r="B16" s="58" t="n">
         <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$32/(B14*1000000)</f>
         <v>0.137869863373019</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="36" t="n">
+      <c r="A17" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="42" t="n">
         <f aca="false">'Pro Forma Financials'!D$11/'Pro Forma Financials'!D$8</f>
         <v>0.0472894966018917</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>332</v>
+      <c r="D17" s="18" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="B18" s="52" t="n">
+        <v>342</v>
+      </c>
+      <c r="B18" s="62" t="n">
         <f aca="false">('Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12)/'Pro Forma Financials'!D$10</f>
         <v>1.12472791389946</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B19" s="51" t="n">
+      <c r="A19" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" s="60" t="n">
         <f aca="false">'Pro Forma Financials'!D$20+'Pro Forma Financials'!D$13</f>
         <v>78392611.3372874</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>336</v>
+      <c r="C19" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B20" s="36" t="n">
+        <v>346</v>
+      </c>
+      <c r="B20" s="63" t="n">
         <f aca="false">1-B19/'Pro Forma Financials'!D$8</f>
         <v>0.0839309221468023</v>
       </c>
@@ -5203,10 +6084,14 @@
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5220,6 +6105,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N38"/>
@@ -5229,1382 +6115,1428 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>348</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>340</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" s="53" t="n">
+      <c r="A5" s="6" t="str">
+        <f aca="false">TEXT($B5,"$0.00")&amp;"/kWh @ "&amp;TEXT($C5,"0%")&amp;" debt"</f>
+        <v>$0.04/kWh @ 50% debt</v>
+      </c>
+      <c r="B5" s="64" t="n">
         <v>0.04</v>
       </c>
-      <c r="C5" s="54" t="n">
+      <c r="C5" s="65" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="55" t="n">
+      <c r="D5" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C5</f>
         <v>164000000</v>
       </c>
-      <c r="E5" s="55" t="n">
+      <c r="E5" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D5</f>
         <v>164000000</v>
       </c>
-      <c r="F5" s="55" t="n">
+      <c r="F5" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D5)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G5" s="55" t="n">
+      <c r="G5" s="66" t="n">
         <f aca="false">-$E5</f>
         <v>-164000000</v>
       </c>
-      <c r="H5" s="55" t="n">
+      <c r="H5" s="66" t="n">
         <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*B23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>22613969.3819162</v>
       </c>
-      <c r="I5" s="55" t="n">
+      <c r="I5" s="66" t="n">
         <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*C23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>32209760.0528743</v>
       </c>
-      <c r="J5" s="55" t="n">
+      <c r="J5" s="66" t="n">
         <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*D23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>33442432.1818188</v>
       </c>
-      <c r="K5" s="55" t="n">
+      <c r="K5" s="66" t="n">
         <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*E23))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>34504206.81576</v>
       </c>
-      <c r="L5" s="55" t="n">
+      <c r="L5" s="66" t="n">
         <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*F23))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>68444231.4374028</v>
       </c>
-      <c r="M5" s="56" t="n">
+      <c r="M5" s="67" t="n">
         <f aca="false">IRR(G5:L5)</f>
         <v>0.0455581791812502</v>
       </c>
-      <c r="N5" s="57" t="n">
+      <c r="N5" s="68" t="n">
         <f aca="false">AVERAGE(B23:F23)/$F5</f>
         <v>1.80849867816635</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="B6" s="53" t="n">
+      <c r="A6" s="6" t="str">
+        <f aca="false">TEXT($B6,"$0.00")&amp;"/kWh @ "&amp;TEXT($C6,"0%")&amp;" debt"</f>
+        <v>$0.04/kWh @ 60% debt</v>
+      </c>
+      <c r="B6" s="64" t="n">
         <v>0.04</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C6</f>
         <v>196800000</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D6</f>
         <v>131200000</v>
       </c>
-      <c r="F6" s="55" t="n">
+      <c r="F6" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D6)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G6" s="55" t="n">
+      <c r="G6" s="66" t="n">
         <f aca="false">-$E6</f>
         <v>-131200000</v>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="66" t="n">
         <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*B24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>14721156.5487186</v>
       </c>
-      <c r="I6" s="55" t="n">
+      <c r="I6" s="66" t="n">
         <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*C24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>24316947.2196767</v>
       </c>
-      <c r="J6" s="55" t="n">
+      <c r="J6" s="66" t="n">
         <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*D24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>25600328.1040539</v>
       </c>
-      <c r="K6" s="55" t="n">
+      <c r="K6" s="66" t="n">
         <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*E24))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>26695457.6844102</v>
       </c>
-      <c r="L6" s="55" t="n">
+      <c r="L6" s="66" t="n">
         <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*F24))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>60594773.4915989</v>
       </c>
-      <c r="M6" s="56" t="n">
+      <c r="M6" s="67" t="n">
         <f aca="false">IRR(G6:L6)</f>
         <v>0.0418311991063475</v>
       </c>
-      <c r="N6" s="57" t="n">
+      <c r="N6" s="68" t="n">
         <f aca="false">AVERAGE(B24:F24)/$F6</f>
         <v>1.50708223180529</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B7" s="53" t="n">
+      <c r="A7" s="6" t="str">
+        <f aca="false">TEXT($B7,"$0.00")&amp;"/kWh @ "&amp;TEXT($C7,"0%")&amp;" debt"</f>
+        <v>$0.04/kWh @ 70% debt</v>
+      </c>
+      <c r="B7" s="64" t="n">
         <v>0.04</v>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="65" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C7</f>
         <v>229600000</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D7</f>
         <v>98400000</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D7)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G7" s="55" t="n">
+      <c r="G7" s="66" t="n">
         <f aca="false">-$E7</f>
         <v>-98400000</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="66" t="n">
         <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*B25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>6828343.71552104</v>
       </c>
-      <c r="I7" s="55" t="n">
+      <c r="I7" s="66" t="n">
         <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*C25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>16424134.3864791</v>
       </c>
-      <c r="J7" s="55" t="n">
+      <c r="J7" s="66" t="n">
         <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*D25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>17707515.2708564</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="66" t="n">
         <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*E25))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>18886708.5530603</v>
       </c>
-      <c r="L7" s="55" t="n">
+      <c r="L7" s="66" t="n">
         <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*F25))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>52745315.5457949</v>
       </c>
-      <c r="M7" s="56" t="n">
+      <c r="M7" s="67" t="n">
         <f aca="false">IRR(G7:L7)</f>
         <v>0.036027847120873</v>
       </c>
-      <c r="N7" s="57" t="n">
+      <c r="N7" s="68" t="n">
         <f aca="false">AVERAGE(B25:F25)/$F7</f>
         <v>1.29178477011882</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="B8" s="53" t="n">
+      <c r="A8" s="6" t="str">
+        <f aca="false">TEXT($B8,"$0.00")&amp;"/kWh @ "&amp;TEXT($C8,"0%")&amp;" debt"</f>
+        <v>$0.04/kWh @ 80% debt</v>
+      </c>
+      <c r="B8" s="64" t="n">
         <v>0.04</v>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="65" t="n">
         <v>0.8</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C8</f>
         <v>262400000</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D8</f>
         <v>65600000</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D8)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G8" s="55" t="n">
+      <c r="G8" s="66" t="n">
         <f aca="false">-$E8</f>
         <v>-65600000</v>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="66" t="n">
         <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*B26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>-1064469.11767652</v>
       </c>
-      <c r="I8" s="55" t="n">
+      <c r="I8" s="66" t="n">
         <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*C26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>8531321.55328157</v>
       </c>
-      <c r="J8" s="55" t="n">
+      <c r="J8" s="66" t="n">
         <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*D26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>9814702.43765881</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="66" t="n">
         <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*E26))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>11077959.4217105</v>
       </c>
-      <c r="L8" s="55" t="n">
+      <c r="L8" s="66" t="n">
         <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*F26))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>44895857.599991</v>
       </c>
-      <c r="M8" s="56" t="n">
+      <c r="M8" s="67" t="n">
         <f aca="false">IRR(G8:L8)</f>
         <v>0.0261453486370609</v>
       </c>
-      <c r="N8" s="57" t="n">
+      <c r="N8" s="68" t="n">
         <f aca="false">AVERAGE(B26:F26)/$F8</f>
         <v>1.13031167385397</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="B9" s="53" t="n">
+      <c r="A9" s="6" t="str">
+        <f aca="false">TEXT($B9,"$0.00")&amp;"/kWh @ "&amp;TEXT($C9,"0%")&amp;" debt"</f>
+        <v>$0.06/kWh @ 50% debt</v>
+      </c>
+      <c r="B9" s="64" t="n">
         <v>0.06</v>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="65" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C9</f>
         <v>164000000</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D9</f>
         <v>164000000</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D9)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G9" s="55" t="n">
+      <c r="G9" s="66" t="n">
         <f aca="false">-$E9</f>
         <v>-164000000</v>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="66" t="n">
         <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*B27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>21291486.1558682</v>
       </c>
-      <c r="I9" s="55" t="n">
+      <c r="I9" s="66" t="n">
         <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*C27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>30860827.1623053</v>
       </c>
-      <c r="J9" s="55" t="n">
+      <c r="J9" s="66" t="n">
         <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*D27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>32117229.3888712</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="66" t="n">
         <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*E27))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>33227085.7165534</v>
       </c>
-      <c r="L9" s="55" t="n">
+      <c r="L9" s="66" t="n">
         <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*F27))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>67141567.9162121</v>
       </c>
-      <c r="M9" s="56" t="n">
+      <c r="M9" s="67" t="n">
         <f aca="false">IRR(G9:L9)</f>
         <v>0.0346975334245463</v>
       </c>
-      <c r="N9" s="57" t="n">
+      <c r="N9" s="68" t="n">
         <f aca="false">AVERAGE(B27:F27)/$F9</f>
         <v>1.77362008182952</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B10" s="53" t="n">
+      <c r="A10" s="6" t="str">
+        <f aca="false">TEXT($B10,"$0.00")&amp;"/kWh @ "&amp;TEXT($C10,"0%")&amp;" debt"</f>
+        <v>$0.06/kWh @ 60% debt</v>
+      </c>
+      <c r="B10" s="64" t="n">
         <v>0.06</v>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="55" t="n">
+      <c r="D10" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C10</f>
         <v>196800000</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D10</f>
         <v>131200000</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D10)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G10" s="55" t="n">
+      <c r="G10" s="66" t="n">
         <f aca="false">-$E10</f>
         <v>-131200000</v>
       </c>
-      <c r="H10" s="55" t="n">
+      <c r="H10" s="66" t="n">
         <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*B28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>13398673.3226706</v>
       </c>
-      <c r="I10" s="55" t="n">
+      <c r="I10" s="66" t="n">
         <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*C28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>22968014.3291077</v>
       </c>
-      <c r="J10" s="55" t="n">
+      <c r="J10" s="66" t="n">
         <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*D28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>24224416.5556736</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="66" t="n">
         <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*E28))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>25418336.5852036</v>
       </c>
-      <c r="L10" s="55" t="n">
+      <c r="L10" s="66" t="n">
         <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*F28))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>59292109.9704081</v>
       </c>
-      <c r="M10" s="56" t="n">
+      <c r="M10" s="67" t="n">
         <f aca="false">IRR(G10:L10)</f>
         <v>0.0285913820637419</v>
       </c>
-      <c r="N10" s="57" t="n">
+      <c r="N10" s="68" t="n">
         <f aca="false">AVERAGE(B28:F28)/$F10</f>
         <v>1.47801673485793</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B11" s="53" t="n">
+      <c r="A11" s="6" t="str">
+        <f aca="false">TEXT($B11,"$0.00")&amp;"/kWh @ "&amp;TEXT($C11,"0%")&amp;" debt"</f>
+        <v>$0.06/kWh @ 70% debt</v>
+      </c>
+      <c r="B11" s="64" t="n">
         <v>0.06</v>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="65" t="n">
         <v>0.7</v>
       </c>
-      <c r="D11" s="55" t="n">
+      <c r="D11" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C11</f>
         <v>229600000</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D11</f>
         <v>98400000</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D11)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G11" s="55" t="n">
+      <c r="G11" s="66" t="n">
         <f aca="false">-$E11</f>
         <v>-98400000</v>
       </c>
-      <c r="H11" s="55" t="n">
+      <c r="H11" s="66" t="n">
         <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*B29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>5505860.48947304</v>
       </c>
-      <c r="I11" s="55" t="n">
+      <c r="I11" s="66" t="n">
         <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*C29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>15075201.4959102</v>
       </c>
-      <c r="J11" s="55" t="n">
+      <c r="J11" s="66" t="n">
         <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*D29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>16331603.722476</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="66" t="n">
         <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*E29))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>17609587.4538537</v>
       </c>
-      <c r="L11" s="55" t="n">
+      <c r="L11" s="66" t="n">
         <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*F29))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>51442652.0246042</v>
       </c>
-      <c r="M11" s="56" t="n">
+      <c r="M11" s="67" t="n">
         <f aca="false">IRR(G11:L11)</f>
         <v>0.0192983072718694</v>
       </c>
-      <c r="N11" s="57" t="n">
+      <c r="N11" s="68" t="n">
         <f aca="false">AVERAGE(B29:F29)/$F11</f>
         <v>1.26687148702109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B12" s="53" t="n">
+      <c r="A12" s="6" t="str">
+        <f aca="false">TEXT($B12,"$0.00")&amp;"/kWh @ "&amp;TEXT($C12,"0%")&amp;" debt"</f>
+        <v>$0.06/kWh @ 80% debt</v>
+      </c>
+      <c r="B12" s="64" t="n">
         <v>0.06</v>
       </c>
-      <c r="C12" s="54" t="n">
+      <c r="C12" s="65" t="n">
         <v>0.8</v>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C12</f>
         <v>262400000</v>
       </c>
-      <c r="E12" s="55" t="n">
+      <c r="E12" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D12</f>
         <v>65600000</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D12)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G12" s="55" t="n">
+      <c r="G12" s="66" t="n">
         <f aca="false">-$E12</f>
         <v>-65600000</v>
       </c>
-      <c r="H12" s="55" t="n">
+      <c r="H12" s="66" t="n">
         <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*B30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>-2386952.34372452</v>
       </c>
-      <c r="I12" s="55" t="n">
+      <c r="I12" s="66" t="n">
         <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*C30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>7182388.6627126</v>
       </c>
-      <c r="J12" s="55" t="n">
+      <c r="J12" s="66" t="n">
         <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*D30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>8438790.88927846</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="66" t="n">
         <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*E30))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>9788081.26112565</v>
       </c>
-      <c r="L12" s="55" t="n">
+      <c r="L12" s="66" t="n">
         <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*F30))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>43593194.0788002</v>
       </c>
-      <c r="M12" s="56" t="n">
+      <c r="M12" s="67" t="n">
         <f aca="false">IRR(G12:L12)</f>
         <v>0.00348283951629246</v>
       </c>
-      <c r="N12" s="57" t="n">
+      <c r="N12" s="68" t="n">
         <f aca="false">AVERAGE(B30:F30)/$F12</f>
         <v>1.10851255114345</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B13" s="53" t="n">
+      <c r="A13" s="6" t="str">
+        <f aca="false">TEXT($B13,"$0.00")&amp;"/kWh @ "&amp;TEXT($C13,"0%")&amp;" debt"</f>
+        <v>$0.08/kWh @ 50% debt</v>
+      </c>
+      <c r="B13" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="65" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="55" t="n">
+      <c r="D13" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C13</f>
         <v>164000000</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D13</f>
         <v>164000000</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D13)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G13" s="55" t="n">
+      <c r="G13" s="66" t="n">
         <f aca="false">-$E13</f>
         <v>-164000000</v>
       </c>
-      <c r="H13" s="55" t="n">
+      <c r="H13" s="66" t="n">
         <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*B31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>19969002.9298202</v>
       </c>
-      <c r="I13" s="55" t="n">
+      <c r="I13" s="66" t="n">
         <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*C31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>29511894.2717363</v>
       </c>
-      <c r="J13" s="55" t="n">
+      <c r="J13" s="66" t="n">
         <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*D31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>30741317.8404908</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="66" t="n">
         <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*E31))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>31949964.6173468</v>
       </c>
-      <c r="L13" s="55" t="n">
+      <c r="L13" s="66" t="n">
         <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*F31))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>65838904.3950213</v>
       </c>
-      <c r="M13" s="56" t="n">
+      <c r="M13" s="67" t="n">
         <f aca="false">IRR(G13:L13)</f>
         <v>0.0236605946278833</v>
       </c>
-      <c r="N13" s="57" t="n">
+      <c r="N13" s="68" t="n">
         <f aca="false">AVERAGE(B31:F31)/$F13</f>
         <v>1.7387414854927</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="B14" s="53" t="n">
+      <c r="A14" s="6" t="str">
+        <f aca="false">TEXT($B14,"$0.00")&amp;"/kWh @ "&amp;TEXT($C14,"0%")&amp;" debt"</f>
+        <v>$0.08/kWh @ 60% debt</v>
+      </c>
+      <c r="B14" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D14" s="55" t="n">
+      <c r="D14" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C14</f>
         <v>196800000</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D14</f>
         <v>131200000</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D14)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="66" t="n">
         <f aca="false">-$E14</f>
         <v>-131200000</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="66" t="n">
         <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*B32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>12076190.0966226</v>
       </c>
-      <c r="I14" s="55" t="n">
+      <c r="I14" s="66" t="n">
         <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*C32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>21619081.4385388</v>
       </c>
-      <c r="J14" s="55" t="n">
+      <c r="J14" s="66" t="n">
         <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*D32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>22848505.0072933</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="66" t="n">
         <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*E32))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>24141215.4859969</v>
       </c>
-      <c r="L14" s="55" t="n">
+      <c r="L14" s="66" t="n">
         <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*F32))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>57989446.4492174</v>
       </c>
-      <c r="M14" s="56" t="n">
+      <c r="M14" s="67" t="n">
         <f aca="false">IRR(G14:L14)</f>
         <v>0.015228148095893</v>
       </c>
-      <c r="N14" s="57" t="n">
+      <c r="N14" s="68" t="n">
         <f aca="false">AVERAGE(B32:F32)/$F14</f>
         <v>1.44895123791058</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B15" s="53" t="n">
+      <c r="A15" s="6" t="str">
+        <f aca="false">TEXT($B15,"$0.00")&amp;"/kWh @ "&amp;TEXT($C15,"0%")&amp;" debt"</f>
+        <v>$0.08/kWh @ 70% debt</v>
+      </c>
+      <c r="B15" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="C15" s="54" t="n">
+      <c r="C15" s="65" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C15</f>
         <v>229600000</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D15</f>
         <v>98400000</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D15)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G15" s="55" t="n">
+      <c r="G15" s="66" t="n">
         <f aca="false">-$E15</f>
         <v>-98400000</v>
       </c>
-      <c r="H15" s="55" t="n">
+      <c r="H15" s="66" t="n">
         <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*B33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>4183377.26342504</v>
       </c>
-      <c r="I15" s="55" t="n">
+      <c r="I15" s="66" t="n">
         <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*C33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>13726268.6053412</v>
       </c>
-      <c r="J15" s="55" t="n">
+      <c r="J15" s="66" t="n">
         <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*D33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>14955692.1740957</v>
       </c>
-      <c r="K15" s="55" t="n">
+      <c r="K15" s="66" t="n">
         <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*E33))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>16277464.3149753</v>
       </c>
-      <c r="L15" s="55" t="n">
+      <c r="L15" s="66" t="n">
         <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*F33))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>50139988.5034134</v>
       </c>
-      <c r="M15" s="56" t="n">
+      <c r="M15" s="67" t="n">
         <f aca="false">IRR(G15:L15)</f>
         <v>0.00226387121737398</v>
       </c>
-      <c r="N15" s="57" t="n">
+      <c r="N15" s="68" t="n">
         <f aca="false">AVERAGE(B33:F33)/$F15</f>
         <v>1.24195820392335</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B16" s="53" t="n">
+      <c r="A16" s="6" t="str">
+        <f aca="false">TEXT($B16,"$0.00")&amp;"/kWh @ "&amp;TEXT($C16,"0%")&amp;" debt"</f>
+        <v>$0.08/kWh @ 80% debt</v>
+      </c>
+      <c r="B16" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="C16" s="54" t="n">
+      <c r="C16" s="65" t="n">
         <v>0.8</v>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C16</f>
         <v>262400000</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D16</f>
         <v>65600000</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D16)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G16" s="55" t="n">
+      <c r="G16" s="66" t="n">
         <f aca="false">-$E16</f>
         <v>-65600000</v>
       </c>
-      <c r="H16" s="55" t="n">
+      <c r="H16" s="66" t="n">
         <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*B34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>-3709435.56977252</v>
       </c>
-      <c r="I16" s="55" t="n">
+      <c r="I16" s="66" t="n">
         <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*C34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>5833455.77214364</v>
       </c>
-      <c r="J16" s="55" t="n">
+      <c r="J16" s="66" t="n">
         <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*D34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>7062879.34089813</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="66" t="n">
         <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*E34))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>8384651.48177771</v>
       </c>
-      <c r="L16" s="55" t="n">
+      <c r="L16" s="66" t="n">
         <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*F34))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>42290530.5576095</v>
       </c>
-      <c r="M16" s="56" t="n">
+      <c r="M16" s="67" t="n">
         <f aca="false">IRR(G16:L16)</f>
         <v>-0.0197751815323907</v>
       </c>
-      <c r="N16" s="57" t="n">
+      <c r="N16" s="68" t="n">
         <f aca="false">AVERAGE(B34:F34)/$F16</f>
         <v>1.08671342843294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="B17" s="53" t="n">
+      <c r="A17" s="6" t="str">
+        <f aca="false">TEXT($B17,"$0.00")&amp;"/kWh @ "&amp;TEXT($C17,"0%")&amp;" debt"</f>
+        <v>$0.10/kWh @ 50% debt</v>
+      </c>
+      <c r="B17" s="64" t="n">
         <v>0.1</v>
       </c>
-      <c r="C17" s="54" t="n">
+      <c r="C17" s="65" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" s="55" t="n">
+      <c r="D17" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C17</f>
         <v>164000000</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D17</f>
         <v>164000000</v>
       </c>
-      <c r="F17" s="55" t="n">
+      <c r="F17" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D17)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G17" s="55" t="n">
+      <c r="G17" s="66" t="n">
         <f aca="false">-$E17</f>
         <v>-164000000</v>
       </c>
-      <c r="H17" s="55" t="n">
+      <c r="H17" s="66" t="n">
         <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*B35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>18646519.7037722</v>
       </c>
-      <c r="I17" s="55" t="n">
+      <c r="I17" s="66" t="n">
         <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*C35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>28162961.3811674</v>
       </c>
-      <c r="J17" s="55" t="n">
+      <c r="J17" s="66" t="n">
         <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*D35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>29365406.2921105</v>
       </c>
-      <c r="K17" s="55" t="n">
+      <c r="K17" s="66" t="n">
         <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*E35))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>30659660.2020225</v>
       </c>
-      <c r="L17" s="55" t="n">
+      <c r="L17" s="66" t="n">
         <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*F35))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>64536240.8738305</v>
       </c>
-      <c r="M17" s="56" t="n">
+      <c r="M17" s="67" t="n">
         <f aca="false">IRR(G17:L17)</f>
         <v>0.0125042874959422</v>
       </c>
-      <c r="N17" s="57" t="n">
+      <c r="N17" s="68" t="n">
         <f aca="false">AVERAGE(B35:F35)/$F17</f>
         <v>1.70386288915587</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="B18" s="53" t="n">
+      <c r="A18" s="6" t="str">
+        <f aca="false">TEXT($B18,"$0.00")&amp;"/kWh @ "&amp;TEXT($C18,"0%")&amp;" debt"</f>
+        <v>$0.10/kWh @ 60% debt</v>
+      </c>
+      <c r="B18" s="64" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" s="54" t="n">
+      <c r="C18" s="65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D18" s="55" t="n">
+      <c r="D18" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C18</f>
         <v>196800000</v>
       </c>
-      <c r="E18" s="55" t="n">
+      <c r="E18" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D18</f>
         <v>131200000</v>
       </c>
-      <c r="F18" s="55" t="n">
+      <c r="F18" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D18)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G18" s="55" t="n">
+      <c r="G18" s="66" t="n">
         <f aca="false">-$E18</f>
         <v>-131200000</v>
       </c>
-      <c r="H18" s="55" t="n">
+      <c r="H18" s="66" t="n">
         <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*B36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>10753706.8705746</v>
       </c>
-      <c r="I18" s="55" t="n">
+      <c r="I18" s="66" t="n">
         <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*C36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>20270148.5479698</v>
       </c>
-      <c r="J18" s="55" t="n">
+      <c r="J18" s="66" t="n">
         <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*D36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>21472593.4589129</v>
       </c>
-      <c r="K18" s="55" t="n">
+      <c r="K18" s="66" t="n">
         <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*E36))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>22766847.3688249</v>
       </c>
-      <c r="L18" s="55" t="n">
+      <c r="L18" s="66" t="n">
         <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*F36))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>56686782.9280266</v>
       </c>
-      <c r="M18" s="56" t="n">
+      <c r="M18" s="67" t="n">
         <f aca="false">IRR(G18:L18)</f>
         <v>0.00153624264902171</v>
       </c>
-      <c r="N18" s="57" t="n">
+      <c r="N18" s="68" t="n">
         <f aca="false">AVERAGE(B36:F36)/$F18</f>
         <v>1.41988574096323</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B19" s="53" t="n">
+      <c r="A19" s="6" t="str">
+        <f aca="false">TEXT($B19,"$0.00")&amp;"/kWh @ "&amp;TEXT($C19,"0%")&amp;" debt"</f>
+        <v>$0.10/kWh @ 70% debt</v>
+      </c>
+      <c r="B19" s="64" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="65" t="n">
         <v>0.7</v>
       </c>
-      <c r="D19" s="55" t="n">
+      <c r="D19" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C19</f>
         <v>229600000</v>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D19</f>
         <v>98400000</v>
       </c>
-      <c r="F19" s="55" t="n">
+      <c r="F19" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D19)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G19" s="55" t="n">
+      <c r="G19" s="66" t="n">
         <f aca="false">-$E19</f>
         <v>-98400000</v>
       </c>
-      <c r="H19" s="55" t="n">
+      <c r="H19" s="66" t="n">
         <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*B37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>2860894.03737704</v>
       </c>
-      <c r="I19" s="55" t="n">
+      <c r="I19" s="66" t="n">
         <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*C37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>12377335.7147722</v>
       </c>
-      <c r="J19" s="55" t="n">
+      <c r="J19" s="66" t="n">
         <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*D37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>13579780.6257153</v>
       </c>
-      <c r="K19" s="55" t="n">
+      <c r="K19" s="66" t="n">
         <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*E37))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>14874034.5356273</v>
       </c>
-      <c r="L19" s="55" t="n">
+      <c r="L19" s="66" t="n">
         <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*F37))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>48837324.9822226</v>
       </c>
-      <c r="M19" s="56" t="n">
+      <c r="M19" s="67" t="n">
         <f aca="false">IRR(G19:L19)</f>
         <v>-0.0151406941408555</v>
       </c>
-      <c r="N19" s="57" t="n">
+      <c r="N19" s="68" t="n">
         <f aca="false">AVERAGE(B37:F37)/$F19</f>
         <v>1.21704492082562</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B20" s="53" t="n">
+      <c r="A20" s="6" t="str">
+        <f aca="false">TEXT($B20,"$0.00")&amp;"/kWh @ "&amp;TEXT($C20,"0%")&amp;" debt"</f>
+        <v>$0.10/kWh @ 80% debt</v>
+      </c>
+      <c r="B20" s="64" t="n">
         <v>0.1</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="65" t="n">
         <v>0.8</v>
       </c>
-      <c r="D20" s="55" t="n">
+      <c r="D20" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C20</f>
         <v>262400000</v>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="66" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D20</f>
         <v>65600000</v>
       </c>
-      <c r="F20" s="55" t="n">
+      <c r="F20" s="66" t="n">
         <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D20)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G20" s="55" t="n">
+      <c r="G20" s="66" t="n">
         <f aca="false">-$E20</f>
         <v>-65600000</v>
       </c>
-      <c r="H20" s="55" t="n">
+      <c r="H20" s="66" t="n">
         <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*B38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>-5031918.79582052</v>
       </c>
-      <c r="I20" s="55" t="n">
+      <c r="I20" s="66" t="n">
         <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*C38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>4484522.88157468</v>
       </c>
-      <c r="J20" s="55" t="n">
+      <c r="J20" s="66" t="n">
         <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*D38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>5686967.79251779</v>
       </c>
-      <c r="K20" s="55" t="n">
+      <c r="K20" s="66" t="n">
         <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*E38))*'Control Panel &amp; Inputs'!$C$42</f>
         <v>6981221.70242975</v>
       </c>
-      <c r="L20" s="55" t="n">
+      <c r="L20" s="66" t="n">
         <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*F38))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
         <v>40987867.0364187</v>
       </c>
-      <c r="M20" s="56" t="n">
+      <c r="M20" s="67" t="n">
         <f aca="false">IRR(G20:L20)</f>
         <v>-0.0432695354488995</v>
       </c>
-      <c r="N20" s="57" t="n">
+      <c r="N20" s="68" t="n">
         <f aca="false">AVERAGE(B38:F38)/$F20</f>
         <v>1.06491430572242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
-        <v>371</v>
+      <c r="A21" s="52" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="58" t="str">
+      <c r="A23" s="69" t="str">
         <f aca="false">A5</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B23" s="55" t="n">
+      <c r="B23" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C23" s="55" t="n">
+      <c r="C23" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D23" s="55" t="n">
+      <c r="D23" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F23" s="55" t="n">
+      <c r="F23" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="58" t="str">
+      <c r="A24" s="69" t="str">
         <f aca="false">A6</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B24" s="55" t="n">
+      <c r="B24" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C24" s="55" t="n">
+      <c r="C24" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D24" s="55" t="n">
+      <c r="D24" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F24" s="55" t="n">
+      <c r="F24" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="58" t="str">
+      <c r="A25" s="69" t="str">
         <f aca="false">A7</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B25" s="55" t="n">
+      <c r="B25" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D25" s="55" t="n">
+      <c r="D25" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F25" s="55" t="n">
+      <c r="F25" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="58" t="str">
+      <c r="A26" s="69" t="str">
         <f aca="false">A8</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B26" s="55" t="n">
+      <c r="B26" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C26" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D26" s="55" t="n">
+      <c r="D26" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F26" s="55" t="n">
+      <c r="F26" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58" t="str">
+      <c r="A27" s="69" t="str">
         <f aca="false">A9</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B27" s="55" t="n">
+      <c r="B27" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C27" s="55" t="n">
+      <c r="C27" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D27" s="55" t="n">
+      <c r="D27" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F27" s="55" t="n">
+      <c r="F27" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="58" t="str">
+      <c r="A28" s="69" t="str">
         <f aca="false">A10</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B28" s="55" t="n">
+      <c r="B28" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C28" s="55" t="n">
+      <c r="C28" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D28" s="55" t="n">
+      <c r="D28" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E28" s="55" t="n">
+      <c r="E28" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F28" s="55" t="n">
+      <c r="F28" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="58" t="str">
+      <c r="A29" s="69" t="str">
         <f aca="false">A11</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B29" s="55" t="n">
+      <c r="B29" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C29" s="55" t="n">
+      <c r="C29" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D29" s="55" t="n">
+      <c r="D29" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F29" s="55" t="n">
+      <c r="F29" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="58" t="str">
+      <c r="A30" s="69" t="str">
         <f aca="false">A12</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B30" s="55" t="n">
+      <c r="B30" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C30" s="55" t="n">
+      <c r="C30" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D30" s="55" t="n">
+      <c r="D30" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E30" s="55" t="n">
+      <c r="E30" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F30" s="55" t="n">
+      <c r="F30" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="58" t="str">
+      <c r="A31" s="69" t="str">
         <f aca="false">A13</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B31" s="55" t="n">
+      <c r="B31" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C31" s="55" t="n">
+      <c r="C31" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D31" s="55" t="n">
+      <c r="D31" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E31" s="55" t="n">
+      <c r="E31" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F31" s="55" t="n">
+      <c r="F31" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="58" t="str">
+      <c r="A32" s="69" t="str">
         <f aca="false">A14</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B32" s="55" t="n">
+      <c r="B32" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C32" s="55" t="n">
+      <c r="C32" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D32" s="55" t="n">
+      <c r="D32" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E32" s="55" t="n">
+      <c r="E32" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F32" s="55" t="n">
+      <c r="F32" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="58" t="str">
+      <c r="A33" s="69" t="str">
         <f aca="false">A15</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B33" s="55" t="n">
+      <c r="B33" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C33" s="55" t="n">
+      <c r="C33" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D33" s="55" t="n">
+      <c r="D33" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E33" s="55" t="n">
+      <c r="E33" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F33" s="55" t="n">
+      <c r="F33" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="58" t="str">
+      <c r="A34" s="69" t="str">
         <f aca="false">A16</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B34" s="55" t="n">
+      <c r="B34" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C34" s="55" t="n">
+      <c r="C34" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D34" s="55" t="n">
+      <c r="D34" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E34" s="55" t="n">
+      <c r="E34" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F34" s="55" t="n">
+      <c r="F34" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="58" t="str">
+      <c r="A35" s="69" t="str">
         <f aca="false">A17</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B35" s="55" t="n">
+      <c r="B35" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C35" s="55" t="n">
+      <c r="C35" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D35" s="55" t="n">
+      <c r="D35" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E35" s="55" t="n">
+      <c r="E35" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F35" s="55" t="n">
+      <c r="F35" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="58" t="str">
+      <c r="A36" s="69" t="str">
         <f aca="false">A18</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B36" s="55" t="n">
+      <c r="B36" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C36" s="55" t="n">
+      <c r="C36" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D36" s="55" t="n">
+      <c r="D36" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E36" s="55" t="n">
+      <c r="E36" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F36" s="55" t="n">
+      <c r="F36" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="58" t="str">
+      <c r="A37" s="69" t="str">
         <f aca="false">A19</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B37" s="55" t="n">
+      <c r="B37" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C37" s="55" t="n">
+      <c r="C37" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D37" s="55" t="n">
+      <c r="D37" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E37" s="55" t="n">
+      <c r="E37" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F37" s="55" t="n">
+      <c r="F37" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="58" t="str">
+      <c r="A38" s="69" t="str">
         <f aca="false">A20</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B38" s="55" t="n">
+      <c r="B38" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C38" s="55" t="n">
+      <c r="C38" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D38" s="55" t="n">
+      <c r="D38" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E38" s="55" t="n">
+      <c r="E38" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F38" s="55" t="n">
+      <c r="F38" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6618,238 +7550,296 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>370</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>378</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>379</v>
+      <c r="A4" s="52" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
+        <v>50% Debt</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$6,"0%")&amp;" Debt"</f>
+        <v>60% Debt</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$7,"0%")&amp;" Debt"</f>
+        <v>70% Debt</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$8,"0%")&amp;" Debt"</f>
+        <v>80% Debt</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B6" s="59" t="n">
+      <c r="A6" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
+        <v>$0.04 / kWh</v>
+      </c>
+      <c r="B6" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M5</f>
         <v>0.0455581791812502</v>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M6</f>
         <v>0.0418311991063475</v>
       </c>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M7</f>
         <v>0.036027847120873</v>
       </c>
-      <c r="E6" s="59" t="n">
+      <c r="E6" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M8</f>
         <v>0.0261453486370609</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B7" s="59" t="n">
+      <c r="A7" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
+        <v>$0.06 / kWh</v>
+      </c>
+      <c r="B7" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M9</f>
         <v>0.0346975334245463</v>
       </c>
-      <c r="C7" s="59" t="n">
+      <c r="C7" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M10</f>
         <v>0.0285913820637419</v>
       </c>
-      <c r="D7" s="59" t="n">
+      <c r="D7" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M11</f>
         <v>0.0192983072718694</v>
       </c>
-      <c r="E7" s="59" t="n">
+      <c r="E7" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M12</f>
         <v>0.00348283951629246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B8" s="59" t="n">
+      <c r="A8" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
+        <v>$0.08 / kWh</v>
+      </c>
+      <c r="B8" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M13</f>
         <v>0.0236605946278833</v>
       </c>
-      <c r="C8" s="59" t="n">
+      <c r="C8" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M14</f>
         <v>0.015228148095893</v>
       </c>
-      <c r="D8" s="59" t="n">
+      <c r="D8" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M15</f>
         <v>0.00226387121737398</v>
       </c>
-      <c r="E8" s="59" t="n">
+      <c r="E8" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M16</f>
         <v>-0.0197751815323907</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="B9" s="59" t="n">
+      <c r="A9" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
+        <v>$0.10 / kWh</v>
+      </c>
+      <c r="B9" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M17</f>
         <v>0.0125042874959422</v>
       </c>
-      <c r="C9" s="59" t="n">
+      <c r="C9" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M18</f>
         <v>0.00153624264902171</v>
       </c>
-      <c r="D9" s="59" t="n">
+      <c r="D9" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M19</f>
         <v>-0.0151406941408555</v>
       </c>
-      <c r="E9" s="59" t="n">
+      <c r="E9" s="70" t="n">
         <f aca="false">'Sensitivity Engine'!M20</f>
         <v>-0.0432695354488995</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>389</v>
+      <c r="A12" s="52" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
+      </c>
+      <c r="B13" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
+        <v>50% Debt</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$6,"0%")&amp;" Debt"</f>
+        <v>60% Debt</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$7,"0%")&amp;" Debt"</f>
+        <v>70% Debt</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$C$8,"0%")&amp;" Debt"</f>
+        <v>80% Debt</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B14" s="60" t="n">
+      <c r="A14" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
+        <v>$0.04 / kWh</v>
+      </c>
+      <c r="B14" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N5</f>
         <v>1.80849867816635</v>
       </c>
-      <c r="C14" s="60" t="n">
+      <c r="C14" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N6</f>
         <v>1.50708223180529</v>
       </c>
-      <c r="D14" s="60" t="n">
+      <c r="D14" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N7</f>
         <v>1.29178477011882</v>
       </c>
-      <c r="E14" s="60" t="n">
+      <c r="E14" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N8</f>
         <v>1.13031167385397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B15" s="60" t="n">
+      <c r="A15" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
+        <v>$0.06 / kWh</v>
+      </c>
+      <c r="B15" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N9</f>
         <v>1.77362008182952</v>
       </c>
-      <c r="C15" s="60" t="n">
+      <c r="C15" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N10</f>
         <v>1.47801673485793</v>
       </c>
-      <c r="D15" s="60" t="n">
+      <c r="D15" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N11</f>
         <v>1.26687148702109</v>
       </c>
-      <c r="E15" s="60" t="n">
+      <c r="E15" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N12</f>
         <v>1.10851255114345</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B16" s="60" t="n">
+      <c r="A16" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
+        <v>$0.08 / kWh</v>
+      </c>
+      <c r="B16" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N13</f>
         <v>1.7387414854927</v>
       </c>
-      <c r="C16" s="60" t="n">
+      <c r="C16" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N14</f>
         <v>1.44895123791058</v>
       </c>
-      <c r="D16" s="60" t="n">
+      <c r="D16" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N15</f>
         <v>1.24195820392335</v>
       </c>
-      <c r="E16" s="60" t="n">
+      <c r="E16" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N16</f>
         <v>1.08671342843294</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="B17" s="60" t="n">
+      <c r="A17" s="6" t="str">
+        <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
+        <v>$0.10 / kWh</v>
+      </c>
+      <c r="B17" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N17</f>
         <v>1.70386288915587</v>
       </c>
-      <c r="C17" s="60" t="n">
+      <c r="C17" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N18</f>
         <v>1.41988574096323</v>
       </c>
-      <c r="D17" s="60" t="n">
+      <c r="D17" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N19</f>
         <v>1.21704492082562</v>
       </c>
-      <c r="E17" s="60" t="n">
+      <c r="E17" s="71" t="n">
         <f aca="false">'Sensitivity Engine'!N20</f>
         <v>1.06491430572242</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:E9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF9DC3E6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>'Control Panel &amp; Inputs'!$C$44</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:E17">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF9DC3E6"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6863,6 +7853,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF00B0A0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
@@ -6872,341 +7863,355 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>375</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>391</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="B5" s="24" t="n">
+        <v>378</v>
+      </c>
+      <c r="B5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="25" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="B6" s="41" t="n">
+      <c r="A6" s="53" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="48" t="n">
         <f aca="false">B5</f>
         <v>2</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="48" t="n">
         <f aca="false">B6+C5</f>
         <v>4</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="48" t="n">
         <f aca="false">C6+D5</f>
         <v>8</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="48" t="n">
         <f aca="false">D6+E5</f>
         <v>12</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="48" t="n">
         <f aca="false">E6+F5</f>
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="B7" s="61" t="n">
+      <c r="A7" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" s="72" t="n">
         <f aca="false">B6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>16.528</v>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="72" t="n">
         <f aca="false">C6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>33.056</v>
       </c>
-      <c r="D7" s="61" t="n">
+      <c r="D7" s="72" t="n">
         <f aca="false">D6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>66.112</v>
       </c>
-      <c r="E7" s="61" t="n">
+      <c r="E7" s="72" t="n">
         <f aca="false">E6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>99.168</v>
       </c>
-      <c r="F7" s="61" t="n">
+      <c r="F7" s="72" t="n">
         <f aca="false">F6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>132.224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B8" s="41" t="n">
+      <c r="A8" s="53" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="48" t="n">
         <f aca="false">B6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>4608</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="48" t="n">
         <f aca="false">C6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>9216</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="48" t="n">
         <f aca="false">D6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>18432</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="48" t="n">
         <f aca="false">E6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>27648</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="48" t="n">
         <f aca="false">F6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>36864</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="B9" s="61" t="n">
+      <c r="A9" s="53" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="72" t="n">
         <f aca="false">B5*'Control Panel &amp; Inputs'!$C$49</f>
         <v>1.8</v>
       </c>
-      <c r="C9" s="61" t="n">
+      <c r="C9" s="72" t="n">
         <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$49</f>
         <v>3.8</v>
       </c>
-      <c r="D9" s="61" t="n">
+      <c r="D9" s="72" t="n">
         <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$49</f>
         <v>7.6</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="72" t="n">
         <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$49</f>
         <v>11.6</v>
       </c>
-      <c r="F9" s="61" t="n">
+      <c r="F9" s="72" t="n">
         <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$49</f>
         <v>15.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B10" s="39" t="n">
+      <c r="A10" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="B10" s="46" t="n">
         <f aca="false">B9*'Pro Forma Financials'!D$8</f>
         <v>154035000</v>
       </c>
-      <c r="C10" s="39" t="n">
+      <c r="C10" s="46" t="n">
         <f aca="false">C9*'Pro Forma Financials'!D$8</f>
         <v>325185000</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="46" t="n">
         <f aca="false">D9*'Pro Forma Financials'!D$8</f>
         <v>650370000</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="46" t="n">
         <f aca="false">E9*'Pro Forma Financials'!D$8</f>
         <v>992670000</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="46" t="n">
         <f aca="false">F9*'Pro Forma Financials'!D$8</f>
         <v>1334970000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="B11" s="39" t="n">
+      <c r="A11" s="53" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11" s="46" t="n">
         <f aca="false">B9*'Pro Forma Financials'!D$14</f>
         <v>126584804.390928</v>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="46" t="n">
         <f aca="false">C9*'Pro Forma Financials'!D$14</f>
         <v>267234587.047514</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="46" t="n">
         <f aca="false">D9*'Pro Forma Financials'!D$14</f>
         <v>534469174.095028</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="46" t="n">
         <f aca="false">E9*'Pro Forma Financials'!D$14</f>
         <v>815768739.4082</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="46" t="n">
         <f aca="false">F9*'Pro Forma Financials'!D$14</f>
         <v>1097068304.72137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="B12" s="39" t="n">
+      <c r="A12" s="53" t="s">
+        <v>385</v>
+      </c>
+      <c r="B12" s="46" t="n">
         <f aca="false">B5*'Control Panel &amp; Inputs'!$C$35</f>
         <v>656000000</v>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="46" t="n">
         <f aca="false">C5*'Control Panel &amp; Inputs'!$C$35</f>
         <v>656000000</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="46" t="n">
         <f aca="false">D5*'Control Panel &amp; Inputs'!$C$35</f>
         <v>1312000000</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="46" t="n">
         <f aca="false">E5*'Control Panel &amp; Inputs'!$C$35</f>
         <v>1312000000</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="46" t="n">
         <f aca="false">F5*'Control Panel &amp; Inputs'!$C$35</f>
         <v>1312000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="B13" s="39" t="n">
+      <c r="A13" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="B13" s="46" t="n">
         <f aca="false">B11-B12</f>
         <v>-529415195.609072</v>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="46" t="n">
         <f aca="false">C11-C12</f>
         <v>-388765412.952486</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="46" t="n">
         <f aca="false">D11-D12</f>
         <v>-777530825.904972</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="46" t="n">
         <f aca="false">E11-E12</f>
         <v>-496231260.5918</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="46" t="n">
         <f aca="false">F11-F12</f>
         <v>-214931695.278627</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="B14" s="39" t="n">
+      <c r="A14" s="53" t="s">
+        <v>387</v>
+      </c>
+      <c r="B14" s="46" t="n">
         <f aca="false">B13</f>
         <v>-529415195.609072</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="46" t="n">
         <f aca="false">B14+C13</f>
         <v>-918180608.561559</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="46" t="n">
         <f aca="false">C14+D13</f>
         <v>-1695711434.46653</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="46" t="n">
         <f aca="false">D14+E13</f>
         <v>-2191942695.05833</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="46" t="n">
         <f aca="false">E14+F13</f>
         <v>-2406874390.33696</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>403</v>
+      <c r="A16" s="52" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B17" s="47" t="n">
+      <c r="A17" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="55" t="n">
         <f aca="false">MIN(B14:F14)</f>
         <v>-2406874390.33696</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="B18" s="62" t="str">
+      <c r="A18" s="53" t="s">
+        <v>389</v>
+      </c>
+      <c r="B18" s="73" t="str">
         <f aca="false">IF(COUNTIF(B14:F14,"&lt;0")=5,"&gt;5",COUNTIF(B14:F14,"&lt;0")+1)</f>
         <v>&gt;5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="B19" s="63" t="n">
+      <c r="A19" s="53" t="s">
+        <v>390</v>
+      </c>
+      <c r="B19" s="74" t="n">
         <f aca="false">F7</f>
         <v>132.224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="B20" s="62" t="n">
+      <c r="A20" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="73" t="n">
         <f aca="false">F8</f>
         <v>36864</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="B21" s="47" t="n">
+      <c r="A21" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" s="55" t="n">
         <f aca="false">F6*'Pro Forma Financials'!D$14</f>
         <v>1125198261.25269</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="B22" s="47" t="n">
+      <c r="A22" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="55" t="n">
         <f aca="false">SUM(B12:F12)</f>
         <v>5248000000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/AI_Factory_Model.xlsx
+++ b/AI_Factory_Model.xlsx
@@ -10,14 +10,21 @@
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Control Panel &amp; Inputs" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ASHRAE Climate Library" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Thermal Hydraulics &amp; MLC" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Pro Forma Financials" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Unit Economics &amp; KPIs" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sensitivity Engine" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sensitivity Matrices" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Phased Expansion" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Rack Type Library" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ASHRAE Climate Library" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Thermal Hydraulics &amp; MLC" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Pro Forma Financials" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Unit Economics &amp; KPIs" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sensitivity Engine" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sensitivity Matrices" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Phased Expansion" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="LocationList" vbProcedure="false">'ASHRAE Climate Library'!$A$5:$A$19</definedName>
+    <definedName function="false" hidden="false" name="RackTypesCompute" vbProcedure="false">'Rack Type Library'!$A$5:$A$9</definedName>
+    <definedName function="false" hidden="false" name="RackTypesNetwork" vbProcedure="false">'Rack Type Library'!$A$10:$A$11</definedName>
+    <definedName function="false" hidden="false" name="RackTypesStorage" vbProcedure="false">'Rack Type Library'!$A$12:$A$13</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -28,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="429">
   <si>
     <t xml:space="preserve">All values live-linked; edit assumptions on 'Control Panel &amp; Inputs' and everything on this page recalculates</t>
   </si>
@@ -276,307 +283,421 @@
     <t xml:space="preserve">Technical Specs</t>
   </si>
   <si>
+    <t xml:space="preserve">VR_Rack_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vera Rubin NVL72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown from 'Rack Type Library' — sets power, GPUs, TDP, cooling, LPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VR_Rack_Power_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kW/rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from rack type — published/reported rack power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPUs_Per_Rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from rack type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VR_GPU_TDP_W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W/GPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from rack type — per-GPU TDP (reported/est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VR_Cooling_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid/Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VR_LPM_Per_Rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from rack type — required flow at the model's dT</t>
+  </si>
+  <si>
     <t xml:space="preserve">VR_Rack_Count</t>
   </si>
   <si>
     <t xml:space="preserve">racks</t>
   </si>
   <si>
-    <t xml:space="preserve">Vera Rubin NVL72 compute racks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VR_Rack_Power_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kW/rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compute &amp; scale-up busbar load per VR rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VR_Cooling_Type</t>
+    <t xml:space="preserve">Any number of compute racks of the selected type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network_Rack_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum-X800 IB fabric rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown from 'Rack Type Library'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network_Rack_Power_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network_Cooling_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network_Rack_Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any number of network racks of the selected type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage_Rack_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVMe flash storage rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage_Rack_Power_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage_Cooling_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage_Rack_Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any number of storage racks of the selected type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid_Cooling_Overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kW/kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling power per kW of liquid-cooled IT (CDU pumps, dry-cooler fans)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air_Cooling_Overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling power per kW of air-cooled IT (high-ambient chillers, CRAHs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid_Supply_Temp_FWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S45 direct-to-chip loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid_Return_Temp_FWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility water return — sets the loop delta-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolant_Specific_Heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kJ/kg·K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: PG25 water/glycol at ~50°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolant_Density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: PG25 mixture density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target_Annualized_PUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drives facility energy = IT energy x PUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_Utilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: avg power/capacity utilization of the fleet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uptime_Availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: contractual availability SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokens_Per_GPU_Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tok/s/GPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: blended inference throughput per Rubin GPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token_Fleet_Share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of fleet serving the API token market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial &amp; Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity_Tariff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abu Dhabi industrial rate (Year 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff_Escalation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: annual power price escalation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CapEx_Initial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-in benchmark midpoint: ~$91M facility (at $9.9-12.2M/MW) + 32 VR racks at ~$7.4M each (reported $6.0-8.8M). Set to ~$91M if IT is leased/vendor-financed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual_Value_Pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: pre-tax residual recovery of CapEx at end of Year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt_Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User adjustable (50% - 80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior debt facility rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt_Tenor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual amortization schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model_Horizon_Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro forma &amp; sensitivity horizon — STRUCTURAL: regenerate the workbook to change (year columns are created at build time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation_Life_Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-line depreciation life for the CapEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAE_Corporate_Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statutory corporate tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIDLR_EBITDA_Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAE interest deduction limit — applied via MIN() in the tax calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity_Discount_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: hurdle rate for equity NPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed_OpEx_Annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff, maintenance, insurance, connectivity (Year 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpEx_Escalation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: annual fixed-OpEx inflation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lease_Revenue_70pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70% bare-metal capacity leases (Year 1, pre-ramp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token_Revenue_30pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% dynamic API token market (Year 1, pre-ramp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year1_Ramp_Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: Year 1 commissioning / fill-up ramp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lease_Price_Escalation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: lease repricing per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token_Price_Decline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core tokenomics: $/token deflation per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token_Volume_Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token demand growth (partially offsets price decline)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansion_Blocks_Per_Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,2,4,4,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocks/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated blocks added per year (padded/truncated to the horizon); one block = this workbook's full rack architecture. Live numeric cells are on the 'Phased Expansion' sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend: yellow cells with blue text are the editable inputs; all other cells in this workbook are formulas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows marked 'Assumption' are user-supplied estimates, not sourced market data — revisit before investment use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geo_Location must exactly match a row on the 'ASHRAE Climate Library' sheet; the four 'Derived from location' rows update automatically. Cooling types must be 'Liquid' or 'Air'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack Type Library — Published Platform Specifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editable reference data (blue cells): rack power and per-GPU TDP are published/reported figures; 'est.' rows need verification. Required LPM is computed live from the Control Panel's coolant inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPUs / Rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack Power (kW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU TDP (W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required LPM / Rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes / Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compute</t>
   </si>
   <si>
     <t xml:space="preserve">Liquid</t>
   </si>
   <si>
-    <t xml:space="preserve">Liquid/Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S45 direct-to-chip liquid loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network_Rack_Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale-out network fabric racks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network_Rack_Power_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switching + optics load per network rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network_Cooling_Type</t>
+    <t xml:space="preserve">Reported envelope 130-250 kW; 227 kW = Max-P design point; TDP est.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GB300 NVL72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor ~132-142 kW nominal, ~155 kW peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GB200 NVL72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~120 kW nominal; 130-132 kW observed at full load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubin Ultra NVL576 (Kyber)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Announced; reported up to ~1 MW class — estimate, verify before design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HGX H100 air rack (4x 8-GPU)</t>
   </si>
   <si>
     <t xml:space="preserve">Air</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot-aisle containment air cooling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage_Rack_Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVMe object/block storage racks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage_Rack_Power_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load per storage rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage_Cooling_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPUs_Per_Rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVL72 = 72 Rubin GPUs per VR compute rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid_Cooling_Overhead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kW/kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooling power per kW of liquid-cooled IT (CDU pumps, dry-cooler fans)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air_Cooling_Overhead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooling power per kW of air-cooled IT (high-ambient chillers, CRAHs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid_Supply_Temp_FWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S45 direct-to-chip loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid_Return_Temp_FWR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facility water return — sets the loop delta-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coolant_Specific_Heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kJ/kg·K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: PG25 water/glycol at ~50°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coolant_Density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kg/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: PG25 mixture density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target_Annualized_PUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drives facility energy = IT energy x PUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_Utilization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: avg power/capacity utilization of the fleet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uptime_Availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: contractual availability SLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tokens_Per_GPU_Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tok/s/GPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: blended inference throughput per Rubin GPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token_Fleet_Share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of fleet serving the API token market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial &amp; Fiscal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electricity_Tariff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abu Dhabi industrial rate (Year 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff_Escalation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: annual power price escalation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CapEx_Initial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All-in benchmark midpoint: ~$91M facility (at $9.9-12.2M/MW) + 32 VR racks at ~$7.4M each (reported $6.0-8.8M). Set to ~$91M if IT is leased/vendor-financed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual_Value_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: pre-tax residual recovery of CapEx at end of Year 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt_Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User adjustable (50% - 80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest_Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior debt facility rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt_Tenor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual amortization schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model_Horizon_Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro forma &amp; sensitivity horizon — STRUCTURAL: regenerate the workbook to change (year columns are created at build time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depreciation_Life_Years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Straight-line depreciation life for the CapEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAE_Corporate_Tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statutory corporate tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIDLR_EBITDA_Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAE interest deduction limit — applied via MIN() in the tax calc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity_Discount_Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: hurdle rate for equity NPV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed_OpEx_Annual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff, maintenance, insurance, connectivity (Year 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpEx_Escalation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: annual fixed-OpEx inflation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue Strategy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lease_Revenue_70pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70% bare-metal capacity leases (Year 1, pre-ramp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token_Revenue_30pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30% dynamic API token market (Year 1, pre-ramp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year1_Ramp_Factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: Year 1 commissioning / fill-up ramp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lease_Price_Escalation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: lease repricing per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token_Price_Decline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core tokenomics: $/token deflation per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token_Volume_Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token demand growth (partially offsets price decline)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion_Blocks_Per_Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,2,4,4,4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blocks/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comma-separated blocks added per year (padded/truncated to the horizon); one block = this workbook's full rack architecture. Live numeric cells are on the 'Phased Expansion' sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend: yellow cells with blue text are the editable inputs; all other cells in this workbook are formulas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rows marked 'Assumption' are user-supplied estimates, not sourced market data — revisit before investment use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geo_Location must exactly match a row on the 'ASHRAE Climate Library' sheet; the four 'Derived from location' rows update automatically. Cooling types must be 'Liquid' or 'Air'.</t>
+    <t xml:space="preserve">Legacy air-cooled baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale-out leaf/spine block — estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spectrum-X CPO fabric rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-packaged-optics switch rack — estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-performance NVMe tier — estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDD object storage rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulk object tier — estimate</t>
   </si>
   <si>
     <t xml:space="preserve">ASHRAE Climate &amp; 90.4 Compliance Library</t>
@@ -757,9 +878,6 @@
   </si>
   <si>
     <t xml:space="preserve">S45 Liquid Flow Rate per VR Rack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPM</t>
   </si>
   <si>
     <t xml:space="preserve">Physics: Q/(rho*Cp*dT)*60 — flow required to absorb one VR rack</t>
@@ -1461,7 +1579,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1562,15 +1680,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1594,7 +1724,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1602,7 +1732,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1610,11 +1748,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1844,7 +1990,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFC000"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFBF8F00"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF737373"/>
       <rgbColor rgb="FFA6A6A6"/>
@@ -1999,11 +2145,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="89999472"/>
-        <c:axId val="43964534"/>
+        <c:axId val="92385135"/>
+        <c:axId val="47252808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89999472"/>
+        <c:axId val="92385135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2035,7 +2181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43964534"/>
+        <c:crossAx val="47252808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2043,7 +2189,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43964534"/>
+        <c:axId val="47252808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2085,7 +2231,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89999472"/>
+        <c:crossAx val="92385135"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2256,11 +2402,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="14707480"/>
-        <c:axId val="59271816"/>
+        <c:axId val="98561328"/>
+        <c:axId val="49993432"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="14707480"/>
+        <c:axId val="98561328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2292,7 +2438,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59271816"/>
+        <c:crossAx val="49993432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2300,7 +2446,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59271816"/>
+        <c:axId val="49993432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2342,7 +2488,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14707480"/>
+        <c:crossAx val="98561328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2628,7 +2774,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
-        <f aca="false">"AI FACTORY DASHBOARD — "&amp;TEXT('Control Panel &amp; Inputs'!$C$12,"0")&amp;"x VERA RUBIN NVL72 · "&amp;UPPER('Control Panel &amp; Inputs'!$C$5)</f>
+        <f aca="false">"AI FACTORY DASHBOARD — "&amp;TEXT('Control Panel &amp; Inputs'!$C$18,"0")&amp;"x "&amp;UPPER('Control Panel &amp; Inputs'!$C$12)&amp;" · "&amp;UPPER('Control Panel &amp; Inputs'!$C$5)</f>
         <v>AI FACTORY DASHBOARD — 32x VERA RUBIN NVL72 · ABU DHABI, UAE</v>
       </c>
       <c r="B1" s="1"/>
@@ -3126,7 +3272,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>'Control Panel &amp; Inputs'!$C$44</formula>
+      <formula>'Control Panel &amp; Inputs'!$C$49</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
@@ -3150,906 +3296,367 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FF00B0A0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="str">
-        <f aca="false">"NVIDIA VERA RUBIN NVL72 AI FACTORY — "&amp;UPPER($C$5)</f>
-        <v>NVIDIA VERA RUBIN NVL72 AI FACTORY — ABU DHABI, UAE</v>
+      <c r="A1" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>413</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>59</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18" t="s">
-        <v>65</v>
+      <c r="C5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="20" t="str">
-        <f aca="false">INDEX('ASHRAE Climate Library'!$B$5:$B$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
-        <v>1A</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
-        <v>67</v>
+      <c r="A6" s="60" t="s">
+        <v>416</v>
+      </c>
+      <c r="B6" s="55" t="n">
+        <f aca="false">B5</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <f aca="false">B6+C5</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <f aca="false">C6+D5</f>
+        <v>8</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <f aca="false">D6+E5</f>
+        <v>12</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <f aca="false">E6+F5</f>
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <f aca="false">INDEX('ASHRAE Climate Library'!$C$5:$C$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
-        <v>0.26</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
-        <v>69</v>
+      <c r="A7" s="60" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="79" t="n">
+        <f aca="false">B6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>16.528</v>
+      </c>
+      <c r="C7" s="79" t="n">
+        <f aca="false">C6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>33.056</v>
+      </c>
+      <c r="D7" s="79" t="n">
+        <f aca="false">D6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>66.112</v>
+      </c>
+      <c r="E7" s="79" t="n">
+        <f aca="false">E6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>99.168</v>
+      </c>
+      <c r="F7" s="79" t="n">
+        <f aca="false">F6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>132.224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <f aca="false">INDEX('ASHRAE Climate Library'!$D$5:$D$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
-        <v>50</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>72</v>
+      <c r="A8" s="60" t="s">
+        <v>418</v>
+      </c>
+      <c r="B8" s="55" t="n">
+        <f aca="false">B6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>4608</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <f aca="false">C6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>9216</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <f aca="false">D6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>18432</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <f aca="false">E6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>27648</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <f aca="false">F6*'Unit Economics &amp; KPIs'!$B$5</f>
+        <v>36864</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">INDEX('ASHRAE Climate Library'!$E$5:$E$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
-        <v>30</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>74</v>
+      <c r="A9" s="60" t="s">
+        <v>419</v>
+      </c>
+      <c r="B9" s="79" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$54</f>
+        <v>1.8</v>
+      </c>
+      <c r="C9" s="79" t="n">
+        <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$54</f>
+        <v>3.8</v>
+      </c>
+      <c r="D9" s="79" t="n">
+        <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$54</f>
+        <v>7.6</v>
+      </c>
+      <c r="E9" s="79" t="n">
+        <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$54</f>
+        <v>11.6</v>
+      </c>
+      <c r="F9" s="79" t="n">
+        <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$54</f>
+        <v>15.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>77</v>
+      <c r="A10" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="53" t="n">
+        <f aca="false">B9*'Pro Forma Financials'!D$8</f>
+        <v>154035000</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <f aca="false">C9*'Pro Forma Financials'!D$8</f>
+        <v>325185000</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <f aca="false">D9*'Pro Forma Financials'!D$8</f>
+        <v>650370000</v>
+      </c>
+      <c r="E10" s="53" t="n">
+        <f aca="false">E9*'Pro Forma Financials'!D$8</f>
+        <v>992670000</v>
+      </c>
+      <c r="F10" s="53" t="n">
+        <f aca="false">F9*'Pro Forma Financials'!D$8</f>
+        <v>1334970000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>80</v>
+      <c r="A11" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="B11" s="53" t="n">
+        <f aca="false">B9*'Pro Forma Financials'!D$14</f>
+        <v>126584804.390928</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <f aca="false">C9*'Pro Forma Financials'!D$14</f>
+        <v>267234587.047514</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <f aca="false">D9*'Pro Forma Financials'!D$14</f>
+        <v>534469174.095028</v>
+      </c>
+      <c r="E11" s="53" t="n">
+        <f aca="false">E9*'Pro Forma Financials'!D$14</f>
+        <v>815768739.4082</v>
+      </c>
+      <c r="F11" s="53" t="n">
+        <f aca="false">F9*'Pro Forma Financials'!D$14</f>
+        <v>1097068304.72137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>84</v>
+      <c r="A12" s="60" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" s="53" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$40</f>
+        <v>656000000</v>
+      </c>
+      <c r="C12" s="53" t="n">
+        <f aca="false">C5*'Control Panel &amp; Inputs'!$C$40</f>
+        <v>656000000</v>
+      </c>
+      <c r="D12" s="53" t="n">
+        <f aca="false">D5*'Control Panel &amp; Inputs'!$C$40</f>
+        <v>1312000000</v>
+      </c>
+      <c r="E12" s="53" t="n">
+        <f aca="false">E5*'Control Panel &amp; Inputs'!$C$40</f>
+        <v>1312000000</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <f aca="false">F5*'Control Panel &amp; Inputs'!$C$40</f>
+        <v>1312000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>227</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>87</v>
+      <c r="A13" s="60" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="53" t="n">
+        <f aca="false">B11-B12</f>
+        <v>-529415195.609072</v>
+      </c>
+      <c r="C13" s="53" t="n">
+        <f aca="false">C11-C12</f>
+        <v>-388765412.952486</v>
+      </c>
+      <c r="D13" s="53" t="n">
+        <f aca="false">D11-D12</f>
+        <v>-777530825.904972</v>
+      </c>
+      <c r="E13" s="53" t="n">
+        <f aca="false">E11-E12</f>
+        <v>-496231260.5918</v>
+      </c>
+      <c r="F13" s="53" t="n">
+        <f aca="false">F11-F12</f>
+        <v>-214931695.278627</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>93</v>
+      <c r="A14" s="60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B14" s="53" t="n">
+        <f aca="false">B13</f>
+        <v>-529415195.609072</v>
+      </c>
+      <c r="C14" s="53" t="n">
+        <f aca="false">B14+C13</f>
+        <v>-918180608.561559</v>
+      </c>
+      <c r="D14" s="53" t="n">
+        <f aca="false">C14+D13</f>
+        <v>-1695711434.46653</v>
+      </c>
+      <c r="E14" s="53" t="n">
+        <f aca="false">D14+E13</f>
+        <v>-2191942695.05833</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <f aca="false">E14+F13</f>
+        <v>-2406874390.33696</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>95</v>
+      <c r="A16" s="59" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>98</v>
+      <c r="A17" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="62" t="n">
+        <f aca="false">MIN(B14:F14)</f>
+        <v>-2406874390.33696</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>100</v>
+      <c r="A18" s="60" t="s">
+        <v>426</v>
+      </c>
+      <c r="B18" s="80" t="str">
+        <f aca="false">IF(COUNTIF(B14:F14,"&lt;0")=5,"&gt;5",COUNTIF(B14:F14,"&lt;0")+1)</f>
+        <v>&gt;5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>102</v>
+      <c r="A19" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B19" s="81" t="n">
+        <f aca="false">F7</f>
+        <v>132.224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>98</v>
+      <c r="A20" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="80" t="n">
+        <f aca="false">F8</f>
+        <v>36864</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>105</v>
+      <c r="A21" s="60" t="s">
+        <v>428</v>
+      </c>
+      <c r="B21" s="62" t="n">
+        <f aca="false">F6*'Pro Forma Financials'!D$14</f>
+        <v>1125198261.25269</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="27" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="27" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" s="25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="31" t="n">
-        <v>328000000</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C38" s="27" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C41" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" s="27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="27" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" s="31" t="n">
-        <v>10877000</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C47" s="31" t="n">
-        <v>58800000</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="31" t="n">
-        <v>25200000</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C50" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="27" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C52" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="32" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32" t="s">
-        <v>182</v>
+      <c r="A22" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="62" t="n">
+        <f aca="false">SUM(B12:F12)</f>
+        <v>5248000000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4061,7 +3668,1353 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="str">
+        <f aca="false">"AI FACTORY CONTROL PANEL — "&amp;TEXT($C$18,"0")&amp;"x "&amp;UPPER($C$12)&amp;" — "&amp;UPPER($C$5)</f>
+        <v>AI FACTORY CONTROL PANEL — 32x VERA RUBIN NVL72 — ABU DHABI, UAE</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="20" t="str">
+        <f aca="false">INDEX('ASHRAE Climate Library'!$B$5:$B$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
+        <v>1A</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <f aca="false">INDEX('ASHRAE Climate Library'!$C$5:$C$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
+        <v>0.26</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <f aca="false">INDEX('ASHRAE Climate Library'!$D$5:$D$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
+        <v>50</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">INDEX('ASHRAE Climate Library'!$E$5:$E$19,MATCH($C$5,'ASHRAE Climate Library'!$A$5:$A$19,0))</f>
+        <v>30</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>227</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$C$5:$C$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>72</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$E$5:$E$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>2300</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="20" t="str">
+        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>Liquid</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$G$5:$G$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>343.462362879839</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$19,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>100</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="28" t="str">
+        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$19,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>Air</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$23,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>40</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="28" t="str">
+        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$23,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>Air</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="32" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" s="33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="34" t="n">
+        <v>328000000</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="29" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="34" t="n">
+        <v>10877000</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="34" t="n">
+        <v>58800000</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="34" t="n">
+        <v>25200000</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5" type="list">
+      <formula1>LocationList</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C12" type="list">
+      <formula1>RackTypesCompute</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C19" type="list">
+      <formula1>RackTypesNetwork</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C23" type="list">
+      <formula1>RackTypesStorage</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Rack count must be a whole number &gt;= 0." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18 C22 C26" type="whole">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFBF8F00"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="D5" s="37" t="n">
+        <v>227</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <f aca="false">IF($F5="Liquid",$D5/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>343.462362879839</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>72</v>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>137</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <f aca="false">IF($F6="Liquid",$D6/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>207.287857773295</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>121</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="39" t="n">
+        <f aca="false">IF($F7="Liquid",$D7/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>183.079056865465</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>576</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="43" t="n">
+        <f aca="false">IF($F8="Liquid",$D8/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>907.830034043626</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>700</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <f aca="false">IF($F9="Liquid",$D9/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <f aca="false">IF($F10="Liquid",$D10/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>80</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <f aca="false">IF($F11="Liquid",$D11/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>121.04400453915</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <f aca="false">IF($F12="Liquid",$D12/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <f aca="false">IF($F13="Liquid",$D13/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
@@ -4079,7 +5032,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4089,7 +5042,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4099,22 +5052,22 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,729 +5075,280 @@
         <v>64</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="33" t="n">
+        <v>229</v>
+      </c>
+      <c r="C5" s="44" t="n">
         <v>0.26</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="37" t="n">
         <v>30</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="35" t="n">
+        <v>232</v>
+      </c>
+      <c r="C6" s="45" t="n">
         <v>0.28</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="41" t="n">
         <v>49.5</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="41" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="33" t="n">
+        <v>232</v>
+      </c>
+      <c r="C7" s="44" t="n">
         <v>0.28</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="37" t="n">
         <v>49</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="37" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="35" t="n">
+        <v>236</v>
+      </c>
+      <c r="C8" s="45" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="41" t="n">
         <v>36.5</v>
       </c>
-      <c r="E8" s="36" t="n">
+      <c r="E8" s="41" t="n">
         <v>29.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" s="33" t="n">
+        <v>236</v>
+      </c>
+      <c r="C9" s="44" t="n">
         <v>0.28</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="37" t="n">
         <v>39.5</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="37" t="n">
         <v>30</v>
       </c>
       <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="35" t="n">
+        <v>240</v>
+      </c>
+      <c r="C10" s="45" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D10" s="41" t="n">
         <v>48.5</v>
       </c>
-      <c r="E10" s="36" t="n">
+      <c r="E10" s="41" t="n">
         <v>26.5</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="33" t="n">
+        <v>242</v>
+      </c>
+      <c r="C11" s="44" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="37" t="n">
         <v>43.5</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="37" t="n">
         <v>27.5</v>
       </c>
       <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="35" t="n">
+        <v>244</v>
+      </c>
+      <c r="C12" s="45" t="n">
         <v>0.19</v>
       </c>
-      <c r="D12" s="36" t="n">
+      <c r="D12" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="E12" s="36" t="n">
+      <c r="E12" s="41" t="n">
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="33" t="n">
+        <v>247</v>
+      </c>
+      <c r="C13" s="44" t="n">
         <v>0.16</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D13" s="37" t="n">
         <v>38.5</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="37" t="n">
         <v>27</v>
       </c>
       <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" s="35" t="n">
+        <v>247</v>
+      </c>
+      <c r="C14" s="45" t="n">
         <v>0.16</v>
       </c>
-      <c r="D14" s="36" t="n">
+      <c r="D14" s="41" t="n">
         <v>37.5</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E14" s="41" t="n">
         <v>23</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="33" t="n">
+        <v>247</v>
+      </c>
+      <c r="C15" s="44" t="n">
         <v>0.16</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="37" t="n">
         <v>35</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="37" t="n">
         <v>22</v>
       </c>
       <c r="F15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="35" t="n">
+        <v>247</v>
+      </c>
+      <c r="C16" s="45" t="n">
         <v>0.16</v>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D16" s="41" t="n">
         <v>28.5</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E16" s="41" t="n">
         <v>19.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C17" s="33" t="n">
+        <v>253</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>0.15</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="37" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="37" t="n">
         <v>21</v>
       </c>
       <c r="F17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="35" t="n">
+        <v>242</v>
+      </c>
+      <c r="C18" s="45" t="n">
         <v>0.21</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="41" t="n">
         <v>37.5</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="41" t="n">
         <v>27.5</v>
       </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="33" t="n">
+        <v>242</v>
+      </c>
+      <c r="C19" s="44" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="37" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="37" t="n">
         <v>24.5</v>
       </c>
       <c r="F19" s="18"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF5B9BD5"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$13</f>
-        <v>7264</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$15*'Control Panel &amp; Inputs'!$C$16</f>
-        <v>600</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$19</f>
-        <v>400</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="38" t="n">
-        <f aca="false">B5+B6+B7</f>
-        <v>8264</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="37" t="n">
-        <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",B7,0)</f>
-        <v>7264</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="38" t="n">
-        <f aca="false">B8-B9</f>
-        <v>1000</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="39" t="n">
-        <f aca="false">IF('Control Panel &amp; Inputs'!$C$14="Liquid",'Control Panel &amp; Inputs'!$C$12,0)+IF('Control Panel &amp; Inputs'!$C$17="Liquid",'Control Panel &amp; Inputs'!$C$15,0)+IF('Control Panel &amp; Inputs'!$C$20="Liquid",'Control Panel &amp; Inputs'!$C$18,0)</f>
-        <v>32</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$24</f>
-        <v>45</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$25</f>
-        <v>55</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="38" t="n">
-        <f aca="false">B13-B12</f>
-        <v>10</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B15" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
-        <v>343.462362879839</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B16" s="38" t="n">
-        <f aca="false">B9/('Control Panel &amp; Inputs'!$C$27*'Control Panel &amp; Inputs'!$C$26*B14)*60</f>
-        <v>10990.7956121548</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="37" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
-        <v>50</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B18" s="38" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
-        <v>30</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="37" t="n">
-        <f aca="false">B13-B17</f>
-        <v>5</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B20" s="38" t="n">
-        <f aca="false">B9*'Control Panel &amp; Inputs'!$C$22</f>
-        <v>363.2</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="B21" s="37" t="n">
-        <f aca="false">B10*'Control Panel &amp; Inputs'!$C$23</f>
-        <v>280</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B22" s="38" t="n">
-        <f aca="false">B20+B21</f>
-        <v>643.2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="B23" s="40" t="n">
-        <f aca="false">B22/B8</f>
-        <v>0.0778315585672798</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B24" s="41" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
-        <v>0.26</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25" s="42" t="n">
-        <f aca="false">(B24-B23)/B24</f>
-        <v>0.700647851664309</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B26" s="38" t="n">
-        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30</f>
-        <v>6989.278</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B27" s="40" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$28</f>
-        <v>1.08</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="43" t="n">
-        <f aca="false">B26*8760*B27/1000</f>
-        <v>66124.1613024</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="39" t="n">
-        <f aca="false">B28*'Control Panel &amp; Inputs'!$C$11</f>
-        <v>9918.62419536</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="43" t="n">
-        <f aca="false">B28*'Control Panel &amp; Inputs'!$C$10</f>
-        <v>25788.422907936</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>272</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4864,6 +5368,455 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF5B9BD5"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$13</f>
+        <v>7264</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="43" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$22*'Control Panel &amp; Inputs'!$C$20</f>
+        <v>600</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$26*'Control Panel &amp; Inputs'!$C$24</f>
+        <v>400</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="43" t="n">
+        <f aca="false">B5+B6+B7</f>
+        <v>8264</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="39" t="n">
+        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$21="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$25="Liquid",B7,0)</f>
+        <v>7264</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" s="43" t="n">
+        <f aca="false">B8-B9</f>
+        <v>1000</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="46" t="n">
+        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",'Control Panel &amp; Inputs'!$C$18,0)+IF('Control Panel &amp; Inputs'!$C$21="Liquid",'Control Panel &amp; Inputs'!$C$22,0)+IF('Control Panel &amp; Inputs'!$C$25="Liquid",'Control Panel &amp; Inputs'!$C$26,0)</f>
+        <v>32</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="43" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$29</f>
+        <v>45</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$30</f>
+        <v>55</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="43" t="n">
+        <f aca="false">B13-B12</f>
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B15" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*B14)*60</f>
+        <v>343.462362879839</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="43" t="n">
+        <f aca="false">B9/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*B14)*60</f>
+        <v>10990.7956121548</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B17" s="39" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
+        <v>50</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" s="43" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
+        <v>30</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B19" s="39" t="n">
+        <f aca="false">B13-B17</f>
+        <v>5</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B20" s="43" t="n">
+        <f aca="false">B9*'Control Panel &amp; Inputs'!$C$27</f>
+        <v>363.2</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="39" t="n">
+        <f aca="false">B10*'Control Panel &amp; Inputs'!$C$28</f>
+        <v>280</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B22" s="43" t="n">
+        <f aca="false">B20+B21</f>
+        <v>643.2</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="47" t="n">
+        <f aca="false">B22/B8</f>
+        <v>0.0778315585672798</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B24" s="48" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
+        <v>0.26</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B25" s="49" t="n">
+        <f aca="false">(B24-B23)/B24</f>
+        <v>0.700647851664309</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B26" s="43" t="n">
+        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$34*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>6989.278</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B27" s="47" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33</f>
+        <v>1.08</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="50" t="n">
+        <f aca="false">B26*8760*B27/1000</f>
+        <v>66124.1613024</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="46" t="n">
+        <f aca="false">B28*'Control Panel &amp; Inputs'!$C$11</f>
+        <v>9918.62419536</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="50" t="n">
+        <f aca="false">B28*'Control Panel &amp; Inputs'!$C$10</f>
+        <v>25788.422907936</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF70AD47"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -4876,7 +5829,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4887,7 +5840,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4898,886 +5851,886 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="45" t="n">
+      <c r="A5" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="45" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$49</f>
+      <c r="C5" s="52" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$54</f>
         <v>0.9</v>
       </c>
-      <c r="D5" s="45" t="n">
+      <c r="D5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="45" t="n">
+      <c r="E5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="45" t="n">
+      <c r="F5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="45" t="n">
+      <c r="G5" s="52" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="46" t="n">
+      <c r="A6" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,0)*C5</f>
+      <c r="C6" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,0)*C5</f>
         <v>52920000</v>
       </c>
-      <c r="D6" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,1)*D5</f>
+      <c r="D6" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,1)*D5</f>
         <v>58800000</v>
       </c>
-      <c r="E6" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,2)*E5</f>
+      <c r="E6" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,2)*E5</f>
         <v>58800000</v>
       </c>
-      <c r="F6" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,3)*F5</f>
+      <c r="F6" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,3)*F5</f>
         <v>58800000</v>
       </c>
-      <c r="G6" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$47*POWER(1+'Control Panel &amp; Inputs'!$C$50,4)*G5</f>
+      <c r="G6" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,4)*G5</f>
         <v>58800000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="B7" s="46" t="n">
+      <c r="A7" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),0)*C5</f>
+      <c r="C7" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),0)*C5</f>
         <v>22680000</v>
       </c>
-      <c r="D7" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),1)*D5</f>
+      <c r="D7" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),1)*D5</f>
         <v>26775000</v>
       </c>
-      <c r="E7" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),2)*E5</f>
+      <c r="E7" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),2)*E5</f>
         <v>28448437.5</v>
       </c>
-      <c r="F7" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),3)*F5</f>
+      <c r="F7" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),3)*F5</f>
         <v>30226464.84375</v>
       </c>
-      <c r="G7" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$48*POWER((1+'Control Panel &amp; Inputs'!$C$52)*(1-'Control Panel &amp; Inputs'!$C$51),4)*G5</f>
+      <c r="G7" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),4)*G5</f>
         <v>32115618.8964844</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="B8" s="46" t="n">
+      <c r="A8" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="53" t="n">
         <f aca="false">C6+C7</f>
         <v>75600000</v>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="53" t="n">
         <f aca="false">D6+D7</f>
         <v>85575000</v>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="53" t="n">
         <f aca="false">E6+E7</f>
         <v>87248437.5</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="53" t="n">
         <f aca="false">F6+F7</f>
         <v>89026464.84375</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">G6+G7</f>
         <v>90915618.8964844</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="B9" s="47" t="n">
+      <c r="A9" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="C9" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="D9" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>0.0612</v>
       </c>
-      <c r="E9" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="E9" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>0.062424</v>
       </c>
-      <c r="F9" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="F9" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>0.06367248</v>
       </c>
-      <c r="G9" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="G9" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>0.0649459296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="B10" s="48" t="n">
+      <c r="A10" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="55" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="55" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="55" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="55" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="55" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="46" t="n">
+      <c r="A11" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="53" t="n">
         <f aca="false">C10*C9</f>
         <v>3967449.678144</v>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="53" t="n">
         <f aca="false">D10*D9</f>
         <v>4046798.67170688</v>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E11" s="53" t="n">
         <f aca="false">E10*E9</f>
         <v>4127734.64514102</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="53" t="n">
         <f aca="false">F10*F9</f>
         <v>4210289.33804384</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">G10*G9</f>
         <v>4294495.12480471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="B12" s="46" t="n">
+      <c r="A12" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,0)</f>
+      <c r="C12" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,0)</f>
         <v>10877000</v>
       </c>
-      <c r="D12" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,1)</f>
+      <c r="D12" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,1)</f>
         <v>11203310</v>
       </c>
-      <c r="E12" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,2)</f>
+      <c r="E12" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,2)</f>
         <v>11539409.3</v>
       </c>
-      <c r="F12" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,3)</f>
+      <c r="F12" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,3)</f>
         <v>11885591.579</v>
       </c>
-      <c r="G12" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$45*POWER(1+'Control Panel &amp; Inputs'!$C$46,4)</f>
+      <c r="G12" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,4)</f>
         <v>12242159.32637</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="46" t="n">
+      <c r="A13" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="53" t="n">
         <f aca="false">C11+C12</f>
         <v>14844449.678144</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="53" t="n">
         <f aca="false">D11+D12</f>
         <v>15250108.6717069</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="53" t="n">
         <f aca="false">E11+E12</f>
         <v>15667143.945141</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="53" t="n">
         <f aca="false">F11+F12</f>
         <v>16095880.9170438</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">G11+G12</f>
         <v>16536654.4511747</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="46" t="n">
+      <c r="A14" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="46" t="n">
+      <c r="C14" s="53" t="n">
         <f aca="false">C8-C13</f>
         <v>60755550.321856</v>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="53" t="n">
         <f aca="false">D8-D13</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="E14" s="53" t="n">
         <f aca="false">E8-E13</f>
         <v>71581293.554859</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="53" t="n">
         <f aca="false">F8-F13</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="G14" s="46" t="n">
+      <c r="G14" s="53" t="n">
         <f aca="false">G8-G13</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="45" t="n">
+      <c r="A15" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="45" t="n">
+      <c r="C15" s="52" t="n">
         <f aca="false">C14/C8</f>
         <v>0.803644845527196</v>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="52" t="n">
         <f aca="false">D14/D8</f>
         <v>0.821792478273948</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="52" t="n">
         <f aca="false">E14/E8</f>
         <v>0.820430664501688</v>
       </c>
-      <c r="F15" s="45" t="n">
+      <c r="F15" s="52" t="n">
         <f aca="false">F14/F8</f>
         <v>0.819201167368673</v>
       </c>
-      <c r="G15" s="45" t="n">
+      <c r="G15" s="52" t="n">
         <f aca="false">G14/G8</f>
         <v>0.818109862178872</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35</f>
+      <c r="A16" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40</f>
         <v>328000000</v>
       </c>
-      <c r="C16" s="46" t="n">
+      <c r="C16" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="46" t="n">
+      <c r="E16" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="46" t="n">
+      <c r="F16" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="46" t="n">
+      <c r="G16" s="53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
-        <v>294</v>
-      </c>
-      <c r="B17" s="46" t="n">
-        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$37</f>
+      <c r="A17" s="51" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" s="53" t="n">
+        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$42</f>
         <v>262400000</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="46" t="n">
+      <c r="E17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="46" t="n">
+      <c r="F17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="46" t="n">
+      <c r="G17" s="53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="B18" s="46" t="n">
+      <c r="A18" s="51" t="s">
+        <v>332</v>
+      </c>
+      <c r="B18" s="53" t="n">
         <f aca="false">B16-B17</f>
         <v>65600000</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="E18" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="46" t="n">
+      <c r="F18" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="46" t="n">
+      <c r="A19" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="n">
+      <c r="C19" s="53" t="n">
         <f aca="false">B17</f>
         <v>262400000</v>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="53" t="n">
         <f aca="false">C23</f>
         <v>216313497.33442</v>
       </c>
-      <c r="E19" s="46" t="n">
+      <c r="E19" s="53" t="n">
         <f aca="false">D23</f>
         <v>167231371.995576</v>
       </c>
-      <c r="F19" s="46" t="n">
+      <c r="F19" s="53" t="n">
         <f aca="false">E23</f>
         <v>114958908.509708</v>
       </c>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="53" t="n">
         <f aca="false">F23</f>
         <v>59288734.8972587</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="B20" s="46" t="n">
+      <c r="A20" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="B20" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="46" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
+      <c r="C20" s="53" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="D20" s="46" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
+      <c r="D20" s="53" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="E20" s="46" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
+      <c r="E20" s="53" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="F20" s="46" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
+      <c r="F20" s="53" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G20" s="46" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,B17),0)</f>
+      <c r="G20" s="53" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
         <v>63142502.6655805</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="B21" s="46" t="n">
+      <c r="A21" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="B21" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="46" t="n">
-        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$38</f>
+      <c r="C21" s="53" t="n">
+        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$43</f>
         <v>17056000</v>
       </c>
-      <c r="D21" s="46" t="n">
-        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$38</f>
+      <c r="D21" s="53" t="n">
+        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$43</f>
         <v>14060377.3267373</v>
       </c>
-      <c r="E21" s="46" t="n">
-        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$38</f>
+      <c r="E21" s="53" t="n">
+        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$43</f>
         <v>10870039.1797125</v>
       </c>
-      <c r="F21" s="46" t="n">
-        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$38</f>
+      <c r="F21" s="53" t="n">
+        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$43</f>
         <v>7472329.05313103</v>
       </c>
-      <c r="G21" s="46" t="n">
-        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$38</f>
+      <c r="G21" s="53" t="n">
+        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$43</f>
         <v>3853767.76832181</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="B22" s="46" t="n">
+      <c r="A22" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="53" t="n">
         <f aca="false">C20-C21</f>
         <v>46086502.6655805</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="53" t="n">
         <f aca="false">D20-D21</f>
         <v>49082125.3388433</v>
       </c>
-      <c r="E22" s="46" t="n">
+      <c r="E22" s="53" t="n">
         <f aca="false">E20-E21</f>
         <v>52272463.4858681</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="F22" s="53" t="n">
         <f aca="false">F20-F21</f>
         <v>55670173.6124495</v>
       </c>
-      <c r="G22" s="46" t="n">
+      <c r="G22" s="53" t="n">
         <f aca="false">G20-G21</f>
         <v>59288734.8972587</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="B23" s="46" t="n">
+      <c r="A23" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">C19-C22</f>
         <v>216313497.33442</v>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="53" t="n">
         <f aca="false">D19-D22</f>
         <v>167231371.995576</v>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="E23" s="53" t="n">
         <f aca="false">E19-E22</f>
         <v>114958908.509708</v>
       </c>
-      <c r="F23" s="46" t="n">
+      <c r="F23" s="53" t="n">
         <f aca="false">F19-F22</f>
         <v>59288734.8972587</v>
       </c>
-      <c r="G23" s="46" t="n">
+      <c r="G23" s="53" t="n">
         <f aca="false">G19-G22</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="B24" s="46" t="n">
+      <c r="A24" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="46" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
+      <c r="C24" s="53" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>65600000</v>
       </c>
-      <c r="D24" s="46" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
+      <c r="D24" s="53" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>65600000</v>
       </c>
-      <c r="E24" s="46" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
+      <c r="E24" s="53" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>65600000</v>
       </c>
-      <c r="F24" s="46" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
+      <c r="F24" s="53" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>65600000</v>
       </c>
-      <c r="G24" s="46" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$41,B16/'Control Panel &amp; Inputs'!$C$41,0)</f>
+      <c r="G24" s="53" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
         <v>65600000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="B25" s="46" t="n">
+      <c r="A25" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="B25" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="46" t="n">
-        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$43*C14)</f>
+      <c r="C25" s="53" t="n">
+        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$48*C14)</f>
         <v>17056000</v>
       </c>
-      <c r="D25" s="46" t="n">
-        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$43*D14)</f>
+      <c r="D25" s="53" t="n">
+        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$48*D14)</f>
         <v>14060377.3267373</v>
       </c>
-      <c r="E25" s="46" t="n">
-        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$43*E14)</f>
+      <c r="E25" s="53" t="n">
+        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$48*E14)</f>
         <v>10870039.1797125</v>
       </c>
-      <c r="F25" s="46" t="n">
-        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$43*F14)</f>
+      <c r="F25" s="53" t="n">
+        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$48*F14)</f>
         <v>7472329.05313103</v>
       </c>
-      <c r="G25" s="46" t="n">
-        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$43*G14)</f>
+      <c r="G25" s="53" t="n">
+        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$48*G14)</f>
         <v>3853767.76832181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="B26" s="46" t="n">
+      <c r="A26" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="B26" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="53" t="n">
         <f aca="false">C14-C24-C25</f>
         <v>-21900449.678144</v>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="53" t="n">
         <f aca="false">D14-D24-D25</f>
         <v>-9335485.99844415</v>
       </c>
-      <c r="E26" s="46" t="n">
+      <c r="E26" s="53" t="n">
         <f aca="false">E14-E24-E25</f>
         <v>-4888745.62485347</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="53" t="n">
         <f aca="false">F14-F24-F25</f>
         <v>-141745.126424866</v>
       </c>
-      <c r="G26" s="46" t="n">
+      <c r="G26" s="53" t="n">
         <f aca="false">G14-G24-G25</f>
         <v>4925196.67698786</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="B27" s="46" t="n">
+      <c r="A27" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="B27" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="46" t="n">
-        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="C27" s="53" t="n">
+        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>0</v>
       </c>
-      <c r="D27" s="46" t="n">
-        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="D27" s="53" t="n">
+        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>0</v>
       </c>
-      <c r="E27" s="46" t="n">
-        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="E27" s="53" t="n">
+        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>0</v>
       </c>
-      <c r="F27" s="46" t="n">
-        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="F27" s="53" t="n">
+        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>0</v>
       </c>
-      <c r="G27" s="46" t="n">
-        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="G27" s="53" t="n">
+        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>443267.700928907</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="B28" s="46" t="n">
+      <c r="A28" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="46" t="n">
+      <c r="C28" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="46" t="n">
+      <c r="E28" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="46" t="n">
+      <c r="F28" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="G28" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>32800000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="B29" s="50" t="n">
+      <c r="A29" s="56" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" s="57" t="n">
         <f aca="false">-B18</f>
         <v>-65600000</v>
       </c>
-      <c r="C29" s="50" t="n">
+      <c r="C29" s="57" t="n">
         <f aca="false">C14-C20-C27+C28</f>
         <v>-2386952.34372452</v>
       </c>
-      <c r="D29" s="50" t="n">
+      <c r="D29" s="57" t="n">
         <f aca="false">D14-D20-D27+D28</f>
         <v>7182388.6627126</v>
       </c>
-      <c r="E29" s="50" t="n">
+      <c r="E29" s="57" t="n">
         <f aca="false">E14-E20-E27+E28</f>
         <v>8438790.88927846</v>
       </c>
-      <c r="F29" s="50" t="n">
+      <c r="F29" s="57" t="n">
         <f aca="false">F14-F20-F27+F28</f>
         <v>9788081.26112565</v>
       </c>
-      <c r="G29" s="50" t="n">
+      <c r="G29" s="57" t="n">
         <f aca="false">G14-G20-G27+G28</f>
         <v>43593194.0788002</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="B30" s="46" t="n">
+      <c r="A30" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" s="53" t="n">
         <f aca="false">B29</f>
         <v>-65600000</v>
       </c>
-      <c r="C30" s="46" t="n">
+      <c r="C30" s="53" t="n">
         <f aca="false">B30+C29</f>
         <v>-67986952.3437245</v>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="53" t="n">
         <f aca="false">C30+D29</f>
         <v>-60804563.6810119</v>
       </c>
-      <c r="E30" s="46" t="n">
+      <c r="E30" s="53" t="n">
         <f aca="false">D30+E29</f>
         <v>-52365772.7917335</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="53" t="n">
         <f aca="false">E30+F29</f>
         <v>-42577691.5306078</v>
       </c>
-      <c r="G30" s="46" t="n">
+      <c r="G30" s="53" t="n">
         <f aca="false">F30+G29</f>
         <v>1015502.54819243</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="B31" s="51" t="n">
+      <c r="A31" s="51" t="s">
+        <v>345</v>
+      </c>
+      <c r="B31" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="51" t="n">
+      <c r="C31" s="58" t="n">
         <f aca="false">IF(C20=0,"",C14/C20)</f>
         <v>0.962197375096669</v>
       </c>
-      <c r="D31" s="51" t="n">
+      <c r="D31" s="58" t="n">
         <f aca="false">IF(D20=0,"",D14/D20)</f>
         <v>1.11374887531387</v>
       </c>
-      <c r="E31" s="51" t="n">
+      <c r="E31" s="58" t="n">
         <f aca="false">IF(E20=0,"",E14/E20)</f>
         <v>1.13364675983739</v>
       </c>
-      <c r="F31" s="51" t="n">
+      <c r="F31" s="58" t="n">
         <f aca="false">IF(F20=0,"",F14/F20)</f>
         <v>1.15501573184335</v>
       </c>
-      <c r="G31" s="51" t="n">
+      <c r="G31" s="58" t="n">
         <f aca="false">IF(G20=0,"",G14/G20)</f>
         <v>1.17795401362598</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="B32" s="46" t="n">
+      <c r="A32" s="51" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="46" t="n">
-        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="C32" s="53" t="n">
+        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>0</v>
       </c>
-      <c r="D32" s="46" t="n">
-        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="D32" s="53" t="n">
+        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>425240.21954638</v>
       </c>
-      <c r="E32" s="46" t="n">
-        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="E32" s="53" t="n">
+        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>538316.419937308</v>
       </c>
-      <c r="F32" s="46" t="n">
-        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="F32" s="53" t="n">
+        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>659752.553403555</v>
       </c>
-      <c r="G32" s="46" t="n">
-        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="G32" s="53" t="n">
+        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$47</f>
         <v>790106.80007787</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="B33" s="46" t="n">
+      <c r="A33" s="51" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" s="53" t="n">
         <f aca="false">-B16</f>
         <v>-328000000</v>
       </c>
-      <c r="C33" s="46" t="n">
+      <c r="C33" s="53" t="n">
         <f aca="false">C14-C32+C28</f>
         <v>60755550.321856</v>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="53" t="n">
         <f aca="false">D14-D32+D28</f>
         <v>69899651.1087467</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="53" t="n">
         <f aca="false">E14-E32+E28</f>
         <v>71042977.1349217</v>
       </c>
-      <c r="F33" s="46" t="n">
+      <c r="F33" s="53" t="n">
         <f aca="false">F14-F32+F28</f>
         <v>72270831.3733026</v>
       </c>
-      <c r="G33" s="46" t="n">
+      <c r="G33" s="53" t="n">
         <f aca="false">G14-G32+G28</f>
         <v>106388857.645232</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="52" t="s">
-        <v>311</v>
+      <c r="A35" s="59" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="54" t="n">
+      <c r="B36" s="61" t="n">
         <f aca="false">IRR(B29:G29)</f>
         <v>0.00348283951629262</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="54" t="n">
+      <c r="B37" s="61" t="n">
         <f aca="false">IRR(B33:G33)</f>
         <v>0.0473981776304923</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="55" t="n">
-        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$44,C29:G29)</f>
+      <c r="B38" s="62" t="n">
+        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$49,C29:G29)</f>
         <v>-29426161.8959998</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53" t="s">
-        <v>312</v>
-      </c>
-      <c r="B39" s="56" t="n">
+      <c r="A39" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="B39" s="63" t="n">
         <f aca="false">SUM(C29:G29)/-B29</f>
         <v>1.01548022177123</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="57" t="n">
+      <c r="B40" s="64" t="n">
         <f aca="false">IFERROR(COUNTIF(B30:G30,"&lt;0")-1+ABS(INDEX(B30:G30,COUNTIF(B30:G30,"&lt;0")))/INDEX(B29:G29,COUNTIF(B30:G30,"&lt;0")+1),"&gt;5 yrs")</f>
         <v>4.97670502082603</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="56" t="n">
+      <c r="B41" s="63" t="n">
         <f aca="false">MIN(C31:G31)</f>
         <v>0.962197375096669</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="53" t="s">
-        <v>313</v>
-      </c>
-      <c r="B42" s="56" t="n">
+      <c r="A42" s="60" t="s">
+        <v>350</v>
+      </c>
+      <c r="B42" s="63" t="n">
         <f aca="false">AVERAGE(C31:G31)</f>
         <v>1.10851255114345</v>
       </c>
@@ -5797,7 +6750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFED7D31"/>
@@ -5815,7 +6768,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5825,7 +6778,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5844,59 +6797,59 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$12*'Control Panel &amp; Inputs'!$C$21</f>
+      <c r="B5" s="46" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$14</f>
         <v>2304</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="43" t="n">
-        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$30</f>
+        <v>355</v>
+      </c>
+      <c r="B6" s="50" t="n">
+        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$35</f>
         <v>20082124.8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B7" s="39" t="n">
-        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$29</f>
+        <v>358</v>
+      </c>
+      <c r="B7" s="46" t="n">
+        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$34</f>
         <v>17069806.08</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="65" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/B7</f>
         <v>5.01323797112521</v>
       </c>
@@ -5904,14 +6857,14 @@
         <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="59" t="n">
+        <v>361</v>
+      </c>
+      <c r="B9" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$13/B7</f>
         <v>0.893396714657164</v>
       </c>
@@ -5919,14 +6872,14 @@
         <v>43</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B10" s="58" t="n">
+        <v>363</v>
+      </c>
+      <c r="B10" s="65" t="n">
         <f aca="false">B8-B9</f>
         <v>4.11984125646805</v>
       </c>
@@ -5934,74 +6887,74 @@
         <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="60" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35/B5</f>
+      <c r="B11" s="67" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40/B5</f>
         <v>142361.111111111</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B12" s="61" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>366</v>
+      </c>
+      <c r="B12" s="68" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>39690222.6524685</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B13" s="60" t="n">
+        <v>369</v>
+      </c>
+      <c r="B13" s="67" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>10355154.8886738</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B14" s="38" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*3600*8760*'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$30/1000000000000</f>
+        <v>372</v>
+      </c>
+      <c r="B14" s="43" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$37*'Control Panel &amp; Inputs'!$C$36*3600*8760*'Control Panel &amp; Inputs'!$C$34*'Control Panel &amp; Inputs'!$C$35/1000000000000</f>
         <v>33.18370301952</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="59" t="n">
+        <v>375</v>
+      </c>
+      <c r="B15" s="66" t="n">
         <f aca="false">'Pro Forma Financials'!D$7/(B14*1000000)</f>
         <v>0.806871975205717</v>
       </c>
@@ -6009,29 +6962,29 @@
         <v>45</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="58" t="n">
-        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$32/(B14*1000000)</f>
+      <c r="B16" s="65" t="n">
+        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$37/(B14*1000000)</f>
         <v>0.137869863373019</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="42" t="n">
+      <c r="B17" s="49" t="n">
         <f aca="false">'Pro Forma Financials'!D$11/'Pro Forma Financials'!D$8</f>
         <v>0.0472894966018917</v>
       </c>
@@ -6039,14 +6992,14 @@
         <v>7</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B18" s="62" t="n">
+        <v>379</v>
+      </c>
+      <c r="B18" s="69" t="n">
         <f aca="false">('Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12)/'Pro Forma Financials'!D$10</f>
         <v>1.12472791389946</v>
       </c>
@@ -6054,14 +7007,14 @@
         <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B19" s="60" t="n">
+        <v>381</v>
+      </c>
+      <c r="B19" s="67" t="n">
         <f aca="false">'Pro Forma Financials'!D$20+'Pro Forma Financials'!D$13</f>
         <v>78392611.3372874</v>
       </c>
@@ -6069,14 +7022,14 @@
         <v>57</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="B20" s="63" t="n">
+        <v>383</v>
+      </c>
+      <c r="B20" s="70" t="n">
         <f aca="false">1-B19/'Pro Forma Financials'!D$8</f>
         <v>0.0839309221468023</v>
       </c>
@@ -6084,7 +7037,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6102,7 +7055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF7030A0"/>
@@ -6117,7 +7070,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6135,7 +7088,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6153,46 +7106,46 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6200,53 +7153,53 @@
         <f aca="false">TEXT($B5,"$0.00")&amp;"/kWh @ "&amp;TEXT($C5,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B5" s="64" t="n">
+      <c r="B5" s="71" t="n">
         <v>0.04</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="72" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C5</f>
+      <c r="D5" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C5</f>
         <v>164000000</v>
       </c>
-      <c r="E5" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D5</f>
+      <c r="E5" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D5</f>
         <v>164000000</v>
       </c>
-      <c r="F5" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D5)</f>
+      <c r="F5" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D5)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G5" s="66" t="n">
+      <c r="G5" s="73" t="n">
         <f aca="false">-$E5</f>
         <v>-164000000</v>
       </c>
-      <c r="H5" s="66" t="n">
-        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*B23))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H5" s="73" t="n">
+        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*B23))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>22613969.3819162</v>
       </c>
-      <c r="I5" s="66" t="n">
-        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*C23))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I5" s="73" t="n">
+        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*C23))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>32209760.0528743</v>
       </c>
-      <c r="J5" s="66" t="n">
-        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*D23))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J5" s="73" t="n">
+        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*D23))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>33442432.1818188</v>
       </c>
-      <c r="K5" s="66" t="n">
-        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*E23))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K5" s="73" t="n">
+        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*E23))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>34504206.81576</v>
       </c>
-      <c r="L5" s="66" t="n">
-        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D5),0),'Control Panel &amp; Inputs'!$C$43*F23))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L5" s="73" t="n">
+        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*F23))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>68444231.4374028</v>
       </c>
-      <c r="M5" s="67" t="n">
+      <c r="M5" s="74" t="n">
         <f aca="false">IRR(G5:L5)</f>
         <v>0.0455581791812502</v>
       </c>
-      <c r="N5" s="68" t="n">
+      <c r="N5" s="75" t="n">
         <f aca="false">AVERAGE(B23:F23)/$F5</f>
         <v>1.80849867816635</v>
       </c>
@@ -6256,53 +7209,53 @@
         <f aca="false">TEXT($B6,"$0.00")&amp;"/kWh @ "&amp;TEXT($C6,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B6" s="64" t="n">
+      <c r="B6" s="71" t="n">
         <v>0.04</v>
       </c>
-      <c r="C6" s="65" t="n">
+      <c r="C6" s="72" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C6</f>
+      <c r="D6" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C6</f>
         <v>196800000</v>
       </c>
-      <c r="E6" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D6</f>
+      <c r="E6" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D6</f>
         <v>131200000</v>
       </c>
-      <c r="F6" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D6)</f>
+      <c r="F6" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D6)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G6" s="66" t="n">
+      <c r="G6" s="73" t="n">
         <f aca="false">-$E6</f>
         <v>-131200000</v>
       </c>
-      <c r="H6" s="66" t="n">
-        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*B24))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H6" s="73" t="n">
+        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*B24))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>14721156.5487186</v>
       </c>
-      <c r="I6" s="66" t="n">
-        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*C24))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I6" s="73" t="n">
+        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*C24))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>24316947.2196767</v>
       </c>
-      <c r="J6" s="66" t="n">
-        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*D24))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J6" s="73" t="n">
+        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*D24))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>25600328.1040539</v>
       </c>
-      <c r="K6" s="66" t="n">
-        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*E24))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K6" s="73" t="n">
+        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*E24))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>26695457.6844102</v>
       </c>
-      <c r="L6" s="66" t="n">
-        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D6),0),'Control Panel &amp; Inputs'!$C$43*F24))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L6" s="73" t="n">
+        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*F24))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>60594773.4915989</v>
       </c>
-      <c r="M6" s="67" t="n">
+      <c r="M6" s="74" t="n">
         <f aca="false">IRR(G6:L6)</f>
         <v>0.0418311991063475</v>
       </c>
-      <c r="N6" s="68" t="n">
+      <c r="N6" s="75" t="n">
         <f aca="false">AVERAGE(B24:F24)/$F6</f>
         <v>1.50708223180529</v>
       </c>
@@ -6312,53 +7265,53 @@
         <f aca="false">TEXT($B7,"$0.00")&amp;"/kWh @ "&amp;TEXT($C7,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B7" s="64" t="n">
+      <c r="B7" s="71" t="n">
         <v>0.04</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="72" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C7</f>
+      <c r="D7" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C7</f>
         <v>229600000</v>
       </c>
-      <c r="E7" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D7</f>
+      <c r="E7" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D7</f>
         <v>98400000</v>
       </c>
-      <c r="F7" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D7)</f>
+      <c r="F7" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D7)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="73" t="n">
         <f aca="false">-$E7</f>
         <v>-98400000</v>
       </c>
-      <c r="H7" s="66" t="n">
-        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*B25))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H7" s="73" t="n">
+        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*B25))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>6828343.71552104</v>
       </c>
-      <c r="I7" s="66" t="n">
-        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*C25))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I7" s="73" t="n">
+        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*C25))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>16424134.3864791</v>
       </c>
-      <c r="J7" s="66" t="n">
-        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*D25))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J7" s="73" t="n">
+        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*D25))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>17707515.2708564</v>
       </c>
-      <c r="K7" s="66" t="n">
-        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*E25))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K7" s="73" t="n">
+        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*E25))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>18886708.5530603</v>
       </c>
-      <c r="L7" s="66" t="n">
-        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D7),0),'Control Panel &amp; Inputs'!$C$43*F25))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L7" s="73" t="n">
+        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*F25))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>52745315.5457949</v>
       </c>
-      <c r="M7" s="67" t="n">
+      <c r="M7" s="74" t="n">
         <f aca="false">IRR(G7:L7)</f>
         <v>0.036027847120873</v>
       </c>
-      <c r="N7" s="68" t="n">
+      <c r="N7" s="75" t="n">
         <f aca="false">AVERAGE(B25:F25)/$F7</f>
         <v>1.29178477011882</v>
       </c>
@@ -6368,53 +7321,53 @@
         <f aca="false">TEXT($B8,"$0.00")&amp;"/kWh @ "&amp;TEXT($C8,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B8" s="64" t="n">
+      <c r="B8" s="71" t="n">
         <v>0.04</v>
       </c>
-      <c r="C8" s="65" t="n">
+      <c r="C8" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="D8" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C8</f>
+      <c r="D8" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C8</f>
         <v>262400000</v>
       </c>
-      <c r="E8" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D8</f>
+      <c r="E8" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D8</f>
         <v>65600000</v>
       </c>
-      <c r="F8" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D8)</f>
+      <c r="F8" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D8)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="73" t="n">
         <f aca="false">-$E8</f>
         <v>-65600000</v>
       </c>
-      <c r="H8" s="66" t="n">
-        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*B26))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H8" s="73" t="n">
+        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*B26))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>-1064469.11767652</v>
       </c>
-      <c r="I8" s="66" t="n">
-        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*C26))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I8" s="73" t="n">
+        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*C26))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>8531321.55328157</v>
       </c>
-      <c r="J8" s="66" t="n">
-        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*D26))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J8" s="73" t="n">
+        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*D26))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>9814702.43765881</v>
       </c>
-      <c r="K8" s="66" t="n">
-        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*E26))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K8" s="73" t="n">
+        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*E26))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>11077959.4217105</v>
       </c>
-      <c r="L8" s="66" t="n">
-        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D8),0),'Control Panel &amp; Inputs'!$C$43*F26))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L8" s="73" t="n">
+        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*F26))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>44895857.599991</v>
       </c>
-      <c r="M8" s="67" t="n">
+      <c r="M8" s="74" t="n">
         <f aca="false">IRR(G8:L8)</f>
         <v>0.0261453486370609</v>
       </c>
-      <c r="N8" s="68" t="n">
+      <c r="N8" s="75" t="n">
         <f aca="false">AVERAGE(B26:F26)/$F8</f>
         <v>1.13031167385397</v>
       </c>
@@ -6424,53 +7377,53 @@
         <f aca="false">TEXT($B9,"$0.00")&amp;"/kWh @ "&amp;TEXT($C9,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B9" s="64" t="n">
+      <c r="B9" s="71" t="n">
         <v>0.06</v>
       </c>
-      <c r="C9" s="65" t="n">
+      <c r="C9" s="72" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C9</f>
+      <c r="D9" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C9</f>
         <v>164000000</v>
       </c>
-      <c r="E9" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D9</f>
+      <c r="E9" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D9</f>
         <v>164000000</v>
       </c>
-      <c r="F9" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D9)</f>
+      <c r="F9" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D9)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="73" t="n">
         <f aca="false">-$E9</f>
         <v>-164000000</v>
       </c>
-      <c r="H9" s="66" t="n">
-        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*B27))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H9" s="73" t="n">
+        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*B27))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>21291486.1558682</v>
       </c>
-      <c r="I9" s="66" t="n">
-        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*C27))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I9" s="73" t="n">
+        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*C27))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>30860827.1623053</v>
       </c>
-      <c r="J9" s="66" t="n">
-        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*D27))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J9" s="73" t="n">
+        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*D27))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>32117229.3888712</v>
       </c>
-      <c r="K9" s="66" t="n">
-        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*E27))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K9" s="73" t="n">
+        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*E27))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>33227085.7165534</v>
       </c>
-      <c r="L9" s="66" t="n">
-        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D9),0),'Control Panel &amp; Inputs'!$C$43*F27))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L9" s="73" t="n">
+        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*F27))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>67141567.9162121</v>
       </c>
-      <c r="M9" s="67" t="n">
+      <c r="M9" s="74" t="n">
         <f aca="false">IRR(G9:L9)</f>
         <v>0.0346975334245463</v>
       </c>
-      <c r="N9" s="68" t="n">
+      <c r="N9" s="75" t="n">
         <f aca="false">AVERAGE(B27:F27)/$F9</f>
         <v>1.77362008182952</v>
       </c>
@@ -6480,53 +7433,53 @@
         <f aca="false">TEXT($B10,"$0.00")&amp;"/kWh @ "&amp;TEXT($C10,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B10" s="64" t="n">
+      <c r="B10" s="71" t="n">
         <v>0.06</v>
       </c>
-      <c r="C10" s="65" t="n">
+      <c r="C10" s="72" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C10</f>
+      <c r="D10" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C10</f>
         <v>196800000</v>
       </c>
-      <c r="E10" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D10</f>
+      <c r="E10" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D10</f>
         <v>131200000</v>
       </c>
-      <c r="F10" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D10)</f>
+      <c r="F10" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D10)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G10" s="66" t="n">
+      <c r="G10" s="73" t="n">
         <f aca="false">-$E10</f>
         <v>-131200000</v>
       </c>
-      <c r="H10" s="66" t="n">
-        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*B28))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H10" s="73" t="n">
+        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*B28))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>13398673.3226706</v>
       </c>
-      <c r="I10" s="66" t="n">
-        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*C28))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I10" s="73" t="n">
+        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*C28))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>22968014.3291077</v>
       </c>
-      <c r="J10" s="66" t="n">
-        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*D28))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J10" s="73" t="n">
+        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*D28))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>24224416.5556736</v>
       </c>
-      <c r="K10" s="66" t="n">
-        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*E28))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K10" s="73" t="n">
+        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*E28))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>25418336.5852036</v>
       </c>
-      <c r="L10" s="66" t="n">
-        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D10),0),'Control Panel &amp; Inputs'!$C$43*F28))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L10" s="73" t="n">
+        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*F28))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>59292109.9704081</v>
       </c>
-      <c r="M10" s="67" t="n">
+      <c r="M10" s="74" t="n">
         <f aca="false">IRR(G10:L10)</f>
         <v>0.0285913820637419</v>
       </c>
-      <c r="N10" s="68" t="n">
+      <c r="N10" s="75" t="n">
         <f aca="false">AVERAGE(B28:F28)/$F10</f>
         <v>1.47801673485793</v>
       </c>
@@ -6536,53 +7489,53 @@
         <f aca="false">TEXT($B11,"$0.00")&amp;"/kWh @ "&amp;TEXT($C11,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B11" s="64" t="n">
+      <c r="B11" s="71" t="n">
         <v>0.06</v>
       </c>
-      <c r="C11" s="65" t="n">
+      <c r="C11" s="72" t="n">
         <v>0.7</v>
       </c>
-      <c r="D11" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C11</f>
+      <c r="D11" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C11</f>
         <v>229600000</v>
       </c>
-      <c r="E11" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D11</f>
+      <c r="E11" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D11</f>
         <v>98400000</v>
       </c>
-      <c r="F11" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D11)</f>
+      <c r="F11" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D11)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G11" s="66" t="n">
+      <c r="G11" s="73" t="n">
         <f aca="false">-$E11</f>
         <v>-98400000</v>
       </c>
-      <c r="H11" s="66" t="n">
-        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*B29))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H11" s="73" t="n">
+        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*B29))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>5505860.48947304</v>
       </c>
-      <c r="I11" s="66" t="n">
-        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*C29))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I11" s="73" t="n">
+        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*C29))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>15075201.4959102</v>
       </c>
-      <c r="J11" s="66" t="n">
-        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*D29))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J11" s="73" t="n">
+        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*D29))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>16331603.722476</v>
       </c>
-      <c r="K11" s="66" t="n">
-        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*E29))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K11" s="73" t="n">
+        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*E29))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>17609587.4538537</v>
       </c>
-      <c r="L11" s="66" t="n">
-        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D11),0),'Control Panel &amp; Inputs'!$C$43*F29))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L11" s="73" t="n">
+        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*F29))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>51442652.0246042</v>
       </c>
-      <c r="M11" s="67" t="n">
+      <c r="M11" s="74" t="n">
         <f aca="false">IRR(G11:L11)</f>
         <v>0.0192983072718694</v>
       </c>
-      <c r="N11" s="68" t="n">
+      <c r="N11" s="75" t="n">
         <f aca="false">AVERAGE(B29:F29)/$F11</f>
         <v>1.26687148702109</v>
       </c>
@@ -6592,53 +7545,53 @@
         <f aca="false">TEXT($B12,"$0.00")&amp;"/kWh @ "&amp;TEXT($C12,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B12" s="64" t="n">
+      <c r="B12" s="71" t="n">
         <v>0.06</v>
       </c>
-      <c r="C12" s="65" t="n">
+      <c r="C12" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="D12" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C12</f>
+      <c r="D12" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C12</f>
         <v>262400000</v>
       </c>
-      <c r="E12" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D12</f>
+      <c r="E12" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D12</f>
         <v>65600000</v>
       </c>
-      <c r="F12" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D12)</f>
+      <c r="F12" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D12)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G12" s="66" t="n">
+      <c r="G12" s="73" t="n">
         <f aca="false">-$E12</f>
         <v>-65600000</v>
       </c>
-      <c r="H12" s="66" t="n">
-        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*B30))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H12" s="73" t="n">
+        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*B30))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>-2386952.34372452</v>
       </c>
-      <c r="I12" s="66" t="n">
-        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*C30))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I12" s="73" t="n">
+        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*C30))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>7182388.6627126</v>
       </c>
-      <c r="J12" s="66" t="n">
-        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*D30))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J12" s="73" t="n">
+        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*D30))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>8438790.88927846</v>
       </c>
-      <c r="K12" s="66" t="n">
-        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*E30))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K12" s="73" t="n">
+        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*E30))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>9788081.26112565</v>
       </c>
-      <c r="L12" s="66" t="n">
-        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D12),0),'Control Panel &amp; Inputs'!$C$43*F30))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L12" s="73" t="n">
+        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*F30))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>43593194.0788002</v>
       </c>
-      <c r="M12" s="67" t="n">
+      <c r="M12" s="74" t="n">
         <f aca="false">IRR(G12:L12)</f>
         <v>0.00348283951629246</v>
       </c>
-      <c r="N12" s="68" t="n">
+      <c r="N12" s="75" t="n">
         <f aca="false">AVERAGE(B30:F30)/$F12</f>
         <v>1.10851255114345</v>
       </c>
@@ -6648,53 +7601,53 @@
         <f aca="false">TEXT($B13,"$0.00")&amp;"/kWh @ "&amp;TEXT($C13,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B13" s="64" t="n">
+      <c r="B13" s="71" t="n">
         <v>0.08</v>
       </c>
-      <c r="C13" s="65" t="n">
+      <c r="C13" s="72" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C13</f>
+      <c r="D13" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C13</f>
         <v>164000000</v>
       </c>
-      <c r="E13" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D13</f>
+      <c r="E13" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D13</f>
         <v>164000000</v>
       </c>
-      <c r="F13" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D13)</f>
+      <c r="F13" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D13)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G13" s="66" t="n">
+      <c r="G13" s="73" t="n">
         <f aca="false">-$E13</f>
         <v>-164000000</v>
       </c>
-      <c r="H13" s="66" t="n">
-        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*B31))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H13" s="73" t="n">
+        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*B31))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>19969002.9298202</v>
       </c>
-      <c r="I13" s="66" t="n">
-        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*C31))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I13" s="73" t="n">
+        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*C31))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>29511894.2717363</v>
       </c>
-      <c r="J13" s="66" t="n">
-        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*D31))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J13" s="73" t="n">
+        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*D31))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>30741317.8404908</v>
       </c>
-      <c r="K13" s="66" t="n">
-        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*E31))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K13" s="73" t="n">
+        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*E31))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>31949964.6173468</v>
       </c>
-      <c r="L13" s="66" t="n">
-        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D13),0),'Control Panel &amp; Inputs'!$C$43*F31))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L13" s="73" t="n">
+        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*F31))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>65838904.3950213</v>
       </c>
-      <c r="M13" s="67" t="n">
+      <c r="M13" s="74" t="n">
         <f aca="false">IRR(G13:L13)</f>
         <v>0.0236605946278833</v>
       </c>
-      <c r="N13" s="68" t="n">
+      <c r="N13" s="75" t="n">
         <f aca="false">AVERAGE(B31:F31)/$F13</f>
         <v>1.7387414854927</v>
       </c>
@@ -6704,53 +7657,53 @@
         <f aca="false">TEXT($B14,"$0.00")&amp;"/kWh @ "&amp;TEXT($C14,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B14" s="64" t="n">
+      <c r="B14" s="71" t="n">
         <v>0.08</v>
       </c>
-      <c r="C14" s="65" t="n">
+      <c r="C14" s="72" t="n">
         <v>0.6</v>
       </c>
-      <c r="D14" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C14</f>
+      <c r="D14" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C14</f>
         <v>196800000</v>
       </c>
-      <c r="E14" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D14</f>
+      <c r="E14" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D14</f>
         <v>131200000</v>
       </c>
-      <c r="F14" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D14)</f>
+      <c r="F14" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D14)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="73" t="n">
         <f aca="false">-$E14</f>
         <v>-131200000</v>
       </c>
-      <c r="H14" s="66" t="n">
-        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*B32))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H14" s="73" t="n">
+        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*B32))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>12076190.0966226</v>
       </c>
-      <c r="I14" s="66" t="n">
-        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*C32))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I14" s="73" t="n">
+        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*C32))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>21619081.4385388</v>
       </c>
-      <c r="J14" s="66" t="n">
-        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*D32))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J14" s="73" t="n">
+        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*D32))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>22848505.0072933</v>
       </c>
-      <c r="K14" s="66" t="n">
-        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*E32))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K14" s="73" t="n">
+        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*E32))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>24141215.4859969</v>
       </c>
-      <c r="L14" s="66" t="n">
-        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D14),0),'Control Panel &amp; Inputs'!$C$43*F32))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L14" s="73" t="n">
+        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*F32))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>57989446.4492174</v>
       </c>
-      <c r="M14" s="67" t="n">
+      <c r="M14" s="74" t="n">
         <f aca="false">IRR(G14:L14)</f>
         <v>0.015228148095893</v>
       </c>
-      <c r="N14" s="68" t="n">
+      <c r="N14" s="75" t="n">
         <f aca="false">AVERAGE(B32:F32)/$F14</f>
         <v>1.44895123791058</v>
       </c>
@@ -6760,53 +7713,53 @@
         <f aca="false">TEXT($B15,"$0.00")&amp;"/kWh @ "&amp;TEXT($C15,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B15" s="64" t="n">
+      <c r="B15" s="71" t="n">
         <v>0.08</v>
       </c>
-      <c r="C15" s="65" t="n">
+      <c r="C15" s="72" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C15</f>
+      <c r="D15" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C15</f>
         <v>229600000</v>
       </c>
-      <c r="E15" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D15</f>
+      <c r="E15" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D15</f>
         <v>98400000</v>
       </c>
-      <c r="F15" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D15)</f>
+      <c r="F15" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D15)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="73" t="n">
         <f aca="false">-$E15</f>
         <v>-98400000</v>
       </c>
-      <c r="H15" s="66" t="n">
-        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*B33))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H15" s="73" t="n">
+        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*B33))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>4183377.26342504</v>
       </c>
-      <c r="I15" s="66" t="n">
-        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*C33))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I15" s="73" t="n">
+        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*C33))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>13726268.6053412</v>
       </c>
-      <c r="J15" s="66" t="n">
-        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*D33))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J15" s="73" t="n">
+        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*D33))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>14955692.1740957</v>
       </c>
-      <c r="K15" s="66" t="n">
-        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*E33))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K15" s="73" t="n">
+        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*E33))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>16277464.3149753</v>
       </c>
-      <c r="L15" s="66" t="n">
-        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D15),0),'Control Panel &amp; Inputs'!$C$43*F33))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L15" s="73" t="n">
+        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*F33))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>50139988.5034134</v>
       </c>
-      <c r="M15" s="67" t="n">
+      <c r="M15" s="74" t="n">
         <f aca="false">IRR(G15:L15)</f>
         <v>0.00226387121737398</v>
       </c>
-      <c r="N15" s="68" t="n">
+      <c r="N15" s="75" t="n">
         <f aca="false">AVERAGE(B33:F33)/$F15</f>
         <v>1.24195820392335</v>
       </c>
@@ -6816,53 +7769,53 @@
         <f aca="false">TEXT($B16,"$0.00")&amp;"/kWh @ "&amp;TEXT($C16,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B16" s="64" t="n">
+      <c r="B16" s="71" t="n">
         <v>0.08</v>
       </c>
-      <c r="C16" s="65" t="n">
+      <c r="C16" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="D16" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C16</f>
+      <c r="D16" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C16</f>
         <v>262400000</v>
       </c>
-      <c r="E16" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D16</f>
+      <c r="E16" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D16</f>
         <v>65600000</v>
       </c>
-      <c r="F16" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D16)</f>
+      <c r="F16" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D16)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="73" t="n">
         <f aca="false">-$E16</f>
         <v>-65600000</v>
       </c>
-      <c r="H16" s="66" t="n">
-        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*B34))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H16" s="73" t="n">
+        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*B34))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>-3709435.56977252</v>
       </c>
-      <c r="I16" s="66" t="n">
-        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*C34))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I16" s="73" t="n">
+        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*C34))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>5833455.77214364</v>
       </c>
-      <c r="J16" s="66" t="n">
-        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*D34))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J16" s="73" t="n">
+        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*D34))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>7062879.34089813</v>
       </c>
-      <c r="K16" s="66" t="n">
-        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*E34))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K16" s="73" t="n">
+        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*E34))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>8384651.48177771</v>
       </c>
-      <c r="L16" s="66" t="n">
-        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D16),0),'Control Panel &amp; Inputs'!$C$43*F34))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L16" s="73" t="n">
+        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*F34))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>42290530.5576095</v>
       </c>
-      <c r="M16" s="67" t="n">
+      <c r="M16" s="74" t="n">
         <f aca="false">IRR(G16:L16)</f>
         <v>-0.0197751815323907</v>
       </c>
-      <c r="N16" s="68" t="n">
+      <c r="N16" s="75" t="n">
         <f aca="false">AVERAGE(B34:F34)/$F16</f>
         <v>1.08671342843294</v>
       </c>
@@ -6872,53 +7825,53 @@
         <f aca="false">TEXT($B17,"$0.00")&amp;"/kWh @ "&amp;TEXT($C17,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B17" s="64" t="n">
+      <c r="B17" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C17" s="65" t="n">
+      <c r="C17" s="72" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C17</f>
+      <c r="D17" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C17</f>
         <v>164000000</v>
       </c>
-      <c r="E17" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D17</f>
+      <c r="E17" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D17</f>
         <v>164000000</v>
       </c>
-      <c r="F17" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D17)</f>
+      <c r="F17" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D17)</f>
         <v>39464064.1659878</v>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="73" t="n">
         <f aca="false">-$E17</f>
         <v>-164000000</v>
       </c>
-      <c r="H17" s="66" t="n">
-        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*B35))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H17" s="73" t="n">
+        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*B35))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>18646519.7037722</v>
       </c>
-      <c r="I17" s="66" t="n">
-        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*C35))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I17" s="73" t="n">
+        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*C35))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>28162961.3811674</v>
       </c>
-      <c r="J17" s="66" t="n">
-        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*D35))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J17" s="73" t="n">
+        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*D35))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>29365406.2921105</v>
       </c>
-      <c r="K17" s="66" t="n">
-        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*E35))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K17" s="73" t="n">
+        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*E35))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>30659660.2020225</v>
       </c>
-      <c r="L17" s="66" t="n">
-        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D17),0),'Control Panel &amp; Inputs'!$C$43*F35))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L17" s="73" t="n">
+        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*F35))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>64536240.8738305</v>
       </c>
-      <c r="M17" s="67" t="n">
+      <c r="M17" s="74" t="n">
         <f aca="false">IRR(G17:L17)</f>
         <v>0.0125042874959422</v>
       </c>
-      <c r="N17" s="68" t="n">
+      <c r="N17" s="75" t="n">
         <f aca="false">AVERAGE(B35:F35)/$F17</f>
         <v>1.70386288915587</v>
       </c>
@@ -6928,53 +7881,53 @@
         <f aca="false">TEXT($B18,"$0.00")&amp;"/kWh @ "&amp;TEXT($C18,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B18" s="64" t="n">
+      <c r="B18" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" s="65" t="n">
+      <c r="C18" s="72" t="n">
         <v>0.6</v>
       </c>
-      <c r="D18" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C18</f>
+      <c r="D18" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C18</f>
         <v>196800000</v>
       </c>
-      <c r="E18" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D18</f>
+      <c r="E18" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D18</f>
         <v>131200000</v>
       </c>
-      <c r="F18" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D18)</f>
+      <c r="F18" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D18)</f>
         <v>47356876.9991854</v>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="73" t="n">
         <f aca="false">-$E18</f>
         <v>-131200000</v>
       </c>
-      <c r="H18" s="66" t="n">
-        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*B36))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H18" s="73" t="n">
+        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*B36))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>10753706.8705746</v>
       </c>
-      <c r="I18" s="66" t="n">
-        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*C36))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I18" s="73" t="n">
+        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*C36))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>20270148.5479698</v>
       </c>
-      <c r="J18" s="66" t="n">
-        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*D36))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J18" s="73" t="n">
+        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*D36))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>21472593.4589129</v>
       </c>
-      <c r="K18" s="66" t="n">
-        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*E36))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K18" s="73" t="n">
+        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*E36))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>22766847.3688249</v>
       </c>
-      <c r="L18" s="66" t="n">
-        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D18),0),'Control Panel &amp; Inputs'!$C$43*F36))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L18" s="73" t="n">
+        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*F36))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>56686782.9280266</v>
       </c>
-      <c r="M18" s="67" t="n">
+      <c r="M18" s="74" t="n">
         <f aca="false">IRR(G18:L18)</f>
         <v>0.00153624264902171</v>
       </c>
-      <c r="N18" s="68" t="n">
+      <c r="N18" s="75" t="n">
         <f aca="false">AVERAGE(B36:F36)/$F18</f>
         <v>1.41988574096323</v>
       </c>
@@ -6984,53 +7937,53 @@
         <f aca="false">TEXT($B19,"$0.00")&amp;"/kWh @ "&amp;TEXT($C19,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B19" s="64" t="n">
+      <c r="B19" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="72" t="n">
         <v>0.7</v>
       </c>
-      <c r="D19" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C19</f>
+      <c r="D19" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C19</f>
         <v>229600000</v>
       </c>
-      <c r="E19" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D19</f>
+      <c r="E19" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D19</f>
         <v>98400000</v>
       </c>
-      <c r="F19" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D19)</f>
+      <c r="F19" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D19)</f>
         <v>55249689.832383</v>
       </c>
-      <c r="G19" s="66" t="n">
+      <c r="G19" s="73" t="n">
         <f aca="false">-$E19</f>
         <v>-98400000</v>
       </c>
-      <c r="H19" s="66" t="n">
-        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*B37))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H19" s="73" t="n">
+        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*B37))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>2860894.03737704</v>
       </c>
-      <c r="I19" s="66" t="n">
-        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*C37))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I19" s="73" t="n">
+        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*C37))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>12377335.7147722</v>
       </c>
-      <c r="J19" s="66" t="n">
-        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*D37))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J19" s="73" t="n">
+        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*D37))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>13579780.6257153</v>
       </c>
-      <c r="K19" s="66" t="n">
-        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*E37))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K19" s="73" t="n">
+        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*E37))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>14874034.5356273</v>
       </c>
-      <c r="L19" s="66" t="n">
-        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D19),0),'Control Panel &amp; Inputs'!$C$43*F37))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L19" s="73" t="n">
+        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*F37))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>48837324.9822226</v>
       </c>
-      <c r="M19" s="67" t="n">
+      <c r="M19" s="74" t="n">
         <f aca="false">IRR(G19:L19)</f>
         <v>-0.0151406941408555</v>
       </c>
-      <c r="N19" s="68" t="n">
+      <c r="N19" s="75" t="n">
         <f aca="false">AVERAGE(B37:F37)/$F19</f>
         <v>1.21704492082562</v>
       </c>
@@ -7040,495 +7993,495 @@
         <f aca="false">TEXT($B20,"$0.00")&amp;"/kWh @ "&amp;TEXT($C20,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B20" s="64" t="n">
+      <c r="B20" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="C20" s="65" t="n">
+      <c r="C20" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="D20" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35*$C20</f>
+      <c r="D20" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C20</f>
         <v>262400000</v>
       </c>
-      <c r="E20" s="66" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$35-$D20</f>
+      <c r="E20" s="73" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D20</f>
         <v>65600000</v>
       </c>
-      <c r="F20" s="66" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$38,'Control Panel &amp; Inputs'!$C$39,$D20)</f>
+      <c r="F20" s="73" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D20)</f>
         <v>63142502.6655805</v>
       </c>
-      <c r="G20" s="66" t="n">
+      <c r="G20" s="73" t="n">
         <f aca="false">-$E20</f>
         <v>-65600000</v>
       </c>
-      <c r="H20" s="66" t="n">
-        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,1,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*B38))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="H20" s="73" t="n">
+        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*B38))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>-5031918.79582052</v>
       </c>
-      <c r="I20" s="66" t="n">
-        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,2,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*C38))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="I20" s="73" t="n">
+        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*C38))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>4484522.88157468</v>
       </c>
-      <c r="J20" s="66" t="n">
-        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,3,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*D38))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="J20" s="73" t="n">
+        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*D38))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>5686967.79251779</v>
       </c>
-      <c r="K20" s="66" t="n">
-        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,4,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*E38))*'Control Panel &amp; Inputs'!$C$42</f>
+      <c r="K20" s="73" t="n">
+        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*E38))*'Control Panel &amp; Inputs'!$C$47</f>
         <v>6981221.70242975</v>
       </c>
-      <c r="L20" s="66" t="n">
-        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$39,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$41,'Control Panel &amp; Inputs'!$C$35/'Control Panel &amp; Inputs'!$C$41,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$39,-IPMT('Control Panel &amp; Inputs'!$C$38,5,'Control Panel &amp; Inputs'!$C$39,$D20),0),'Control Panel &amp; Inputs'!$C$43*F38))*'Control Panel &amp; Inputs'!$C$42+'Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$36</f>
+      <c r="L20" s="73" t="n">
+        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*F38))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
         <v>40987867.0364187</v>
       </c>
-      <c r="M20" s="67" t="n">
+      <c r="M20" s="74" t="n">
         <f aca="false">IRR(G20:L20)</f>
         <v>-0.0432695354488995</v>
       </c>
-      <c r="N20" s="68" t="n">
+      <c r="N20" s="75" t="n">
         <f aca="false">AVERAGE(B38:F38)/$F20</f>
         <v>1.06491430572242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="52" t="s">
-        <v>364</v>
+      <c r="A21" s="59" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="69" t="str">
+      <c r="A23" s="76" t="str">
         <f aca="false">A5</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B23" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B23" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C23" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C23" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D23" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D23" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E23" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E23" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F23" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F23" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="69" t="str">
+      <c r="A24" s="76" t="str">
         <f aca="false">A6</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B24" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B24" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C24" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C24" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D24" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D24" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E24" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E24" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F24" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F24" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="69" t="str">
+      <c r="A25" s="76" t="str">
         <f aca="false">A7</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B25" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B25" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C25" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C25" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D25" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D25" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E25" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E25" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F25" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F25" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="69" t="str">
+      <c r="A26" s="76" t="str">
         <f aca="false">A8</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B26" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B26" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>62078033.547904</v>
       </c>
-      <c r="C26" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C26" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>71673824.2188621</v>
       </c>
-      <c r="D26" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D26" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>72957205.1032393</v>
       </c>
-      <c r="E26" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E26" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>74334013.7060541</v>
       </c>
-      <c r="F26" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F26" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>75810462.8202446</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="69" t="str">
+      <c r="A27" s="76" t="str">
         <f aca="false">A9</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B27" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B27" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C27" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C27" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D27" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D27" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E27" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E27" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F27" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F27" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="69" t="str">
+      <c r="A28" s="76" t="str">
         <f aca="false">A10</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B28" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B28" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C28" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C28" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D28" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D28" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E28" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E28" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F28" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F28" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="69" t="str">
+      <c r="A29" s="76" t="str">
         <f aca="false">A11</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B29" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B29" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C29" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C29" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D29" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D29" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E29" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E29" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F29" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F29" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="69" t="str">
+      <c r="A30" s="76" t="str">
         <f aca="false">A12</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B30" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B30" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>60755550.321856</v>
       </c>
-      <c r="C30" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C30" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>70324891.3282931</v>
       </c>
-      <c r="D30" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D30" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>71581293.554859</v>
       </c>
-      <c r="E30" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E30" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>72930583.9267062</v>
       </c>
-      <c r="F30" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F30" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>74378964.4453097</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="69" t="str">
+      <c r="A31" s="76" t="str">
         <f aca="false">A13</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B31" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B31" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C31" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C31" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D31" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D31" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E31" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E31" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F31" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F31" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="69" t="str">
+      <c r="A32" s="76" t="str">
         <f aca="false">A14</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B32" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B32" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C32" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C32" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D32" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D32" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E32" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E32" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F32" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F32" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="69" t="str">
+      <c r="A33" s="76" t="str">
         <f aca="false">A15</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B33" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B33" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C33" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C33" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D33" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D33" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E33" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E33" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F33" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F33" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="69" t="str">
+      <c r="A34" s="76" t="str">
         <f aca="false">A16</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B34" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B34" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>59433067.095808</v>
       </c>
-      <c r="C34" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C34" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>68975958.4377242</v>
       </c>
-      <c r="D34" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D34" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>70205382.0064787</v>
       </c>
-      <c r="E34" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E34" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>71527154.1473582</v>
       </c>
-      <c r="F34" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F34" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>72947466.0703748</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="69" t="str">
+      <c r="A35" s="76" t="str">
         <f aca="false">A17</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B35" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B35" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C35" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C35" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D35" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D35" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E35" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E35" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F35" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F35" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="69" t="str">
+      <c r="A36" s="76" t="str">
         <f aca="false">A18</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B36" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B36" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C36" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C36" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D36" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D36" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E36" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E36" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F36" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F36" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="69" t="str">
+      <c r="A37" s="76" t="str">
         <f aca="false">A19</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B37" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B37" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C37" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C37" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D37" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D37" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E37" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E37" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F37" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F37" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="69" t="str">
+      <c r="A38" s="76" t="str">
         <f aca="false">A20</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B38" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,0)</f>
+      <c r="B38" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
         <v>58110583.86976</v>
       </c>
-      <c r="C38" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,1)</f>
+      <c r="C38" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
         <v>67627025.5471552</v>
       </c>
-      <c r="D38" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,2)</f>
+      <c r="D38" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
         <v>68829470.4580983</v>
       </c>
-      <c r="E38" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,3)</f>
+      <c r="E38" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
         <v>70123724.3680103</v>
       </c>
-      <c r="F38" s="66" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$34,4)</f>
+      <c r="F38" s="73" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
         <v>71515967.6954399</v>
       </c>
     </row>
@@ -7547,7 +8500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFC00000"/>
@@ -7563,7 +8516,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7573,7 +8526,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7582,13 +8535,13 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="s">
-        <v>372</v>
+      <c r="A4" s="59" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="B5" s="3" t="str">
         <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
@@ -7612,19 +8565,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
         <v>$0.04 / kWh</v>
       </c>
-      <c r="B6" s="70" t="n">
+      <c r="B6" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M5</f>
         <v>0.0455581791812502</v>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M6</f>
         <v>0.0418311991063475</v>
       </c>
-      <c r="D6" s="70" t="n">
+      <c r="D6" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M7</f>
         <v>0.036027847120873</v>
       </c>
-      <c r="E6" s="70" t="n">
+      <c r="E6" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M8</f>
         <v>0.0261453486370609</v>
       </c>
@@ -7634,19 +8587,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
         <v>$0.06 / kWh</v>
       </c>
-      <c r="B7" s="70" t="n">
+      <c r="B7" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M9</f>
         <v>0.0346975334245463</v>
       </c>
-      <c r="C7" s="70" t="n">
+      <c r="C7" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M10</f>
         <v>0.0285913820637419</v>
       </c>
-      <c r="D7" s="70" t="n">
+      <c r="D7" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M11</f>
         <v>0.0192983072718694</v>
       </c>
-      <c r="E7" s="70" t="n">
+      <c r="E7" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M12</f>
         <v>0.00348283951629246</v>
       </c>
@@ -7656,19 +8609,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
         <v>$0.08 / kWh</v>
       </c>
-      <c r="B8" s="70" t="n">
+      <c r="B8" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M13</f>
         <v>0.0236605946278833</v>
       </c>
-      <c r="C8" s="70" t="n">
+      <c r="C8" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M14</f>
         <v>0.015228148095893</v>
       </c>
-      <c r="D8" s="70" t="n">
+      <c r="D8" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M15</f>
         <v>0.00226387121737398</v>
       </c>
-      <c r="E8" s="70" t="n">
+      <c r="E8" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M16</f>
         <v>-0.0197751815323907</v>
       </c>
@@ -7678,31 +8631,31 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
         <v>$0.10 / kWh</v>
       </c>
-      <c r="B9" s="70" t="n">
+      <c r="B9" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M17</f>
         <v>0.0125042874959422</v>
       </c>
-      <c r="C9" s="70" t="n">
+      <c r="C9" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M18</f>
         <v>0.00153624264902171</v>
       </c>
-      <c r="D9" s="70" t="n">
+      <c r="D9" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M19</f>
         <v>-0.0151406941408555</v>
       </c>
-      <c r="E9" s="70" t="n">
+      <c r="E9" s="77" t="n">
         <f aca="false">'Sensitivity Engine'!M20</f>
         <v>-0.0432695354488995</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
-        <v>374</v>
+      <c r="A12" s="59" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="B13" s="3" t="str">
         <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
@@ -7726,19 +8679,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
         <v>$0.04 / kWh</v>
       </c>
-      <c r="B14" s="71" t="n">
+      <c r="B14" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N5</f>
         <v>1.80849867816635</v>
       </c>
-      <c r="C14" s="71" t="n">
+      <c r="C14" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N6</f>
         <v>1.50708223180529</v>
       </c>
-      <c r="D14" s="71" t="n">
+      <c r="D14" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N7</f>
         <v>1.29178477011882</v>
       </c>
-      <c r="E14" s="71" t="n">
+      <c r="E14" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N8</f>
         <v>1.13031167385397</v>
       </c>
@@ -7748,19 +8701,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
         <v>$0.06 / kWh</v>
       </c>
-      <c r="B15" s="71" t="n">
+      <c r="B15" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N9</f>
         <v>1.77362008182952</v>
       </c>
-      <c r="C15" s="71" t="n">
+      <c r="C15" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N10</f>
         <v>1.47801673485793</v>
       </c>
-      <c r="D15" s="71" t="n">
+      <c r="D15" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N11</f>
         <v>1.26687148702109</v>
       </c>
-      <c r="E15" s="71" t="n">
+      <c r="E15" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N12</f>
         <v>1.10851255114345</v>
       </c>
@@ -7770,19 +8723,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
         <v>$0.08 / kWh</v>
       </c>
-      <c r="B16" s="71" t="n">
+      <c r="B16" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N13</f>
         <v>1.7387414854927</v>
       </c>
-      <c r="C16" s="71" t="n">
+      <c r="C16" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N14</f>
         <v>1.44895123791058</v>
       </c>
-      <c r="D16" s="71" t="n">
+      <c r="D16" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N15</f>
         <v>1.24195820392335</v>
       </c>
-      <c r="E16" s="71" t="n">
+      <c r="E16" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N16</f>
         <v>1.08671342843294</v>
       </c>
@@ -7792,19 +8745,19 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
         <v>$0.10 / kWh</v>
       </c>
-      <c r="B17" s="71" t="n">
+      <c r="B17" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N17</f>
         <v>1.70386288915587</v>
       </c>
-      <c r="C17" s="71" t="n">
+      <c r="C17" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N18</f>
         <v>1.41988574096323</v>
       </c>
-      <c r="D17" s="71" t="n">
+      <c r="D17" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N19</f>
         <v>1.21704492082562</v>
       </c>
-      <c r="E17" s="71" t="n">
+      <c r="E17" s="78" t="n">
         <f aca="false">'Sensitivity Engine'!N20</f>
         <v>1.06491430572242</v>
       </c>
@@ -7824,7 +8777,7 @@
       </colorScale>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>'Control Panel &amp; Inputs'!$C$44</formula>
+      <formula>'Control Panel &amp; Inputs'!$C$49</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:E17">
@@ -7848,376 +8801,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF00B0A0"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
-        <v>379</v>
-      </c>
-      <c r="B6" s="48" t="n">
-        <f aca="false">B5</f>
-        <v>2</v>
-      </c>
-      <c r="C6" s="48" t="n">
-        <f aca="false">B6+C5</f>
-        <v>4</v>
-      </c>
-      <c r="D6" s="48" t="n">
-        <f aca="false">C6+D5</f>
-        <v>8</v>
-      </c>
-      <c r="E6" s="48" t="n">
-        <f aca="false">D6+E5</f>
-        <v>12</v>
-      </c>
-      <c r="F6" s="48" t="n">
-        <f aca="false">E6+F5</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="s">
-        <v>380</v>
-      </c>
-      <c r="B7" s="72" t="n">
-        <f aca="false">B6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>16.528</v>
-      </c>
-      <c r="C7" s="72" t="n">
-        <f aca="false">C6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>33.056</v>
-      </c>
-      <c r="D7" s="72" t="n">
-        <f aca="false">D6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>66.112</v>
-      </c>
-      <c r="E7" s="72" t="n">
-        <f aca="false">E6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>99.168</v>
-      </c>
-      <c r="F7" s="72" t="n">
-        <f aca="false">F6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>132.224</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="s">
-        <v>381</v>
-      </c>
-      <c r="B8" s="48" t="n">
-        <f aca="false">B6*'Unit Economics &amp; KPIs'!$B$5</f>
-        <v>4608</v>
-      </c>
-      <c r="C8" s="48" t="n">
-        <f aca="false">C6*'Unit Economics &amp; KPIs'!$B$5</f>
-        <v>9216</v>
-      </c>
-      <c r="D8" s="48" t="n">
-        <f aca="false">D6*'Unit Economics &amp; KPIs'!$B$5</f>
-        <v>18432</v>
-      </c>
-      <c r="E8" s="48" t="n">
-        <f aca="false">E6*'Unit Economics &amp; KPIs'!$B$5</f>
-        <v>27648</v>
-      </c>
-      <c r="F8" s="48" t="n">
-        <f aca="false">F6*'Unit Economics &amp; KPIs'!$B$5</f>
-        <v>36864</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="s">
-        <v>382</v>
-      </c>
-      <c r="B9" s="72" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$49</f>
-        <v>1.8</v>
-      </c>
-      <c r="C9" s="72" t="n">
-        <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$49</f>
-        <v>3.8</v>
-      </c>
-      <c r="D9" s="72" t="n">
-        <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$49</f>
-        <v>7.6</v>
-      </c>
-      <c r="E9" s="72" t="n">
-        <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$49</f>
-        <v>11.6</v>
-      </c>
-      <c r="F9" s="72" t="n">
-        <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$49</f>
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="53" t="s">
-        <v>383</v>
-      </c>
-      <c r="B10" s="46" t="n">
-        <f aca="false">B9*'Pro Forma Financials'!D$8</f>
-        <v>154035000</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <f aca="false">C9*'Pro Forma Financials'!D$8</f>
-        <v>325185000</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <f aca="false">D9*'Pro Forma Financials'!D$8</f>
-        <v>650370000</v>
-      </c>
-      <c r="E10" s="46" t="n">
-        <f aca="false">E9*'Pro Forma Financials'!D$8</f>
-        <v>992670000</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <f aca="false">F9*'Pro Forma Financials'!D$8</f>
-        <v>1334970000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="s">
-        <v>384</v>
-      </c>
-      <c r="B11" s="46" t="n">
-        <f aca="false">B9*'Pro Forma Financials'!D$14</f>
-        <v>126584804.390928</v>
-      </c>
-      <c r="C11" s="46" t="n">
-        <f aca="false">C9*'Pro Forma Financials'!D$14</f>
-        <v>267234587.047514</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <f aca="false">D9*'Pro Forma Financials'!D$14</f>
-        <v>534469174.095028</v>
-      </c>
-      <c r="E11" s="46" t="n">
-        <f aca="false">E9*'Pro Forma Financials'!D$14</f>
-        <v>815768739.4082</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <f aca="false">F9*'Pro Forma Financials'!D$14</f>
-        <v>1097068304.72137</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
-        <v>385</v>
-      </c>
-      <c r="B12" s="46" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$35</f>
-        <v>656000000</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <f aca="false">C5*'Control Panel &amp; Inputs'!$C$35</f>
-        <v>656000000</v>
-      </c>
-      <c r="D12" s="46" t="n">
-        <f aca="false">D5*'Control Panel &amp; Inputs'!$C$35</f>
-        <v>1312000000</v>
-      </c>
-      <c r="E12" s="46" t="n">
-        <f aca="false">E5*'Control Panel &amp; Inputs'!$C$35</f>
-        <v>1312000000</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <f aca="false">F5*'Control Panel &amp; Inputs'!$C$35</f>
-        <v>1312000000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="s">
-        <v>386</v>
-      </c>
-      <c r="B13" s="46" t="n">
-        <f aca="false">B11-B12</f>
-        <v>-529415195.609072</v>
-      </c>
-      <c r="C13" s="46" t="n">
-        <f aca="false">C11-C12</f>
-        <v>-388765412.952486</v>
-      </c>
-      <c r="D13" s="46" t="n">
-        <f aca="false">D11-D12</f>
-        <v>-777530825.904972</v>
-      </c>
-      <c r="E13" s="46" t="n">
-        <f aca="false">E11-E12</f>
-        <v>-496231260.5918</v>
-      </c>
-      <c r="F13" s="46" t="n">
-        <f aca="false">F11-F12</f>
-        <v>-214931695.278627</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="s">
-        <v>387</v>
-      </c>
-      <c r="B14" s="46" t="n">
-        <f aca="false">B13</f>
-        <v>-529415195.609072</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <f aca="false">B14+C13</f>
-        <v>-918180608.561559</v>
-      </c>
-      <c r="D14" s="46" t="n">
-        <f aca="false">C14+D13</f>
-        <v>-1695711434.46653</v>
-      </c>
-      <c r="E14" s="46" t="n">
-        <f aca="false">D14+E13</f>
-        <v>-2191942695.05833</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <f aca="false">E14+F13</f>
-        <v>-2406874390.33696</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="52" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="55" t="n">
-        <f aca="false">MIN(B14:F14)</f>
-        <v>-2406874390.33696</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="s">
-        <v>389</v>
-      </c>
-      <c r="B18" s="73" t="str">
-        <f aca="false">IF(COUNTIF(B14:F14,"&lt;0")=5,"&gt;5",COUNTIF(B14:F14,"&lt;0")+1)</f>
-        <v>&gt;5</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="53" t="s">
-        <v>390</v>
-      </c>
-      <c r="B19" s="74" t="n">
-        <f aca="false">F7</f>
-        <v>132.224</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="73" t="n">
-        <f aca="false">F8</f>
-        <v>36864</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="53" t="s">
-        <v>391</v>
-      </c>
-      <c r="B21" s="55" t="n">
-        <f aca="false">F6*'Pro Forma Financials'!D$14</f>
-        <v>1125198261.25269</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="55" t="n">
-        <f aca="false">SUM(B12:F12)</f>
-        <v>5248000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/AI_Factory_Model.xlsx
+++ b/AI_Factory_Model.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="443">
   <si>
     <t xml:space="preserve">All values live-linked; edit assumptions on 'Control Panel &amp; Inputs' and everything on this page recalculates</t>
   </si>
@@ -331,6 +331,15 @@
     <t xml:space="preserve">Derived from rack type — required flow at the model's dT</t>
   </si>
   <si>
+    <t xml:space="preserve">VR_Rack_CapEx_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$M/rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived from rack type — reported platform price</t>
+  </si>
+  <si>
     <t xml:space="preserve">VR_Rack_Count</t>
   </si>
   <si>
@@ -355,6 +364,9 @@
     <t xml:space="preserve">Network_Cooling_Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Network_Rack_CapEx_M</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network_Rack_Count</t>
   </si>
   <si>
@@ -373,6 +385,9 @@
     <t xml:space="preserve">Storage_Cooling_Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Storage_Rack_CapEx_M</t>
+  </si>
+  <si>
     <t xml:space="preserve">Storage_Rack_Count</t>
   </si>
   <si>
@@ -475,10 +490,19 @@
     <t xml:space="preserve">Assumption: annual power price escalation</t>
   </si>
   <si>
+    <t xml:space="preserve">Facility_CapEx_Per_MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility-only build cost per MW of IT (benchmark $9.9-12.2M/MW midpoint) — scales with the configured racks</t>
+  </si>
+  <si>
     <t xml:space="preserve">CapEx_Initial</t>
   </si>
   <si>
-    <t xml:space="preserve">All-in benchmark midpoint: ~$91M facility (at $9.9-12.2M/MW) + 32 VR racks at ~$7.4M each (reported $6.0-8.8M). Set to ~$91M if IT is leased/vendor-financed.</t>
+    <t xml:space="preserve">DERIVED: facility $/MW x IT MW + per-rack prices from the Rack Type Library — scales with any rack count/type</t>
   </si>
   <si>
     <t xml:space="preserve">Residual_Value_Pct</t>
@@ -538,10 +562,19 @@
     <t xml:space="preserve">Assumption: hurdle rate for equity NPV</t>
   </si>
   <si>
+    <t xml:space="preserve">Fixed_OpEx_Per_MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/MW/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff, maintenance, insurance, connectivity per MW of IT (calibrated from the prior $10.877M @ 8.264 MW baseline)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixed_OpEx_Annual</t>
   </si>
   <si>
-    <t xml:space="preserve">Staff, maintenance, insurance, connectivity (Year 1)</t>
+    <t xml:space="preserve">DERIVED: fixed OpEx $/MW x configured IT MW</t>
   </si>
   <si>
     <t xml:space="preserve">OpEx_Escalation</t>
@@ -553,16 +586,28 @@
     <t xml:space="preserve">Revenue Strategy</t>
   </si>
   <si>
+    <t xml:space="preserve">Lease_Price_Per_GPU_Hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended bare-metal lease rate (calibrated to the prior $58.8M @ 32-rack baseline; market GB200-class $8-11)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lease_Revenue_70pct</t>
   </si>
   <si>
-    <t xml:space="preserve">70% bare-metal capacity leases (Year 1, pre-ramp)</t>
+    <t xml:space="preserve">DERIVED: lease $/GPU-hr x sold GPU-hours x lease fleet share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token_Price_Per_M_Tok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realized blended token price (calibrated to the prior $25.2M baseline)</t>
   </si>
   <si>
     <t xml:space="preserve">Token_Revenue_30pct</t>
   </si>
   <si>
-    <t xml:space="preserve">30% dynamic API token market (Year 1, pre-ramp)</t>
+    <t xml:space="preserve">DERIVED: token $/M x annual token capacity of the token fleet</t>
   </si>
   <si>
     <t xml:space="preserve">Year1_Ramp_Factor</t>
@@ -637,6 +682,9 @@
     <t xml:space="preserve">Required LPM / Rack</t>
   </si>
   <si>
+    <t xml:space="preserve">Rack CapEx ($M)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes / Source</t>
   </si>
   <si>
@@ -646,25 +694,25 @@
     <t xml:space="preserve">Liquid</t>
   </si>
   <si>
-    <t xml:space="preserve">Reported envelope 130-250 kW; 227 kW = Max-P design point; TDP est.</t>
+    <t xml:space="preserve">Reported envelope 130-250 kW; 227 kW = Max-P; $6.0-8.8M reported</t>
   </si>
   <si>
     <t xml:space="preserve">GB300 NVL72</t>
   </si>
   <si>
-    <t xml:space="preserve">Vendor ~132-142 kW nominal, ~155 kW peak</t>
+    <t xml:space="preserve">Vendor ~132-142 kW nominal, ~155 kW peak; price est.</t>
   </si>
   <si>
     <t xml:space="preserve">GB200 NVL72</t>
   </si>
   <si>
-    <t xml:space="preserve">~120 kW nominal; 130-132 kW observed at full load</t>
+    <t xml:space="preserve">~120 kW nominal; $3.1-3.9M all-in reported</t>
   </si>
   <si>
     <t xml:space="preserve">Rubin Ultra NVL576 (Kyber)</t>
   </si>
   <si>
-    <t xml:space="preserve">Announced; reported up to ~1 MW class — estimate, verify before design</t>
+    <t xml:space="preserve">Announced; power &amp; price are estimates — verify before design</t>
   </si>
   <si>
     <t xml:space="preserve">HGX H100 air rack (4x 8-GPU)</t>
@@ -1138,16 +1186,10 @@
     <t xml:space="preserve">CapEx per MW of IT Load</t>
   </si>
   <si>
-    <t xml:space="preserve">$/MW</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total CapEx / total IT MW</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue per MW of IT Load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$/MW/yr</t>
   </si>
   <si>
     <t xml:space="preserve">Year 2 revenue / total IT MW</t>
@@ -1579,7 +1621,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="89">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1688,7 +1730,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1720,6 +1770,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1740,6 +1802,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1753,6 +1819,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2122,22 +2192,22 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-65600000</c:v>
+                  <c:v>-67023440</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2386952.34372452</c:v>
+                  <c:v>-3748267.8575959</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7182388.6627126</c:v>
+                  <c:v>5823148.96570393</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8438790.88927846</c:v>
+                  <c:v>7080902.40243621</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9788081.26112565</c:v>
+                  <c:v>8431626.85238719</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43593194.0788002</c:v>
+                  <c:v>43084250.8656978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2145,11 +2215,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="92385135"/>
-        <c:axId val="47252808"/>
+        <c:axId val="68827581"/>
+        <c:axId val="37916503"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92385135"/>
+        <c:axId val="68827581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2181,7 +2251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47252808"/>
+        <c:crossAx val="37916503"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2189,7 +2259,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47252808"/>
+        <c:axId val="37916503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2231,7 +2301,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92385135"/>
+        <c:crossAx val="68827581"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2375,19 +2445,19 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-529415195.609072</c:v>
+                  <c:v>-543630019.515064</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-918180608.561559</c:v>
+                  <c:v>-946588505.157977</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1695711434.46653</c:v>
+                  <c:v>-1752505476.4438</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2191942695.05833</c:v>
+                  <c:v>-2277079379.98533</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2406874390.33696</c:v>
+                  <c:v>-2520310215.78255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2402,11 +2472,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98561328"/>
-        <c:axId val="49993432"/>
+        <c:axId val="97053795"/>
+        <c:axId val="63966406"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98561328"/>
+        <c:axId val="97053795"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2438,7 +2508,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49993432"/>
+        <c:crossAx val="63966406"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2446,7 +2516,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49993432"/>
+        <c:axId val="63966406"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2488,7 +2558,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98561328"/>
+        <c:crossAx val="97053795"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2774,7 +2844,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
-        <f aca="false">"AI FACTORY DASHBOARD — "&amp;TEXT('Control Panel &amp; Inputs'!$C$18,"0")&amp;"x "&amp;UPPER('Control Panel &amp; Inputs'!$C$12)&amp;" · "&amp;UPPER('Control Panel &amp; Inputs'!$C$5)</f>
+        <f aca="false">"AI FACTORY DASHBOARD — "&amp;TEXT('Control Panel &amp; Inputs'!$C$19,"0")&amp;"x "&amp;UPPER('Control Panel &amp; Inputs'!$C$12)&amp;" · "&amp;UPPER('Control Panel &amp; Inputs'!$C$5)</f>
         <v>AI FACTORY DASHBOARD — 32x VERA RUBIN NVL72 · ABU DHABI, UAE</v>
       </c>
       <c r="B1" s="1"/>
@@ -2831,7 +2901,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!B36</f>
-        <v>0.00348283951629262</v>
+        <v>-0.0214572858678818</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>7</v>
@@ -2846,7 +2916,7 @@
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!B37</f>
-        <v>0.0473981776304923</v>
+        <v>0.0413579090753861</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>7</v>
@@ -2861,7 +2931,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!B38</f>
-        <v>-29426161.8959998</v>
+        <v>-34982560.663758</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>11</v>
@@ -2876,7 +2946,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">'Pro Forma Financials'!B39</f>
-        <v>1.01548022177123</v>
+        <v>0.905230486955449</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
@@ -2889,9 +2959,9 @@
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="11" t="str">
         <f aca="false">'Pro Forma Financials'!B40</f>
-        <v>4.97670502082603</v>
+        <v>&gt;5 yrs</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>15</v>
@@ -2906,7 +2976,7 @@
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">'Pro Forma Financials'!B41</f>
-        <v>0.962197375096669</v>
+        <v>0.941898686248985</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>13</v>
@@ -2929,7 +2999,7 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!C$8</f>
-        <v>75600000</v>
+        <v>75607223.7909197</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>11</v>
@@ -2944,7 +3014,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">'Pro Forma Financials'!C$14</f>
-        <v>60755550.321856</v>
+        <v>60764350.1127757</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>11</v>
@@ -2959,7 +3029,7 @@
       </c>
       <c r="B15" s="7" t="n">
         <f aca="false">'Pro Forma Financials'!C$15</f>
-        <v>0.803644845527196</v>
+        <v>0.803684450586498</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>7</v>
@@ -3108,7 +3178,7 @@
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B11</f>
-        <v>142361.111111111</v>
+        <v>145450.173611111</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>41</v>
@@ -3123,7 +3193,7 @@
       </c>
       <c r="B27" s="15" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B8</f>
-        <v>5.01323797112521</v>
+        <v>5.01378</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>43</v>
@@ -3138,7 +3208,7 @@
       </c>
       <c r="B28" s="15" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B16</f>
-        <v>0.137869863373019</v>
+        <v>0.137855187976494</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>45</v>
@@ -3153,7 +3223,7 @@
       </c>
       <c r="B29" s="7" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B17</f>
-        <v>0.0472894966018917</v>
+        <v>0.0472843842370427</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>7</v>
@@ -3168,7 +3238,7 @@
       </c>
       <c r="B30" s="16" t="n">
         <f aca="false">'Unit Economics &amp; KPIs'!B18</f>
-        <v>1.12472791389946</v>
+        <v>1.12489238642461</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>48</v>
@@ -3221,7 +3291,7 @@
       </c>
       <c r="B34" s="9" t="n">
         <f aca="false">'Phased Expansion'!B22</f>
-        <v>5248000000</v>
+        <v>5361875200</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>11</v>
@@ -3236,7 +3306,7 @@
       </c>
       <c r="B35" s="9" t="n">
         <f aca="false">'Phased Expansion'!B17</f>
-        <v>-2406874390.33696</v>
+        <v>-2520310215.78255</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>11</v>
@@ -3251,7 +3321,7 @@
       </c>
       <c r="B36" s="9" t="n">
         <f aca="false">'Phased Expansion'!B21</f>
-        <v>1125198261.25269</v>
+        <v>1125372270.97721</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>57</v>
@@ -3272,7 +3342,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>'Control Panel &amp; Inputs'!$C$49</formula>
+      <formula>'Control Panel &amp; Inputs'!$C$53</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
@@ -3311,7 +3381,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3321,7 +3391,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3331,326 +3401,326 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="B5" s="27" t="n">
+        <v>429</v>
+      </c>
+      <c r="B5" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="60" t="s">
-        <v>416</v>
-      </c>
-      <c r="B6" s="55" t="n">
+      <c r="A6" s="67" t="s">
+        <v>430</v>
+      </c>
+      <c r="B6" s="62" t="n">
         <f aca="false">B5</f>
         <v>2</v>
       </c>
-      <c r="C6" s="55" t="n">
+      <c r="C6" s="62" t="n">
         <f aca="false">B6+C5</f>
         <v>4</v>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="62" t="n">
         <f aca="false">C6+D5</f>
         <v>8</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="62" t="n">
         <f aca="false">D6+E5</f>
         <v>12</v>
       </c>
-      <c r="F6" s="55" t="n">
+      <c r="F6" s="62" t="n">
         <f aca="false">E6+F5</f>
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="60" t="s">
-        <v>417</v>
-      </c>
-      <c r="B7" s="79" t="n">
+      <c r="A7" s="67" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" s="86" t="n">
         <f aca="false">B6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>16.528</v>
       </c>
-      <c r="C7" s="79" t="n">
+      <c r="C7" s="86" t="n">
         <f aca="false">C6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>33.056</v>
       </c>
-      <c r="D7" s="79" t="n">
+      <c r="D7" s="86" t="n">
         <f aca="false">D6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>66.112</v>
       </c>
-      <c r="E7" s="79" t="n">
+      <c r="E7" s="86" t="n">
         <f aca="false">E6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>99.168</v>
       </c>
-      <c r="F7" s="79" t="n">
+      <c r="F7" s="86" t="n">
         <f aca="false">F6*('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
         <v>132.224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="60" t="s">
-        <v>418</v>
-      </c>
-      <c r="B8" s="55" t="n">
+      <c r="A8" s="67" t="s">
+        <v>432</v>
+      </c>
+      <c r="B8" s="62" t="n">
         <f aca="false">B6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>4608</v>
       </c>
-      <c r="C8" s="55" t="n">
+      <c r="C8" s="62" t="n">
         <f aca="false">C6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>9216</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="62" t="n">
         <f aca="false">D6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>18432</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="62" t="n">
         <f aca="false">E6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>27648</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="62" t="n">
         <f aca="false">F6*'Unit Economics &amp; KPIs'!$B$5</f>
         <v>36864</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="60" t="s">
-        <v>419</v>
-      </c>
-      <c r="B9" s="79" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="A9" s="67" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="86" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$61</f>
         <v>1.8</v>
       </c>
-      <c r="C9" s="79" t="n">
-        <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="C9" s="86" t="n">
+        <f aca="false">B6+C5*'Control Panel &amp; Inputs'!$C$61</f>
         <v>3.8</v>
       </c>
-      <c r="D9" s="79" t="n">
-        <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="D9" s="86" t="n">
+        <f aca="false">C6+D5*'Control Panel &amp; Inputs'!$C$61</f>
         <v>7.6</v>
       </c>
-      <c r="E9" s="79" t="n">
-        <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="E9" s="86" t="n">
+        <f aca="false">D6+E5*'Control Panel &amp; Inputs'!$C$61</f>
         <v>11.6</v>
       </c>
-      <c r="F9" s="79" t="n">
-        <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="F9" s="86" t="n">
+        <f aca="false">E6+F5*'Control Panel &amp; Inputs'!$C$61</f>
         <v>15.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="B10" s="53" t="n">
+      <c r="A10" s="67" t="s">
+        <v>434</v>
+      </c>
+      <c r="B10" s="60" t="n">
         <f aca="false">B9*'Pro Forma Financials'!D$8</f>
-        <v>154035000</v>
-      </c>
-      <c r="C10" s="53" t="n">
+        <v>154051654.190008</v>
+      </c>
+      <c r="C10" s="60" t="n">
         <f aca="false">C9*'Pro Forma Financials'!D$8</f>
-        <v>325185000</v>
-      </c>
-      <c r="D10" s="53" t="n">
+        <v>325220158.845573</v>
+      </c>
+      <c r="D10" s="60" t="n">
         <f aca="false">D9*'Pro Forma Financials'!D$8</f>
-        <v>650370000</v>
-      </c>
-      <c r="E10" s="53" t="n">
+        <v>650440317.691146</v>
+      </c>
+      <c r="E10" s="60" t="n">
         <f aca="false">E9*'Pro Forma Financials'!D$8</f>
-        <v>992670000</v>
-      </c>
-      <c r="F10" s="53" t="n">
+        <v>992777327.002276</v>
+      </c>
+      <c r="F10" s="60" t="n">
         <f aca="false">F9*'Pro Forma Financials'!D$8</f>
-        <v>1334970000</v>
+        <v>1335114336.31341</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="60" t="s">
-        <v>421</v>
-      </c>
-      <c r="B11" s="53" t="n">
+      <c r="A11" s="67" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" s="60" t="n">
         <f aca="false">B9*'Pro Forma Financials'!D$14</f>
-        <v>126584804.390928</v>
-      </c>
-      <c r="C11" s="53" t="n">
+        <v>126604380.484936</v>
+      </c>
+      <c r="C11" s="60" t="n">
         <f aca="false">C9*'Pro Forma Financials'!D$14</f>
-        <v>267234587.047514</v>
-      </c>
-      <c r="D11" s="53" t="n">
+        <v>267275914.357087</v>
+      </c>
+      <c r="D11" s="60" t="n">
         <f aca="false">D9*'Pro Forma Financials'!D$14</f>
-        <v>534469174.095028</v>
-      </c>
-      <c r="E11" s="53" t="n">
+        <v>534551828.714174</v>
+      </c>
+      <c r="E11" s="60" t="n">
         <f aca="false">E9*'Pro Forma Financials'!D$14</f>
-        <v>815768739.4082</v>
-      </c>
-      <c r="F11" s="53" t="n">
+        <v>815894896.458476</v>
+      </c>
+      <c r="F11" s="60" t="n">
         <f aca="false">F9*'Pro Forma Financials'!D$14</f>
-        <v>1097068304.72137</v>
+        <v>1097237964.20278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="60" t="s">
-        <v>422</v>
-      </c>
-      <c r="B12" s="53" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$40</f>
-        <v>656000000</v>
-      </c>
-      <c r="C12" s="53" t="n">
-        <f aca="false">C5*'Control Panel &amp; Inputs'!$C$40</f>
-        <v>656000000</v>
-      </c>
-      <c r="D12" s="53" t="n">
-        <f aca="false">D5*'Control Panel &amp; Inputs'!$C$40</f>
-        <v>1312000000</v>
-      </c>
-      <c r="E12" s="53" t="n">
-        <f aca="false">E5*'Control Panel &amp; Inputs'!$C$40</f>
-        <v>1312000000</v>
-      </c>
-      <c r="F12" s="53" t="n">
-        <f aca="false">F5*'Control Panel &amp; Inputs'!$C$40</f>
-        <v>1312000000</v>
+      <c r="A12" s="67" t="s">
+        <v>436</v>
+      </c>
+      <c r="B12" s="60" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$44</f>
+        <v>670234400</v>
+      </c>
+      <c r="C12" s="60" t="n">
+        <f aca="false">C5*'Control Panel &amp; Inputs'!$C$44</f>
+        <v>670234400</v>
+      </c>
+      <c r="D12" s="60" t="n">
+        <f aca="false">D5*'Control Panel &amp; Inputs'!$C$44</f>
+        <v>1340468800</v>
+      </c>
+      <c r="E12" s="60" t="n">
+        <f aca="false">E5*'Control Panel &amp; Inputs'!$C$44</f>
+        <v>1340468800</v>
+      </c>
+      <c r="F12" s="60" t="n">
+        <f aca="false">F5*'Control Panel &amp; Inputs'!$C$44</f>
+        <v>1340468800</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="60" t="s">
-        <v>423</v>
-      </c>
-      <c r="B13" s="53" t="n">
+      <c r="A13" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" s="60" t="n">
         <f aca="false">B11-B12</f>
-        <v>-529415195.609072</v>
-      </c>
-      <c r="C13" s="53" t="n">
+        <v>-543630019.515064</v>
+      </c>
+      <c r="C13" s="60" t="n">
         <f aca="false">C11-C12</f>
-        <v>-388765412.952486</v>
-      </c>
-      <c r="D13" s="53" t="n">
+        <v>-402958485.642913</v>
+      </c>
+      <c r="D13" s="60" t="n">
         <f aca="false">D11-D12</f>
-        <v>-777530825.904972</v>
-      </c>
-      <c r="E13" s="53" t="n">
+        <v>-805916971.285826</v>
+      </c>
+      <c r="E13" s="60" t="n">
         <f aca="false">E11-E12</f>
-        <v>-496231260.5918</v>
-      </c>
-      <c r="F13" s="53" t="n">
+        <v>-524573903.541524</v>
+      </c>
+      <c r="F13" s="60" t="n">
         <f aca="false">F11-F12</f>
-        <v>-214931695.278627</v>
+        <v>-243230835.797222</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="60" t="s">
-        <v>424</v>
-      </c>
-      <c r="B14" s="53" t="n">
+      <c r="A14" s="67" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" s="60" t="n">
         <f aca="false">B13</f>
-        <v>-529415195.609072</v>
-      </c>
-      <c r="C14" s="53" t="n">
+        <v>-543630019.515064</v>
+      </c>
+      <c r="C14" s="60" t="n">
         <f aca="false">B14+C13</f>
-        <v>-918180608.561559</v>
-      </c>
-      <c r="D14" s="53" t="n">
+        <v>-946588505.157977</v>
+      </c>
+      <c r="D14" s="60" t="n">
         <f aca="false">C14+D13</f>
-        <v>-1695711434.46653</v>
-      </c>
-      <c r="E14" s="53" t="n">
+        <v>-1752505476.4438</v>
+      </c>
+      <c r="E14" s="60" t="n">
         <f aca="false">D14+E13</f>
-        <v>-2191942695.05833</v>
-      </c>
-      <c r="F14" s="53" t="n">
+        <v>-2277079379.98533</v>
+      </c>
+      <c r="F14" s="60" t="n">
         <f aca="false">E14+F13</f>
-        <v>-2406874390.33696</v>
+        <v>-2520310215.78255</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="59" t="s">
-        <v>425</v>
+      <c r="A16" s="66" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="62" t="n">
+      <c r="B17" s="69" t="n">
         <f aca="false">MIN(B14:F14)</f>
-        <v>-2406874390.33696</v>
+        <v>-2520310215.78255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="60" t="s">
-        <v>426</v>
-      </c>
-      <c r="B18" s="80" t="str">
+      <c r="A18" s="67" t="s">
+        <v>440</v>
+      </c>
+      <c r="B18" s="87" t="str">
         <f aca="false">IF(COUNTIF(B14:F14,"&lt;0")=5,"&gt;5",COUNTIF(B14:F14,"&lt;0")+1)</f>
         <v>&gt;5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="60" t="s">
-        <v>427</v>
-      </c>
-      <c r="B19" s="81" t="n">
+      <c r="A19" s="67" t="s">
+        <v>441</v>
+      </c>
+      <c r="B19" s="88" t="n">
         <f aca="false">F7</f>
         <v>132.224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="80" t="n">
+      <c r="B20" s="87" t="n">
         <f aca="false">F8</f>
         <v>36864</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="60" t="s">
-        <v>428</v>
-      </c>
-      <c r="B21" s="62" t="n">
+      <c r="A21" s="67" t="s">
+        <v>442</v>
+      </c>
+      <c r="B21" s="69" t="n">
         <f aca="false">F6*'Pro Forma Financials'!D$14</f>
-        <v>1125198261.25269</v>
+        <v>1125372270.97721</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="62" t="n">
+      <c r="B22" s="69" t="n">
         <f aca="false">SUM(B12:F12)</f>
-        <v>5248000000</v>
+        <v>5361875200</v>
       </c>
     </row>
   </sheetData>
@@ -3674,7 +3744,7 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -3686,7 +3756,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="str">
-        <f aca="false">"AI FACTORY CONTROL PANEL — "&amp;TEXT($C$18,"0")&amp;"x "&amp;UPPER($C$12)&amp;" — "&amp;UPPER($C$5)</f>
+        <f aca="false">"AI FACTORY CONTROL PANEL — "&amp;TEXT($C$19,"0")&amp;"x "&amp;UPPER($C$12)&amp;" — "&amp;UPPER($C$5)</f>
         <v>AI FACTORY CONTROL PANEL — 32x VERA RUBIN NVL72 — ABU DHABI, UAE</v>
       </c>
       <c r="B1" s="1"/>
@@ -3950,7 +4020,8 @@
         <v>98</v>
       </c>
       <c r="C18" s="27" t="n">
-        <v>32</v>
+        <f aca="false">INDEX('Rack Type Library'!$H$5:$H$13,MATCH($C$12,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>7.4</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>99</v>
@@ -3966,10 +4037,12 @@
       <c r="B19" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="18"/>
       <c r="E19" s="18" t="s">
         <v>103</v>
       </c>
@@ -3981,15 +4054,12 @@
       <c r="B20" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="22" t="n">
-        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$19,'Rack Type Library'!$A$5:$A$13,0))</f>
-        <v>100</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>86</v>
-      </c>
+      <c r="C20" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3997,14 +4067,14 @@
         <v>81</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="28" t="str">
-        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$19,'Rack Type Library'!$A$5:$A$13,0))</f>
-        <v>Air</v>
+        <v>107</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$20,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>100</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>89</v>
@@ -4015,16 +4085,17 @@
         <v>81</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="27" t="n">
-        <v>6</v>
+        <v>108</v>
+      </c>
+      <c r="C22" s="20" t="str">
+        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$20,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>Air</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4032,14 +4103,17 @@
         <v>81</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="C23" s="29" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$H$5:$H$13,MATCH($C$20,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>99</v>
+      </c>
       <c r="E23" s="18" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4049,15 +4123,14 @@
       <c r="B24" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="22" t="n">
-        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$23,'Rack Type Library'!$A$5:$A$13,0))</f>
-        <v>40</v>
+      <c r="C24" s="28" t="n">
+        <v>6</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4065,17 +4138,14 @@
         <v>81</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="28" t="str">
-        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$23,'Rack Type Library'!$A$5:$A$13,0))</f>
-        <v>Air</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>94</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="18"/>
       <c r="E25" s="18" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4083,16 +4153,17 @@
         <v>81</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>10</v>
+        <v>114</v>
+      </c>
+      <c r="C26" s="22" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$D$5:$D$13,MATCH($C$25,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>40</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4100,16 +4171,17 @@
         <v>81</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="29" t="n">
-        <v>0.05</v>
+        <v>115</v>
+      </c>
+      <c r="C27" s="30" t="str">
+        <f aca="false">INDEX('Rack Type Library'!$F$5:$F$13,MATCH($C$25,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>Air</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4117,16 +4189,17 @@
         <v>81</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>0.28</v>
+        <v>116</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <f aca="false">INDEX('Rack Type Library'!$H$5:$H$13,MATCH($C$25,'Rack Type Library'!$A$5:$A$13,0))</f>
+        <v>0.4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4134,16 +4207,16 @@
         <v>81</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="30" t="n">
-        <v>45</v>
+        <v>117</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4151,16 +4224,16 @@
         <v>81</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C30" s="30" t="n">
-        <v>55</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4168,16 +4241,16 @@
         <v>81</v>
       </c>
       <c r="B31" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="31" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="C31" s="31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4185,16 +4258,16 @@
         <v>81</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="31" t="n">
-        <v>1.03</v>
+        <v>124</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>45</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4202,14 +4275,16 @@
         <v>81</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D33" s="18"/>
+        <v>126</v>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>71</v>
+      </c>
       <c r="E33" s="18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4217,16 +4292,16 @@
         <v>81</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="29" t="n">
-        <v>0.85</v>
+        <v>128</v>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>3.85</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4234,16 +4309,16 @@
         <v>81</v>
       </c>
       <c r="B35" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>133</v>
-      </c>
-      <c r="C35" s="32" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,16 +4326,14 @@
         <v>81</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4268,115 +4341,115 @@
         <v>81</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="29" t="n">
-        <v>0.3</v>
+        <v>136</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>0.85</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" s="33" t="n">
-        <v>0.06</v>
+        <v>138</v>
+      </c>
+      <c r="C38" s="34" t="n">
+        <v>0.995</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="29" t="n">
-        <v>0.02</v>
+      <c r="C39" s="28" t="n">
+        <v>1800</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="34" t="n">
-        <v>328000000</v>
+        <v>143</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>0.3</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C41" s="29" t="n">
-        <v>0.1</v>
+        <v>146</v>
+      </c>
+      <c r="C41" s="35" t="n">
+        <v>0.06</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="C42" s="29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="36" t="n">
+        <v>11050000</v>
+      </c>
+      <c r="D43" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="C43" s="29" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>7</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>153</v>
@@ -4384,84 +4457,85 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="27" t="n">
-        <v>5</v>
+      <c r="C44" s="37" t="n">
+        <f aca="false">$C$43*(($C$19*$C$13+$C$24*$C$21+$C$29*$C$26)/1000)+($C$19*$C$18+$C$24*$C$23+$C$29*$C$28)*1000000</f>
+        <v>335117200</v>
       </c>
       <c r="D44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B45" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="18" t="s">
         <v>157</v>
-      </c>
-      <c r="C45" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="C46" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C47" s="29" t="n">
-        <v>0.09</v>
+        <v>160</v>
+      </c>
+      <c r="C47" s="31" t="n">
+        <v>0.065</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="C48" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>164</v>
@@ -4469,16 +4543,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C49" s="29" t="n">
-        <v>0.15</v>
+      <c r="C49" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>7</v>
+        <v>163</v>
       </c>
       <c r="E49" s="18" t="s">
         <v>166</v>
@@ -4486,16 +4560,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C50" s="34" t="n">
-        <v>10877000</v>
+      <c r="C50" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>168</v>
@@ -4503,16 +4577,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B51" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C51" s="29" t="n">
-        <v>0.03</v>
+      <c r="C51" s="31" t="n">
+        <v>0.09</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>170</v>
@@ -4520,50 +4594,50 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="C52" s="34" t="n">
-        <v>58800000</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B53" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="18" t="s">
         <v>174</v>
-      </c>
-      <c r="C53" s="34" t="n">
-        <v>25200000</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="36" t="n">
+        <v>1316000</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="C54" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>177</v>
@@ -4571,16 +4645,17 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C55" s="29" t="n">
-        <v>0</v>
+      <c r="C55" s="38" t="n">
+        <f aca="false">$C$54*(($C$19*$C$13+$C$24*$C$21+$C$29*$C$26)/1000)</f>
+        <v>10875424</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>179</v>
@@ -4588,16 +4663,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="29" t="n">
-        <v>0.15</v>
+      <c r="C56" s="31" t="n">
+        <v>0.03</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>181</v>
@@ -4605,51 +4680,172 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="29" t="n">
-        <v>0.25</v>
+        <v>183</v>
+      </c>
+      <c r="C57" s="39" t="n">
+        <v>4.92</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="37" t="n">
+        <f aca="false">$C$57*$C$19*$C$14*8760*$C$38*$C$37*(1-$C$40)</f>
+        <v>58788412.13952</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" s="39" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C60" s="37" t="n">
+        <f aca="false">$C$59*$C$19*$C$14*$C$40*$C$39*3600*8760*$C$37*$C$38/1000000</f>
+        <v>25219614.2948352</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C63" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="35" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="35" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="35" t="s">
-        <v>190</v>
+      <c r="B65" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="40" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4666,15 +4862,15 @@
       <formula1>RackTypesCompute</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C19" type="list">
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C20" type="list">
       <formula1>RackTypesNetwork</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C23" type="list">
+    <dataValidation allowBlank="false" error="Pick a value from the dropdown (or add a new row to the library sheet first)." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C25" type="list">
       <formula1>RackTypesStorage</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Rack count must be a whole number &gt;= 0." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18 C22 C26" type="whole">
+    <dataValidation allowBlank="false" error="Rack count must be a whole number &gt;= 0." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19 C24 C29" type="whole">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
@@ -4695,7 +4891,7 @@
     <tabColor rgb="FFBF8F00"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4705,12 +4901,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4721,7 +4918,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4732,28 +4929,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4761,242 +4961,269 @@
         <v>83</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="C5" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="42" t="n">
         <v>227</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="41" t="n">
         <v>2300</v>
       </c>
-      <c r="F5" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="39" t="n">
-        <f aca="false">IF($F5="Liquid",$D5/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F5" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="44" t="n">
+        <f aca="false">IF($F5="Liquid",$D5/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>343.462362879839</v>
       </c>
-      <c r="H5" s="18" t="s">
-        <v>203</v>
+      <c r="H5" s="45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="40" t="n">
+        <v>217</v>
+      </c>
+      <c r="C6" s="46" t="n">
         <v>72</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="47" t="n">
         <v>137</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="46" t="n">
         <v>1400</v>
       </c>
-      <c r="F6" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <f aca="false">IF($F6="Liquid",$D6/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F6" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <f aca="false">IF($F6="Liquid",$D6/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>207.287857773295</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>205</v>
+      <c r="H6" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="C7" s="41" t="n">
         <v>72</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="42" t="n">
         <v>121</v>
       </c>
-      <c r="E7" s="36" t="n">
+      <c r="E7" s="41" t="n">
         <v>1200</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="39" t="n">
-        <f aca="false">IF($F7="Liquid",$D7/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="44" t="n">
+        <f aca="false">IF($F7="Liquid",$D7/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>183.079056865465</v>
       </c>
-      <c r="H7" s="18" t="s">
-        <v>207</v>
+      <c r="H7" s="45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="40" t="n">
+        <v>217</v>
+      </c>
+      <c r="C8" s="46" t="n">
         <v>576</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="47" t="n">
         <v>600</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="46" t="n">
         <v>2300</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="43" t="n">
-        <f aca="false">IF($F8="Liquid",$D8/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F8" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" s="49" t="n">
+        <f aca="false">IF($F8="Liquid",$D8/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>907.830034043626</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>209</v>
+      <c r="H8" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="C9" s="41" t="n">
         <v>32</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="42" t="n">
         <v>44</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="41" t="n">
         <v>700</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="G9" s="39" t="n">
-        <f aca="false">IF($F9="Liquid",$D9/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F9" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <f aca="false">IF($F9="Liquid",$D9/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>212</v>
+      <c r="H9" s="45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="40" t="n">
+        <v>229</v>
+      </c>
+      <c r="C10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="47" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <f aca="false">IF($F10="Liquid",$D10/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F10" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="49" t="n">
+        <f aca="false">IF($F10="Liquid",$D10/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>214</v>
+      <c r="H10" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="36" t="n">
+        <v>229</v>
+      </c>
+      <c r="C11" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="42" t="n">
         <v>80</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="39" t="n">
-        <f aca="false">IF($F11="Liquid",$D11/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F11" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G11" s="44" t="n">
+        <f aca="false">IF($F11="Liquid",$D11/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>121.04400453915</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>216</v>
+      <c r="H11" s="45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="40" t="n">
+        <v>233</v>
+      </c>
+      <c r="C12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="47" t="n">
         <v>40</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <f aca="false">IF($F12="Liquid",$D12/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F12" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <f aca="false">IF($F12="Liquid",$D12/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>218</v>
+      <c r="H12" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="36" t="n">
+        <v>233</v>
+      </c>
+      <c r="C13" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="E13" s="36" t="n">
+      <c r="E13" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <f aca="false">IF($F13="Liquid",$D13/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*('Control Panel &amp; Inputs'!$C$30-'Control Panel &amp; Inputs'!$C$29))*60,0)</f>
+      <c r="F13" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" s="44" t="n">
+        <f aca="false">IF($F13="Liquid",$D13/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*('Control Panel &amp; Inputs'!$C$33-'Control Panel &amp; Inputs'!$C$32))*60,0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>220</v>
+      <c r="H13" s="45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +5259,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5042,7 +5269,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5052,22 +5279,22 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5075,277 +5302,277 @@
         <v>64</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" s="44" t="n">
+        <v>245</v>
+      </c>
+      <c r="C5" s="51" t="n">
         <v>0.26</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="42" t="n">
         <v>30</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="45" t="n">
+        <v>248</v>
+      </c>
+      <c r="C6" s="52" t="n">
         <v>0.28</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="47" t="n">
         <v>49.5</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="47" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="44" t="n">
+        <v>248</v>
+      </c>
+      <c r="C7" s="51" t="n">
         <v>0.28</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="42" t="n">
         <v>49</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="42" t="n">
         <v>24</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C8" s="45" t="n">
+        <v>252</v>
+      </c>
+      <c r="C8" s="52" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="47" t="n">
         <v>29.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C9" s="44" t="n">
+        <v>252</v>
+      </c>
+      <c r="C9" s="51" t="n">
         <v>0.28</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="42" t="n">
         <v>39.5</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="42" t="n">
         <v>30</v>
       </c>
       <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="45" t="n">
+        <v>256</v>
+      </c>
+      <c r="C10" s="52" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="47" t="n">
         <v>48.5</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="47" t="n">
         <v>26.5</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C11" s="44" t="n">
+        <v>258</v>
+      </c>
+      <c r="C11" s="51" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="42" t="n">
         <v>43.5</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="42" t="n">
         <v>27.5</v>
       </c>
       <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C12" s="45" t="n">
+        <v>260</v>
+      </c>
+      <c r="C12" s="52" t="n">
         <v>0.19</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="47" t="n">
         <v>39</v>
       </c>
-      <c r="E12" s="41" t="n">
+      <c r="E12" s="47" t="n">
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13" s="44" t="n">
+        <v>263</v>
+      </c>
+      <c r="C13" s="51" t="n">
         <v>0.16</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="42" t="n">
         <v>38.5</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="42" t="n">
         <v>27</v>
       </c>
       <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="45" t="n">
+        <v>263</v>
+      </c>
+      <c r="C14" s="52" t="n">
         <v>0.16</v>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D14" s="47" t="n">
         <v>37.5</v>
       </c>
-      <c r="E14" s="41" t="n">
+      <c r="E14" s="47" t="n">
         <v>23</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="44" t="n">
+        <v>263</v>
+      </c>
+      <c r="C15" s="51" t="n">
         <v>0.16</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="42" t="n">
         <v>22</v>
       </c>
       <c r="F15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C16" s="45" t="n">
+        <v>263</v>
+      </c>
+      <c r="C16" s="52" t="n">
         <v>0.16</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="47" t="n">
         <v>28.5</v>
       </c>
-      <c r="E16" s="41" t="n">
+      <c r="E16" s="47" t="n">
         <v>19.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" s="44" t="n">
+        <v>269</v>
+      </c>
+      <c r="C17" s="51" t="n">
         <v>0.15</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="42" t="n">
         <v>21</v>
       </c>
       <c r="F17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C18" s="45" t="n">
+        <v>258</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <v>0.21</v>
       </c>
-      <c r="D18" s="41" t="n">
+      <c r="D18" s="47" t="n">
         <v>37.5</v>
       </c>
-      <c r="E18" s="41" t="n">
+      <c r="E18" s="47" t="n">
         <v>27.5</v>
       </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="44" t="n">
+        <v>258</v>
+      </c>
+      <c r="C19" s="51" t="n">
         <v>0.21</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="42" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="42" t="n">
         <v>24.5</v>
       </c>
       <c r="F19" s="18"/>
@@ -5383,7 +5610,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5393,7 +5620,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5403,7 +5630,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -5412,149 +5639,149 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$13</f>
+        <v>275</v>
+      </c>
+      <c r="B5" s="44" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$19*'Control Panel &amp; Inputs'!$C$13</f>
         <v>7264</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="43" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$22*'Control Panel &amp; Inputs'!$C$20</f>
+        <v>278</v>
+      </c>
+      <c r="B6" s="49" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$24*'Control Panel &amp; Inputs'!$C$21</f>
         <v>600</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$26*'Control Panel &amp; Inputs'!$C$24</f>
+        <v>280</v>
+      </c>
+      <c r="B7" s="44" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$29*'Control Panel &amp; Inputs'!$C$26</f>
         <v>400</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="43" t="n">
+        <v>282</v>
+      </c>
+      <c r="B8" s="49" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>8264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B9" s="39" t="n">
-        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$21="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$25="Liquid",B7,0)</f>
+        <v>284</v>
+      </c>
+      <c r="B9" s="44" t="n">
+        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",B5,0)+IF('Control Panel &amp; Inputs'!$C$22="Liquid",B6,0)+IF('Control Panel &amp; Inputs'!$C$27="Liquid",B7,0)</f>
         <v>7264</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B10" s="43" t="n">
+        <v>286</v>
+      </c>
+      <c r="B10" s="49" t="n">
         <f aca="false">B8-B9</f>
         <v>1000</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="B11" s="46" t="n">
-        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",'Control Panel &amp; Inputs'!$C$18,0)+IF('Control Panel &amp; Inputs'!$C$21="Liquid",'Control Panel &amp; Inputs'!$C$22,0)+IF('Control Panel &amp; Inputs'!$C$25="Liquid",'Control Panel &amp; Inputs'!$C$26,0)</f>
+        <v>288</v>
+      </c>
+      <c r="B11" s="53" t="n">
+        <f aca="false">IF('Control Panel &amp; Inputs'!$C$16="Liquid",'Control Panel &amp; Inputs'!$C$19,0)+IF('Control Panel &amp; Inputs'!$C$22="Liquid",'Control Panel &amp; Inputs'!$C$24,0)+IF('Control Panel &amp; Inputs'!$C$27="Liquid",'Control Panel &amp; Inputs'!$C$29,0)</f>
         <v>32</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="43" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$29</f>
+        <v>290</v>
+      </c>
+      <c r="B12" s="49" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$32</f>
         <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$30</f>
+        <v>292</v>
+      </c>
+      <c r="B13" s="44" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$33</f>
         <v>55</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>71</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B14" s="43" t="n">
+        <v>294</v>
+      </c>
+      <c r="B14" s="49" t="n">
         <f aca="false">B13-B12</f>
         <v>10</v>
       </c>
@@ -5562,44 +5789,44 @@
         <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" s="39" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*B14)*60</f>
+        <v>296</v>
+      </c>
+      <c r="B15" s="44" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$13/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*B14)*60</f>
         <v>343.462362879839</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" s="43" t="n">
-        <f aca="false">B9/('Control Panel &amp; Inputs'!$C$32*'Control Panel &amp; Inputs'!$C$31*B14)*60</f>
+        <v>298</v>
+      </c>
+      <c r="B16" s="49" t="n">
+        <f aca="false">B9/('Control Panel &amp; Inputs'!$C$35*'Control Panel &amp; Inputs'!$C$34*B14)*60</f>
         <v>10990.7956121548</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="B17" s="44" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$8</f>
         <v>50</v>
       </c>
@@ -5607,14 +5834,14 @@
         <v>71</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B18" s="43" t="n">
+        <v>302</v>
+      </c>
+      <c r="B18" s="49" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$9</f>
         <v>30</v>
       </c>
@@ -5622,100 +5849,100 @@
         <v>71</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B19" s="39" t="n">
+        <v>304</v>
+      </c>
+      <c r="B19" s="44" t="n">
         <f aca="false">B13-B17</f>
         <v>5</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B20" s="43" t="n">
-        <f aca="false">B9*'Control Panel &amp; Inputs'!$C$27</f>
+        <v>307</v>
+      </c>
+      <c r="B20" s="49" t="n">
+        <f aca="false">B9*'Control Panel &amp; Inputs'!$C$30</f>
         <v>363.2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="B21" s="39" t="n">
-        <f aca="false">B10*'Control Panel &amp; Inputs'!$C$28</f>
+        <v>309</v>
+      </c>
+      <c r="B21" s="44" t="n">
+        <f aca="false">B10*'Control Panel &amp; Inputs'!$C$31</f>
         <v>280</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B22" s="43" t="n">
+        <v>311</v>
+      </c>
+      <c r="B22" s="49" t="n">
         <f aca="false">B20+B21</f>
         <v>643.2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B23" s="47" t="n">
+        <v>313</v>
+      </c>
+      <c r="B23" s="54" t="n">
         <f aca="false">B22/B8</f>
         <v>0.0778315585672798</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B24" s="48" t="n">
+        <v>315</v>
+      </c>
+      <c r="B24" s="55" t="n">
         <f aca="false">'Control Panel &amp; Inputs'!$C$7</f>
         <v>0.26</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="B25" s="49" t="n">
+        <v>317</v>
+      </c>
+      <c r="B25" s="56" t="n">
         <f aca="false">(B24-B23)/B24</f>
         <v>0.700647851664309</v>
       </c>
@@ -5723,42 +5950,42 @@
         <v>7</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B26" s="43" t="n">
-        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$34*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>319</v>
+      </c>
+      <c r="B26" s="49" t="n">
+        <f aca="false">B8*'Control Panel &amp; Inputs'!$C$37*'Control Panel &amp; Inputs'!$C$38</f>
         <v>6989.278</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="B27" s="47" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$33</f>
+        <v>321</v>
+      </c>
+      <c r="B27" s="54" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$36</f>
         <v>1.08</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="50" t="n">
+      <c r="B28" s="57" t="n">
         <f aca="false">B26*8760*B27/1000</f>
         <v>66124.1613024</v>
       </c>
@@ -5766,14 +5993,14 @@
         <v>31</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="46" t="n">
+      <c r="B29" s="53" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$11</f>
         <v>9918.62419536</v>
       </c>
@@ -5781,14 +6008,14 @@
         <v>35</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="50" t="n">
+      <c r="B30" s="57" t="n">
         <f aca="false">B28*'Control Panel &amp; Inputs'!$C$10</f>
         <v>25788.422907936</v>
       </c>
@@ -5796,7 +6023,7 @@
         <v>33</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -5829,7 +6056,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5840,7 +6067,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5851,888 +6078,888 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="B5" s="52" t="n">
+      <c r="A5" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="52" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$54</f>
+      <c r="C5" s="59" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$61</f>
         <v>0.9</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="53" t="n">
+      <c r="A6" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,0)*C5</f>
-        <v>52920000</v>
-      </c>
-      <c r="D6" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,1)*D5</f>
-        <v>58800000</v>
-      </c>
-      <c r="E6" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,2)*E5</f>
-        <v>58800000</v>
-      </c>
-      <c r="F6" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,3)*F5</f>
-        <v>58800000</v>
-      </c>
-      <c r="G6" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$52*POWER(1+'Control Panel &amp; Inputs'!$C$55,4)*G5</f>
-        <v>58800000</v>
+      <c r="C6" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$58*POWER(1+'Control Panel &amp; Inputs'!$C$62,0)*C5</f>
+        <v>52909570.925568</v>
+      </c>
+      <c r="D6" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$58*POWER(1+'Control Panel &amp; Inputs'!$C$62,1)*D5</f>
+        <v>58788412.13952</v>
+      </c>
+      <c r="E6" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$58*POWER(1+'Control Panel &amp; Inputs'!$C$62,2)*E5</f>
+        <v>58788412.13952</v>
+      </c>
+      <c r="F6" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$58*POWER(1+'Control Panel &amp; Inputs'!$C$62,3)*F5</f>
+        <v>58788412.13952</v>
+      </c>
+      <c r="G6" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$58*POWER(1+'Control Panel &amp; Inputs'!$C$62,4)*G5</f>
+        <v>58788412.13952</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="B7" s="53" t="n">
+      <c r="A7" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),0)*C5</f>
-        <v>22680000</v>
-      </c>
-      <c r="D7" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),1)*D5</f>
-        <v>26775000</v>
-      </c>
-      <c r="E7" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),2)*E5</f>
-        <v>28448437.5</v>
-      </c>
-      <c r="F7" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),3)*F5</f>
-        <v>30226464.84375</v>
-      </c>
-      <c r="G7" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$53*POWER((1+'Control Panel &amp; Inputs'!$C$57)*(1-'Control Panel &amp; Inputs'!$C$56),4)*G5</f>
-        <v>32115618.8964844</v>
+      <c r="C7" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$60*POWER((1+'Control Panel &amp; Inputs'!$C$64)*(1-'Control Panel &amp; Inputs'!$C$63),0)*C5</f>
+        <v>22697652.8653517</v>
+      </c>
+      <c r="D7" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$60*POWER((1+'Control Panel &amp; Inputs'!$C$64)*(1-'Control Panel &amp; Inputs'!$C$63),1)*D5</f>
+        <v>26795840.1882624</v>
+      </c>
+      <c r="E7" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$60*POWER((1+'Control Panel &amp; Inputs'!$C$64)*(1-'Control Panel &amp; Inputs'!$C$63),2)*E5</f>
+        <v>28470580.2000288</v>
+      </c>
+      <c r="F7" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$60*POWER((1+'Control Panel &amp; Inputs'!$C$64)*(1-'Control Panel &amp; Inputs'!$C$63),3)*F5</f>
+        <v>30249991.4625306</v>
+      </c>
+      <c r="G7" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$60*POWER((1+'Control Panel &amp; Inputs'!$C$64)*(1-'Control Panel &amp; Inputs'!$C$63),4)*G5</f>
+        <v>32140615.9289388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="B8" s="53" t="n">
+      <c r="A8" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="60" t="n">
         <f aca="false">C6+C7</f>
-        <v>75600000</v>
-      </c>
-      <c r="D8" s="53" t="n">
+        <v>75607223.7909197</v>
+      </c>
+      <c r="D8" s="60" t="n">
         <f aca="false">D6+D7</f>
-        <v>85575000</v>
-      </c>
-      <c r="E8" s="53" t="n">
+        <v>85584252.3277824</v>
+      </c>
+      <c r="E8" s="60" t="n">
         <f aca="false">E6+E7</f>
-        <v>87248437.5</v>
-      </c>
-      <c r="F8" s="53" t="n">
+        <v>87258992.3395488</v>
+      </c>
+      <c r="F8" s="60" t="n">
         <f aca="false">F6+F7</f>
-        <v>89026464.84375</v>
-      </c>
-      <c r="G8" s="53" t="n">
+        <v>89038403.6020506</v>
+      </c>
+      <c r="G8" s="60" t="n">
         <f aca="false">G6+G7</f>
-        <v>90915618.8964844</v>
+        <v>90929028.0684588</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="B9" s="54" t="n">
+      <c r="A9" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
+      <c r="C9" s="61" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$41*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
+      <c r="D9" s="61" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$41*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
         <v>0.0612</v>
       </c>
-      <c r="E9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
+      <c r="E9" s="61" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$41*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
         <v>0.062424</v>
       </c>
-      <c r="F9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
+      <c r="F9" s="61" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$41*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
         <v>0.06367248</v>
       </c>
-      <c r="G9" s="54" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$38*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
+      <c r="G9" s="61" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$41*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
         <v>0.0649459296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="B10" s="55" t="n">
+      <c r="A10" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="55" t="n">
+      <c r="C10" s="62" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="D10" s="55" t="n">
+      <c r="D10" s="62" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="62" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="62" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
-      <c r="G10" s="55" t="n">
+      <c r="G10" s="62" t="n">
         <f aca="false">'Thermal Hydraulics &amp; MLC'!$B$28*1000</f>
         <v>66124161.3024</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="B11" s="53" t="n">
+      <c r="A11" s="58" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="53" t="n">
+      <c r="C11" s="60" t="n">
         <f aca="false">C10*C9</f>
         <v>3967449.678144</v>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="60" t="n">
         <f aca="false">D10*D9</f>
         <v>4046798.67170688</v>
       </c>
-      <c r="E11" s="53" t="n">
+      <c r="E11" s="60" t="n">
         <f aca="false">E10*E9</f>
         <v>4127734.64514102</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="60" t="n">
         <f aca="false">F10*F9</f>
         <v>4210289.33804384</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="60" t="n">
         <f aca="false">G10*G9</f>
         <v>4294495.12480471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="53" t="n">
+      <c r="A12" s="58" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,0)</f>
-        <v>10877000</v>
-      </c>
-      <c r="D12" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,1)</f>
-        <v>11203310</v>
-      </c>
-      <c r="E12" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,2)</f>
-        <v>11539409.3</v>
-      </c>
-      <c r="F12" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,3)</f>
-        <v>11885591.579</v>
-      </c>
-      <c r="G12" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$50*POWER(1+'Control Panel &amp; Inputs'!$C$51,4)</f>
-        <v>12242159.32637</v>
+      <c r="C12" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$55*POWER(1+'Control Panel &amp; Inputs'!$C$56,0)</f>
+        <v>10875424</v>
+      </c>
+      <c r="D12" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$55*POWER(1+'Control Panel &amp; Inputs'!$C$56,1)</f>
+        <v>11201686.72</v>
+      </c>
+      <c r="E12" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$55*POWER(1+'Control Panel &amp; Inputs'!$C$56,2)</f>
+        <v>11537737.3216</v>
+      </c>
+      <c r="F12" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$55*POWER(1+'Control Panel &amp; Inputs'!$C$56,3)</f>
+        <v>11883869.441248</v>
+      </c>
+      <c r="G12" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$55*POWER(1+'Control Panel &amp; Inputs'!$C$56,4)</f>
+        <v>12240385.5244854</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="53" t="n">
+      <c r="A13" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="53" t="n">
+      <c r="C13" s="60" t="n">
         <f aca="false">C11+C12</f>
-        <v>14844449.678144</v>
-      </c>
-      <c r="D13" s="53" t="n">
+        <v>14842873.678144</v>
+      </c>
+      <c r="D13" s="60" t="n">
         <f aca="false">D11+D12</f>
-        <v>15250108.6717069</v>
-      </c>
-      <c r="E13" s="53" t="n">
+        <v>15248485.3917069</v>
+      </c>
+      <c r="E13" s="60" t="n">
         <f aca="false">E11+E12</f>
-        <v>15667143.945141</v>
-      </c>
-      <c r="F13" s="53" t="n">
+        <v>15665471.966741</v>
+      </c>
+      <c r="F13" s="60" t="n">
         <f aca="false">F11+F12</f>
-        <v>16095880.9170438</v>
-      </c>
-      <c r="G13" s="53" t="n">
+        <v>16094158.7792918</v>
+      </c>
+      <c r="G13" s="60" t="n">
         <f aca="false">G11+G12</f>
-        <v>16536654.4511747</v>
+        <v>16534880.6492902</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="B14" s="53" t="n">
+      <c r="A14" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="53" t="n">
+      <c r="C14" s="60" t="n">
         <f aca="false">C8-C13</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="D14" s="53" t="n">
+        <v>60764350.1127757</v>
+      </c>
+      <c r="D14" s="60" t="n">
         <f aca="false">D8-D13</f>
-        <v>70324891.3282931</v>
-      </c>
-      <c r="E14" s="53" t="n">
+        <v>70335766.9360755</v>
+      </c>
+      <c r="E14" s="60" t="n">
         <f aca="false">E8-E13</f>
-        <v>71581293.554859</v>
-      </c>
-      <c r="F14" s="53" t="n">
+        <v>71593520.3728078</v>
+      </c>
+      <c r="F14" s="60" t="n">
         <f aca="false">F8-F13</f>
-        <v>72930583.9267062</v>
-      </c>
-      <c r="G14" s="53" t="n">
+        <v>72944244.8227588</v>
+      </c>
+      <c r="G14" s="60" t="n">
         <f aca="false">G8-G13</f>
-        <v>74378964.4453097</v>
+        <v>74394147.4191686</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="B15" s="52" t="n">
+      <c r="A15" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="52" t="n">
+      <c r="C15" s="59" t="n">
         <f aca="false">C14/C8</f>
-        <v>0.803644845527196</v>
-      </c>
-      <c r="D15" s="52" t="n">
+        <v>0.803684450586498</v>
+      </c>
+      <c r="D15" s="59" t="n">
         <f aca="false">D14/D8</f>
-        <v>0.821792478273948</v>
-      </c>
-      <c r="E15" s="52" t="n">
+        <v>0.821830710943105</v>
+      </c>
+      <c r="E15" s="59" t="n">
         <f aca="false">E14/E8</f>
-        <v>0.820430664501688</v>
-      </c>
-      <c r="F15" s="52" t="n">
+        <v>0.820471546293105</v>
+      </c>
+      <c r="F15" s="59" t="n">
         <f aca="false">F14/F8</f>
-        <v>0.819201167368673</v>
-      </c>
-      <c r="G15" s="52" t="n">
+        <v>0.819244751385893</v>
+      </c>
+      <c r="G15" s="59" t="n">
         <f aca="false">G14/G8</f>
-        <v>0.818109862178872</v>
+        <v>0.818156192796415</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40</f>
-        <v>328000000</v>
-      </c>
-      <c r="C16" s="53" t="n">
+      <c r="A16" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44</f>
+        <v>335117200</v>
+      </c>
+      <c r="C16" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="53" t="n">
+      <c r="D16" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="53" t="n">
+      <c r="E16" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="53" t="n">
+      <c r="F16" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="53" t="n">
+      <c r="G16" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="B17" s="53" t="n">
-        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$42</f>
-        <v>262400000</v>
-      </c>
-      <c r="C17" s="53" t="n">
+      <c r="A17" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" s="60" t="n">
+        <f aca="false">B16*'Control Panel &amp; Inputs'!$C$46</f>
+        <v>268093760</v>
+      </c>
+      <c r="C17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="53" t="n">
+      <c r="D17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="53" t="n">
+      <c r="E17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="53" t="n">
+      <c r="F17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="53" t="n">
+      <c r="G17" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" s="53" t="n">
+      <c r="A18" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="60" t="n">
         <f aca="false">B16-B17</f>
-        <v>65600000</v>
-      </c>
-      <c r="C18" s="53" t="n">
+        <v>67023440</v>
+      </c>
+      <c r="C18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="53" t="n">
+      <c r="D18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="53" t="n">
+      <c r="E18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="53" t="n">
+      <c r="F18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="53" t="n">
+      <c r="G18" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="B19" s="53" t="n">
+      <c r="A19" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="B19" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">B17</f>
-        <v>262400000</v>
-      </c>
-      <c r="D19" s="53" t="n">
+        <v>268093760</v>
+      </c>
+      <c r="D19" s="60" t="n">
         <f aca="false">C23</f>
-        <v>216313497.33442</v>
-      </c>
-      <c r="E19" s="53" t="n">
+        <v>221007236.429628</v>
+      </c>
+      <c r="E19" s="60" t="n">
         <f aca="false">D23</f>
-        <v>167231371.995576</v>
-      </c>
-      <c r="F19" s="53" t="n">
+        <v>170860088.827183</v>
+      </c>
+      <c r="F19" s="60" t="n">
         <f aca="false">E23</f>
-        <v>114958908.509708</v>
-      </c>
-      <c r="G19" s="53" t="n">
+        <v>117453376.630578</v>
+      </c>
+      <c r="G19" s="60" t="n">
         <f aca="false">F23</f>
-        <v>59288734.8972587</v>
+        <v>60575228.141194</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="B20" s="53" t="n">
+      <c r="A20" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="B20" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="53" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="D20" s="53" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="E20" s="53" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="F20" s="53" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="G20" s="53" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,B17),0)</f>
-        <v>63142502.6655805</v>
+      <c r="C20" s="60" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,B17),0)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="D20" s="60" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,B17),0)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="E20" s="60" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,B17),0)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="F20" s="60" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,B17),0)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="G20" s="60" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,B17),0)</f>
+        <v>64512617.9703716</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="B21" s="53" t="n">
+      <c r="A21" s="58" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="53" t="n">
-        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$43</f>
-        <v>17056000</v>
-      </c>
-      <c r="D21" s="53" t="n">
-        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$43</f>
-        <v>14060377.3267373</v>
-      </c>
-      <c r="E21" s="53" t="n">
-        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$43</f>
-        <v>10870039.1797125</v>
-      </c>
-      <c r="F21" s="53" t="n">
-        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$43</f>
-        <v>7472329.05313103</v>
-      </c>
-      <c r="G21" s="53" t="n">
-        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$43</f>
-        <v>3853767.76832181</v>
+      <c r="C21" s="60" t="n">
+        <f aca="false">C19*'Control Panel &amp; Inputs'!$C$47</f>
+        <v>17426094.4</v>
+      </c>
+      <c r="D21" s="60" t="n">
+        <f aca="false">D19*'Control Panel &amp; Inputs'!$C$47</f>
+        <v>14365470.3679258</v>
+      </c>
+      <c r="E21" s="60" t="n">
+        <f aca="false">E19*'Control Panel &amp; Inputs'!$C$47</f>
+        <v>11105905.7737669</v>
+      </c>
+      <c r="F21" s="60" t="n">
+        <f aca="false">F19*'Control Panel &amp; Inputs'!$C$47</f>
+        <v>7634469.48098757</v>
+      </c>
+      <c r="G21" s="60" t="n">
+        <f aca="false">G19*'Control Panel &amp; Inputs'!$C$47</f>
+        <v>3937389.82917761</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="B22" s="53" t="n">
+      <c r="A22" s="58" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="53" t="n">
+      <c r="C22" s="60" t="n">
         <f aca="false">C20-C21</f>
-        <v>46086502.6655805</v>
-      </c>
-      <c r="D22" s="53" t="n">
+        <v>47086523.5703716</v>
+      </c>
+      <c r="D22" s="60" t="n">
         <f aca="false">D20-D21</f>
-        <v>49082125.3388433</v>
-      </c>
-      <c r="E22" s="53" t="n">
+        <v>50147147.6024457</v>
+      </c>
+      <c r="E22" s="60" t="n">
         <f aca="false">E20-E21</f>
-        <v>52272463.4858681</v>
-      </c>
-      <c r="F22" s="53" t="n">
+        <v>53406712.1966047</v>
+      </c>
+      <c r="F22" s="60" t="n">
         <f aca="false">F20-F21</f>
-        <v>55670173.6124495</v>
-      </c>
-      <c r="G22" s="53" t="n">
+        <v>56878148.489384</v>
+      </c>
+      <c r="G22" s="60" t="n">
         <f aca="false">G20-G21</f>
-        <v>59288734.8972587</v>
+        <v>60575228.141194</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="B23" s="53" t="n">
+      <c r="A23" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="B23" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="53" t="n">
+      <c r="C23" s="60" t="n">
         <f aca="false">C19-C22</f>
-        <v>216313497.33442</v>
-      </c>
-      <c r="D23" s="53" t="n">
+        <v>221007236.429628</v>
+      </c>
+      <c r="D23" s="60" t="n">
         <f aca="false">D19-D22</f>
-        <v>167231371.995576</v>
-      </c>
-      <c r="E23" s="53" t="n">
+        <v>170860088.827183</v>
+      </c>
+      <c r="E23" s="60" t="n">
         <f aca="false">E19-E22</f>
-        <v>114958908.509708</v>
-      </c>
-      <c r="F23" s="53" t="n">
+        <v>117453376.630578</v>
+      </c>
+      <c r="F23" s="60" t="n">
         <f aca="false">F19-F22</f>
-        <v>59288734.8972587</v>
-      </c>
-      <c r="G23" s="53" t="n">
+        <v>60575228.141194</v>
+      </c>
+      <c r="G23" s="60" t="n">
         <f aca="false">G19-G22</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="B24" s="53" t="n">
+      <c r="A24" s="58" t="s">
+        <v>354</v>
+      </c>
+      <c r="B24" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="53" t="n">
-        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
-        <v>65600000</v>
-      </c>
-      <c r="D24" s="53" t="n">
-        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
-        <v>65600000</v>
-      </c>
-      <c r="E24" s="53" t="n">
-        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
-        <v>65600000</v>
-      </c>
-      <c r="F24" s="53" t="n">
-        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
-        <v>65600000</v>
-      </c>
-      <c r="G24" s="53" t="n">
-        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$46,B16/'Control Panel &amp; Inputs'!$C$46,0)</f>
-        <v>65600000</v>
+      <c r="C24" s="60" t="n">
+        <f aca="false">IF(1&lt;='Control Panel &amp; Inputs'!$C$50,B16/'Control Panel &amp; Inputs'!$C$50,0)</f>
+        <v>67023440</v>
+      </c>
+      <c r="D24" s="60" t="n">
+        <f aca="false">IF(2&lt;='Control Panel &amp; Inputs'!$C$50,B16/'Control Panel &amp; Inputs'!$C$50,0)</f>
+        <v>67023440</v>
+      </c>
+      <c r="E24" s="60" t="n">
+        <f aca="false">IF(3&lt;='Control Panel &amp; Inputs'!$C$50,B16/'Control Panel &amp; Inputs'!$C$50,0)</f>
+        <v>67023440</v>
+      </c>
+      <c r="F24" s="60" t="n">
+        <f aca="false">IF(4&lt;='Control Panel &amp; Inputs'!$C$50,B16/'Control Panel &amp; Inputs'!$C$50,0)</f>
+        <v>67023440</v>
+      </c>
+      <c r="G24" s="60" t="n">
+        <f aca="false">IF(5&lt;='Control Panel &amp; Inputs'!$C$50,B16/'Control Panel &amp; Inputs'!$C$50,0)</f>
+        <v>67023440</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="B25" s="53" t="n">
+      <c r="A25" s="58" t="s">
+        <v>355</v>
+      </c>
+      <c r="B25" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="53" t="n">
-        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$48*C14)</f>
-        <v>17056000</v>
-      </c>
-      <c r="D25" s="53" t="n">
-        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$48*D14)</f>
-        <v>14060377.3267373</v>
-      </c>
-      <c r="E25" s="53" t="n">
-        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$48*E14)</f>
-        <v>10870039.1797125</v>
-      </c>
-      <c r="F25" s="53" t="n">
-        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$48*F14)</f>
-        <v>7472329.05313103</v>
-      </c>
-      <c r="G25" s="53" t="n">
-        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$48*G14)</f>
-        <v>3853767.76832181</v>
+      <c r="C25" s="60" t="n">
+        <f aca="false">MIN(C21,'Control Panel &amp; Inputs'!$C$52*C14)</f>
+        <v>17426094.4</v>
+      </c>
+      <c r="D25" s="60" t="n">
+        <f aca="false">MIN(D21,'Control Panel &amp; Inputs'!$C$52*D14)</f>
+        <v>14365470.3679258</v>
+      </c>
+      <c r="E25" s="60" t="n">
+        <f aca="false">MIN(E21,'Control Panel &amp; Inputs'!$C$52*E14)</f>
+        <v>11105905.7737669</v>
+      </c>
+      <c r="F25" s="60" t="n">
+        <f aca="false">MIN(F21,'Control Panel &amp; Inputs'!$C$52*F14)</f>
+        <v>7634469.48098757</v>
+      </c>
+      <c r="G25" s="60" t="n">
+        <f aca="false">MIN(G21,'Control Panel &amp; Inputs'!$C$52*G14)</f>
+        <v>3937389.82917761</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="B26" s="53" t="n">
+      <c r="A26" s="58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B26" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="53" t="n">
+      <c r="C26" s="60" t="n">
         <f aca="false">C14-C24-C25</f>
-        <v>-21900449.678144</v>
-      </c>
-      <c r="D26" s="53" t="n">
+        <v>-23685184.2872243</v>
+      </c>
+      <c r="D26" s="60" t="n">
         <f aca="false">D14-D24-D25</f>
-        <v>-9335485.99844415</v>
-      </c>
-      <c r="E26" s="53" t="n">
+        <v>-11053143.4318503</v>
+      </c>
+      <c r="E26" s="60" t="n">
         <f aca="false">E14-E24-E25</f>
-        <v>-4888745.62485347</v>
-      </c>
-      <c r="F26" s="53" t="n">
+        <v>-6535825.40095909</v>
+      </c>
+      <c r="F26" s="60" t="n">
         <f aca="false">F14-F24-F25</f>
-        <v>-141745.126424866</v>
-      </c>
-      <c r="G26" s="53" t="n">
+        <v>-1713664.65822881</v>
+      </c>
+      <c r="G26" s="60" t="n">
         <f aca="false">G14-G24-G25</f>
-        <v>4925196.67698786</v>
+        <v>3433317.589991</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="B27" s="53" t="n">
+      <c r="A27" s="58" t="s">
+        <v>357</v>
+      </c>
+      <c r="B27" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="53" t="n">
-        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$47</f>
+      <c r="C27" s="60" t="n">
+        <f aca="false">MAX(0,C26)*'Control Panel &amp; Inputs'!$C$51</f>
         <v>0</v>
       </c>
-      <c r="D27" s="53" t="n">
-        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$47</f>
+      <c r="D27" s="60" t="n">
+        <f aca="false">MAX(0,D26)*'Control Panel &amp; Inputs'!$C$51</f>
         <v>0</v>
       </c>
-      <c r="E27" s="53" t="n">
-        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$47</f>
+      <c r="E27" s="60" t="n">
+        <f aca="false">MAX(0,E26)*'Control Panel &amp; Inputs'!$C$51</f>
         <v>0</v>
       </c>
-      <c r="F27" s="53" t="n">
-        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$47</f>
+      <c r="F27" s="60" t="n">
+        <f aca="false">MAX(0,F26)*'Control Panel &amp; Inputs'!$C$51</f>
         <v>0</v>
       </c>
-      <c r="G27" s="53" t="n">
-        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>443267.700928907</v>
+      <c r="G27" s="60" t="n">
+        <f aca="false">MAX(0,G26)*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>308998.58309919</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="B28" s="53" t="n">
+      <c r="A28" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="53" t="n">
+      <c r="C28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="53" t="n">
+      <c r="D28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="53" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>32800000</v>
+      <c r="G28" s="60" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>33511720</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="56" t="s">
-        <v>343</v>
-      </c>
-      <c r="B29" s="57" t="n">
+      <c r="A29" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B29" s="64" t="n">
         <f aca="false">-B18</f>
-        <v>-65600000</v>
-      </c>
-      <c r="C29" s="57" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="C29" s="64" t="n">
         <f aca="false">C14-C20-C27+C28</f>
-        <v>-2386952.34372452</v>
-      </c>
-      <c r="D29" s="57" t="n">
+        <v>-3748267.8575959</v>
+      </c>
+      <c r="D29" s="64" t="n">
         <f aca="false">D14-D20-D27+D28</f>
-        <v>7182388.6627126</v>
-      </c>
-      <c r="E29" s="57" t="n">
+        <v>5823148.96570393</v>
+      </c>
+      <c r="E29" s="64" t="n">
         <f aca="false">E14-E20-E27+E28</f>
-        <v>8438790.88927846</v>
-      </c>
-      <c r="F29" s="57" t="n">
+        <v>7080902.40243621</v>
+      </c>
+      <c r="F29" s="64" t="n">
         <f aca="false">F14-F20-F27+F28</f>
-        <v>9788081.26112565</v>
-      </c>
-      <c r="G29" s="57" t="n">
+        <v>8431626.85238719</v>
+      </c>
+      <c r="G29" s="64" t="n">
         <f aca="false">G14-G20-G27+G28</f>
-        <v>43593194.0788002</v>
+        <v>43084250.8656978</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="s">
-        <v>344</v>
-      </c>
-      <c r="B30" s="53" t="n">
+      <c r="A30" s="58" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" s="60" t="n">
         <f aca="false">B29</f>
-        <v>-65600000</v>
-      </c>
-      <c r="C30" s="53" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="C30" s="60" t="n">
         <f aca="false">B30+C29</f>
-        <v>-67986952.3437245</v>
-      </c>
-      <c r="D30" s="53" t="n">
+        <v>-70771707.8575959</v>
+      </c>
+      <c r="D30" s="60" t="n">
         <f aca="false">C30+D29</f>
-        <v>-60804563.6810119</v>
-      </c>
-      <c r="E30" s="53" t="n">
+        <v>-64948558.891892</v>
+      </c>
+      <c r="E30" s="60" t="n">
         <f aca="false">D30+E29</f>
-        <v>-52365772.7917335</v>
-      </c>
-      <c r="F30" s="53" t="n">
+        <v>-57867656.4894557</v>
+      </c>
+      <c r="F30" s="60" t="n">
         <f aca="false">E30+F29</f>
-        <v>-42577691.5306078</v>
-      </c>
-      <c r="G30" s="53" t="n">
+        <v>-49436029.6370686</v>
+      </c>
+      <c r="G30" s="60" t="n">
         <f aca="false">F30+G29</f>
-        <v>1015502.54819243</v>
+        <v>-6351778.77137071</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="B31" s="58" t="n">
+      <c r="A31" s="58" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="58" t="n">
+      <c r="C31" s="65" t="n">
         <f aca="false">IF(C20=0,"",C14/C20)</f>
-        <v>0.962197375096669</v>
-      </c>
-      <c r="D31" s="58" t="n">
+        <v>0.941898686248985</v>
+      </c>
+      <c r="D31" s="65" t="n">
         <f aca="false">IF(D20=0,"",D14/D20)</f>
-        <v>1.11374887531387</v>
-      </c>
-      <c r="E31" s="58" t="n">
+        <v>1.09026372125184</v>
+      </c>
+      <c r="E31" s="65" t="n">
         <f aca="false">IF(E20=0,"",E14/E20)</f>
-        <v>1.13364675983739</v>
-      </c>
-      <c r="F31" s="58" t="n">
+        <v>1.10975996053498</v>
+      </c>
+      <c r="F31" s="65" t="n">
         <f aca="false">IF(F20=0,"",F14/F20)</f>
-        <v>1.15501573184335</v>
-      </c>
-      <c r="G31" s="58" t="n">
+        <v>1.13069732895136</v>
+      </c>
+      <c r="G31" s="65" t="n">
         <f aca="false">IF(G20=0,"",G14/G20)</f>
-        <v>1.17795401362598</v>
+        <v>1.15317204230241</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="s">
-        <v>346</v>
-      </c>
-      <c r="B32" s="53" t="n">
+      <c r="A32" s="58" t="s">
+        <v>362</v>
+      </c>
+      <c r="B32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="53" t="n">
-        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$47</f>
+      <c r="C32" s="60" t="n">
+        <f aca="false">MAX(0,C14-C24)*'Control Panel &amp; Inputs'!$C$51</f>
         <v>0</v>
       </c>
-      <c r="D32" s="53" t="n">
-        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>425240.21954638</v>
-      </c>
-      <c r="E32" s="53" t="n">
-        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>538316.419937308</v>
-      </c>
-      <c r="F32" s="53" t="n">
-        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>659752.553403555</v>
-      </c>
-      <c r="G32" s="53" t="n">
-        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>790106.80007787</v>
+      <c r="D32" s="60" t="n">
+        <f aca="false">MAX(0,D14-D24)*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>298109.424246796</v>
+      </c>
+      <c r="E32" s="60" t="n">
+        <f aca="false">MAX(0,E14-E24)*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>411307.233552701</v>
+      </c>
+      <c r="F32" s="60" t="n">
+        <f aca="false">MAX(0,F14-F24)*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>532872.434048289</v>
+      </c>
+      <c r="G32" s="60" t="n">
+        <f aca="false">MAX(0,G14-G24)*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>663363.667725175</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="s">
-        <v>347</v>
-      </c>
-      <c r="B33" s="53" t="n">
+      <c r="A33" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="B33" s="60" t="n">
         <f aca="false">-B16</f>
-        <v>-328000000</v>
-      </c>
-      <c r="C33" s="53" t="n">
+        <v>-335117200</v>
+      </c>
+      <c r="C33" s="60" t="n">
         <f aca="false">C14-C32+C28</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="D33" s="53" t="n">
+        <v>60764350.1127757</v>
+      </c>
+      <c r="D33" s="60" t="n">
         <f aca="false">D14-D32+D28</f>
-        <v>69899651.1087467</v>
-      </c>
-      <c r="E33" s="53" t="n">
+        <v>70037657.5118287</v>
+      </c>
+      <c r="E33" s="60" t="n">
         <f aca="false">E14-E32+E28</f>
-        <v>71042977.1349217</v>
-      </c>
-      <c r="F33" s="53" t="n">
+        <v>71182213.1392551</v>
+      </c>
+      <c r="F33" s="60" t="n">
         <f aca="false">F14-F32+F28</f>
-        <v>72270831.3733026</v>
-      </c>
-      <c r="G33" s="53" t="n">
+        <v>72411372.3887105</v>
+      </c>
+      <c r="G33" s="60" t="n">
         <f aca="false">G14-G32+G28</f>
-        <v>106388857.645232</v>
+        <v>107242503.751443</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="59" t="s">
-        <v>348</v>
+      <c r="A35" s="66" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="61" t="n">
+      <c r="B36" s="68" t="n">
         <f aca="false">IRR(B29:G29)</f>
-        <v>0.00348283951629262</v>
+        <v>-0.0214572858678818</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="61" t="n">
+      <c r="B37" s="68" t="n">
         <f aca="false">IRR(B33:G33)</f>
-        <v>0.0473981776304923</v>
+        <v>0.0413579090753861</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="62" t="n">
-        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$49,C29:G29)</f>
-        <v>-29426161.8959998</v>
+      <c r="B38" s="69" t="n">
+        <f aca="false">B29+NPV('Control Panel &amp; Inputs'!$C$53,C29:G29)</f>
+        <v>-34982560.663758</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="60" t="s">
-        <v>349</v>
-      </c>
-      <c r="B39" s="63" t="n">
+      <c r="A39" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="B39" s="70" t="n">
         <f aca="false">SUM(C29:G29)/-B29</f>
-        <v>1.01548022177123</v>
+        <v>0.905230486955449</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="64" t="n">
+      <c r="B40" s="71" t="str">
         <f aca="false">IFERROR(COUNTIF(B30:G30,"&lt;0")-1+ABS(INDEX(B30:G30,COUNTIF(B30:G30,"&lt;0")))/INDEX(B29:G29,COUNTIF(B30:G30,"&lt;0")+1),"&gt;5 yrs")</f>
-        <v>4.97670502082603</v>
+        <v>&gt;5 yrs</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="63" t="n">
+      <c r="B41" s="70" t="n">
         <f aca="false">MIN(C31:G31)</f>
-        <v>0.962197375096669</v>
+        <v>0.941898686248985</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="60" t="s">
-        <v>350</v>
-      </c>
-      <c r="B42" s="63" t="n">
+      <c r="A42" s="67" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" s="70" t="n">
         <f aca="false">AVERAGE(C31:G31)</f>
-        <v>1.10851255114345</v>
+        <v>1.08515834785792</v>
       </c>
     </row>
   </sheetData>
@@ -6768,7 +6995,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6778,7 +7005,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6797,247 +7024,247 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="46" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$18*'Control Panel &amp; Inputs'!$C$14</f>
+      <c r="B5" s="53" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$19*'Control Panel &amp; Inputs'!$C$14</f>
         <v>2304</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" s="50" t="n">
-        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$35</f>
+        <v>371</v>
+      </c>
+      <c r="B6" s="57" t="n">
+        <f aca="false">B5*8760*'Control Panel &amp; Inputs'!$C$38</f>
         <v>20082124.8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B7" s="46" t="n">
-        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$34</f>
+        <v>374</v>
+      </c>
+      <c r="B7" s="53" t="n">
+        <f aca="false">B6*'Control Panel &amp; Inputs'!$C$37</f>
         <v>17069806.08</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="65" t="n">
+      <c r="B8" s="72" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/B7</f>
-        <v>5.01323797112521</v>
+        <v>5.01378</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="B9" s="66" t="n">
+        <v>377</v>
+      </c>
+      <c r="B9" s="73" t="n">
         <f aca="false">'Pro Forma Financials'!D$13/B7</f>
-        <v>0.893396714657164</v>
+        <v>0.893301618087678</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" s="65" t="n">
+        <v>379</v>
+      </c>
+      <c r="B10" s="72" t="n">
         <f aca="false">B8-B9</f>
-        <v>4.11984125646805</v>
+        <v>4.12047838191232</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="67" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40/B5</f>
-        <v>142361.111111111</v>
+      <c r="B11" s="74" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44/B5</f>
+        <v>145450.173611111</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B12" s="68" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>39690222.6524685</v>
+        <v>382</v>
+      </c>
+      <c r="B12" s="75" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
+        <v>40551452.0813166</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="B13" s="67" t="n">
+        <v>384</v>
+      </c>
+      <c r="B13" s="74" t="n">
         <f aca="false">'Pro Forma Financials'!D$8/('Thermal Hydraulics &amp; MLC'!$B$8/1000)</f>
-        <v>10355154.8886738</v>
+        <v>10356274.4830327</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>370</v>
+        <v>176</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="B14" s="43" t="n">
-        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$37*'Control Panel &amp; Inputs'!$C$36*3600*8760*'Control Panel &amp; Inputs'!$C$34*'Control Panel &amp; Inputs'!$C$35/1000000000000</f>
+        <v>386</v>
+      </c>
+      <c r="B14" s="49" t="n">
+        <f aca="false">B5*'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$39*3600*8760*'Control Panel &amp; Inputs'!$C$37*'Control Panel &amp; Inputs'!$C$38/1000000000000</f>
         <v>33.18370301952</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="B15" s="66" t="n">
+        <v>389</v>
+      </c>
+      <c r="B15" s="73" t="n">
         <f aca="false">'Pro Forma Financials'!D$7/(B14*1000000)</f>
-        <v>0.806871975205717</v>
+        <v>0.8075</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="65" t="n">
-        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$37/(B14*1000000)</f>
-        <v>0.137869863373019</v>
+      <c r="B16" s="72" t="n">
+        <f aca="false">'Pro Forma Financials'!D$13*'Control Panel &amp; Inputs'!$C$40/(B14*1000000)</f>
+        <v>0.137855187976494</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="56" t="n">
         <f aca="false">'Pro Forma Financials'!D$11/'Pro Forma Financials'!D$8</f>
-        <v>0.0472894966018917</v>
+        <v>0.0472843842370427</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="B18" s="69" t="n">
+        <v>393</v>
+      </c>
+      <c r="B18" s="76" t="n">
         <f aca="false">('Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12)/'Pro Forma Financials'!D$10</f>
-        <v>1.12472791389946</v>
+        <v>1.12489238642461</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="B19" s="67" t="n">
+        <v>395</v>
+      </c>
+      <c r="B19" s="74" t="n">
         <f aca="false">'Pro Forma Financials'!D$20+'Pro Forma Financials'!D$13</f>
-        <v>78392611.3372874</v>
+        <v>79761103.3620785</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>57</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="B20" s="70" t="n">
+        <v>397</v>
+      </c>
+      <c r="B20" s="77" t="n">
         <f aca="false">1-B19/'Pro Forma Financials'!D$8</f>
-        <v>0.0839309221468023</v>
+        <v>0.0680399583722673</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -7070,7 +7297,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7088,7 +7315,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7106,46 +7333,46 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7153,55 +7380,55 @@
         <f aca="false">TEXT($B5,"$0.00")&amp;"/kWh @ "&amp;TEXT($C5,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B5" s="71" t="n">
+      <c r="B5" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="C5" s="72" t="n">
+      <c r="C5" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C5</f>
-        <v>164000000</v>
-      </c>
-      <c r="E5" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D5</f>
-        <v>164000000</v>
-      </c>
-      <c r="F5" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D5)</f>
-        <v>39464064.1659878</v>
-      </c>
-      <c r="G5" s="73" t="n">
+      <c r="D5" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C5</f>
+        <v>167558600</v>
+      </c>
+      <c r="E5" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D5</f>
+        <v>167558600</v>
+      </c>
+      <c r="F5" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D5)</f>
+        <v>40320386.2314822</v>
+      </c>
+      <c r="G5" s="80" t="n">
         <f aca="false">-$E5</f>
-        <v>-164000000</v>
-      </c>
-      <c r="H5" s="73" t="n">
-        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*B23))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>22613969.3819162</v>
-      </c>
-      <c r="I5" s="73" t="n">
-        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*C23))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>32209760.0528743</v>
-      </c>
-      <c r="J5" s="73" t="n">
-        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*D23))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>33442432.1818188</v>
-      </c>
-      <c r="K5" s="73" t="n">
-        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*E23))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>34504206.81576</v>
-      </c>
-      <c r="L5" s="73" t="n">
-        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D5),0),'Control Panel &amp; Inputs'!$C$48*F23))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>68444231.4374028</v>
-      </c>
-      <c r="M5" s="74" t="n">
+        <v>-167558600</v>
+      </c>
+      <c r="H5" s="80" t="n">
+        <f aca="false">B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F5,0)-MAX(0,B23-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D5),0),'Control Panel &amp; Inputs'!$C$52*B23))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>21766447.1073414</v>
+      </c>
+      <c r="I5" s="80" t="n">
+        <f aca="false">C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F5,0)-MAX(0,C23-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D5),0),'Control Panel &amp; Inputs'!$C$52*C23))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>31364313.5951622</v>
+      </c>
+      <c r="J5" s="80" t="n">
+        <f aca="false">D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F5,0)-MAX(0,D23-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D5),0),'Control Panel &amp; Inputs'!$C$52*D23))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>32649045.6897059</v>
+      </c>
+      <c r="K5" s="80" t="n">
+        <f aca="false">E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F5,0)-MAX(0,E23-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D5),0),'Control Panel &amp; Inputs'!$C$52*E23))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>33797546.1647404</v>
+      </c>
+      <c r="L5" s="80" t="n">
+        <f aca="false">F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F5,0)-MAX(0,F23-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D5),0),'Control Panel &amp; Inputs'!$C$52*F23))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>68446259.2190432</v>
+      </c>
+      <c r="M5" s="81" t="n">
         <f aca="false">IRR(G5:L5)</f>
-        <v>0.0455581791812502</v>
-      </c>
-      <c r="N5" s="75" t="n">
+        <v>0.0337070096722301</v>
+      </c>
+      <c r="N5" s="82" t="n">
         <f aca="false">AVERAGE(B23:F23)/$F5</f>
-        <v>1.80849867816635</v>
+        <v>1.77039120326773</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7209,55 +7436,55 @@
         <f aca="false">TEXT($B6,"$0.00")&amp;"/kWh @ "&amp;TEXT($C6,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B6" s="71" t="n">
+      <c r="B6" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="C6" s="72" t="n">
+      <c r="C6" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D6" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C6</f>
-        <v>196800000</v>
-      </c>
-      <c r="E6" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D6</f>
-        <v>131200000</v>
-      </c>
-      <c r="F6" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D6)</f>
-        <v>47356876.9991854</v>
-      </c>
-      <c r="G6" s="73" t="n">
+      <c r="D6" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C6</f>
+        <v>201070320</v>
+      </c>
+      <c r="E6" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D6</f>
+        <v>134046880</v>
+      </c>
+      <c r="F6" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D6)</f>
+        <v>48384463.4777787</v>
+      </c>
+      <c r="G6" s="80" t="n">
         <f aca="false">-$E6</f>
-        <v>-131200000</v>
-      </c>
-      <c r="H6" s="73" t="n">
-        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*B24))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>14721156.5487186</v>
-      </c>
-      <c r="I6" s="73" t="n">
-        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*C24))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>24316947.2196767</v>
-      </c>
-      <c r="J6" s="73" t="n">
-        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*D24))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>25600328.1040539</v>
-      </c>
-      <c r="K6" s="73" t="n">
-        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*E24))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>26695457.6844102</v>
-      </c>
-      <c r="L6" s="73" t="n">
-        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D6),0),'Control Panel &amp; Inputs'!$C$48*F24))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>60594773.4915989</v>
-      </c>
-      <c r="M6" s="74" t="n">
+        <v>-134046880</v>
+      </c>
+      <c r="H6" s="80" t="n">
+        <f aca="false">B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F6,0)-MAX(0,B24-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D6),0),'Control Panel &amp; Inputs'!$C$52*B24))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>13702369.861045</v>
+      </c>
+      <c r="I6" s="80" t="n">
+        <f aca="false">C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F6,0)-MAX(0,C24-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D6),0),'Control Panel &amp; Inputs'!$C$52*C24))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>23300236.3488658</v>
+      </c>
+      <c r="J6" s="80" t="n">
+        <f aca="false">D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F6,0)-MAX(0,D24-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D6),0),'Control Panel &amp; Inputs'!$C$52*D24))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>24584968.4434094</v>
+      </c>
+      <c r="K6" s="80" t="n">
+        <f aca="false">E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F6,0)-MAX(0,E24-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D6),0),'Control Panel &amp; Inputs'!$C$52*E24))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>25819356.7001051</v>
+      </c>
+      <c r="L6" s="80" t="n">
+        <f aca="false">F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F6,0)-MAX(0,F24-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D6),0),'Control Panel &amp; Inputs'!$C$52*F24))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>60426477.608325</v>
+      </c>
+      <c r="M6" s="81" t="n">
         <f aca="false">IRR(G6:L6)</f>
-        <v>0.0418311991063475</v>
-      </c>
-      <c r="N6" s="75" t="n">
+        <v>0.0273884979465043</v>
+      </c>
+      <c r="N6" s="82" t="n">
         <f aca="false">AVERAGE(B24:F24)/$F6</f>
-        <v>1.50708223180529</v>
+        <v>1.47532600272311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7265,55 +7492,55 @@
         <f aca="false">TEXT($B7,"$0.00")&amp;"/kWh @ "&amp;TEXT($C7,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B7" s="71" t="n">
+      <c r="B7" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="C7" s="72" t="n">
+      <c r="C7" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C7</f>
-        <v>229600000</v>
-      </c>
-      <c r="E7" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D7</f>
-        <v>98400000</v>
-      </c>
-      <c r="F7" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D7)</f>
-        <v>55249689.832383</v>
-      </c>
-      <c r="G7" s="73" t="n">
+      <c r="D7" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C7</f>
+        <v>234582040</v>
+      </c>
+      <c r="E7" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D7</f>
+        <v>100535160</v>
+      </c>
+      <c r="F7" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D7)</f>
+        <v>56448540.7240751</v>
+      </c>
+      <c r="G7" s="80" t="n">
         <f aca="false">-$E7</f>
-        <v>-98400000</v>
-      </c>
-      <c r="H7" s="73" t="n">
-        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*B25))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>6828343.71552104</v>
-      </c>
-      <c r="I7" s="73" t="n">
-        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*C25))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>16424134.3864791</v>
-      </c>
-      <c r="J7" s="73" t="n">
-        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*D25))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>17707515.2708564</v>
-      </c>
-      <c r="K7" s="73" t="n">
-        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*E25))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>18886708.5530603</v>
-      </c>
-      <c r="L7" s="73" t="n">
-        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D7),0),'Control Panel &amp; Inputs'!$C$48*F25))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>52745315.5457949</v>
-      </c>
-      <c r="M7" s="74" t="n">
+        <v>-100535160</v>
+      </c>
+      <c r="H7" s="80" t="n">
+        <f aca="false">B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F7,0)-MAX(0,B25-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D7),0),'Control Panel &amp; Inputs'!$C$52*B25))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>5638292.61474855</v>
+      </c>
+      <c r="I7" s="80" t="n">
+        <f aca="false">C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F7,0)-MAX(0,C25-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D7),0),'Control Panel &amp; Inputs'!$C$52*C25))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>15236159.1025694</v>
+      </c>
+      <c r="J7" s="80" t="n">
+        <f aca="false">D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F7,0)-MAX(0,D25-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D7),0),'Control Panel &amp; Inputs'!$C$52*D25))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>16520891.197113</v>
+      </c>
+      <c r="K7" s="80" t="n">
+        <f aca="false">E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F7,0)-MAX(0,E25-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D7),0),'Control Panel &amp; Inputs'!$C$52*E25))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>17841167.2354697</v>
+      </c>
+      <c r="L7" s="80" t="n">
+        <f aca="false">F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F7,0)-MAX(0,F25-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D7),0),'Control Panel &amp; Inputs'!$C$52*F25))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>52406695.9976068</v>
+      </c>
+      <c r="M7" s="81" t="n">
         <f aca="false">IRR(G7:L7)</f>
-        <v>0.036027847120873</v>
-      </c>
-      <c r="N7" s="75" t="n">
+        <v>0.0177702105428679</v>
+      </c>
+      <c r="N7" s="82" t="n">
         <f aca="false">AVERAGE(B25:F25)/$F7</f>
-        <v>1.29178477011882</v>
+        <v>1.26456514519123</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7321,55 +7548,55 @@
         <f aca="false">TEXT($B8,"$0.00")&amp;"/kWh @ "&amp;TEXT($C8,"0%")&amp;" debt"</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B8" s="71" t="n">
+      <c r="B8" s="78" t="n">
         <v>0.04</v>
       </c>
-      <c r="C8" s="72" t="n">
+      <c r="C8" s="79" t="n">
         <v>0.8</v>
       </c>
-      <c r="D8" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C8</f>
-        <v>262400000</v>
-      </c>
-      <c r="E8" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D8</f>
-        <v>65600000</v>
-      </c>
-      <c r="F8" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D8)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="G8" s="73" t="n">
+      <c r="D8" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C8</f>
+        <v>268093760</v>
+      </c>
+      <c r="E8" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D8</f>
+        <v>67023440</v>
+      </c>
+      <c r="F8" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D8)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="G8" s="80" t="n">
         <f aca="false">-$E8</f>
-        <v>-65600000</v>
-      </c>
-      <c r="H8" s="73" t="n">
-        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*B26))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>-1064469.11767652</v>
-      </c>
-      <c r="I8" s="73" t="n">
-        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*C26))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>8531321.55328157</v>
-      </c>
-      <c r="J8" s="73" t="n">
-        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*D26))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>9814702.43765881</v>
-      </c>
-      <c r="K8" s="73" t="n">
-        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*E26))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>11077959.4217105</v>
-      </c>
-      <c r="L8" s="73" t="n">
-        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D8),0),'Control Panel &amp; Inputs'!$C$48*F26))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>44895857.599991</v>
-      </c>
-      <c r="M8" s="74" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="H8" s="80" t="n">
+        <f aca="false">B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F8,0)-MAX(0,B26-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D8),0),'Control Panel &amp; Inputs'!$C$52*B26))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>-2425784.6315479</v>
+      </c>
+      <c r="I8" s="80" t="n">
+        <f aca="false">C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F8,0)-MAX(0,C26-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D8),0),'Control Panel &amp; Inputs'!$C$52*C26))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>7172081.85627291</v>
+      </c>
+      <c r="J8" s="80" t="n">
+        <f aca="false">D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F8,0)-MAX(0,D26-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D8),0),'Control Panel &amp; Inputs'!$C$52*D26))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>8456813.95081654</v>
+      </c>
+      <c r="K8" s="80" t="n">
+        <f aca="false">E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F8,0)-MAX(0,E26-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D8),0),'Control Panel &amp; Inputs'!$C$52*E26))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>9835056.63173513</v>
+      </c>
+      <c r="L8" s="80" t="n">
+        <f aca="false">F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F8,0)-MAX(0,F26-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D8),0),'Control Panel &amp; Inputs'!$C$52*F26))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>44386914.3868886</v>
+      </c>
+      <c r="M8" s="81" t="n">
         <f aca="false">IRR(G8:L8)</f>
-        <v>0.0261453486370609</v>
-      </c>
-      <c r="N8" s="75" t="n">
+        <v>0.00135032626637098</v>
+      </c>
+      <c r="N8" s="82" t="n">
         <f aca="false">AVERAGE(B26:F26)/$F8</f>
-        <v>1.13031167385397</v>
+        <v>1.10649450204233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7377,55 +7604,55 @@
         <f aca="false">TEXT($B9,"$0.00")&amp;"/kWh @ "&amp;TEXT($C9,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B9" s="71" t="n">
+      <c r="B9" s="78" t="n">
         <v>0.06</v>
       </c>
-      <c r="C9" s="72" t="n">
+      <c r="C9" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C9</f>
-        <v>164000000</v>
-      </c>
-      <c r="E9" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D9</f>
-        <v>164000000</v>
-      </c>
-      <c r="F9" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D9)</f>
-        <v>39464064.1659878</v>
-      </c>
-      <c r="G9" s="73" t="n">
+      <c r="D9" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C9</f>
+        <v>167558600</v>
+      </c>
+      <c r="E9" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D9</f>
+        <v>167558600</v>
+      </c>
+      <c r="F9" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D9)</f>
+        <v>40320386.2314822</v>
+      </c>
+      <c r="G9" s="80" t="n">
         <f aca="false">-$E9</f>
-        <v>-164000000</v>
-      </c>
-      <c r="H9" s="73" t="n">
-        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*B27))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>21291486.1558682</v>
-      </c>
-      <c r="I9" s="73" t="n">
-        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*C27))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>30860827.1623053</v>
-      </c>
-      <c r="J9" s="73" t="n">
-        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*D27))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>32117229.3888712</v>
-      </c>
-      <c r="K9" s="73" t="n">
-        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*E27))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>33227085.7165534</v>
-      </c>
-      <c r="L9" s="73" t="n">
-        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D9),0),'Control Panel &amp; Inputs'!$C$48*F27))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>67141567.9162121</v>
-      </c>
-      <c r="M9" s="74" t="n">
+        <v>-167558600</v>
+      </c>
+      <c r="H9" s="80" t="n">
+        <f aca="false">B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F9,0)-MAX(0,B27-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D9),0),'Control Panel &amp; Inputs'!$C$52*B27))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>20443963.8812934</v>
+      </c>
+      <c r="I9" s="80" t="n">
+        <f aca="false">C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F9,0)-MAX(0,C27-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D9),0),'Control Panel &amp; Inputs'!$C$52*C27))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>30015380.7045933</v>
+      </c>
+      <c r="J9" s="80" t="n">
+        <f aca="false">D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F9,0)-MAX(0,D27-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D9),0),'Control Panel &amp; Inputs'!$C$52*D27))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>31273134.1413255</v>
+      </c>
+      <c r="K9" s="80" t="n">
+        <f aca="false">E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F9,0)-MAX(0,E27-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D9),0),'Control Panel &amp; Inputs'!$C$52*E27))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>32520425.0655338</v>
+      </c>
+      <c r="L9" s="80" t="n">
+        <f aca="false">F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F9,0)-MAX(0,F27-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D9),0),'Control Panel &amp; Inputs'!$C$52*F27))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>67143595.6978524</v>
+      </c>
+      <c r="M9" s="81" t="n">
         <f aca="false">IRR(G9:L9)</f>
-        <v>0.0346975334245463</v>
-      </c>
-      <c r="N9" s="75" t="n">
+        <v>0.0228912959711814</v>
+      </c>
+      <c r="N9" s="82" t="n">
         <f aca="false">AVERAGE(B27:F27)/$F9</f>
-        <v>1.77362008182952</v>
+        <v>1.73625335657266</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7433,55 +7660,55 @@
         <f aca="false">TEXT($B10,"$0.00")&amp;"/kWh @ "&amp;TEXT($C10,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B10" s="71" t="n">
+      <c r="B10" s="78" t="n">
         <v>0.06</v>
       </c>
-      <c r="C10" s="72" t="n">
+      <c r="C10" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D10" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C10</f>
-        <v>196800000</v>
-      </c>
-      <c r="E10" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D10</f>
-        <v>131200000</v>
-      </c>
-      <c r="F10" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D10)</f>
-        <v>47356876.9991854</v>
-      </c>
-      <c r="G10" s="73" t="n">
+      <c r="D10" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C10</f>
+        <v>201070320</v>
+      </c>
+      <c r="E10" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D10</f>
+        <v>134046880</v>
+      </c>
+      <c r="F10" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D10)</f>
+        <v>48384463.4777787</v>
+      </c>
+      <c r="G10" s="80" t="n">
         <f aca="false">-$E10</f>
-        <v>-131200000</v>
-      </c>
-      <c r="H10" s="73" t="n">
-        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*B28))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>13398673.3226706</v>
-      </c>
-      <c r="I10" s="73" t="n">
-        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*C28))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>22968014.3291077</v>
-      </c>
-      <c r="J10" s="73" t="n">
-        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*D28))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>24224416.5556736</v>
-      </c>
-      <c r="K10" s="73" t="n">
-        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*E28))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>25418336.5852036</v>
-      </c>
-      <c r="L10" s="73" t="n">
-        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D10),0),'Control Panel &amp; Inputs'!$C$48*F28))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>59292109.9704081</v>
-      </c>
-      <c r="M10" s="74" t="n">
+        <v>-134046880</v>
+      </c>
+      <c r="H10" s="80" t="n">
+        <f aca="false">B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F10,0)-MAX(0,B28-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D10),0),'Control Panel &amp; Inputs'!$C$52*B28))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>12379886.634997</v>
+      </c>
+      <c r="I10" s="80" t="n">
+        <f aca="false">C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F10,0)-MAX(0,C28-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D10),0),'Control Panel &amp; Inputs'!$C$52*C28))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>21951303.4582968</v>
+      </c>
+      <c r="J10" s="80" t="n">
+        <f aca="false">D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F10,0)-MAX(0,D28-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D10),0),'Control Panel &amp; Inputs'!$C$52*D28))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>23209056.8950291</v>
+      </c>
+      <c r="K10" s="80" t="n">
+        <f aca="false">E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F10,0)-MAX(0,E28-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D10),0),'Control Panel &amp; Inputs'!$C$52*E28))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>24542235.6008985</v>
+      </c>
+      <c r="L10" s="80" t="n">
+        <f aca="false">F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F10,0)-MAX(0,F28-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D10),0),'Control Panel &amp; Inputs'!$C$52*F28))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>59123814.0871342</v>
+      </c>
+      <c r="M10" s="81" t="n">
         <f aca="false">IRR(G10:L10)</f>
-        <v>0.0285913820637419</v>
-      </c>
-      <c r="N10" s="75" t="n">
+        <v>0.0142907188238313</v>
+      </c>
+      <c r="N10" s="82" t="n">
         <f aca="false">AVERAGE(B28:F28)/$F10</f>
-        <v>1.47801673485793</v>
+        <v>1.44687779714389</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7489,55 +7716,55 @@
         <f aca="false">TEXT($B11,"$0.00")&amp;"/kWh @ "&amp;TEXT($C11,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B11" s="71" t="n">
+      <c r="B11" s="78" t="n">
         <v>0.06</v>
       </c>
-      <c r="C11" s="72" t="n">
+      <c r="C11" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D11" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C11</f>
-        <v>229600000</v>
-      </c>
-      <c r="E11" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D11</f>
-        <v>98400000</v>
-      </c>
-      <c r="F11" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D11)</f>
-        <v>55249689.832383</v>
-      </c>
-      <c r="G11" s="73" t="n">
+      <c r="D11" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C11</f>
+        <v>234582040</v>
+      </c>
+      <c r="E11" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D11</f>
+        <v>100535160</v>
+      </c>
+      <c r="F11" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D11)</f>
+        <v>56448540.7240751</v>
+      </c>
+      <c r="G11" s="80" t="n">
         <f aca="false">-$E11</f>
-        <v>-98400000</v>
-      </c>
-      <c r="H11" s="73" t="n">
-        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*B29))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>5505860.48947304</v>
-      </c>
-      <c r="I11" s="73" t="n">
-        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*C29))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>15075201.4959102</v>
-      </c>
-      <c r="J11" s="73" t="n">
-        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*D29))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>16331603.722476</v>
-      </c>
-      <c r="K11" s="73" t="n">
-        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*E29))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>17609587.4538537</v>
-      </c>
-      <c r="L11" s="73" t="n">
-        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D11),0),'Control Panel &amp; Inputs'!$C$48*F29))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>51442652.0246042</v>
-      </c>
-      <c r="M11" s="74" t="n">
+        <v>-100535160</v>
+      </c>
+      <c r="H11" s="80" t="n">
+        <f aca="false">B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F11,0)-MAX(0,B29-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D11),0),'Control Panel &amp; Inputs'!$C$52*B29))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>4315809.38870055</v>
+      </c>
+      <c r="I11" s="80" t="n">
+        <f aca="false">C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F11,0)-MAX(0,C29-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D11),0),'Control Panel &amp; Inputs'!$C$52*C29))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>13887226.2120004</v>
+      </c>
+      <c r="J11" s="80" t="n">
+        <f aca="false">D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F11,0)-MAX(0,D29-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D11),0),'Control Panel &amp; Inputs'!$C$52*D29))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>15144979.6487326</v>
+      </c>
+      <c r="K11" s="80" t="n">
+        <f aca="false">E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F11,0)-MAX(0,E29-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D11),0),'Control Panel &amp; Inputs'!$C$52*E29))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>16495704.0986836</v>
+      </c>
+      <c r="L11" s="80" t="n">
+        <f aca="false">F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F11,0)-MAX(0,F29-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D11),0),'Control Panel &amp; Inputs'!$C$52*F29))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>51104032.476416</v>
+      </c>
+      <c r="M11" s="81" t="n">
         <f aca="false">IRR(G11:L11)</f>
-        <v>0.0192983072718694</v>
-      </c>
-      <c r="N11" s="75" t="n">
+        <v>0.00103686365560702</v>
+      </c>
+      <c r="N11" s="82" t="n">
         <f aca="false">AVERAGE(B29:F29)/$F11</f>
-        <v>1.26687148702109</v>
+        <v>1.24018096898047</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7545,55 +7772,55 @@
         <f aca="false">TEXT($B12,"$0.00")&amp;"/kWh @ "&amp;TEXT($C12,"0%")&amp;" debt"</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B12" s="71" t="n">
+      <c r="B12" s="78" t="n">
         <v>0.06</v>
       </c>
-      <c r="C12" s="72" t="n">
+      <c r="C12" s="79" t="n">
         <v>0.8</v>
       </c>
-      <c r="D12" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C12</f>
-        <v>262400000</v>
-      </c>
-      <c r="E12" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D12</f>
-        <v>65600000</v>
-      </c>
-      <c r="F12" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D12)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="G12" s="73" t="n">
+      <c r="D12" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C12</f>
+        <v>268093760</v>
+      </c>
+      <c r="E12" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D12</f>
+        <v>67023440</v>
+      </c>
+      <c r="F12" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D12)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="G12" s="80" t="n">
         <f aca="false">-$E12</f>
-        <v>-65600000</v>
-      </c>
-      <c r="H12" s="73" t="n">
-        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*B30))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>-2386952.34372452</v>
-      </c>
-      <c r="I12" s="73" t="n">
-        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*C30))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>7182388.6627126</v>
-      </c>
-      <c r="J12" s="73" t="n">
-        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*D30))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>8438790.88927846</v>
-      </c>
-      <c r="K12" s="73" t="n">
-        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*E30))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>9788081.26112565</v>
-      </c>
-      <c r="L12" s="73" t="n">
-        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D12),0),'Control Panel &amp; Inputs'!$C$48*F30))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>43593194.0788002</v>
-      </c>
-      <c r="M12" s="74" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="H12" s="80" t="n">
+        <f aca="false">B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F12,0)-MAX(0,B30-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D12),0),'Control Panel &amp; Inputs'!$C$52*B30))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>-3748267.8575959</v>
+      </c>
+      <c r="I12" s="80" t="n">
+        <f aca="false">C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F12,0)-MAX(0,C30-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D12),0),'Control Panel &amp; Inputs'!$C$52*C30))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>5823148.96570393</v>
+      </c>
+      <c r="J12" s="80" t="n">
+        <f aca="false">D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F12,0)-MAX(0,D30-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D12),0),'Control Panel &amp; Inputs'!$C$52*D30))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>7080902.4024362</v>
+      </c>
+      <c r="K12" s="80" t="n">
+        <f aca="false">E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F12,0)-MAX(0,E30-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D12),0),'Control Panel &amp; Inputs'!$C$52*E30))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>8431626.85238719</v>
+      </c>
+      <c r="L12" s="80" t="n">
+        <f aca="false">F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F12,0)-MAX(0,F30-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D12),0),'Control Panel &amp; Inputs'!$C$52*F30))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>43084250.8656978</v>
+      </c>
+      <c r="M12" s="81" t="n">
         <f aca="false">IRR(G12:L12)</f>
-        <v>0.00348283951629246</v>
-      </c>
-      <c r="N12" s="75" t="n">
+        <v>-0.0214572858678818</v>
+      </c>
+      <c r="N12" s="82" t="n">
         <f aca="false">AVERAGE(B30:F30)/$F12</f>
-        <v>1.10851255114345</v>
+        <v>1.08515834785792</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7601,55 +7828,55 @@
         <f aca="false">TEXT($B13,"$0.00")&amp;"/kWh @ "&amp;TEXT($C13,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B13" s="71" t="n">
+      <c r="B13" s="78" t="n">
         <v>0.08</v>
       </c>
-      <c r="C13" s="72" t="n">
+      <c r="C13" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C13</f>
-        <v>164000000</v>
-      </c>
-      <c r="E13" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D13</f>
-        <v>164000000</v>
-      </c>
-      <c r="F13" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D13)</f>
-        <v>39464064.1659878</v>
-      </c>
-      <c r="G13" s="73" t="n">
+      <c r="D13" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C13</f>
+        <v>167558600</v>
+      </c>
+      <c r="E13" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D13</f>
+        <v>167558600</v>
+      </c>
+      <c r="F13" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D13)</f>
+        <v>40320386.2314822</v>
+      </c>
+      <c r="G13" s="80" t="n">
         <f aca="false">-$E13</f>
-        <v>-164000000</v>
-      </c>
-      <c r="H13" s="73" t="n">
-        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*B31))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>19969002.9298202</v>
-      </c>
-      <c r="I13" s="73" t="n">
-        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*C31))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>29511894.2717363</v>
-      </c>
-      <c r="J13" s="73" t="n">
-        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*D31))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>30741317.8404908</v>
-      </c>
-      <c r="K13" s="73" t="n">
-        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*E31))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>31949964.6173468</v>
-      </c>
-      <c r="L13" s="73" t="n">
-        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D13),0),'Control Panel &amp; Inputs'!$C$48*F31))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>65838904.3950213</v>
-      </c>
-      <c r="M13" s="74" t="n">
+        <v>-167558600</v>
+      </c>
+      <c r="H13" s="80" t="n">
+        <f aca="false">B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F13,0)-MAX(0,B31-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D13),0),'Control Panel &amp; Inputs'!$C$52*B31))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>19121480.6552454</v>
+      </c>
+      <c r="I13" s="80" t="n">
+        <f aca="false">C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F13,0)-MAX(0,C31-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D13),0),'Control Panel &amp; Inputs'!$C$52*C31))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>28666447.8140243</v>
+      </c>
+      <c r="J13" s="80" t="n">
+        <f aca="false">D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F13,0)-MAX(0,D31-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D13),0),'Control Panel &amp; Inputs'!$C$52*D31))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>29897222.5929452</v>
+      </c>
+      <c r="K13" s="80" t="n">
+        <f aca="false">E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F13,0)-MAX(0,E31-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D13),0),'Control Panel &amp; Inputs'!$C$52*E31))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>31220428.8119286</v>
+      </c>
+      <c r="L13" s="80" t="n">
+        <f aca="false">F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F13,0)-MAX(0,F31-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D13),0),'Control Panel &amp; Inputs'!$C$52*F31))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>65840932.1766617</v>
+      </c>
+      <c r="M13" s="81" t="n">
         <f aca="false">IRR(G13:L13)</f>
-        <v>0.0236605946278833</v>
-      </c>
-      <c r="N13" s="75" t="n">
+        <v>0.0119444660484369</v>
+      </c>
+      <c r="N13" s="82" t="n">
         <f aca="false">AVERAGE(B31:F31)/$F13</f>
-        <v>1.7387414854927</v>
+        <v>1.7021155098776</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7657,55 +7884,55 @@
         <f aca="false">TEXT($B14,"$0.00")&amp;"/kWh @ "&amp;TEXT($C14,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B14" s="71" t="n">
+      <c r="B14" s="78" t="n">
         <v>0.08</v>
       </c>
-      <c r="C14" s="72" t="n">
+      <c r="C14" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D14" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C14</f>
-        <v>196800000</v>
-      </c>
-      <c r="E14" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D14</f>
-        <v>131200000</v>
-      </c>
-      <c r="F14" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D14)</f>
-        <v>47356876.9991854</v>
-      </c>
-      <c r="G14" s="73" t="n">
+      <c r="D14" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C14</f>
+        <v>201070320</v>
+      </c>
+      <c r="E14" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D14</f>
+        <v>134046880</v>
+      </c>
+      <c r="F14" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D14)</f>
+        <v>48384463.4777787</v>
+      </c>
+      <c r="G14" s="80" t="n">
         <f aca="false">-$E14</f>
-        <v>-131200000</v>
-      </c>
-      <c r="H14" s="73" t="n">
-        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*B32))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>12076190.0966226</v>
-      </c>
-      <c r="I14" s="73" t="n">
-        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*C32))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>21619081.4385388</v>
-      </c>
-      <c r="J14" s="73" t="n">
-        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*D32))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>22848505.0072933</v>
-      </c>
-      <c r="K14" s="73" t="n">
-        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*E32))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>24141215.4859969</v>
-      </c>
-      <c r="L14" s="73" t="n">
-        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D14),0),'Control Panel &amp; Inputs'!$C$48*F32))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>57989446.4492174</v>
-      </c>
-      <c r="M14" s="74" t="n">
+        <v>-134046880</v>
+      </c>
+      <c r="H14" s="80" t="n">
+        <f aca="false">B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F14,0)-MAX(0,B32-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D14),0),'Control Panel &amp; Inputs'!$C$52*B32))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>11057403.408949</v>
+      </c>
+      <c r="I14" s="80" t="n">
+        <f aca="false">C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F14,0)-MAX(0,C32-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D14),0),'Control Panel &amp; Inputs'!$C$52*C32))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>20602370.5677279</v>
+      </c>
+      <c r="J14" s="80" t="n">
+        <f aca="false">D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F14,0)-MAX(0,D32-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D14),0),'Control Panel &amp; Inputs'!$C$52*D32))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>21833145.3466488</v>
+      </c>
+      <c r="K14" s="80" t="n">
+        <f aca="false">E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F14,0)-MAX(0,E32-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D14),0),'Control Panel &amp; Inputs'!$C$52*E32))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>23156351.5656321</v>
+      </c>
+      <c r="L14" s="80" t="n">
+        <f aca="false">F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F14,0)-MAX(0,F32-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D14),0),'Control Panel &amp; Inputs'!$C$52*F32))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>57821150.5659435</v>
+      </c>
+      <c r="M14" s="81" t="n">
         <f aca="false">IRR(G14:L14)</f>
-        <v>0.015228148095893</v>
-      </c>
-      <c r="N14" s="75" t="n">
+        <v>0.000849823326162686</v>
+      </c>
+      <c r="N14" s="82" t="n">
         <f aca="false">AVERAGE(B32:F32)/$F14</f>
-        <v>1.44895123791058</v>
+        <v>1.41842959156467</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7713,55 +7940,55 @@
         <f aca="false">TEXT($B15,"$0.00")&amp;"/kWh @ "&amp;TEXT($C15,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B15" s="71" t="n">
+      <c r="B15" s="78" t="n">
         <v>0.08</v>
       </c>
-      <c r="C15" s="72" t="n">
+      <c r="C15" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C15</f>
-        <v>229600000</v>
-      </c>
-      <c r="E15" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D15</f>
-        <v>98400000</v>
-      </c>
-      <c r="F15" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D15)</f>
-        <v>55249689.832383</v>
-      </c>
-      <c r="G15" s="73" t="n">
+      <c r="D15" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C15</f>
+        <v>234582040</v>
+      </c>
+      <c r="E15" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D15</f>
+        <v>100535160</v>
+      </c>
+      <c r="F15" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D15)</f>
+        <v>56448540.7240751</v>
+      </c>
+      <c r="G15" s="80" t="n">
         <f aca="false">-$E15</f>
-        <v>-98400000</v>
-      </c>
-      <c r="H15" s="73" t="n">
-        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*B33))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>4183377.26342504</v>
-      </c>
-      <c r="I15" s="73" t="n">
-        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*C33))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>13726268.6053412</v>
-      </c>
-      <c r="J15" s="73" t="n">
-        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*D33))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>14955692.1740957</v>
-      </c>
-      <c r="K15" s="73" t="n">
-        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*E33))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>16277464.3149753</v>
-      </c>
-      <c r="L15" s="73" t="n">
-        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D15),0),'Control Panel &amp; Inputs'!$C$48*F33))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>50139988.5034134</v>
-      </c>
-      <c r="M15" s="74" t="n">
+        <v>-100535160</v>
+      </c>
+      <c r="H15" s="80" t="n">
+        <f aca="false">B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F15,0)-MAX(0,B33-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D15),0),'Control Panel &amp; Inputs'!$C$52*B33))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>2993326.16265254</v>
+      </c>
+      <c r="I15" s="80" t="n">
+        <f aca="false">C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F15,0)-MAX(0,C33-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D15),0),'Control Panel &amp; Inputs'!$C$52*C33))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>12538293.3214314</v>
+      </c>
+      <c r="J15" s="80" t="n">
+        <f aca="false">D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F15,0)-MAX(0,D33-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D15),0),'Control Panel &amp; Inputs'!$C$52*D33))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>13769068.1003523</v>
+      </c>
+      <c r="K15" s="80" t="n">
+        <f aca="false">E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F15,0)-MAX(0,E33-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D15),0),'Control Panel &amp; Inputs'!$C$52*E33))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>15092274.3193357</v>
+      </c>
+      <c r="L15" s="80" t="n">
+        <f aca="false">F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F15,0)-MAX(0,F33-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D15),0),'Control Panel &amp; Inputs'!$C$52*F33))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>49801368.9552253</v>
+      </c>
+      <c r="M15" s="81" t="n">
         <f aca="false">IRR(G15:L15)</f>
-        <v>0.00226387121737398</v>
-      </c>
-      <c r="N15" s="75" t="n">
+        <v>-0.0160239933487293</v>
+      </c>
+      <c r="N15" s="82" t="n">
         <f aca="false">AVERAGE(B33:F33)/$F15</f>
-        <v>1.24195820392335</v>
+        <v>1.21579679276972</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7769,55 +7996,55 @@
         <f aca="false">TEXT($B16,"$0.00")&amp;"/kWh @ "&amp;TEXT($C16,"0%")&amp;" debt"</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B16" s="71" t="n">
+      <c r="B16" s="78" t="n">
         <v>0.08</v>
       </c>
-      <c r="C16" s="72" t="n">
+      <c r="C16" s="79" t="n">
         <v>0.8</v>
       </c>
-      <c r="D16" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C16</f>
-        <v>262400000</v>
-      </c>
-      <c r="E16" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D16</f>
-        <v>65600000</v>
-      </c>
-      <c r="F16" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D16)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="G16" s="73" t="n">
+      <c r="D16" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C16</f>
+        <v>268093760</v>
+      </c>
+      <c r="E16" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D16</f>
+        <v>67023440</v>
+      </c>
+      <c r="F16" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D16)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="G16" s="80" t="n">
         <f aca="false">-$E16</f>
-        <v>-65600000</v>
-      </c>
-      <c r="H16" s="73" t="n">
-        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*B34))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>-3709435.56977252</v>
-      </c>
-      <c r="I16" s="73" t="n">
-        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*C34))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>5833455.77214364</v>
-      </c>
-      <c r="J16" s="73" t="n">
-        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*D34))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>7062879.34089813</v>
-      </c>
-      <c r="K16" s="73" t="n">
-        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*E34))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>8384651.48177771</v>
-      </c>
-      <c r="L16" s="73" t="n">
-        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D16),0),'Control Panel &amp; Inputs'!$C$48*F34))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>42290530.5576095</v>
-      </c>
-      <c r="M16" s="74" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="H16" s="80" t="n">
+        <f aca="false">B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F16,0)-MAX(0,B34-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D16),0),'Control Panel &amp; Inputs'!$C$52*B34))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>-5070751.0836439</v>
+      </c>
+      <c r="I16" s="80" t="n">
+        <f aca="false">C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F16,0)-MAX(0,C34-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D16),0),'Control Panel &amp; Inputs'!$C$52*C34))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>4474216.07513498</v>
+      </c>
+      <c r="J16" s="80" t="n">
+        <f aca="false">D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F16,0)-MAX(0,D34-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D16),0),'Control Panel &amp; Inputs'!$C$52*D34))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>5704990.85405587</v>
+      </c>
+      <c r="K16" s="80" t="n">
+        <f aca="false">E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F16,0)-MAX(0,E34-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D16),0),'Control Panel &amp; Inputs'!$C$52*E34))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>7028197.07303925</v>
+      </c>
+      <c r="L16" s="80" t="n">
+        <f aca="false">F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F16,0)-MAX(0,F34-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D16),0),'Control Panel &amp; Inputs'!$C$52*F34))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>41781587.3445071</v>
+      </c>
+      <c r="M16" s="81" t="n">
         <f aca="false">IRR(G16:L16)</f>
-        <v>-0.0197751815323907</v>
-      </c>
-      <c r="N16" s="75" t="n">
+        <v>-0.0444931314018822</v>
+      </c>
+      <c r="N16" s="82" t="n">
         <f aca="false">AVERAGE(B34:F34)/$F16</f>
-        <v>1.08671342843294</v>
+        <v>1.0638221936735</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7825,55 +8052,55 @@
         <f aca="false">TEXT($B17,"$0.00")&amp;"/kWh @ "&amp;TEXT($C17,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B17" s="71" t="n">
+      <c r="B17" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="C17" s="72" t="n">
+      <c r="C17" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C17</f>
-        <v>164000000</v>
-      </c>
-      <c r="E17" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D17</f>
-        <v>164000000</v>
-      </c>
-      <c r="F17" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D17)</f>
-        <v>39464064.1659878</v>
-      </c>
-      <c r="G17" s="73" t="n">
+      <c r="D17" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C17</f>
+        <v>167558600</v>
+      </c>
+      <c r="E17" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D17</f>
+        <v>167558600</v>
+      </c>
+      <c r="F17" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D17)</f>
+        <v>40320386.2314822</v>
+      </c>
+      <c r="G17" s="80" t="n">
         <f aca="false">-$E17</f>
-        <v>-164000000</v>
-      </c>
-      <c r="H17" s="73" t="n">
-        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*B35))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>18646519.7037722</v>
-      </c>
-      <c r="I17" s="73" t="n">
-        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*C35))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>28162961.3811674</v>
-      </c>
-      <c r="J17" s="73" t="n">
-        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*D35))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>29365406.2921105</v>
-      </c>
-      <c r="K17" s="73" t="n">
-        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*E35))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>30659660.2020225</v>
-      </c>
-      <c r="L17" s="73" t="n">
-        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D17),0),'Control Panel &amp; Inputs'!$C$48*F35))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>64536240.8738305</v>
-      </c>
-      <c r="M17" s="74" t="n">
+        <v>-167558600</v>
+      </c>
+      <c r="H17" s="80" t="n">
+        <f aca="false">B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F17,0)-MAX(0,B35-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D17),0),'Control Panel &amp; Inputs'!$C$52*B35))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>17798997.4291974</v>
+      </c>
+      <c r="I17" s="80" t="n">
+        <f aca="false">C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F17,0)-MAX(0,C35-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D17),0),'Control Panel &amp; Inputs'!$C$52*C35))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>27317514.9234554</v>
+      </c>
+      <c r="J17" s="80" t="n">
+        <f aca="false">D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F17,0)-MAX(0,D35-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D17),0),'Control Panel &amp; Inputs'!$C$52*D35))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>28521311.0445649</v>
+      </c>
+      <c r="K17" s="80" t="n">
+        <f aca="false">E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F17,0)-MAX(0,E35-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D17),0),'Control Panel &amp; Inputs'!$C$52*E35))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>29816999.0325806</v>
+      </c>
+      <c r="L17" s="80" t="n">
+        <f aca="false">F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F17,0)-MAX(0,F35-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D17),0),'Control Panel &amp; Inputs'!$C$52*F35))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>64538268.6554709</v>
+      </c>
+      <c r="M17" s="81" t="n">
         <f aca="false">IRR(G17:L17)</f>
-        <v>0.0125042874959422</v>
-      </c>
-      <c r="N17" s="75" t="n">
+        <v>0.00072554999484047</v>
+      </c>
+      <c r="N17" s="82" t="n">
         <f aca="false">AVERAGE(B35:F35)/$F17</f>
-        <v>1.70386288915587</v>
+        <v>1.66797766318254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7881,55 +8108,55 @@
         <f aca="false">TEXT($B18,"$0.00")&amp;"/kWh @ "&amp;TEXT($C18,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B18" s="71" t="n">
+      <c r="B18" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" s="72" t="n">
+      <c r="C18" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D18" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C18</f>
-        <v>196800000</v>
-      </c>
-      <c r="E18" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D18</f>
-        <v>131200000</v>
-      </c>
-      <c r="F18" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D18)</f>
-        <v>47356876.9991854</v>
-      </c>
-      <c r="G18" s="73" t="n">
+      <c r="D18" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C18</f>
+        <v>201070320</v>
+      </c>
+      <c r="E18" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D18</f>
+        <v>134046880</v>
+      </c>
+      <c r="F18" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D18)</f>
+        <v>48384463.4777787</v>
+      </c>
+      <c r="G18" s="80" t="n">
         <f aca="false">-$E18</f>
-        <v>-131200000</v>
-      </c>
-      <c r="H18" s="73" t="n">
-        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*B36))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>10753706.8705746</v>
-      </c>
-      <c r="I18" s="73" t="n">
-        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*C36))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>20270148.5479698</v>
-      </c>
-      <c r="J18" s="73" t="n">
-        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*D36))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>21472593.4589129</v>
-      </c>
-      <c r="K18" s="73" t="n">
-        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*E36))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>22766847.3688249</v>
-      </c>
-      <c r="L18" s="73" t="n">
-        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D18),0),'Control Panel &amp; Inputs'!$C$48*F36))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>56686782.9280266</v>
-      </c>
-      <c r="M18" s="74" t="n">
+        <v>-134046880</v>
+      </c>
+      <c r="H18" s="80" t="n">
+        <f aca="false">B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F18,0)-MAX(0,B36-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D18),0),'Control Panel &amp; Inputs'!$C$52*B36))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>9734920.18290099</v>
+      </c>
+      <c r="I18" s="80" t="n">
+        <f aca="false">C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F18,0)-MAX(0,C36-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D18),0),'Control Panel &amp; Inputs'!$C$52*C36))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>19253437.6771589</v>
+      </c>
+      <c r="J18" s="80" t="n">
+        <f aca="false">D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F18,0)-MAX(0,D36-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D18),0),'Control Panel &amp; Inputs'!$C$52*D36))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>20457233.7982684</v>
+      </c>
+      <c r="K18" s="80" t="n">
+        <f aca="false">E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F18,0)-MAX(0,E36-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D18),0),'Control Panel &amp; Inputs'!$C$52*E36))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>21752921.7862842</v>
+      </c>
+      <c r="L18" s="80" t="n">
+        <f aca="false">F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F18,0)-MAX(0,F36-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D18),0),'Control Panel &amp; Inputs'!$C$52*F36))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>56518487.0447527</v>
+      </c>
+      <c r="M18" s="81" t="n">
         <f aca="false">IRR(G18:L18)</f>
-        <v>0.00153624264902171</v>
-      </c>
-      <c r="N18" s="75" t="n">
+        <v>-0.0127695193347756</v>
+      </c>
+      <c r="N18" s="82" t="n">
         <f aca="false">AVERAGE(B36:F36)/$F18</f>
-        <v>1.41988574096323</v>
+        <v>1.38998138598545</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7937,55 +8164,55 @@
         <f aca="false">TEXT($B19,"$0.00")&amp;"/kWh @ "&amp;TEXT($C19,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B19" s="71" t="n">
+      <c r="B19" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="72" t="n">
+      <c r="C19" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D19" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C19</f>
-        <v>229600000</v>
-      </c>
-      <c r="E19" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D19</f>
-        <v>98400000</v>
-      </c>
-      <c r="F19" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D19)</f>
-        <v>55249689.832383</v>
-      </c>
-      <c r="G19" s="73" t="n">
+      <c r="D19" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C19</f>
+        <v>234582040</v>
+      </c>
+      <c r="E19" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D19</f>
+        <v>100535160</v>
+      </c>
+      <c r="F19" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D19)</f>
+        <v>56448540.7240751</v>
+      </c>
+      <c r="G19" s="80" t="n">
         <f aca="false">-$E19</f>
-        <v>-98400000</v>
-      </c>
-      <c r="H19" s="73" t="n">
-        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*B37))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>2860894.03737704</v>
-      </c>
-      <c r="I19" s="73" t="n">
-        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*C37))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>12377335.7147722</v>
-      </c>
-      <c r="J19" s="73" t="n">
-        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*D37))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>13579780.6257153</v>
-      </c>
-      <c r="K19" s="73" t="n">
-        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*E37))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>14874034.5356273</v>
-      </c>
-      <c r="L19" s="73" t="n">
-        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D19),0),'Control Panel &amp; Inputs'!$C$48*F37))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>48837324.9822226</v>
-      </c>
-      <c r="M19" s="74" t="n">
+        <v>-100535160</v>
+      </c>
+      <c r="H19" s="80" t="n">
+        <f aca="false">B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F19,0)-MAX(0,B37-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D19),0),'Control Panel &amp; Inputs'!$C$52*B37))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>1670842.93660454</v>
+      </c>
+      <c r="I19" s="80" t="n">
+        <f aca="false">C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F19,0)-MAX(0,C37-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D19),0),'Control Panel &amp; Inputs'!$C$52*C37))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>11189360.4308625</v>
+      </c>
+      <c r="J19" s="80" t="n">
+        <f aca="false">D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F19,0)-MAX(0,D37-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D19),0),'Control Panel &amp; Inputs'!$C$52*D37))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>12393156.551972</v>
+      </c>
+      <c r="K19" s="80" t="n">
+        <f aca="false">E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F19,0)-MAX(0,E37-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D19),0),'Control Panel &amp; Inputs'!$C$52*E37))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>13688844.5399877</v>
+      </c>
+      <c r="L19" s="80" t="n">
+        <f aca="false">F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F19,0)-MAX(0,F37-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D19),0),'Control Panel &amp; Inputs'!$C$52*F37))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>48498705.4340345</v>
+      </c>
+      <c r="M19" s="81" t="n">
         <f aca="false">IRR(G19:L19)</f>
-        <v>-0.0151406941408555</v>
-      </c>
-      <c r="N19" s="75" t="n">
+        <v>-0.0332825031375496</v>
+      </c>
+      <c r="N19" s="82" t="n">
         <f aca="false">AVERAGE(B37:F37)/$F19</f>
-        <v>1.21704492082562</v>
+        <v>1.19141261655896</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7993,496 +8220,496 @@
         <f aca="false">TEXT($B20,"$0.00")&amp;"/kWh @ "&amp;TEXT($C20,"0%")&amp;" debt"</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B20" s="71" t="n">
+      <c r="B20" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="C20" s="72" t="n">
+      <c r="C20" s="79" t="n">
         <v>0.8</v>
       </c>
-      <c r="D20" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40*$C20</f>
-        <v>262400000</v>
-      </c>
-      <c r="E20" s="73" t="n">
-        <f aca="false">'Control Panel &amp; Inputs'!$C$40-$D20</f>
-        <v>65600000</v>
-      </c>
-      <c r="F20" s="73" t="n">
-        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$43,'Control Panel &amp; Inputs'!$C$44,$D20)</f>
-        <v>63142502.6655805</v>
-      </c>
-      <c r="G20" s="73" t="n">
+      <c r="D20" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44*$C20</f>
+        <v>268093760</v>
+      </c>
+      <c r="E20" s="80" t="n">
+        <f aca="false">'Control Panel &amp; Inputs'!$C$44-$D20</f>
+        <v>67023440</v>
+      </c>
+      <c r="F20" s="80" t="n">
+        <f aca="false">-PMT('Control Panel &amp; Inputs'!$C$47,'Control Panel &amp; Inputs'!$C$48,$D20)</f>
+        <v>64512617.9703716</v>
+      </c>
+      <c r="G20" s="80" t="n">
         <f aca="false">-$E20</f>
-        <v>-65600000</v>
-      </c>
-      <c r="H20" s="73" t="n">
-        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,1,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*B38))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>-5031918.79582052</v>
-      </c>
-      <c r="I20" s="73" t="n">
-        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,2,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*C38))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>4484522.88157468</v>
-      </c>
-      <c r="J20" s="73" t="n">
-        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,3,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*D38))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>5686967.79251779</v>
-      </c>
-      <c r="K20" s="73" t="n">
-        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,4,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*E38))*'Control Panel &amp; Inputs'!$C$47</f>
-        <v>6981221.70242975</v>
-      </c>
-      <c r="L20" s="73" t="n">
-        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$44,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$46,'Control Panel &amp; Inputs'!$C$40/'Control Panel &amp; Inputs'!$C$46,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$44,-IPMT('Control Panel &amp; Inputs'!$C$43,5,'Control Panel &amp; Inputs'!$C$44,$D20),0),'Control Panel &amp; Inputs'!$C$48*F38))*'Control Panel &amp; Inputs'!$C$47+'Control Panel &amp; Inputs'!$C$40*'Control Panel &amp; Inputs'!$C$41</f>
-        <v>40987867.0364187</v>
-      </c>
-      <c r="M20" s="74" t="n">
+        <v>-67023440</v>
+      </c>
+      <c r="H20" s="80" t="n">
+        <f aca="false">B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$48,$F20,0)-MAX(0,B38-IF(1&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(1&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,1,'Control Panel &amp; Inputs'!$C$48,$D20),0),'Control Panel &amp; Inputs'!$C$52*B38))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>-6393234.3096919</v>
+      </c>
+      <c r="I20" s="80" t="n">
+        <f aca="false">C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$48,$F20,0)-MAX(0,C38-IF(2&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(2&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,2,'Control Panel &amp; Inputs'!$C$48,$D20),0),'Control Panel &amp; Inputs'!$C$52*C38))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>3125283.18456602</v>
+      </c>
+      <c r="J20" s="80" t="n">
+        <f aca="false">D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$48,$F20,0)-MAX(0,D38-IF(3&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(3&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,3,'Control Panel &amp; Inputs'!$C$48,$D20),0),'Control Panel &amp; Inputs'!$C$52*D38))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>4329079.30567552</v>
+      </c>
+      <c r="K20" s="80" t="n">
+        <f aca="false">E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$48,$F20,0)-MAX(0,E38-IF(4&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(4&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,4,'Control Panel &amp; Inputs'!$C$48,$D20),0),'Control Panel &amp; Inputs'!$C$52*E38))*'Control Panel &amp; Inputs'!$C$51</f>
+        <v>5624767.29369129</v>
+      </c>
+      <c r="L20" s="80" t="n">
+        <f aca="false">F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$48,$F20,0)-MAX(0,F38-IF(5&lt;='Control Panel &amp; Inputs'!$C$50,'Control Panel &amp; Inputs'!$C$44/'Control Panel &amp; Inputs'!$C$50,0)-MIN(IF(5&lt;='Control Panel &amp; Inputs'!$C$48,-IPMT('Control Panel &amp; Inputs'!$C$47,5,'Control Panel &amp; Inputs'!$C$48,$D20),0),'Control Panel &amp; Inputs'!$C$52*F38))*'Control Panel &amp; Inputs'!$C$51+'Control Panel &amp; Inputs'!$C$44*'Control Panel &amp; Inputs'!$C$45</f>
+        <v>40478923.8233163</v>
+      </c>
+      <c r="M20" s="81" t="n">
         <f aca="false">IRR(G20:L20)</f>
-        <v>-0.0432695354488995</v>
-      </c>
-      <c r="N20" s="75" t="n">
+        <v>-0.0677738939261027</v>
+      </c>
+      <c r="N20" s="82" t="n">
         <f aca="false">AVERAGE(B38:F38)/$F20</f>
-        <v>1.06491430572242</v>
+        <v>1.04248603948909</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="59" t="s">
-        <v>401</v>
+      <c r="A21" s="66" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="76" t="str">
+      <c r="A23" s="83" t="str">
         <f aca="false">A5</f>
         <v>$0.04/kWh @ 50% debt</v>
       </c>
-      <c r="B23" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>62078033.547904</v>
-      </c>
-      <c r="C23" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>71673824.2188621</v>
-      </c>
-      <c r="D23" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>72957205.1032393</v>
-      </c>
-      <c r="E23" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>74334013.7060541</v>
-      </c>
-      <c r="F23" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>75810462.8202446</v>
+      <c r="B23" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>62086833.3388237</v>
+      </c>
+      <c r="C23" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>71684699.8266445</v>
+      </c>
+      <c r="D23" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>72969431.9211881</v>
+      </c>
+      <c r="E23" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>74347674.6021067</v>
+      </c>
+      <c r="F23" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B5*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>75825645.7941035</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="76" t="str">
+      <c r="A24" s="83" t="str">
         <f aca="false">A6</f>
         <v>$0.04/kWh @ 60% debt</v>
       </c>
-      <c r="B24" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>62078033.547904</v>
-      </c>
-      <c r="C24" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>71673824.2188621</v>
-      </c>
-      <c r="D24" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>72957205.1032393</v>
-      </c>
-      <c r="E24" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>74334013.7060541</v>
-      </c>
-      <c r="F24" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>75810462.8202446</v>
+      <c r="B24" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>62086833.3388237</v>
+      </c>
+      <c r="C24" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>71684699.8266445</v>
+      </c>
+      <c r="D24" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>72969431.9211881</v>
+      </c>
+      <c r="E24" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>74347674.6021067</v>
+      </c>
+      <c r="F24" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B6*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>75825645.7941035</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="76" t="str">
+      <c r="A25" s="83" t="str">
         <f aca="false">A7</f>
         <v>$0.04/kWh @ 70% debt</v>
       </c>
-      <c r="B25" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>62078033.547904</v>
-      </c>
-      <c r="C25" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>71673824.2188621</v>
-      </c>
-      <c r="D25" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>72957205.1032393</v>
-      </c>
-      <c r="E25" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>74334013.7060541</v>
-      </c>
-      <c r="F25" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>75810462.8202446</v>
+      <c r="B25" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>62086833.3388237</v>
+      </c>
+      <c r="C25" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>71684699.8266445</v>
+      </c>
+      <c r="D25" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>72969431.9211881</v>
+      </c>
+      <c r="E25" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>74347674.6021067</v>
+      </c>
+      <c r="F25" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B7*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>75825645.7941035</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76" t="str">
+      <c r="A26" s="83" t="str">
         <f aca="false">A8</f>
         <v>$0.04/kWh @ 80% debt</v>
       </c>
-      <c r="B26" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>62078033.547904</v>
-      </c>
-      <c r="C26" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>71673824.2188621</v>
-      </c>
-      <c r="D26" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>72957205.1032393</v>
-      </c>
-      <c r="E26" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>74334013.7060541</v>
-      </c>
-      <c r="F26" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>75810462.8202446</v>
+      <c r="B26" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>62086833.3388237</v>
+      </c>
+      <c r="C26" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>71684699.8266445</v>
+      </c>
+      <c r="D26" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>72969431.9211881</v>
+      </c>
+      <c r="E26" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>74347674.6021067</v>
+      </c>
+      <c r="F26" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B8*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>75825645.7941035</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="76" t="str">
+      <c r="A27" s="83" t="str">
         <f aca="false">A9</f>
         <v>$0.06/kWh @ 50% debt</v>
       </c>
-      <c r="B27" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="C27" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>70324891.3282931</v>
-      </c>
-      <c r="D27" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>71581293.554859</v>
-      </c>
-      <c r="E27" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>72930583.9267062</v>
-      </c>
-      <c r="F27" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>74378964.4453097</v>
+      <c r="B27" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>60764350.1127757</v>
+      </c>
+      <c r="C27" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>70335766.9360755</v>
+      </c>
+      <c r="D27" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>71593520.3728078</v>
+      </c>
+      <c r="E27" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>72944244.8227588</v>
+      </c>
+      <c r="F27" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B9*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>74394147.4191686</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="76" t="str">
+      <c r="A28" s="83" t="str">
         <f aca="false">A10</f>
         <v>$0.06/kWh @ 60% debt</v>
       </c>
-      <c r="B28" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="C28" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>70324891.3282931</v>
-      </c>
-      <c r="D28" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>71581293.554859</v>
-      </c>
-      <c r="E28" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>72930583.9267062</v>
-      </c>
-      <c r="F28" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>74378964.4453097</v>
+      <c r="B28" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>60764350.1127757</v>
+      </c>
+      <c r="C28" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>70335766.9360755</v>
+      </c>
+      <c r="D28" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>71593520.3728078</v>
+      </c>
+      <c r="E28" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>72944244.8227588</v>
+      </c>
+      <c r="F28" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B10*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>74394147.4191686</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="76" t="str">
+      <c r="A29" s="83" t="str">
         <f aca="false">A11</f>
         <v>$0.06/kWh @ 70% debt</v>
       </c>
-      <c r="B29" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="C29" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>70324891.3282931</v>
-      </c>
-      <c r="D29" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>71581293.554859</v>
-      </c>
-      <c r="E29" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>72930583.9267062</v>
-      </c>
-      <c r="F29" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>74378964.4453097</v>
+      <c r="B29" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>60764350.1127757</v>
+      </c>
+      <c r="C29" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>70335766.9360755</v>
+      </c>
+      <c r="D29" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>71593520.3728078</v>
+      </c>
+      <c r="E29" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>72944244.8227588</v>
+      </c>
+      <c r="F29" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B11*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>74394147.4191686</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="76" t="str">
+      <c r="A30" s="83" t="str">
         <f aca="false">A12</f>
         <v>$0.06/kWh @ 80% debt</v>
       </c>
-      <c r="B30" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>60755550.321856</v>
-      </c>
-      <c r="C30" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>70324891.3282931</v>
-      </c>
-      <c r="D30" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>71581293.554859</v>
-      </c>
-      <c r="E30" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>72930583.9267062</v>
-      </c>
-      <c r="F30" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>74378964.4453097</v>
+      <c r="B30" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>60764350.1127757</v>
+      </c>
+      <c r="C30" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>70335766.9360755</v>
+      </c>
+      <c r="D30" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>71593520.3728078</v>
+      </c>
+      <c r="E30" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>72944244.8227588</v>
+      </c>
+      <c r="F30" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B12*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>74394147.4191686</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="76" t="str">
+      <c r="A31" s="83" t="str">
         <f aca="false">A13</f>
         <v>$0.08/kWh @ 50% debt</v>
       </c>
-      <c r="B31" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>59433067.095808</v>
-      </c>
-      <c r="C31" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>68975958.4377242</v>
-      </c>
-      <c r="D31" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>70205382.0064787</v>
-      </c>
-      <c r="E31" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>71527154.1473582</v>
-      </c>
-      <c r="F31" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>72947466.0703748</v>
+      <c r="B31" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>59441866.8867277</v>
+      </c>
+      <c r="C31" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>68986834.0455066</v>
+      </c>
+      <c r="D31" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>70217608.8244274</v>
+      </c>
+      <c r="E31" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>71540815.0434108</v>
+      </c>
+      <c r="F31" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B13*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>72962649.0442337</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="76" t="str">
+      <c r="A32" s="83" t="str">
         <f aca="false">A14</f>
         <v>$0.08/kWh @ 60% debt</v>
       </c>
-      <c r="B32" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>59433067.095808</v>
-      </c>
-      <c r="C32" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>68975958.4377242</v>
-      </c>
-      <c r="D32" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>70205382.0064787</v>
-      </c>
-      <c r="E32" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>71527154.1473582</v>
-      </c>
-      <c r="F32" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>72947466.0703748</v>
+      <c r="B32" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>59441866.8867277</v>
+      </c>
+      <c r="C32" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>68986834.0455066</v>
+      </c>
+      <c r="D32" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>70217608.8244274</v>
+      </c>
+      <c r="E32" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>71540815.0434108</v>
+      </c>
+      <c r="F32" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B14*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>72962649.0442337</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="76" t="str">
+      <c r="A33" s="83" t="str">
         <f aca="false">A15</f>
         <v>$0.08/kWh @ 70% debt</v>
       </c>
-      <c r="B33" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>59433067.095808</v>
-      </c>
-      <c r="C33" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>68975958.4377242</v>
-      </c>
-      <c r="D33" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>70205382.0064787</v>
-      </c>
-      <c r="E33" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>71527154.1473582</v>
-      </c>
-      <c r="F33" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>72947466.0703748</v>
+      <c r="B33" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>59441866.8867277</v>
+      </c>
+      <c r="C33" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>68986834.0455066</v>
+      </c>
+      <c r="D33" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>70217608.8244274</v>
+      </c>
+      <c r="E33" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>71540815.0434108</v>
+      </c>
+      <c r="F33" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B15*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>72962649.0442337</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="76" t="str">
+      <c r="A34" s="83" t="str">
         <f aca="false">A16</f>
         <v>$0.08/kWh @ 80% debt</v>
       </c>
-      <c r="B34" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>59433067.095808</v>
-      </c>
-      <c r="C34" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>68975958.4377242</v>
-      </c>
-      <c r="D34" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>70205382.0064787</v>
-      </c>
-      <c r="E34" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>71527154.1473582</v>
-      </c>
-      <c r="F34" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>72947466.0703748</v>
+      <c r="B34" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>59441866.8867277</v>
+      </c>
+      <c r="C34" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>68986834.0455066</v>
+      </c>
+      <c r="D34" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>70217608.8244274</v>
+      </c>
+      <c r="E34" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>71540815.0434108</v>
+      </c>
+      <c r="F34" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B16*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>72962649.0442337</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="76" t="str">
+      <c r="A35" s="83" t="str">
         <f aca="false">A17</f>
         <v>$0.10/kWh @ 50% debt</v>
       </c>
-      <c r="B35" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>58110583.86976</v>
-      </c>
-      <c r="C35" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>67627025.5471552</v>
-      </c>
-      <c r="D35" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>68829470.4580983</v>
-      </c>
-      <c r="E35" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>70123724.3680103</v>
-      </c>
-      <c r="F35" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>71515967.6954399</v>
+      <c r="B35" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>58119383.6606797</v>
+      </c>
+      <c r="C35" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>67637901.1549376</v>
+      </c>
+      <c r="D35" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>68841697.2760471</v>
+      </c>
+      <c r="E35" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>70137385.2640629</v>
+      </c>
+      <c r="F35" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B17*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>71531150.6692988</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="76" t="str">
+      <c r="A36" s="83" t="str">
         <f aca="false">A18</f>
         <v>$0.10/kWh @ 60% debt</v>
       </c>
-      <c r="B36" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>58110583.86976</v>
-      </c>
-      <c r="C36" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>67627025.5471552</v>
-      </c>
-      <c r="D36" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>68829470.4580983</v>
-      </c>
-      <c r="E36" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>70123724.3680103</v>
-      </c>
-      <c r="F36" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>71515967.6954399</v>
+      <c r="B36" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>58119383.6606797</v>
+      </c>
+      <c r="C36" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>67637901.1549376</v>
+      </c>
+      <c r="D36" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>68841697.2760471</v>
+      </c>
+      <c r="E36" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>70137385.2640629</v>
+      </c>
+      <c r="F36" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B18*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>71531150.6692988</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="76" t="str">
+      <c r="A37" s="83" t="str">
         <f aca="false">A19</f>
         <v>$0.10/kWh @ 70% debt</v>
       </c>
-      <c r="B37" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>58110583.86976</v>
-      </c>
-      <c r="C37" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>67627025.5471552</v>
-      </c>
-      <c r="D37" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>68829470.4580983</v>
-      </c>
-      <c r="E37" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>70123724.3680103</v>
-      </c>
-      <c r="F37" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>71515967.6954399</v>
+      <c r="B37" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>58119383.6606797</v>
+      </c>
+      <c r="C37" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>67637901.1549376</v>
+      </c>
+      <c r="D37" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>68841697.2760471</v>
+      </c>
+      <c r="E37" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>70137385.2640629</v>
+      </c>
+      <c r="F37" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B19*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>71531150.6692988</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="76" t="str">
+      <c r="A38" s="83" t="str">
         <f aca="false">A20</f>
         <v>$0.10/kWh @ 80% debt</v>
       </c>
-      <c r="B38" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,0)</f>
-        <v>58110583.86976</v>
-      </c>
-      <c r="C38" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,1)</f>
-        <v>67627025.5471552</v>
-      </c>
-      <c r="D38" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,2)</f>
-        <v>68829470.4580983</v>
-      </c>
-      <c r="E38" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,3)</f>
-        <v>70123724.3680103</v>
-      </c>
-      <c r="F38" s="73" t="n">
-        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$39,4)</f>
-        <v>71515967.6954399</v>
+      <c r="B38" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!C$8-'Pro Forma Financials'!C$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$42,0)</f>
+        <v>58119383.6606797</v>
+      </c>
+      <c r="C38" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!D$8-'Pro Forma Financials'!D$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$42,1)</f>
+        <v>67637901.1549376</v>
+      </c>
+      <c r="D38" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!E$8-'Pro Forma Financials'!E$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$42,2)</f>
+        <v>68841697.2760471</v>
+      </c>
+      <c r="E38" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!F$8-'Pro Forma Financials'!F$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$42,3)</f>
+        <v>70137385.2640629</v>
+      </c>
+      <c r="F38" s="80" t="n">
+        <f aca="false">'Pro Forma Financials'!G$8-'Pro Forma Financials'!G$12-'Pro Forma Financials'!C$10*$B20*POWER(1+'Control Panel &amp; Inputs'!$C$42,4)</f>
+        <v>71531150.6692988</v>
       </c>
     </row>
   </sheetData>
@@ -8516,7 +8743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8526,7 +8753,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8535,13 +8762,13 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="59" t="s">
-        <v>409</v>
+      <c r="A4" s="66" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B5" s="3" t="str">
         <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
@@ -8565,21 +8792,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
         <v>$0.04 / kWh</v>
       </c>
-      <c r="B6" s="77" t="n">
+      <c r="B6" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M5</f>
-        <v>0.0455581791812502</v>
-      </c>
-      <c r="C6" s="77" t="n">
+        <v>0.0337070096722301</v>
+      </c>
+      <c r="C6" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M6</f>
-        <v>0.0418311991063475</v>
-      </c>
-      <c r="D6" s="77" t="n">
+        <v>0.0273884979465043</v>
+      </c>
+      <c r="D6" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M7</f>
-        <v>0.036027847120873</v>
-      </c>
-      <c r="E6" s="77" t="n">
+        <v>0.0177702105428679</v>
+      </c>
+      <c r="E6" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M8</f>
-        <v>0.0261453486370609</v>
+        <v>0.00135032626637098</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8587,21 +8814,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
         <v>$0.06 / kWh</v>
       </c>
-      <c r="B7" s="77" t="n">
+      <c r="B7" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M9</f>
-        <v>0.0346975334245463</v>
-      </c>
-      <c r="C7" s="77" t="n">
+        <v>0.0228912959711814</v>
+      </c>
+      <c r="C7" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M10</f>
-        <v>0.0285913820637419</v>
-      </c>
-      <c r="D7" s="77" t="n">
+        <v>0.0142907188238313</v>
+      </c>
+      <c r="D7" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M11</f>
-        <v>0.0192983072718694</v>
-      </c>
-      <c r="E7" s="77" t="n">
+        <v>0.00103686365560702</v>
+      </c>
+      <c r="E7" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M12</f>
-        <v>0.00348283951629246</v>
+        <v>-0.0214572858678818</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8609,21 +8836,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
         <v>$0.08 / kWh</v>
       </c>
-      <c r="B8" s="77" t="n">
+      <c r="B8" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M13</f>
-        <v>0.0236605946278833</v>
-      </c>
-      <c r="C8" s="77" t="n">
+        <v>0.0119444660484369</v>
+      </c>
+      <c r="C8" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M14</f>
-        <v>0.015228148095893</v>
-      </c>
-      <c r="D8" s="77" t="n">
+        <v>0.000849823326162686</v>
+      </c>
+      <c r="D8" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M15</f>
-        <v>0.00226387121737398</v>
-      </c>
-      <c r="E8" s="77" t="n">
+        <v>-0.0160239933487293</v>
+      </c>
+      <c r="E8" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M16</f>
-        <v>-0.0197751815323907</v>
+        <v>-0.0444931314018822</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8631,31 +8858,31 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
         <v>$0.10 / kWh</v>
       </c>
-      <c r="B9" s="77" t="n">
+      <c r="B9" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M17</f>
-        <v>0.0125042874959422</v>
-      </c>
-      <c r="C9" s="77" t="n">
+        <v>0.00072554999484047</v>
+      </c>
+      <c r="C9" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M18</f>
-        <v>0.00153624264902171</v>
-      </c>
-      <c r="D9" s="77" t="n">
+        <v>-0.0127695193347756</v>
+      </c>
+      <c r="D9" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M19</f>
-        <v>-0.0151406941408555</v>
-      </c>
-      <c r="E9" s="77" t="n">
+        <v>-0.0332825031375496</v>
+      </c>
+      <c r="E9" s="84" t="n">
         <f aca="false">'Sensitivity Engine'!M20</f>
-        <v>-0.0432695354488995</v>
+        <v>-0.0677738939261027</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="59" t="s">
-        <v>411</v>
+      <c r="A12" s="66" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B13" s="3" t="str">
         <f aca="false">TEXT('Sensitivity Engine'!$C$5,"0%")&amp;" Debt"</f>
@@ -8679,21 +8906,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$5,"$0.00")&amp;" / kWh"</f>
         <v>$0.04 / kWh</v>
       </c>
-      <c r="B14" s="78" t="n">
+      <c r="B14" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N5</f>
-        <v>1.80849867816635</v>
-      </c>
-      <c r="C14" s="78" t="n">
+        <v>1.77039120326773</v>
+      </c>
+      <c r="C14" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N6</f>
-        <v>1.50708223180529</v>
-      </c>
-      <c r="D14" s="78" t="n">
+        <v>1.47532600272311</v>
+      </c>
+      <c r="D14" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N7</f>
-        <v>1.29178477011882</v>
-      </c>
-      <c r="E14" s="78" t="n">
+        <v>1.26456514519123</v>
+      </c>
+      <c r="E14" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N8</f>
-        <v>1.13031167385397</v>
+        <v>1.10649450204233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8701,21 +8928,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$9,"$0.00")&amp;" / kWh"</f>
         <v>$0.06 / kWh</v>
       </c>
-      <c r="B15" s="78" t="n">
+      <c r="B15" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N9</f>
-        <v>1.77362008182952</v>
-      </c>
-      <c r="C15" s="78" t="n">
+        <v>1.73625335657266</v>
+      </c>
+      <c r="C15" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N10</f>
-        <v>1.47801673485793</v>
-      </c>
-      <c r="D15" s="78" t="n">
+        <v>1.44687779714389</v>
+      </c>
+      <c r="D15" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N11</f>
-        <v>1.26687148702109</v>
-      </c>
-      <c r="E15" s="78" t="n">
+        <v>1.24018096898047</v>
+      </c>
+      <c r="E15" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N12</f>
-        <v>1.10851255114345</v>
+        <v>1.08515834785792</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8723,21 +8950,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$13,"$0.00")&amp;" / kWh"</f>
         <v>$0.08 / kWh</v>
       </c>
-      <c r="B16" s="78" t="n">
+      <c r="B16" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N13</f>
-        <v>1.7387414854927</v>
-      </c>
-      <c r="C16" s="78" t="n">
+        <v>1.7021155098776</v>
+      </c>
+      <c r="C16" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N14</f>
-        <v>1.44895123791058</v>
-      </c>
-      <c r="D16" s="78" t="n">
+        <v>1.41842959156467</v>
+      </c>
+      <c r="D16" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N15</f>
-        <v>1.24195820392335</v>
-      </c>
-      <c r="E16" s="78" t="n">
+        <v>1.21579679276972</v>
+      </c>
+      <c r="E16" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N16</f>
-        <v>1.08671342843294</v>
+        <v>1.0638221936735</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8745,21 +8972,21 @@
         <f aca="false">TEXT('Sensitivity Engine'!$B$17,"$0.00")&amp;" / kWh"</f>
         <v>$0.10 / kWh</v>
       </c>
-      <c r="B17" s="78" t="n">
+      <c r="B17" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N17</f>
-        <v>1.70386288915587</v>
-      </c>
-      <c r="C17" s="78" t="n">
+        <v>1.66797766318254</v>
+      </c>
+      <c r="C17" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N18</f>
-        <v>1.41988574096323</v>
-      </c>
-      <c r="D17" s="78" t="n">
+        <v>1.38998138598545</v>
+      </c>
+      <c r="D17" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N19</f>
-        <v>1.21704492082562</v>
-      </c>
-      <c r="E17" s="78" t="n">
+        <v>1.19141261655896</v>
+      </c>
+      <c r="E17" s="85" t="n">
         <f aca="false">'Sensitivity Engine'!N20</f>
-        <v>1.06491430572242</v>
+        <v>1.04248603948909</v>
       </c>
     </row>
   </sheetData>
@@ -8777,7 +9004,7 @@
       </colorScale>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>'Control Panel &amp; Inputs'!$C$49</formula>
+      <formula>'Control Panel &amp; Inputs'!$C$53</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:E17">
